--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -793,11 +793,11 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>2039.6</v>
+        <v>2375.57</v>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Yurimaguas, 184 m s. n. m. (SENAMHI); dentro del rango 1,800 - 2,400 mm de la memoria de arquitectura</t>
+          <t>Promedio de Navarro (2,349.79), Pelejo (2,332.92) y Shanusi (2,444.00), SENAMHI 2013-2017 (estudio hidrologico de Barranquita)</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3221,7 @@
         <v/>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.012461</v>
+        <v>0.012456</v>
       </c>
       <c r="G9" s="21">
         <f>EXP(-EXP(-(B9-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3265,7 +3265,7 @@
         <v/>
       </c>
       <c r="F10" s="21" t="n">
-        <v>0.040028</v>
+        <v>0.04002</v>
       </c>
       <c r="G10" s="21">
         <f>EXP(-EXP(-(B10-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3309,7 +3309,7 @@
         <v/>
       </c>
       <c r="F11" s="21" t="n">
-        <v>0.047805</v>
+        <v>0.047822</v>
       </c>
       <c r="G11" s="21">
         <f>EXP(-EXP(-(B11-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3353,7 +3353,7 @@
         <v/>
       </c>
       <c r="F12" s="21" t="n">
-        <v>0.24132</v>
+        <v>0.241319</v>
       </c>
       <c r="G12" s="21">
         <f>EXP(-EXP(-(B12-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3397,7 +3397,7 @@
         <v/>
       </c>
       <c r="F13" s="21" t="n">
-        <v>0.254943</v>
+        <v>0.254951</v>
       </c>
       <c r="G13" s="21">
         <f>EXP(-EXP(-(B13-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3441,7 +3441,7 @@
         <v/>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.254943</v>
+        <v>0.254951</v>
       </c>
       <c r="G14" s="21">
         <f>EXP(-EXP(-(B14-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3485,7 +3485,7 @@
         <v/>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0.274757</v>
+        <v>0.274829</v>
       </c>
       <c r="G15" s="21">
         <f>EXP(-EXP(-(B15-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3529,7 +3529,7 @@
         <v/>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.365203</v>
+        <v>0.365201</v>
       </c>
       <c r="G16" s="21">
         <f>EXP(-EXP(-(B16-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3573,7 +3573,7 @@
         <v/>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.394381</v>
+        <v>0.394397</v>
       </c>
       <c r="G17" s="21">
         <f>EXP(-EXP(-(B17-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3617,7 +3617,7 @@
         <v/>
       </c>
       <c r="F18" s="21" t="n">
-        <v>0.408943</v>
+        <v>0.408968</v>
       </c>
       <c r="G18" s="21">
         <f>EXP(-EXP(-(B18-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3661,7 +3661,7 @@
         <v/>
       </c>
       <c r="F19" s="21" t="n">
-        <v>0.419318</v>
+        <v>0.419283</v>
       </c>
       <c r="G19" s="21">
         <f>EXP(-EXP(-(B19-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3705,7 +3705,7 @@
         <v/>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.446136</v>
+        <v>0.446131</v>
       </c>
       <c r="G20" s="21">
         <f>EXP(-EXP(-(B20-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3749,7 +3749,7 @@
         <v/>
       </c>
       <c r="F21" s="21" t="n">
-        <v>0.448187</v>
+        <v>0.44817</v>
       </c>
       <c r="G21" s="21">
         <f>EXP(-EXP(-(B21-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3793,7 +3793,7 @@
         <v/>
       </c>
       <c r="F22" s="21" t="n">
-        <v>0.494723</v>
+        <v>0.494709</v>
       </c>
       <c r="G22" s="21">
         <f>EXP(-EXP(-(B22-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3837,7 +3837,7 @@
         <v/>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.560482</v>
+        <v>0.56052</v>
       </c>
       <c r="G23" s="21">
         <f>EXP(-EXP(-(B23-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3881,7 +3881,7 @@
         <v/>
       </c>
       <c r="F24" s="21" t="n">
-        <v>0.618032</v>
+        <v>0.618056</v>
       </c>
       <c r="G24" s="21">
         <f>EXP(-EXP(-(B24-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3925,7 +3925,7 @@
         <v/>
       </c>
       <c r="F25" s="21" t="n">
-        <v>0.651616</v>
+        <v>0.651583</v>
       </c>
       <c r="G25" s="21">
         <f>EXP(-EXP(-(B25-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3969,7 +3969,7 @@
         <v/>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.662863</v>
+        <v>0.662839</v>
       </c>
       <c r="G26" s="21">
         <f>EXP(-EXP(-(B26-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4013,7 +4013,7 @@
         <v/>
       </c>
       <c r="F27" s="21" t="n">
-        <v>0.68913</v>
+        <v>0.689093</v>
       </c>
       <c r="G27" s="21">
         <f>EXP(-EXP(-(B27-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4057,7 +4057,7 @@
         <v/>
       </c>
       <c r="F28" s="21" t="n">
-        <v>0.726397</v>
+        <v>0.726401</v>
       </c>
       <c r="G28" s="21">
         <f>EXP(-EXP(-(B28-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4101,7 +4101,7 @@
         <v/>
       </c>
       <c r="F29" s="21" t="n">
-        <v>0.746301</v>
+        <v>0.746308</v>
       </c>
       <c r="G29" s="21">
         <f>EXP(-EXP(-(B29-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4145,7 +4145,7 @@
         <v/>
       </c>
       <c r="F30" s="21" t="n">
-        <v>0.763839</v>
+        <v>0.763856</v>
       </c>
       <c r="G30" s="21">
         <f>EXP(-EXP(-(B30-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4189,7 +4189,7 @@
         <v/>
       </c>
       <c r="F31" s="21" t="n">
-        <v>0.82824</v>
+        <v>0.8282119999999999</v>
       </c>
       <c r="G31" s="21">
         <f>EXP(-EXP(-(B31-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4233,7 +4233,7 @@
         <v/>
       </c>
       <c r="F32" s="21" t="n">
-        <v>0.846911</v>
+        <v>0.846896</v>
       </c>
       <c r="G32" s="21">
         <f>EXP(-EXP(-(B32-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4277,7 +4277,7 @@
         <v/>
       </c>
       <c r="F33" s="21" t="n">
-        <v>0.926405</v>
+        <v>0.926423</v>
       </c>
       <c r="G33" s="21">
         <f>EXP(-EXP(-(B33-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -5580,7 +5580,7 @@
         </is>
       </c>
       <c r="B41" s="30" t="n">
-        <v>1419.7651</v>
+        <v>1653.6294</v>
       </c>
     </row>
     <row r="42">
@@ -5977,7 +5977,7 @@
         <v>0.3</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.0832</v>
+        <v>0.0925</v>
       </c>
       <c r="L9" s="21">
         <f>DATOS!$B$12*K9</f>
@@ -6004,7 +6004,7 @@
         <v/>
       </c>
       <c r="R9" s="25" t="n">
-        <v>0.0755</v>
+        <v>0.0839</v>
       </c>
       <c r="S9" s="26">
         <f>G9/(DATOS!$B$12*R9)</f>
@@ -6056,7 +6056,7 @@
         <v>0.46</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0955</v>
       </c>
       <c r="L10" s="21">
         <f>DATOS!$B$12*K10</f>
@@ -6083,7 +6083,7 @@
         <v/>
       </c>
       <c r="R10" s="25" t="n">
-        <v>0.0781</v>
+        <v>0.0866</v>
       </c>
       <c r="S10" s="26">
         <f>G10/(DATOS!$B$12*R10)</f>
@@ -6135,7 +6135,7 @@
         <v>0.3</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>0.0701</v>
+        <v>0.0776</v>
       </c>
       <c r="L11" s="21">
         <f>DATOS!$B$12*K11</f>
@@ -6162,7 +6162,7 @@
         <v/>
       </c>
       <c r="R11" s="25" t="n">
-        <v>0.06370000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="S11" s="26">
         <f>G11/(DATOS!$B$12*R11)</f>
@@ -6214,7 +6214,7 @@
         <v>0.46</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>0.0732</v>
+        <v>0.081</v>
       </c>
       <c r="L12" s="21">
         <f>DATOS!$B$12*K12</f>
@@ -6241,7 +6241,7 @@
         <v/>
       </c>
       <c r="R12" s="25" t="n">
-        <v>0.0665</v>
+        <v>0.0736</v>
       </c>
       <c r="S12" s="26">
         <f>G12/(DATOS!$B$12*R12)</f>
@@ -6293,7 +6293,7 @@
         <v>0.46</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0.0827</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="L13" s="21">
         <f>DATOS!$B$12*K13</f>
@@ -6320,7 +6320,7 @@
         <v/>
       </c>
       <c r="R13" s="25" t="n">
-        <v>0.0751</v>
+        <v>0.0833</v>
       </c>
       <c r="S13" s="26">
         <f>G13/(DATOS!$B$12*R13)</f>
@@ -6372,7 +6372,7 @@
         <v>0.52</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0688</v>
+        <v>0.0762</v>
       </c>
       <c r="L14" s="21">
         <f>DATOS!$B$12*K14</f>
@@ -6399,7 +6399,7 @@
         <v/>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0.0625</v>
+        <v>0.0692</v>
       </c>
       <c r="S14" s="26">
         <f>G14/(DATOS!$B$12*R14)</f>
@@ -6451,7 +6451,7 @@
         <v>0.77</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.2533</v>
+        <v>0.2853</v>
       </c>
       <c r="L15" s="21">
         <f>DATOS!$B$12*K15</f>
@@ -6478,7 +6478,7 @@
         <v/>
       </c>
       <c r="R15" s="25" t="n">
-        <v>0.2269</v>
+        <v>0.2552</v>
       </c>
       <c r="S15" s="26">
         <f>G15/(DATOS!$B$12*R15)</f>
@@ -6530,7 +6530,7 @@
         <v>0.83</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.2534</v>
+        <v>0.2853</v>
       </c>
       <c r="L16" s="21">
         <f>DATOS!$B$12*K16</f>
@@ -6557,7 +6557,7 @@
         <v/>
       </c>
       <c r="R16" s="25" t="n">
-        <v>0.2271</v>
+        <v>0.2552</v>
       </c>
       <c r="S16" s="26">
         <f>G16/(DATOS!$B$12*R16)</f>
@@ -6609,7 +6609,7 @@
         <v>0.83</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.327</v>
+        <v>0.3697</v>
       </c>
       <c r="L17" s="21">
         <f>DATOS!$B$12*K17</f>
@@ -6636,7 +6636,7 @@
         <v/>
       </c>
       <c r="R17" s="25" t="n">
-        <v>0.2919</v>
+        <v>0.3295</v>
       </c>
       <c r="S17" s="26">
         <f>G17/(DATOS!$B$12*R17)</f>
@@ -6688,7 +6688,7 @@
         <v>0.79</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.3272</v>
+        <v>0.3697</v>
       </c>
       <c r="L18" s="21">
         <f>DATOS!$B$12*K18</f>
@@ -6715,7 +6715,7 @@
         <v/>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0.2921</v>
+        <v>0.3295</v>
       </c>
       <c r="S18" s="26">
         <f>G18/(DATOS!$B$12*R18)</f>
@@ -6767,7 +6767,7 @@
         <v>0.79</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.3692</v>
+        <v>0.418</v>
       </c>
       <c r="L19" s="21">
         <f>DATOS!$B$12*K19</f>
@@ -6794,7 +6794,7 @@
         <v/>
       </c>
       <c r="R19" s="25" t="n">
-        <v>0.3291</v>
+        <v>0.3719</v>
       </c>
       <c r="S19" s="26">
         <f>G19/(DATOS!$B$12*R19)</f>
@@ -6846,7 +6846,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0655</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="L20" s="21">
         <f>DATOS!$B$12*K20</f>
@@ -6873,7 +6873,7 @@
         <v/>
       </c>
       <c r="R20" s="25" t="n">
-        <v>0.0595</v>
+        <v>0.0658</v>
       </c>
       <c r="S20" s="26">
         <f>G20/(DATOS!$B$12*R20)</f>
@@ -6925,7 +6925,7 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.0827</v>
+        <v>0.0916</v>
       </c>
       <c r="L21" s="21">
         <f>DATOS!$B$12*K21</f>
@@ -6952,7 +6952,7 @@
         <v/>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0.0751</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="S21" s="26">
         <f>G21/(DATOS!$B$12*R21)</f>
@@ -7004,7 +7004,7 @@
         <v>0.43</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.0893</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="L22" s="21">
         <f>DATOS!$B$12*K22</f>
@@ -7031,7 +7031,7 @@
         <v/>
       </c>
       <c r="R22" s="25" t="n">
-        <v>0.081</v>
+        <v>0.0898</v>
       </c>
       <c r="S22" s="26">
         <f>G22/(DATOS!$B$12*R22)</f>
@@ -7083,7 +7083,7 @@
         <v>0.47</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>0.0898</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="L23" s="21">
         <f>DATOS!$B$12*K23</f>
@@ -7110,7 +7110,7 @@
         <v/>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0.0814</v>
+        <v>0.0902</v>
       </c>
       <c r="S23" s="26">
         <f>G23/(DATOS!$B$12*R23)</f>
@@ -7162,7 +7162,7 @@
         <v>0.48</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.1118</v>
+        <v>0.1245</v>
       </c>
       <c r="L24" s="21">
         <f>DATOS!$B$12*K24</f>
@@ -7189,7 +7189,7 @@
         <v/>
       </c>
       <c r="R24" s="25" t="n">
-        <v>0.1012</v>
+        <v>0.1126</v>
       </c>
       <c r="S24" s="26">
         <f>G24/(DATOS!$B$12*R24)</f>
@@ -7241,7 +7241,7 @@
         <v>0.49</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>0.1315</v>
+        <v>0.1469</v>
       </c>
       <c r="L25" s="21">
         <f>DATOS!$B$12*K25</f>
@@ -7268,7 +7268,7 @@
         <v/>
       </c>
       <c r="R25" s="25" t="n">
-        <v>0.1188</v>
+        <v>0.1325</v>
       </c>
       <c r="S25" s="26">
         <f>G25/(DATOS!$B$12*R25)</f>
@@ -7320,7 +7320,7 @@
         <v>0.57</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.1395</v>
+        <v>0.1557</v>
       </c>
       <c r="L26" s="21">
         <f>DATOS!$B$12*K26</f>
@@ -7347,7 +7347,7 @@
         <v/>
       </c>
       <c r="R26" s="25" t="n">
-        <v>0.1259</v>
+        <v>0.1404</v>
       </c>
       <c r="S26" s="26">
         <f>G26/(DATOS!$B$12*R26)</f>
@@ -7399,7 +7399,7 @@
         <v>0.61</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.1668</v>
+        <v>0.1867</v>
       </c>
       <c r="L27" s="21">
         <f>DATOS!$B$12*K27</f>
@@ -7426,7 +7426,7 @@
         <v/>
       </c>
       <c r="R27" s="25" t="n">
-        <v>0.1503</v>
+        <v>0.168</v>
       </c>
       <c r="S27" s="26">
         <f>G27/(DATOS!$B$12*R27)</f>
@@ -7478,7 +7478,7 @@
         <v>0.3</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>0.0668</v>
+        <v>0.0742</v>
       </c>
       <c r="L28" s="21">
         <f>DATOS!$B$12*K28</f>
@@ -7505,7 +7505,7 @@
         <v/>
       </c>
       <c r="R28" s="25" t="n">
-        <v>0.0607</v>
+        <v>0.0674</v>
       </c>
       <c r="S28" s="26">
         <f>G28/(DATOS!$B$12*R28)</f>
@@ -7557,7 +7557,7 @@
         <v>0.41</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>0.0721</v>
+        <v>0.08</v>
       </c>
       <c r="L29" s="21">
         <f>DATOS!$B$12*K29</f>
@@ -7584,7 +7584,7 @@
         <v/>
       </c>
       <c r="R29" s="25" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="S29" s="26">
         <f>G29/(DATOS!$B$12*R29)</f>
@@ -7636,7 +7636,7 @@
         <v>0.44</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="L30" s="21">
         <f>DATOS!$B$12*K30</f>
@@ -7663,7 +7663,7 @@
         <v/>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.0789</v>
+        <v>0.0876</v>
       </c>
       <c r="S30" s="26">
         <f>G30/(DATOS!$B$12*R30)</f>
@@ -7715,7 +7715,7 @@
         <v>0.53</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.0916</v>
+        <v>0.1018</v>
       </c>
       <c r="L31" s="21">
         <f>DATOS!$B$12*K31</f>
@@ -7742,7 +7742,7 @@
         <v/>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="S31" s="26">
         <f>G31/(DATOS!$B$12*R31)</f>
@@ -7794,7 +7794,7 @@
         <v>0.55</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0.1197</v>
+        <v>0.1334</v>
       </c>
       <c r="L32" s="21">
         <f>DATOS!$B$12*K32</f>
@@ -7821,7 +7821,7 @@
         <v/>
       </c>
       <c r="R32" s="25" t="n">
-        <v>0.1083</v>
+        <v>0.1205</v>
       </c>
       <c r="S32" s="26">
         <f>G32/(DATOS!$B$12*R32)</f>
@@ -7873,7 +7873,7 @@
         <v>0.3</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>0.0432</v>
+        <v>0.0478</v>
       </c>
       <c r="L33" s="21">
         <f>DATOS!$B$12*K33</f>
@@ -7900,7 +7900,7 @@
         <v/>
       </c>
       <c r="R33" s="25" t="n">
-        <v>0.0394</v>
+        <v>0.0436</v>
       </c>
       <c r="S33" s="26">
         <f>G33/(DATOS!$B$12*R33)</f>
@@ -7952,7 +7952,7 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0.0295</v>
+        <v>0.0326</v>
       </c>
       <c r="L34" s="21">
         <f>DATOS!$B$12*K34</f>
@@ -7979,7 +7979,7 @@
         <v/>
       </c>
       <c r="R34" s="25" t="n">
-        <v>0.027</v>
+        <v>0.0297</v>
       </c>
       <c r="S34" s="26">
         <f>G34/(DATOS!$B$12*R34)</f>
@@ -8031,7 +8031,7 @@
         <v>0.5</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>0.1344</v>
+        <v>0.15</v>
       </c>
       <c r="L35" s="21">
         <f>DATOS!$B$12*K35</f>
@@ -8058,7 +8058,7 @@
         <v/>
       </c>
       <c r="R35" s="25" t="n">
-        <v>0.1214</v>
+        <v>0.1353</v>
       </c>
       <c r="S35" s="26">
         <f>G35/(DATOS!$B$12*R35)</f>
@@ -8110,7 +8110,7 @@
         <v>0.59</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0.1752</v>
+        <v>0.1962</v>
       </c>
       <c r="L36" s="21">
         <f>DATOS!$B$12*K36</f>
@@ -8137,7 +8137,7 @@
         <v/>
       </c>
       <c r="R36" s="25" t="n">
-        <v>0.1577</v>
+        <v>0.1764</v>
       </c>
       <c r="S36" s="26">
         <f>G36/(DATOS!$B$12*R36)</f>
@@ -8189,7 +8189,7 @@
         <v>0.61</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>0.1752</v>
+        <v>0.1962</v>
       </c>
       <c r="L37" s="21">
         <f>DATOS!$B$12*K37</f>
@@ -8216,7 +8216,7 @@
         <v/>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.1577</v>
+        <v>0.1764</v>
       </c>
       <c r="S37" s="26">
         <f>G37/(DATOS!$B$12*R37)</f>
@@ -8268,7 +8268,7 @@
         <v>0.62</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0.2075</v>
+        <v>0.2328</v>
       </c>
       <c r="L38" s="21">
         <f>DATOS!$B$12*K38</f>
@@ -8295,7 +8295,7 @@
         <v/>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0.1864</v>
+        <v>0.2088</v>
       </c>
       <c r="S38" s="26">
         <f>G38/(DATOS!$B$12*R38)</f>
@@ -8347,7 +8347,7 @@
         <v>0.73</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>0.2075</v>
+        <v>0.233</v>
       </c>
       <c r="L39" s="21">
         <f>DATOS!$B$12*K39</f>
@@ -8374,7 +8374,7 @@
         <v/>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0.1864</v>
+        <v>0.209</v>
       </c>
       <c r="S39" s="26">
         <f>G39/(DATOS!$B$12*R39)</f>
@@ -8426,7 +8426,7 @@
         <v>0.73</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.2708</v>
+        <v>0.3053</v>
       </c>
       <c r="L40" s="21">
         <f>DATOS!$B$12*K40</f>
@@ -8453,7 +8453,7 @@
         <v/>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0.2424</v>
+        <v>0.2728</v>
       </c>
       <c r="S40" s="26">
         <f>G40/(DATOS!$B$12*R40)</f>
@@ -8505,7 +8505,7 @@
         <v>0.79</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.3121</v>
+        <v>0.3526</v>
       </c>
       <c r="L41" s="21">
         <f>DATOS!$B$12*K41</f>
@@ -8532,7 +8532,7 @@
         <v/>
       </c>
       <c r="R41" s="25" t="n">
-        <v>0.2789</v>
+        <v>0.3144</v>
       </c>
       <c r="S41" s="26">
         <f>G41/(DATOS!$B$12*R41)</f>
@@ -8584,7 +8584,7 @@
         <v>0.7</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>0.3121</v>
+        <v>0.3527</v>
       </c>
       <c r="L42" s="21">
         <f>DATOS!$B$12*K42</f>
@@ -8611,7 +8611,7 @@
         <v/>
       </c>
       <c r="R42" s="25" t="n">
-        <v>0.2789</v>
+        <v>0.3146</v>
       </c>
       <c r="S42" s="26">
         <f>G42/(DATOS!$B$12*R42)</f>
@@ -8663,7 +8663,7 @@
         <v>0.7</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>0.3133</v>
+        <v>0.3539</v>
       </c>
       <c r="L43" s="21">
         <f>DATOS!$B$12*K43</f>
@@ -8690,7 +8690,7 @@
         <v/>
       </c>
       <c r="R43" s="25" t="n">
-        <v>0.2799</v>
+        <v>0.3156</v>
       </c>
       <c r="S43" s="26">
         <f>G43/(DATOS!$B$12*R43)</f>
@@ -8742,7 +8742,7 @@
         <v>0.74</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>0.3135</v>
+        <v>0.3542</v>
       </c>
       <c r="L44" s="21">
         <f>DATOS!$B$12*K44</f>
@@ -8769,7 +8769,7 @@
         <v/>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0.2801</v>
+        <v>0.3159</v>
       </c>
       <c r="S44" s="26">
         <f>G44/(DATOS!$B$12*R44)</f>
@@ -8821,7 +8821,7 @@
         <v>0.74</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>0.3154</v>
+        <v>0.3563</v>
       </c>
       <c r="L45" s="21">
         <f>DATOS!$B$12*K45</f>
@@ -8848,7 +8848,7 @@
         <v/>
       </c>
       <c r="R45" s="25" t="n">
-        <v>0.2817</v>
+        <v>0.3177</v>
       </c>
       <c r="S45" s="26">
         <f>G45/(DATOS!$B$12*R45)</f>
@@ -8900,7 +8900,7 @@
         <v>0.77</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>0.3154</v>
+        <v>0.3564</v>
       </c>
       <c r="L46" s="21">
         <f>DATOS!$B$12*K46</f>
@@ -8927,7 +8927,7 @@
         <v/>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0.2817</v>
+        <v>0.3178</v>
       </c>
       <c r="S46" s="26">
         <f>G46/(DATOS!$B$12*R46)</f>
@@ -8979,7 +8979,7 @@
         <v>0.77</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0.3193</v>
+        <v>0.3608</v>
       </c>
       <c r="L47" s="21">
         <f>DATOS!$B$12*K47</f>
@@ -9006,7 +9006,7 @@
         <v/>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0.2852</v>
+        <v>0.3217</v>
       </c>
       <c r="S47" s="26">
         <f>G47/(DATOS!$B$12*R47)</f>
@@ -9058,7 +9058,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>0.3203</v>
+        <v>0.362</v>
       </c>
       <c r="L48" s="21">
         <f>DATOS!$B$12*K48</f>
@@ -9085,7 +9085,7 @@
         <v/>
       </c>
       <c r="R48" s="25" t="n">
-        <v>0.2861</v>
+        <v>0.3227</v>
       </c>
       <c r="S48" s="26">
         <f>G48/(DATOS!$B$12*R48)</f>
@@ -9137,7 +9137,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.3205</v>
+        <v>0.3621</v>
       </c>
       <c r="L49" s="21">
         <f>DATOS!$B$12*K49</f>
@@ -9164,7 +9164,7 @@
         <v/>
       </c>
       <c r="R49" s="25" t="n">
-        <v>0.2862</v>
+        <v>0.3229</v>
       </c>
       <c r="S49" s="26">
         <f>G49/(DATOS!$B$12*R49)</f>
@@ -9216,7 +9216,7 @@
         <v>0.3</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>0.0274</v>
+        <v>0.0301</v>
       </c>
       <c r="L50" s="21">
         <f>DATOS!$B$12*K50</f>
@@ -9243,7 +9243,7 @@
         <v/>
       </c>
       <c r="R50" s="25" t="n">
-        <v>0.025</v>
+        <v>0.0275</v>
       </c>
       <c r="S50" s="26">
         <f>G50/(DATOS!$B$12*R50)</f>
@@ -9295,7 +9295,7 @@
         <v>0.32</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.095</v>
       </c>
       <c r="L51" s="21">
         <f>DATOS!$B$12*K51</f>
@@ -9322,7 +9322,7 @@
         <v/>
       </c>
       <c r="R51" s="25" t="n">
-        <v>0.0776</v>
+        <v>0.0862</v>
       </c>
       <c r="S51" s="26">
         <f>G51/(DATOS!$B$12*R51)</f>
@@ -9374,7 +9374,7 @@
         <v>0.3</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>0.0732</v>
+        <v>0.081</v>
       </c>
       <c r="L52" s="21">
         <f>DATOS!$B$12*K52</f>
@@ -9401,7 +9401,7 @@
         <v/>
       </c>
       <c r="R52" s="25" t="n">
-        <v>0.0665</v>
+        <v>0.0736</v>
       </c>
       <c r="S52" s="26">
         <f>G52/(DATOS!$B$12*R52)</f>
@@ -9453,7 +9453,7 @@
         <v>0.3</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.062</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="L53" s="21">
         <f>DATOS!$B$12*K53</f>
@@ -9480,7 +9480,7 @@
         <v/>
       </c>
       <c r="R53" s="25" t="n">
-        <v>0.0564</v>
+        <v>0.0623</v>
       </c>
       <c r="S53" s="26">
         <f>G53/(DATOS!$B$12*R53)</f>
@@ -9532,7 +9532,7 @@
         <v>0.39</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>0.0675</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="L54" s="21">
         <f>DATOS!$B$12*K54</f>
@@ -9559,7 +9559,7 @@
         <v/>
       </c>
       <c r="R54" s="25" t="n">
-        <v>0.0614</v>
+        <v>0.068</v>
       </c>
       <c r="S54" s="26">
         <f>G54/(DATOS!$B$12*R54)</f>
@@ -9611,7 +9611,7 @@
         <v>0.42</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>0.0709</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="L55" s="21">
         <f>DATOS!$B$12*K55</f>
@@ -9638,7 +9638,7 @@
         <v/>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0.0644</v>
+        <v>0.0712</v>
       </c>
       <c r="S55" s="26">
         <f>G55/(DATOS!$B$12*R55)</f>
@@ -9690,7 +9690,7 @@
         <v>0.42</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1009</v>
       </c>
       <c r="L56" s="21">
         <f>DATOS!$B$12*K56</f>
@@ -9717,7 +9717,7 @@
         <v/>
       </c>
       <c r="R56" s="25" t="n">
-        <v>0.0825</v>
+        <v>0.0914</v>
       </c>
       <c r="S56" s="26">
         <f>G56/(DATOS!$B$12*R56)</f>
@@ -9769,7 +9769,7 @@
         <v>0.48</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.1009</v>
       </c>
       <c r="L57" s="21">
         <f>DATOS!$B$12*K57</f>
@@ -9796,7 +9796,7 @@
         <v/>
       </c>
       <c r="R57" s="25" t="n">
-        <v>0.0825</v>
+        <v>0.0914</v>
       </c>
       <c r="S57" s="26">
         <f>G57/(DATOS!$B$12*R57)</f>
@@ -9848,7 +9848,7 @@
         <v>0.2</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>0.0808</v>
+        <v>0.0895</v>
       </c>
       <c r="L58" s="21">
         <f>DATOS!$B$12*K58</f>
@@ -9875,7 +9875,7 @@
         <v/>
       </c>
       <c r="R58" s="25" t="n">
-        <v>0.0733</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="S58" s="26">
         <f>G58/(DATOS!$B$12*R58)</f>
@@ -9927,7 +9927,7 @@
         <v>0.3</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>0.0574</v>
+        <v>0.0633</v>
       </c>
       <c r="L59" s="21">
         <f>DATOS!$B$12*K59</f>
@@ -9954,7 +9954,7 @@
         <v/>
       </c>
       <c r="R59" s="25" t="n">
-        <v>0.0522</v>
+        <v>0.0576</v>
       </c>
       <c r="S59" s="26">
         <f>G59/(DATOS!$B$12*R59)</f>
@@ -10006,7 +10006,7 @@
         <v>0.38</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>0.0596</v>
+        <v>0.066</v>
       </c>
       <c r="L60" s="21">
         <f>DATOS!$B$12*K60</f>
@@ -10033,7 +10033,7 @@
         <v/>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0.0542</v>
+        <v>0.06</v>
       </c>
       <c r="S60" s="26">
         <f>G60/(DATOS!$B$12*R60)</f>
@@ -10085,7 +10085,7 @@
         <v>0.38</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1024</v>
       </c>
       <c r="L61" s="21">
         <f>DATOS!$B$12*K61</f>
@@ -10112,7 +10112,7 @@
         <v/>
       </c>
       <c r="R61" s="25" t="n">
-        <v>0.0837</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="S61" s="26">
         <f>G61/(DATOS!$B$12*R61)</f>
@@ -10164,7 +10164,7 @@
         <v>0.49</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>0.0925</v>
+        <v>0.1029</v>
       </c>
       <c r="L62" s="21">
         <f>DATOS!$B$12*K62</f>
@@ -10191,7 +10191,7 @@
         <v/>
       </c>
       <c r="R62" s="25" t="n">
-        <v>0.0839</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="S62" s="26">
         <f>G62/(DATOS!$B$12*R62)</f>
@@ -10243,7 +10243,7 @@
         <v>0.5</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>0.1237</v>
+        <v>0.138</v>
       </c>
       <c r="L63" s="21">
         <f>DATOS!$B$12*K63</f>
@@ -10270,7 +10270,7 @@
         <v/>
       </c>
       <c r="R63" s="25" t="n">
-        <v>0.1118</v>
+        <v>0.1247</v>
       </c>
       <c r="S63" s="26">
         <f>G63/(DATOS!$B$12*R63)</f>
@@ -10322,7 +10322,7 @@
         <v>0.52</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>0.161</v>
+        <v>0.1801</v>
       </c>
       <c r="L64" s="21">
         <f>DATOS!$B$12*K64</f>
@@ -10349,7 +10349,7 @@
         <v/>
       </c>
       <c r="R64" s="25" t="n">
-        <v>0.1451</v>
+        <v>0.1621</v>
       </c>
       <c r="S64" s="26">
         <f>G64/(DATOS!$B$12*R64)</f>
@@ -10401,7 +10401,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>0.279</v>
+        <v>0.3147</v>
       </c>
       <c r="L65" s="21">
         <f>DATOS!$B$12*K65</f>
@@ -10428,7 +10428,7 @@
         <v/>
       </c>
       <c r="R65" s="25" t="n">
-        <v>0.2497</v>
+        <v>0.2811</v>
       </c>
       <c r="S65" s="26">
         <f>G65/(DATOS!$B$12*R65)</f>
@@ -10480,7 +10480,7 @@
         <v>0.62</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>0.3598</v>
+        <v>0.4074</v>
       </c>
       <c r="L66" s="21">
         <f>DATOS!$B$12*K66</f>
@@ -10507,7 +10507,7 @@
         <v/>
       </c>
       <c r="R66" s="25" t="n">
-        <v>0.3208</v>
+        <v>0.3626</v>
       </c>
       <c r="S66" s="26">
         <f>G66/(DATOS!$B$12*R66)</f>
@@ -10559,7 +10559,7 @@
         <v>0.57</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>0.3797</v>
+        <v>0.4302</v>
       </c>
       <c r="L67" s="21">
         <f>DATOS!$B$12*K67</f>
@@ -10586,7 +10586,7 @@
         <v/>
       </c>
       <c r="R67" s="25" t="n">
-        <v>0.3383</v>
+        <v>0.3826</v>
       </c>
       <c r="S67" s="26">
         <f>G67/(DATOS!$B$12*R67)</f>
@@ -10638,7 +10638,7 @@
         <v>0.63</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.3819</v>
+        <v>0.4327</v>
       </c>
       <c r="L68" s="21">
         <f>DATOS!$B$12*K68</f>
@@ -10665,7 +10665,7 @@
         <v/>
       </c>
       <c r="R68" s="25" t="n">
-        <v>0.3402</v>
+        <v>0.3848</v>
       </c>
       <c r="S68" s="26">
         <f>G68/(DATOS!$B$12*R68)</f>
@@ -10717,7 +10717,7 @@
         <v>0.64</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>0.3819</v>
+        <v>0.4327</v>
       </c>
       <c r="L69" s="21">
         <f>DATOS!$B$12*K69</f>
@@ -10744,7 +10744,7 @@
         <v/>
       </c>
       <c r="R69" s="25" t="n">
-        <v>0.3402</v>
+        <v>0.3848</v>
       </c>
       <c r="S69" s="26">
         <f>G69/(DATOS!$B$12*R69)</f>
@@ -10796,7 +10796,7 @@
         <v>0.64</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>0.4503</v>
+        <v>0.5115</v>
       </c>
       <c r="L70" s="21">
         <f>DATOS!$B$12*K70</f>
@@ -10823,7 +10823,7 @@
         <v/>
       </c>
       <c r="R70" s="25" t="n">
-        <v>0.4002</v>
+        <v>0.4538</v>
       </c>
       <c r="S70" s="26">
         <f>G70/(DATOS!$B$12*R70)</f>
@@ -10875,7 +10875,7 @@
         <v>0.3</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>0.0644</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="L71" s="21">
         <f>DATOS!$B$12*K71</f>
@@ -10902,7 +10902,7 @@
         <v/>
       </c>
       <c r="R71" s="25" t="n">
-        <v>0.0586</v>
+        <v>0.0649</v>
       </c>
       <c r="S71" s="26">
         <f>G71/(DATOS!$B$12*R71)</f>
@@ -10954,7 +10954,7 @@
         <v>0.3</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>0.0727</v>
+        <v>0.0805</v>
       </c>
       <c r="L72" s="21">
         <f>DATOS!$B$12*K72</f>
@@ -10981,7 +10981,7 @@
         <v/>
       </c>
       <c r="R72" s="25" t="n">
-        <v>0.066</v>
+        <v>0.0731</v>
       </c>
       <c r="S72" s="26">
         <f>G72/(DATOS!$B$12*R72)</f>
@@ -11033,7 +11033,7 @@
         <v>0.38</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0837</v>
       </c>
       <c r="L73" s="21">
         <f>DATOS!$B$12*K73</f>
@@ -11060,7 +11060,7 @@
         <v/>
       </c>
       <c r="R73" s="25" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="S73" s="26">
         <f>G73/(DATOS!$B$12*R73)</f>
@@ -11112,7 +11112,7 @@
         <v>0.35</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>0.1197</v>
+        <v>0.1334</v>
       </c>
       <c r="L74" s="21">
         <f>DATOS!$B$12*K74</f>
@@ -11139,7 +11139,7 @@
         <v/>
       </c>
       <c r="R74" s="25" t="n">
-        <v>0.1083</v>
+        <v>0.1205</v>
       </c>
       <c r="S74" s="26">
         <f>G74/(DATOS!$B$12*R74)</f>
@@ -11191,7 +11191,7 @@
         <v>0.35</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>0.1199</v>
+        <v>0.1338</v>
       </c>
       <c r="L75" s="21">
         <f>DATOS!$B$12*K75</f>
@@ -11218,7 +11218,7 @@
         <v/>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.1085</v>
+        <v>0.1209</v>
       </c>
       <c r="S75" s="26">
         <f>G75/(DATOS!$B$12*R75)</f>
@@ -11270,7 +11270,7 @@
         <v>0.35</v>
       </c>
       <c r="K76" s="25" t="n">
-        <v>0.1216</v>
+        <v>0.1356</v>
       </c>
       <c r="L76" s="21">
         <f>DATOS!$B$12*K76</f>
@@ -11297,7 +11297,7 @@
         <v/>
       </c>
       <c r="R76" s="25" t="n">
-        <v>0.11</v>
+        <v>0.1225</v>
       </c>
       <c r="S76" s="26">
         <f>G76/(DATOS!$B$12*R76)</f>
@@ -11349,7 +11349,7 @@
         <v>0.35</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.1577</v>
+        <v>0.1763</v>
       </c>
       <c r="L77" s="21">
         <f>DATOS!$B$12*K77</f>
@@ -11376,7 +11376,7 @@
         <v/>
       </c>
       <c r="R77" s="25" t="n">
-        <v>0.1422</v>
+        <v>0.1588</v>
       </c>
       <c r="S77" s="26">
         <f>G77/(DATOS!$B$12*R77)</f>
@@ -11428,7 +11428,7 @@
         <v>0.45</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0.1614</v>
+        <v>0.1805</v>
       </c>
       <c r="L78" s="21">
         <f>DATOS!$B$12*K78</f>
@@ -11455,7 +11455,7 @@
         <v/>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0.1455</v>
+        <v>0.1625</v>
       </c>
       <c r="S78" s="26">
         <f>G78/(DATOS!$B$12*R78)</f>
@@ -11507,7 +11507,7 @@
         <v>0.3</v>
       </c>
       <c r="K79" s="25" t="n">
-        <v>0.0615</v>
+        <v>0.06809999999999999</v>
       </c>
       <c r="L79" s="21">
         <f>DATOS!$B$12*K79</f>
@@ -11534,7 +11534,7 @@
         <v/>
       </c>
       <c r="R79" s="25" t="n">
-        <v>0.0559</v>
+        <v>0.0619</v>
       </c>
       <c r="S79" s="26">
         <f>G79/(DATOS!$B$12*R79)</f>
@@ -11586,7 +11586,7 @@
         <v>0.36</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>0.0617</v>
+        <v>0.0683</v>
       </c>
       <c r="L80" s="21">
         <f>DATOS!$B$12*K80</f>
@@ -11613,7 +11613,7 @@
         <v/>
       </c>
       <c r="R80" s="25" t="n">
-        <v>0.0562</v>
+        <v>0.0621</v>
       </c>
       <c r="S80" s="26">
         <f>G80/(DATOS!$B$12*R80)</f>
@@ -11665,7 +11665,7 @@
         <v>0.35</v>
       </c>
       <c r="K81" s="25" t="n">
-        <v>0.1168</v>
+        <v>0.1302</v>
       </c>
       <c r="L81" s="21">
         <f>DATOS!$B$12*K81</f>
@@ -11692,7 +11692,7 @@
         <v/>
       </c>
       <c r="R81" s="25" t="n">
-        <v>0.1056</v>
+        <v>0.1176</v>
       </c>
       <c r="S81" s="26">
         <f>G81/(DATOS!$B$12*R81)</f>
@@ -11744,7 +11744,7 @@
         <v>0.35</v>
       </c>
       <c r="K82" s="25" t="n">
-        <v>0.1282</v>
+        <v>0.1431</v>
       </c>
       <c r="L82" s="21">
         <f>DATOS!$B$12*K82</f>
@@ -11771,7 +11771,7 @@
         <v/>
       </c>
       <c r="R82" s="25" t="n">
-        <v>0.1159</v>
+        <v>0.1291</v>
       </c>
       <c r="S82" s="26">
         <f>G82/(DATOS!$B$12*R82)</f>
@@ -11823,7 +11823,7 @@
         <v>0.3</v>
       </c>
       <c r="K83" s="25" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.1024</v>
       </c>
       <c r="L83" s="21">
         <f>DATOS!$B$12*K83</f>
@@ -11850,7 +11850,7 @@
         <v/>
       </c>
       <c r="R83" s="25" t="n">
-        <v>0.0837</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="S83" s="26">
         <f>G83/(DATOS!$B$12*R83)</f>
@@ -11902,7 +11902,7 @@
         <v>0.45</v>
       </c>
       <c r="K84" s="25" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1075</v>
       </c>
       <c r="L84" s="21">
         <f>DATOS!$B$12*K84</f>
@@ -11929,7 +11929,7 @@
         <v/>
       </c>
       <c r="R84" s="25" t="n">
-        <v>0.0876</v>
+        <v>0.0973</v>
       </c>
       <c r="S84" s="26">
         <f>G84/(DATOS!$B$12*R84)</f>
@@ -11981,7 +11981,7 @@
         <v>0.46</v>
       </c>
       <c r="K85" s="25" t="n">
-        <v>0.0989</v>
+        <v>0.1099</v>
       </c>
       <c r="L85" s="21">
         <f>DATOS!$B$12*K85</f>
@@ -12008,7 +12008,7 @@
         <v/>
       </c>
       <c r="R85" s="25" t="n">
-        <v>0.0896</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="S85" s="26">
         <f>G85/(DATOS!$B$12*R85)</f>
@@ -12060,7 +12060,7 @@
         <v>0.47</v>
       </c>
       <c r="K86" s="25" t="n">
-        <v>0.0989</v>
+        <v>0.1101</v>
       </c>
       <c r="L86" s="21">
         <f>DATOS!$B$12*K86</f>
@@ -12087,7 +12087,7 @@
         <v/>
       </c>
       <c r="R86" s="25" t="n">
-        <v>0.0896</v>
+        <v>0.0997</v>
       </c>
       <c r="S86" s="26">
         <f>G86/(DATOS!$B$12*R86)</f>
@@ -12139,7 +12139,7 @@
         <v>0.4</v>
       </c>
       <c r="K87" s="25" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="L87" s="21">
         <f>DATOS!$B$12*K87</f>
@@ -12166,7 +12166,7 @@
         <v/>
       </c>
       <c r="R87" s="25" t="n">
-        <v>0.1103</v>
+        <v>0.1228</v>
       </c>
       <c r="S87" s="26">
         <f>G87/(DATOS!$B$12*R87)</f>
@@ -12218,7 +12218,7 @@
         <v>0.4</v>
       </c>
       <c r="K88" s="25" t="n">
-        <v>0.122</v>
+        <v>0.136</v>
       </c>
       <c r="L88" s="21">
         <f>DATOS!$B$12*K88</f>
@@ -12245,7 +12245,7 @@
         <v/>
       </c>
       <c r="R88" s="25" t="n">
-        <v>0.1103</v>
+        <v>0.1228</v>
       </c>
       <c r="S88" s="26">
         <f>G88/(DATOS!$B$12*R88)</f>
@@ -12297,7 +12297,7 @@
         <v>0.2</v>
       </c>
       <c r="K89" s="25" t="n">
-        <v>0.0798</v>
+        <v>0.0885</v>
       </c>
       <c r="L89" s="21">
         <f>DATOS!$B$12*K89</f>
@@ -12324,7 +12324,7 @@
         <v/>
       </c>
       <c r="R89" s="25" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="S89" s="26">
         <f>G89/(DATOS!$B$12*R89)</f>
@@ -12376,7 +12376,7 @@
         <v>0.5</v>
       </c>
       <c r="K90" s="25" t="n">
-        <v>0.0803</v>
+        <v>0.0891</v>
       </c>
       <c r="L90" s="21">
         <f>DATOS!$B$12*K90</f>
@@ -12403,7 +12403,7 @@
         <v/>
       </c>
       <c r="R90" s="25" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.0808</v>
       </c>
       <c r="S90" s="26">
         <f>G90/(DATOS!$B$12*R90)</f>
@@ -12455,7 +12455,7 @@
         <v>0.5</v>
       </c>
       <c r="K91" s="25" t="n">
-        <v>0.1224</v>
+        <v>0.1364</v>
       </c>
       <c r="L91" s="21">
         <f>DATOS!$B$12*K91</f>
@@ -12482,7 +12482,7 @@
         <v/>
       </c>
       <c r="R91" s="25" t="n">
-        <v>0.1107</v>
+        <v>0.1232</v>
       </c>
       <c r="S91" s="26">
         <f>G91/(DATOS!$B$12*R91)</f>
@@ -12534,7 +12534,7 @@
         <v>0.4</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>0.1228</v>
+        <v>0.1368</v>
       </c>
       <c r="L92" s="21">
         <f>DATOS!$B$12*K92</f>
@@ -12561,7 +12561,7 @@
         <v/>
       </c>
       <c r="R92" s="25" t="n">
-        <v>0.1111</v>
+        <v>0.1236</v>
       </c>
       <c r="S92" s="26">
         <f>G92/(DATOS!$B$12*R92)</f>
@@ -12613,7 +12613,7 @@
         <v>0.3</v>
       </c>
       <c r="K93" s="25" t="n">
-        <v>0.0363</v>
+        <v>0.04</v>
       </c>
       <c r="L93" s="21">
         <f>DATOS!$B$12*K93</f>
@@ -12640,7 +12640,7 @@
         <v/>
       </c>
       <c r="R93" s="25" t="n">
-        <v>0.0331</v>
+        <v>0.0365</v>
       </c>
       <c r="S93" s="26">
         <f>G93/(DATOS!$B$12*R93)</f>
@@ -12692,7 +12692,7 @@
         <v>0.36</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0.0366</v>
+        <v>0.0403</v>
       </c>
       <c r="L94" s="21">
         <f>DATOS!$B$12*K94</f>
@@ -12719,7 +12719,7 @@
         <v/>
       </c>
       <c r="R94" s="25" t="n">
-        <v>0.0334</v>
+        <v>0.0368</v>
       </c>
       <c r="S94" s="26">
         <f>G94/(DATOS!$B$12*R94)</f>
@@ -12771,7 +12771,7 @@
         <v>0.36</v>
       </c>
       <c r="K95" s="25" t="n">
-        <v>0.0582</v>
+        <v>0.0641</v>
       </c>
       <c r="L95" s="21">
         <f>DATOS!$B$12*K95</f>
@@ -12798,7 +12798,7 @@
         <v/>
       </c>
       <c r="R95" s="25" t="n">
-        <v>0.053</v>
+        <v>0.0583</v>
       </c>
       <c r="S95" s="26">
         <f>G95/(DATOS!$B$12*R95)</f>
@@ -12850,7 +12850,7 @@
         <v>0.48</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0.0582</v>
+        <v>0.0641</v>
       </c>
       <c r="L96" s="21">
         <f>DATOS!$B$12*K96</f>
@@ -12877,7 +12877,7 @@
         <v/>
       </c>
       <c r="R96" s="25" t="n">
-        <v>0.053</v>
+        <v>0.0583</v>
       </c>
       <c r="S96" s="26">
         <f>G96/(DATOS!$B$12*R96)</f>
@@ -12929,7 +12929,7 @@
         <v>0.49</v>
       </c>
       <c r="K97" s="25" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0791</v>
       </c>
       <c r="L97" s="21">
         <f>DATOS!$B$12*K97</f>
@@ -12956,7 +12956,7 @@
         <v/>
       </c>
       <c r="R97" s="25" t="n">
-        <v>0.0649</v>
+        <v>0.0718</v>
       </c>
       <c r="S97" s="26">
         <f>G97/(DATOS!$B$12*R97)</f>
@@ -13008,7 +13008,7 @@
         <v>0.3</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>0.0297</v>
+        <v>0.0327</v>
       </c>
       <c r="L98" s="21">
         <f>DATOS!$B$12*K98</f>
@@ -13035,7 +13035,7 @@
         <v/>
       </c>
       <c r="R98" s="25" t="n">
-        <v>0.0271</v>
+        <v>0.0299</v>
       </c>
       <c r="S98" s="26">
         <f>G98/(DATOS!$B$12*R98)</f>
@@ -13087,7 +13087,7 @@
         <v>0.37</v>
       </c>
       <c r="K99" s="25" t="n">
-        <v>0.0297</v>
+        <v>0.0327</v>
       </c>
       <c r="L99" s="21">
         <f>DATOS!$B$12*K99</f>
@@ -13114,7 +13114,7 @@
         <v/>
       </c>
       <c r="R99" s="25" t="n">
-        <v>0.0271</v>
+        <v>0.0299</v>
       </c>
       <c r="S99" s="26">
         <f>G99/(DATOS!$B$12*R99)</f>

--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Duracion minima (OS.060)</t>
+          <t>Duracion minima (Norma CE.040)</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>OS.060; mismo valor de los proyectos de Morales</t>
+          <t>CE.040; mismo valor de los proyectos de Morales</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>OS.060</t>
+          <t>CE.040</t>
         </is>
       </c>
     </row>
@@ -918,7 +918,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>OS.060</t>
+          <t>CE.040</t>
         </is>
       </c>
     </row>
@@ -1012,6 +1012,21 @@
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>T = 25 anos (pendiente moderada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Factor de seguridad de los caudales FS</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Mismo criterio de los proyectos de Morales (Q = C I A FS)</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5978,7 @@
         <v/>
       </c>
       <c r="G9" s="21">
-        <f>E9*F9*D9/3600000</f>
+        <f>E9*F9*D9*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H9" s="18">
@@ -5977,7 +5992,7 @@
         <v>0.3</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.0925</v>
+        <v>0.1018</v>
       </c>
       <c r="L9" s="21">
         <f>DATOS!$B$12*K9</f>
@@ -6004,7 +6019,7 @@
         <v/>
       </c>
       <c r="R9" s="25" t="n">
-        <v>0.0839</v>
+        <v>0.0922</v>
       </c>
       <c r="S9" s="26">
         <f>G9/(DATOS!$B$12*R9)</f>
@@ -6042,7 +6057,7 @@
         <v/>
       </c>
       <c r="G10" s="21">
-        <f>E10*F10*D10/3600000</f>
+        <f>E10*F10*D10*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H10" s="18">
@@ -6056,7 +6071,7 @@
         <v>0.46</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>0.0955</v>
+        <v>0.1053</v>
       </c>
       <c r="L10" s="21">
         <f>DATOS!$B$12*K10</f>
@@ -6083,7 +6098,7 @@
         <v/>
       </c>
       <c r="R10" s="25" t="n">
-        <v>0.0866</v>
+        <v>0.0954</v>
       </c>
       <c r="S10" s="26">
         <f>G10/(DATOS!$B$12*R10)</f>
@@ -6121,7 +6136,7 @@
         <v/>
       </c>
       <c r="G11" s="21">
-        <f>E11*F11*D11/3600000</f>
+        <f>E11*F11*D11*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H11" s="18">
@@ -6135,7 +6150,7 @@
         <v>0.3</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>0.0776</v>
+        <v>0.0853</v>
       </c>
       <c r="L11" s="21">
         <f>DATOS!$B$12*K11</f>
@@ -6162,7 +6177,7 @@
         <v/>
       </c>
       <c r="R11" s="25" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.0774</v>
       </c>
       <c r="S11" s="26">
         <f>G11/(DATOS!$B$12*R11)</f>
@@ -6200,7 +6215,7 @@
         <v/>
       </c>
       <c r="G12" s="21">
-        <f>E12*F12*D12/3600000</f>
+        <f>E12*F12*D12*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H12" s="18">
@@ -6214,7 +6229,7 @@
         <v>0.46</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>0.081</v>
+        <v>0.0893</v>
       </c>
       <c r="L12" s="21">
         <f>DATOS!$B$12*K12</f>
@@ -6241,7 +6256,7 @@
         <v/>
       </c>
       <c r="R12" s="25" t="n">
-        <v>0.0736</v>
+        <v>0.081</v>
       </c>
       <c r="S12" s="26">
         <f>G12/(DATOS!$B$12*R12)</f>
@@ -6279,7 +6294,7 @@
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>E13*F13*D13/3600000</f>
+        <f>E13*F13*D13*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H13" s="18">
@@ -6293,7 +6308,7 @@
         <v>0.46</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0.09180000000000001</v>
+        <v>0.1011</v>
       </c>
       <c r="L13" s="21">
         <f>DATOS!$B$12*K13</f>
@@ -6320,7 +6335,7 @@
         <v/>
       </c>
       <c r="R13" s="25" t="n">
-        <v>0.0833</v>
+        <v>0.0916</v>
       </c>
       <c r="S13" s="26">
         <f>G13/(DATOS!$B$12*R13)</f>
@@ -6358,7 +6373,7 @@
         <v/>
       </c>
       <c r="G14" s="21">
-        <f>E14*F14*D14/3600000</f>
+        <f>E14*F14*D14*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H14" s="18">
@@ -6372,7 +6387,7 @@
         <v>0.52</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0762</v>
+        <v>0.0838</v>
       </c>
       <c r="L14" s="21">
         <f>DATOS!$B$12*K14</f>
@@ -6399,7 +6414,7 @@
         <v/>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0.0692</v>
+        <v>0.0761</v>
       </c>
       <c r="S14" s="26">
         <f>G14/(DATOS!$B$12*R14)</f>
@@ -6437,7 +6452,7 @@
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>E15*F15*D15/3600000</f>
+        <f>E15*F15*D15*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H15" s="18">
@@ -6451,7 +6466,7 @@
         <v>0.77</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.2853</v>
+        <v>0.3186</v>
       </c>
       <c r="L15" s="21">
         <f>DATOS!$B$12*K15</f>
@@ -6478,7 +6493,7 @@
         <v/>
       </c>
       <c r="R15" s="25" t="n">
-        <v>0.2552</v>
+        <v>0.2846</v>
       </c>
       <c r="S15" s="26">
         <f>G15/(DATOS!$B$12*R15)</f>
@@ -6516,7 +6531,7 @@
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>E16*F16*D16/3600000</f>
+        <f>E16*F16*D16*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H16" s="18">
@@ -6530,7 +6545,7 @@
         <v>0.83</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.2853</v>
+        <v>0.3186</v>
       </c>
       <c r="L16" s="21">
         <f>DATOS!$B$12*K16</f>
@@ -6557,7 +6572,7 @@
         <v/>
       </c>
       <c r="R16" s="25" t="n">
-        <v>0.2552</v>
+        <v>0.2846</v>
       </c>
       <c r="S16" s="26">
         <f>G16/(DATOS!$B$12*R16)</f>
@@ -6595,7 +6610,7 @@
         <v/>
       </c>
       <c r="G17" s="21">
-        <f>E17*F17*D17/3600000</f>
+        <f>E17*F17*D17*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H17" s="18">
@@ -6609,7 +6624,7 @@
         <v>0.83</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.3697</v>
+        <v>0.4144</v>
       </c>
       <c r="L17" s="21">
         <f>DATOS!$B$12*K17</f>
@@ -6636,7 +6651,7 @@
         <v/>
       </c>
       <c r="R17" s="25" t="n">
-        <v>0.3295</v>
+        <v>0.3687</v>
       </c>
       <c r="S17" s="26">
         <f>G17/(DATOS!$B$12*R17)</f>
@@ -6674,7 +6689,7 @@
         <v/>
       </c>
       <c r="G18" s="21">
-        <f>E18*F18*D18/3600000</f>
+        <f>E18*F18*D18*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H18" s="18">
@@ -6688,7 +6703,7 @@
         <v>0.79</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.3697</v>
+        <v>0.4144</v>
       </c>
       <c r="L18" s="21">
         <f>DATOS!$B$12*K18</f>
@@ -6715,7 +6730,7 @@
         <v/>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0.3295</v>
+        <v>0.3687</v>
       </c>
       <c r="S18" s="26">
         <f>G18/(DATOS!$B$12*R18)</f>
@@ -6753,7 +6768,7 @@
         <v/>
       </c>
       <c r="G19" s="21">
-        <f>E19*F19*D19/3600000</f>
+        <f>E19*F19*D19*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H19" s="18">
@@ -6767,7 +6782,7 @@
         <v>0.79</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.418</v>
+        <v>0.4694</v>
       </c>
       <c r="L19" s="21">
         <f>DATOS!$B$12*K19</f>
@@ -6794,7 +6809,7 @@
         <v/>
       </c>
       <c r="R19" s="25" t="n">
-        <v>0.3719</v>
+        <v>0.4169</v>
       </c>
       <c r="S19" s="26">
         <f>G19/(DATOS!$B$12*R19)</f>
@@ -6832,7 +6847,7 @@
         <v/>
       </c>
       <c r="G20" s="21">
-        <f>E20*F20*D20/3600000</f>
+        <f>E20*F20*D20*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H20" s="18">
@@ -6846,7 +6861,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0796</v>
       </c>
       <c r="L20" s="21">
         <f>DATOS!$B$12*K20</f>
@@ -6873,7 +6888,7 @@
         <v/>
       </c>
       <c r="R20" s="25" t="n">
-        <v>0.0658</v>
+        <v>0.0722</v>
       </c>
       <c r="S20" s="26">
         <f>G20/(DATOS!$B$12*R20)</f>
@@ -6911,7 +6926,7 @@
         <v/>
       </c>
       <c r="G21" s="21">
-        <f>E21*F21*D21/3600000</f>
+        <f>E21*F21*D21*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H21" s="18">
@@ -6925,7 +6940,7 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.0916</v>
+        <v>0.1009</v>
       </c>
       <c r="L21" s="21">
         <f>DATOS!$B$12*K21</f>
@@ -6952,7 +6967,7 @@
         <v/>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0.08309999999999999</v>
+        <v>0.0914</v>
       </c>
       <c r="S21" s="26">
         <f>G21/(DATOS!$B$12*R21)</f>
@@ -6990,7 +7005,7 @@
         <v/>
       </c>
       <c r="G22" s="21">
-        <f>E22*F22*D22/3600000</f>
+        <f>E22*F22*D22*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H22" s="18">
@@ -7004,7 +7019,7 @@
         <v>0.43</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.09909999999999999</v>
+        <v>0.1092</v>
       </c>
       <c r="L22" s="21">
         <f>DATOS!$B$12*K22</f>
@@ -7031,7 +7046,7 @@
         <v/>
       </c>
       <c r="R22" s="25" t="n">
-        <v>0.0898</v>
+        <v>0.0989</v>
       </c>
       <c r="S22" s="26">
         <f>G22/(DATOS!$B$12*R22)</f>
@@ -7069,7 +7084,7 @@
         <v/>
       </c>
       <c r="G23" s="21">
-        <f>E23*F23*D23/3600000</f>
+        <f>E23*F23*D23*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H23" s="18">
@@ -7083,7 +7098,7 @@
         <v>0.47</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1099</v>
       </c>
       <c r="L23" s="21">
         <f>DATOS!$B$12*K23</f>
@@ -7110,7 +7125,7 @@
         <v/>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0.0902</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="S23" s="26">
         <f>G23/(DATOS!$B$12*R23)</f>
@@ -7148,7 +7163,7 @@
         <v/>
       </c>
       <c r="G24" s="21">
-        <f>E24*F24*D24/3600000</f>
+        <f>E24*F24*D24*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H24" s="18">
@@ -7162,7 +7177,7 @@
         <v>0.48</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.1245</v>
+        <v>0.1374</v>
       </c>
       <c r="L24" s="21">
         <f>DATOS!$B$12*K24</f>
@@ -7189,7 +7204,7 @@
         <v/>
       </c>
       <c r="R24" s="25" t="n">
-        <v>0.1126</v>
+        <v>0.1241</v>
       </c>
       <c r="S24" s="26">
         <f>G24/(DATOS!$B$12*R24)</f>
@@ -7227,7 +7242,7 @@
         <v/>
       </c>
       <c r="G25" s="21">
-        <f>E25*F25*D25/3600000</f>
+        <f>E25*F25*D25*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H25" s="18">
@@ -7241,7 +7256,7 @@
         <v>0.49</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>0.1469</v>
+        <v>0.1625</v>
       </c>
       <c r="L25" s="21">
         <f>DATOS!$B$12*K25</f>
@@ -7268,7 +7283,7 @@
         <v/>
       </c>
       <c r="R25" s="25" t="n">
-        <v>0.1325</v>
+        <v>0.1465</v>
       </c>
       <c r="S25" s="26">
         <f>G25/(DATOS!$B$12*R25)</f>
@@ -7306,7 +7321,7 @@
         <v/>
       </c>
       <c r="G26" s="21">
-        <f>E26*F26*D26/3600000</f>
+        <f>E26*F26*D26*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H26" s="18">
@@ -7320,7 +7335,7 @@
         <v>0.57</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.1557</v>
+        <v>0.1723</v>
       </c>
       <c r="L26" s="21">
         <f>DATOS!$B$12*K26</f>
@@ -7347,7 +7362,7 @@
         <v/>
       </c>
       <c r="R26" s="25" t="n">
-        <v>0.1404</v>
+        <v>0.1552</v>
       </c>
       <c r="S26" s="26">
         <f>G26/(DATOS!$B$12*R26)</f>
@@ -7385,7 +7400,7 @@
         <v/>
       </c>
       <c r="G27" s="21">
-        <f>E27*F27*D27/3600000</f>
+        <f>E27*F27*D27*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H27" s="18">
@@ -7399,7 +7414,7 @@
         <v>0.61</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.1867</v>
+        <v>0.2073</v>
       </c>
       <c r="L27" s="21">
         <f>DATOS!$B$12*K27</f>
@@ -7426,7 +7441,7 @@
         <v/>
       </c>
       <c r="R27" s="25" t="n">
-        <v>0.168</v>
+        <v>0.1862</v>
       </c>
       <c r="S27" s="26">
         <f>G27/(DATOS!$B$12*R27)</f>
@@ -7464,7 +7479,7 @@
         <v/>
       </c>
       <c r="G28" s="21">
-        <f>E28*F28*D28/3600000</f>
+        <f>E28*F28*D28*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H28" s="18">
@@ -7478,7 +7493,7 @@
         <v>0.3</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>0.0742</v>
+        <v>0.0815</v>
       </c>
       <c r="L28" s="21">
         <f>DATOS!$B$12*K28</f>
@@ -7505,7 +7520,7 @@
         <v/>
       </c>
       <c r="R28" s="25" t="n">
-        <v>0.0674</v>
+        <v>0.074</v>
       </c>
       <c r="S28" s="26">
         <f>G28/(DATOS!$B$12*R28)</f>
@@ -7543,7 +7558,7 @@
         <v/>
       </c>
       <c r="G29" s="21">
-        <f>E29*F29*D29/3600000</f>
+        <f>E29*F29*D29*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H29" s="18">
@@ -7557,7 +7572,7 @@
         <v>0.41</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>0.08</v>
+        <v>0.0881</v>
       </c>
       <c r="L29" s="21">
         <f>DATOS!$B$12*K29</f>
@@ -7584,7 +7599,7 @@
         <v/>
       </c>
       <c r="R29" s="25" t="n">
-        <v>0.0727</v>
+        <v>0.08</v>
       </c>
       <c r="S29" s="26">
         <f>G29/(DATOS!$B$12*R29)</f>
@@ -7622,7 +7637,7 @@
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>E30*F30*D30/3600000</f>
+        <f>E30*F30*D30*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H30" s="18">
@@ -7636,7 +7651,7 @@
         <v>0.44</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.1064</v>
       </c>
       <c r="L30" s="21">
         <f>DATOS!$B$12*K30</f>
@@ -7663,7 +7678,7 @@
         <v/>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.0876</v>
+        <v>0.0964</v>
       </c>
       <c r="S30" s="26">
         <f>G30/(DATOS!$B$12*R30)</f>
@@ -7701,7 +7716,7 @@
         <v/>
       </c>
       <c r="G31" s="21">
-        <f>E31*F31*D31/3600000</f>
+        <f>E31*F31*D31*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H31" s="18">
@@ -7715,7 +7730,7 @@
         <v>0.53</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.1018</v>
+        <v>0.1123</v>
       </c>
       <c r="L31" s="21">
         <f>DATOS!$B$12*K31</f>
@@ -7742,7 +7757,7 @@
         <v/>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0.0922</v>
+        <v>0.1016</v>
       </c>
       <c r="S31" s="26">
         <f>G31/(DATOS!$B$12*R31)</f>
@@ -7780,7 +7795,7 @@
         <v/>
       </c>
       <c r="G32" s="21">
-        <f>E32*F32*D32/3600000</f>
+        <f>E32*F32*D32*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H32" s="18">
@@ -7794,7 +7809,7 @@
         <v>0.55</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0.1334</v>
+        <v>0.1475</v>
       </c>
       <c r="L32" s="21">
         <f>DATOS!$B$12*K32</f>
@@ -7821,7 +7836,7 @@
         <v/>
       </c>
       <c r="R32" s="25" t="n">
-        <v>0.1205</v>
+        <v>0.1331</v>
       </c>
       <c r="S32" s="26">
         <f>G32/(DATOS!$B$12*R32)</f>
@@ -7859,7 +7874,7 @@
         <v/>
       </c>
       <c r="G33" s="21">
-        <f>E33*F33*D33/3600000</f>
+        <f>E33*F33*D33*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H33" s="18">
@@ -7873,7 +7888,7 @@
         <v>0.3</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>0.0478</v>
+        <v>0.0523</v>
       </c>
       <c r="L33" s="21">
         <f>DATOS!$B$12*K33</f>
@@ -7900,7 +7915,7 @@
         <v/>
       </c>
       <c r="R33" s="25" t="n">
-        <v>0.0436</v>
+        <v>0.0476</v>
       </c>
       <c r="S33" s="26">
         <f>G33/(DATOS!$B$12*R33)</f>
@@ -7938,7 +7953,7 @@
         <v/>
       </c>
       <c r="G34" s="21">
-        <f>E34*F34*D34/3600000</f>
+        <f>E34*F34*D34*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H34" s="18">
@@ -7952,7 +7967,7 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0.0326</v>
+        <v>0.0356</v>
       </c>
       <c r="L34" s="21">
         <f>DATOS!$B$12*K34</f>
@@ -7979,7 +7994,7 @@
         <v/>
       </c>
       <c r="R34" s="25" t="n">
-        <v>0.0297</v>
+        <v>0.0325</v>
       </c>
       <c r="S34" s="26">
         <f>G34/(DATOS!$B$12*R34)</f>
@@ -8017,7 +8032,7 @@
         <v/>
       </c>
       <c r="G35" s="21">
-        <f>E35*F35*D35/3600000</f>
+        <f>E35*F35*D35*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H35" s="18">
@@ -8031,7 +8046,7 @@
         <v>0.5</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>0.15</v>
+        <v>0.1662</v>
       </c>
       <c r="L35" s="21">
         <f>DATOS!$B$12*K35</f>
@@ -8058,7 +8073,7 @@
         <v/>
       </c>
       <c r="R35" s="25" t="n">
-        <v>0.1353</v>
+        <v>0.1498</v>
       </c>
       <c r="S35" s="26">
         <f>G35/(DATOS!$B$12*R35)</f>
@@ -8096,7 +8111,7 @@
         <v/>
       </c>
       <c r="G36" s="21">
-        <f>E36*F36*D36/3600000</f>
+        <f>E36*F36*D36*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H36" s="18">
@@ -8110,7 +8125,7 @@
         <v>0.59</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0.1962</v>
+        <v>0.218</v>
       </c>
       <c r="L36" s="21">
         <f>DATOS!$B$12*K36</f>
@@ -8137,7 +8152,7 @@
         <v/>
       </c>
       <c r="R36" s="25" t="n">
-        <v>0.1764</v>
+        <v>0.1958</v>
       </c>
       <c r="S36" s="26">
         <f>G36/(DATOS!$B$12*R36)</f>
@@ -8175,7 +8190,7 @@
         <v/>
       </c>
       <c r="G37" s="21">
-        <f>E37*F37*D37/3600000</f>
+        <f>E37*F37*D37*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H37" s="18">
@@ -8189,7 +8204,7 @@
         <v>0.61</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>0.1962</v>
+        <v>0.218</v>
       </c>
       <c r="L37" s="21">
         <f>DATOS!$B$12*K37</f>
@@ -8216,7 +8231,7 @@
         <v/>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.1764</v>
+        <v>0.1958</v>
       </c>
       <c r="S37" s="26">
         <f>G37/(DATOS!$B$12*R37)</f>
@@ -8254,7 +8269,7 @@
         <v/>
       </c>
       <c r="G38" s="21">
-        <f>E38*F38*D38/3600000</f>
+        <f>E38*F38*D38*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H38" s="18">
@@ -8268,7 +8283,7 @@
         <v>0.62</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0.2328</v>
+        <v>0.2593</v>
       </c>
       <c r="L38" s="21">
         <f>DATOS!$B$12*K38</f>
@@ -8295,7 +8310,7 @@
         <v/>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0.2088</v>
+        <v>0.2322</v>
       </c>
       <c r="S38" s="26">
         <f>G38/(DATOS!$B$12*R38)</f>
@@ -8333,7 +8348,7 @@
         <v/>
       </c>
       <c r="G39" s="21">
-        <f>E39*F39*D39/3600000</f>
+        <f>E39*F39*D39*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H39" s="18">
@@ -8347,7 +8362,7 @@
         <v>0.73</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>0.233</v>
+        <v>0.2594</v>
       </c>
       <c r="L39" s="21">
         <f>DATOS!$B$12*K39</f>
@@ -8374,7 +8389,7 @@
         <v/>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0.209</v>
+        <v>0.2324</v>
       </c>
       <c r="S39" s="26">
         <f>G39/(DATOS!$B$12*R39)</f>
@@ -8412,7 +8427,7 @@
         <v/>
       </c>
       <c r="G40" s="21">
-        <f>E40*F40*D40/3600000</f>
+        <f>E40*F40*D40*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H40" s="18">
@@ -8426,7 +8441,7 @@
         <v>0.73</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.3053</v>
+        <v>0.3412</v>
       </c>
       <c r="L40" s="21">
         <f>DATOS!$B$12*K40</f>
@@ -8453,7 +8468,7 @@
         <v/>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0.2728</v>
+        <v>0.3045</v>
       </c>
       <c r="S40" s="26">
         <f>G40/(DATOS!$B$12*R40)</f>
@@ -8491,7 +8506,7 @@
         <v/>
       </c>
       <c r="G41" s="21">
-        <f>E41*F41*D41/3600000</f>
+        <f>E41*F41*D41*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H41" s="18">
@@ -8505,7 +8520,7 @@
         <v>0.79</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.3526</v>
+        <v>0.3949</v>
       </c>
       <c r="L41" s="21">
         <f>DATOS!$B$12*K41</f>
@@ -8532,7 +8547,7 @@
         <v/>
       </c>
       <c r="R41" s="25" t="n">
-        <v>0.3144</v>
+        <v>0.3516</v>
       </c>
       <c r="S41" s="26">
         <f>G41/(DATOS!$B$12*R41)</f>
@@ -8570,7 +8585,7 @@
         <v/>
       </c>
       <c r="G42" s="21">
-        <f>E42*F42*D42/3600000</f>
+        <f>E42*F42*D42*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H42" s="18">
@@ -8584,7 +8599,7 @@
         <v>0.7</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>0.3527</v>
+        <v>0.3951</v>
       </c>
       <c r="L42" s="21">
         <f>DATOS!$B$12*K42</f>
@@ -8611,7 +8626,7 @@
         <v/>
       </c>
       <c r="R42" s="25" t="n">
-        <v>0.3146</v>
+        <v>0.3518</v>
       </c>
       <c r="S42" s="26">
         <f>G42/(DATOS!$B$12*R42)</f>
@@ -8649,7 +8664,7 @@
         <v/>
       </c>
       <c r="G43" s="21">
-        <f>E43*F43*D43/3600000</f>
+        <f>E43*F43*D43*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H43" s="18">
@@ -8663,7 +8678,7 @@
         <v>0.7</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>0.3539</v>
+        <v>0.3964</v>
       </c>
       <c r="L43" s="21">
         <f>DATOS!$B$12*K43</f>
@@ -8690,7 +8705,7 @@
         <v/>
       </c>
       <c r="R43" s="25" t="n">
-        <v>0.3156</v>
+        <v>0.353</v>
       </c>
       <c r="S43" s="26">
         <f>G43/(DATOS!$B$12*R43)</f>
@@ -8728,7 +8743,7 @@
         <v/>
       </c>
       <c r="G44" s="21">
-        <f>E44*F44*D44/3600000</f>
+        <f>E44*F44*D44*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H44" s="18">
@@ -8742,7 +8757,7 @@
         <v>0.74</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>0.3542</v>
+        <v>0.3968</v>
       </c>
       <c r="L44" s="21">
         <f>DATOS!$B$12*K44</f>
@@ -8769,7 +8784,7 @@
         <v/>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0.3159</v>
+        <v>0.3533</v>
       </c>
       <c r="S44" s="26">
         <f>G44/(DATOS!$B$12*R44)</f>
@@ -8807,7 +8822,7 @@
         <v/>
       </c>
       <c r="G45" s="21">
-        <f>E45*F45*D45/3600000</f>
+        <f>E45*F45*D45*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H45" s="18">
@@ -8821,7 +8836,7 @@
         <v>0.74</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>0.3563</v>
+        <v>0.3991</v>
       </c>
       <c r="L45" s="21">
         <f>DATOS!$B$12*K45</f>
@@ -8848,7 +8863,7 @@
         <v/>
       </c>
       <c r="R45" s="25" t="n">
-        <v>0.3177</v>
+        <v>0.3553</v>
       </c>
       <c r="S45" s="26">
         <f>G45/(DATOS!$B$12*R45)</f>
@@ -8886,7 +8901,7 @@
         <v/>
       </c>
       <c r="G46" s="21">
-        <f>E46*F46*D46/3600000</f>
+        <f>E46*F46*D46*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H46" s="18">
@@ -8900,7 +8915,7 @@
         <v>0.77</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>0.3564</v>
+        <v>0.3992</v>
       </c>
       <c r="L46" s="21">
         <f>DATOS!$B$12*K46</f>
@@ -8927,7 +8942,7 @@
         <v/>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0.3178</v>
+        <v>0.3554</v>
       </c>
       <c r="S46" s="26">
         <f>G46/(DATOS!$B$12*R46)</f>
@@ -8965,7 +8980,7 @@
         <v/>
       </c>
       <c r="G47" s="21">
-        <f>E47*F47*D47/3600000</f>
+        <f>E47*F47*D47*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H47" s="18">
@@ -8979,7 +8994,7 @@
         <v>0.77</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0.3608</v>
+        <v>0.4042</v>
       </c>
       <c r="L47" s="21">
         <f>DATOS!$B$12*K47</f>
@@ -9006,7 +9021,7 @@
         <v/>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0.3217</v>
+        <v>0.3598</v>
       </c>
       <c r="S47" s="26">
         <f>G47/(DATOS!$B$12*R47)</f>
@@ -9044,7 +9059,7 @@
         <v/>
       </c>
       <c r="G48" s="21">
-        <f>E48*F48*D48/3600000</f>
+        <f>E48*F48*D48*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H48" s="18">
@@ -9058,7 +9073,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>0.362</v>
+        <v>0.4057</v>
       </c>
       <c r="L48" s="21">
         <f>DATOS!$B$12*K48</f>
@@ -9085,7 +9100,7 @@
         <v/>
       </c>
       <c r="R48" s="25" t="n">
-        <v>0.3227</v>
+        <v>0.3611</v>
       </c>
       <c r="S48" s="26">
         <f>G48/(DATOS!$B$12*R48)</f>
@@ -9123,7 +9138,7 @@
         <v/>
       </c>
       <c r="G49" s="21">
-        <f>E49*F49*D49/3600000</f>
+        <f>E49*F49*D49*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H49" s="18">
@@ -9137,7 +9152,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.3621</v>
+        <v>0.4057</v>
       </c>
       <c r="L49" s="21">
         <f>DATOS!$B$12*K49</f>
@@ -9164,7 +9179,7 @@
         <v/>
       </c>
       <c r="R49" s="25" t="n">
-        <v>0.3229</v>
+        <v>0.3611</v>
       </c>
       <c r="S49" s="26">
         <f>G49/(DATOS!$B$12*R49)</f>
@@ -9202,7 +9217,7 @@
         <v/>
       </c>
       <c r="G50" s="21">
-        <f>E50*F50*D50/3600000</f>
+        <f>E50*F50*D50*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H50" s="18">
@@ -9216,7 +9231,7 @@
         <v>0.3</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>0.0301</v>
+        <v>0.0327</v>
       </c>
       <c r="L50" s="21">
         <f>DATOS!$B$12*K50</f>
@@ -9243,7 +9258,7 @@
         <v/>
       </c>
       <c r="R50" s="25" t="n">
-        <v>0.0275</v>
+        <v>0.0299</v>
       </c>
       <c r="S50" s="26">
         <f>G50/(DATOS!$B$12*R50)</f>
@@ -9281,7 +9296,7 @@
         <v/>
       </c>
       <c r="G51" s="21">
-        <f>E51*F51*D51/3600000</f>
+        <f>E51*F51*D51*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H51" s="18">
@@ -9295,7 +9310,7 @@
         <v>0.32</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.095</v>
+        <v>0.1046</v>
       </c>
       <c r="L51" s="21">
         <f>DATOS!$B$12*K51</f>
@@ -9322,7 +9337,7 @@
         <v/>
       </c>
       <c r="R51" s="25" t="n">
-        <v>0.0862</v>
+        <v>0.0948</v>
       </c>
       <c r="S51" s="26">
         <f>G51/(DATOS!$B$12*R51)</f>
@@ -9360,7 +9375,7 @@
         <v/>
       </c>
       <c r="G52" s="21">
-        <f>E52*F52*D52/3600000</f>
+        <f>E52*F52*D52*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H52" s="18">
@@ -9374,7 +9389,7 @@
         <v>0.3</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>0.081</v>
+        <v>0.0891</v>
       </c>
       <c r="L52" s="21">
         <f>DATOS!$B$12*K52</f>
@@ -9401,7 +9416,7 @@
         <v/>
       </c>
       <c r="R52" s="25" t="n">
-        <v>0.0736</v>
+        <v>0.0808</v>
       </c>
       <c r="S52" s="26">
         <f>G52/(DATOS!$B$12*R52)</f>
@@ -9439,7 +9454,7 @@
         <v/>
       </c>
       <c r="G53" s="21">
-        <f>E53*F53*D53/3600000</f>
+        <f>E53*F53*D53*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H53" s="18">
@@ -9453,7 +9468,7 @@
         <v>0.3</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="L53" s="21">
         <f>DATOS!$B$12*K53</f>
@@ -9480,7 +9495,7 @@
         <v/>
       </c>
       <c r="R53" s="25" t="n">
-        <v>0.0623</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="S53" s="26">
         <f>G53/(DATOS!$B$12*R53)</f>
@@ -9518,7 +9533,7 @@
         <v/>
       </c>
       <c r="G54" s="21">
-        <f>E54*F54*D54/3600000</f>
+        <f>E54*F54*D54*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H54" s="18">
@@ -9532,7 +9547,7 @@
         <v>0.39</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0825</v>
       </c>
       <c r="L54" s="21">
         <f>DATOS!$B$12*K54</f>
@@ -9559,7 +9574,7 @@
         <v/>
       </c>
       <c r="R54" s="25" t="n">
-        <v>0.068</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="S54" s="26">
         <f>G54/(DATOS!$B$12*R54)</f>
@@ -9597,7 +9612,7 @@
         <v/>
       </c>
       <c r="G55" s="21">
-        <f>E55*F55*D55/3600000</f>
+        <f>E55*F55*D55*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H55" s="18">
@@ -9611,7 +9626,7 @@
         <v>0.42</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="L55" s="21">
         <f>DATOS!$B$12*K55</f>
@@ -9638,7 +9653,7 @@
         <v/>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0.0712</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="S55" s="26">
         <f>G55/(DATOS!$B$12*R55)</f>
@@ -9676,7 +9691,7 @@
         <v/>
       </c>
       <c r="G56" s="21">
-        <f>E56*F56*D56/3600000</f>
+        <f>E56*F56*D56*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H56" s="18">
@@ -9690,7 +9705,7 @@
         <v>0.42</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>0.1009</v>
+        <v>0.1112</v>
       </c>
       <c r="L56" s="21">
         <f>DATOS!$B$12*K56</f>
@@ -9717,7 +9732,7 @@
         <v/>
       </c>
       <c r="R56" s="25" t="n">
-        <v>0.0914</v>
+        <v>0.1006</v>
       </c>
       <c r="S56" s="26">
         <f>G56/(DATOS!$B$12*R56)</f>
@@ -9755,7 +9770,7 @@
         <v/>
       </c>
       <c r="G57" s="21">
-        <f>E57*F57*D57/3600000</f>
+        <f>E57*F57*D57*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H57" s="18">
@@ -9769,7 +9784,7 @@
         <v>0.48</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>0.1009</v>
+        <v>0.1112</v>
       </c>
       <c r="L57" s="21">
         <f>DATOS!$B$12*K57</f>
@@ -9796,7 +9811,7 @@
         <v/>
       </c>
       <c r="R57" s="25" t="n">
-        <v>0.0914</v>
+        <v>0.1006</v>
       </c>
       <c r="S57" s="26">
         <f>G57/(DATOS!$B$12*R57)</f>
@@ -9834,7 +9849,7 @@
         <v/>
       </c>
       <c r="G58" s="21">
-        <f>E58*F58*D58/3600000</f>
+        <f>E58*F58*D58*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H58" s="18">
@@ -9848,7 +9863,7 @@
         <v>0.2</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>0.0895</v>
+        <v>0.0987</v>
       </c>
       <c r="L58" s="21">
         <f>DATOS!$B$12*K58</f>
@@ -9875,7 +9890,7 @@
         <v/>
       </c>
       <c r="R58" s="25" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="S58" s="26">
         <f>G58/(DATOS!$B$12*R58)</f>
@@ -9913,7 +9928,7 @@
         <v/>
       </c>
       <c r="G59" s="21">
-        <f>E59*F59*D59/3600000</f>
+        <f>E59*F59*D59*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H59" s="18">
@@ -9927,7 +9942,7 @@
         <v>0.3</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>0.0633</v>
+        <v>0.0696</v>
       </c>
       <c r="L59" s="21">
         <f>DATOS!$B$12*K59</f>
@@ -9954,7 +9969,7 @@
         <v/>
       </c>
       <c r="R59" s="25" t="n">
-        <v>0.0576</v>
+        <v>0.0633</v>
       </c>
       <c r="S59" s="26">
         <f>G59/(DATOS!$B$12*R59)</f>
@@ -9992,7 +10007,7 @@
         <v/>
       </c>
       <c r="G60" s="21">
-        <f>E60*F60*D60/3600000</f>
+        <f>E60*F60*D60*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H60" s="18">
@@ -10006,7 +10021,7 @@
         <v>0.38</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>0.066</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="L60" s="21">
         <f>DATOS!$B$12*K60</f>
@@ -10033,7 +10048,7 @@
         <v/>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0.06</v>
+        <v>0.0658</v>
       </c>
       <c r="S60" s="26">
         <f>G60/(DATOS!$B$12*R60)</f>
@@ -10071,7 +10086,7 @@
         <v/>
       </c>
       <c r="G61" s="21">
-        <f>E61*F61*D61/3600000</f>
+        <f>E61*F61*D61*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H61" s="18">
@@ -10085,7 +10100,7 @@
         <v>0.38</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0.1024</v>
+        <v>0.1131</v>
       </c>
       <c r="L61" s="21">
         <f>DATOS!$B$12*K61</f>
@@ -10112,7 +10127,7 @@
         <v/>
       </c>
       <c r="R61" s="25" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1024</v>
       </c>
       <c r="S61" s="26">
         <f>G61/(DATOS!$B$12*R61)</f>
@@ -10150,7 +10165,7 @@
         <v/>
       </c>
       <c r="G62" s="21">
-        <f>E62*F62*D62/3600000</f>
+        <f>E62*F62*D62*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H62" s="18">
@@ -10164,7 +10179,7 @@
         <v>0.49</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>0.1029</v>
+        <v>0.1133</v>
       </c>
       <c r="L62" s="21">
         <f>DATOS!$B$12*K62</f>
@@ -10191,7 +10206,7 @@
         <v/>
       </c>
       <c r="R62" s="25" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.1026</v>
       </c>
       <c r="S62" s="26">
         <f>G62/(DATOS!$B$12*R62)</f>
@@ -10229,7 +10244,7 @@
         <v/>
       </c>
       <c r="G63" s="21">
-        <f>E63*F63*D63/3600000</f>
+        <f>E63*F63*D63*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H63" s="18">
@@ -10243,7 +10258,7 @@
         <v>0.5</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>0.138</v>
+        <v>0.1526</v>
       </c>
       <c r="L63" s="21">
         <f>DATOS!$B$12*K63</f>
@@ -10270,7 +10285,7 @@
         <v/>
       </c>
       <c r="R63" s="25" t="n">
-        <v>0.1247</v>
+        <v>0.1376</v>
       </c>
       <c r="S63" s="26">
         <f>G63/(DATOS!$B$12*R63)</f>
@@ -10308,7 +10323,7 @@
         <v/>
       </c>
       <c r="G64" s="21">
-        <f>E64*F64*D64/3600000</f>
+        <f>E64*F64*D64*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H64" s="18">
@@ -10322,7 +10337,7 @@
         <v>0.52</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>0.1801</v>
+        <v>0.1999</v>
       </c>
       <c r="L64" s="21">
         <f>DATOS!$B$12*K64</f>
@@ -10349,7 +10364,7 @@
         <v/>
       </c>
       <c r="R64" s="25" t="n">
-        <v>0.1621</v>
+        <v>0.1797</v>
       </c>
       <c r="S64" s="26">
         <f>G64/(DATOS!$B$12*R64)</f>
@@ -10387,7 +10402,7 @@
         <v/>
       </c>
       <c r="G65" s="21">
-        <f>E65*F65*D65/3600000</f>
+        <f>E65*F65*D65*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H65" s="18">
@@ -10401,7 +10416,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>0.3147</v>
+        <v>0.3519</v>
       </c>
       <c r="L65" s="21">
         <f>DATOS!$B$12*K65</f>
@@ -10428,7 +10443,7 @@
         <v/>
       </c>
       <c r="R65" s="25" t="n">
-        <v>0.2811</v>
+        <v>0.3138</v>
       </c>
       <c r="S65" s="26">
         <f>G65/(DATOS!$B$12*R65)</f>
@@ -10466,7 +10481,7 @@
         <v/>
       </c>
       <c r="G66" s="21">
-        <f>E66*F66*D66/3600000</f>
+        <f>E66*F66*D66*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H66" s="18">
@@ -10480,7 +10495,7 @@
         <v>0.62</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>0.4074</v>
+        <v>0.4572</v>
       </c>
       <c r="L66" s="21">
         <f>DATOS!$B$12*K66</f>
@@ -10507,7 +10522,7 @@
         <v/>
       </c>
       <c r="R66" s="25" t="n">
-        <v>0.3626</v>
+        <v>0.4063</v>
       </c>
       <c r="S66" s="26">
         <f>G66/(DATOS!$B$12*R66)</f>
@@ -10545,7 +10560,7 @@
         <v/>
       </c>
       <c r="G67" s="21">
-        <f>E67*F67*D67/3600000</f>
+        <f>E67*F67*D67*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H67" s="18">
@@ -10559,7 +10574,7 @@
         <v>0.57</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>0.4302</v>
+        <v>0.4833</v>
       </c>
       <c r="L67" s="21">
         <f>DATOS!$B$12*K67</f>
@@ -10586,7 +10601,7 @@
         <v/>
       </c>
       <c r="R67" s="25" t="n">
-        <v>0.3826</v>
+        <v>0.4291</v>
       </c>
       <c r="S67" s="26">
         <f>G67/(DATOS!$B$12*R67)</f>
@@ -10624,7 +10639,7 @@
         <v/>
       </c>
       <c r="G68" s="21">
-        <f>E68*F68*D68/3600000</f>
+        <f>E68*F68*D68*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H68" s="18">
@@ -10638,7 +10653,7 @@
         <v>0.63</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.4327</v>
+        <v>0.4861</v>
       </c>
       <c r="L68" s="21">
         <f>DATOS!$B$12*K68</f>
@@ -10665,7 +10680,7 @@
         <v/>
       </c>
       <c r="R68" s="25" t="n">
-        <v>0.3848</v>
+        <v>0.4315</v>
       </c>
       <c r="S68" s="26">
         <f>G68/(DATOS!$B$12*R68)</f>
@@ -10703,7 +10718,7 @@
         <v/>
       </c>
       <c r="G69" s="21">
-        <f>E69*F69*D69/3600000</f>
+        <f>E69*F69*D69*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H69" s="18">
@@ -10717,7 +10732,7 @@
         <v>0.64</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>0.4327</v>
+        <v>0.4861</v>
       </c>
       <c r="L69" s="21">
         <f>DATOS!$B$12*K69</f>
@@ -10744,7 +10759,7 @@
         <v/>
       </c>
       <c r="R69" s="25" t="n">
-        <v>0.3848</v>
+        <v>0.4315</v>
       </c>
       <c r="S69" s="26">
         <f>G69/(DATOS!$B$12*R69)</f>
@@ -10782,7 +10797,7 @@
         <v/>
       </c>
       <c r="G70" s="21">
-        <f>E70*F70*D70/3600000</f>
+        <f>E70*F70*D70*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H70" s="18">
@@ -10796,7 +10811,7 @@
         <v>0.64</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>0.5115</v>
+        <v>0.5758</v>
       </c>
       <c r="L70" s="21">
         <f>DATOS!$B$12*K70</f>
@@ -10823,7 +10838,7 @@
         <v/>
       </c>
       <c r="R70" s="25" t="n">
-        <v>0.4538</v>
+        <v>0.51</v>
       </c>
       <c r="S70" s="26">
         <f>G70/(DATOS!$B$12*R70)</f>
@@ -10861,7 +10876,7 @@
         <v/>
       </c>
       <c r="G71" s="21">
-        <f>E71*F71*D71/3600000</f>
+        <f>E71*F71*D71*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H71" s="18">
@@ -10875,7 +10890,7 @@
         <v>0.3</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="L71" s="21">
         <f>DATOS!$B$12*K71</f>
@@ -10902,7 +10917,7 @@
         <v/>
       </c>
       <c r="R71" s="25" t="n">
-        <v>0.0649</v>
+        <v>0.0712</v>
       </c>
       <c r="S71" s="26">
         <f>G71/(DATOS!$B$12*R71)</f>
@@ -10940,7 +10955,7 @@
         <v/>
       </c>
       <c r="G72" s="21">
-        <f>E72*F72*D72/3600000</f>
+        <f>E72*F72*D72*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H72" s="18">
@@ -10954,7 +10969,7 @@
         <v>0.3</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>0.0805</v>
+        <v>0.0886</v>
       </c>
       <c r="L72" s="21">
         <f>DATOS!$B$12*K72</f>
@@ -10981,7 +10996,7 @@
         <v/>
       </c>
       <c r="R72" s="25" t="n">
-        <v>0.0731</v>
+        <v>0.0804</v>
       </c>
       <c r="S72" s="26">
         <f>G72/(DATOS!$B$12*R72)</f>
@@ -11019,7 +11034,7 @@
         <v/>
       </c>
       <c r="G73" s="21">
-        <f>E73*F73*D73/3600000</f>
+        <f>E73*F73*D73*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H73" s="18">
@@ -11033,7 +11048,7 @@
         <v>0.38</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>0.0837</v>
+        <v>0.0921</v>
       </c>
       <c r="L73" s="21">
         <f>DATOS!$B$12*K73</f>
@@ -11060,7 +11075,7 @@
         <v/>
       </c>
       <c r="R73" s="25" t="n">
-        <v>0.0759</v>
+        <v>0.0835</v>
       </c>
       <c r="S73" s="26">
         <f>G73/(DATOS!$B$12*R73)</f>
@@ -11098,7 +11113,7 @@
         <v/>
       </c>
       <c r="G74" s="21">
-        <f>E74*F74*D74/3600000</f>
+        <f>E74*F74*D74*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H74" s="18">
@@ -11112,7 +11127,7 @@
         <v>0.35</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>0.1334</v>
+        <v>0.1475</v>
       </c>
       <c r="L74" s="21">
         <f>DATOS!$B$12*K74</f>
@@ -11139,7 +11154,7 @@
         <v/>
       </c>
       <c r="R74" s="25" t="n">
-        <v>0.1205</v>
+        <v>0.1331</v>
       </c>
       <c r="S74" s="26">
         <f>G74/(DATOS!$B$12*R74)</f>
@@ -11177,7 +11192,7 @@
         <v/>
       </c>
       <c r="G75" s="21">
-        <f>E75*F75*D75/3600000</f>
+        <f>E75*F75*D75*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H75" s="18">
@@ -11191,7 +11206,7 @@
         <v>0.35</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>0.1338</v>
+        <v>0.1479</v>
       </c>
       <c r="L75" s="21">
         <f>DATOS!$B$12*K75</f>
@@ -11218,7 +11233,7 @@
         <v/>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.1209</v>
+        <v>0.1334</v>
       </c>
       <c r="S75" s="26">
         <f>G75/(DATOS!$B$12*R75)</f>
@@ -11256,7 +11271,7 @@
         <v/>
       </c>
       <c r="G76" s="21">
-        <f>E76*F76*D76/3600000</f>
+        <f>E76*F76*D76*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H76" s="18">
@@ -11270,7 +11285,7 @@
         <v>0.35</v>
       </c>
       <c r="K76" s="25" t="n">
-        <v>0.1356</v>
+        <v>0.15</v>
       </c>
       <c r="L76" s="21">
         <f>DATOS!$B$12*K76</f>
@@ -11297,7 +11312,7 @@
         <v/>
       </c>
       <c r="R76" s="25" t="n">
-        <v>0.1225</v>
+        <v>0.1353</v>
       </c>
       <c r="S76" s="26">
         <f>G76/(DATOS!$B$12*R76)</f>
@@ -11335,7 +11350,7 @@
         <v/>
       </c>
       <c r="G77" s="21">
-        <f>E77*F77*D77/3600000</f>
+        <f>E77*F77*D77*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H77" s="18">
@@ -11349,7 +11364,7 @@
         <v>0.35</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.1763</v>
+        <v>0.1957</v>
       </c>
       <c r="L77" s="21">
         <f>DATOS!$B$12*K77</f>
@@ -11376,7 +11391,7 @@
         <v/>
       </c>
       <c r="R77" s="25" t="n">
-        <v>0.1588</v>
+        <v>0.1759</v>
       </c>
       <c r="S77" s="26">
         <f>G77/(DATOS!$B$12*R77)</f>
@@ -11414,7 +11429,7 @@
         <v/>
       </c>
       <c r="G78" s="21">
-        <f>E78*F78*D78/3600000</f>
+        <f>E78*F78*D78*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H78" s="18">
@@ -11428,7 +11443,7 @@
         <v>0.45</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0.1805</v>
+        <v>0.2005</v>
       </c>
       <c r="L78" s="21">
         <f>DATOS!$B$12*K78</f>
@@ -11455,7 +11470,7 @@
         <v/>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0.1625</v>
+        <v>0.1802</v>
       </c>
       <c r="S78" s="26">
         <f>G78/(DATOS!$B$12*R78)</f>
@@ -11493,7 +11508,7 @@
         <v/>
       </c>
       <c r="G79" s="21">
-        <f>E79*F79*D79/3600000</f>
+        <f>E79*F79*D79*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H79" s="18">
@@ -11507,7 +11522,7 @@
         <v>0.3</v>
       </c>
       <c r="K79" s="25" t="n">
-        <v>0.06809999999999999</v>
+        <v>0.0747</v>
       </c>
       <c r="L79" s="21">
         <f>DATOS!$B$12*K79</f>
@@ -11534,7 +11549,7 @@
         <v/>
       </c>
       <c r="R79" s="25" t="n">
-        <v>0.0619</v>
+        <v>0.0678</v>
       </c>
       <c r="S79" s="26">
         <f>G79/(DATOS!$B$12*R79)</f>
@@ -11572,7 +11587,7 @@
         <v/>
       </c>
       <c r="G80" s="21">
-        <f>E80*F80*D80/3600000</f>
+        <f>E80*F80*D80*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H80" s="18">
@@ -11586,7 +11601,7 @@
         <v>0.36</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>0.0683</v>
+        <v>0.0751</v>
       </c>
       <c r="L80" s="21">
         <f>DATOS!$B$12*K80</f>
@@ -11613,7 +11628,7 @@
         <v/>
       </c>
       <c r="R80" s="25" t="n">
-        <v>0.0621</v>
+        <v>0.0683</v>
       </c>
       <c r="S80" s="26">
         <f>G80/(DATOS!$B$12*R80)</f>
@@ -11651,7 +11666,7 @@
         <v/>
       </c>
       <c r="G81" s="21">
-        <f>E81*F81*D81/3600000</f>
+        <f>E81*F81*D81*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H81" s="18">
@@ -11665,7 +11680,7 @@
         <v>0.35</v>
       </c>
       <c r="K81" s="25" t="n">
-        <v>0.1302</v>
+        <v>0.1439</v>
       </c>
       <c r="L81" s="21">
         <f>DATOS!$B$12*K81</f>
@@ -11692,7 +11707,7 @@
         <v/>
       </c>
       <c r="R81" s="25" t="n">
-        <v>0.1176</v>
+        <v>0.1299</v>
       </c>
       <c r="S81" s="26">
         <f>G81/(DATOS!$B$12*R81)</f>
@@ -11730,7 +11745,7 @@
         <v/>
       </c>
       <c r="G82" s="21">
-        <f>E82*F82*D82/3600000</f>
+        <f>E82*F82*D82*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H82" s="18">
@@ -11744,7 +11759,7 @@
         <v>0.35</v>
       </c>
       <c r="K82" s="25" t="n">
-        <v>0.1431</v>
+        <v>0.1583</v>
       </c>
       <c r="L82" s="21">
         <f>DATOS!$B$12*K82</f>
@@ -11771,7 +11786,7 @@
         <v/>
       </c>
       <c r="R82" s="25" t="n">
-        <v>0.1291</v>
+        <v>0.1427</v>
       </c>
       <c r="S82" s="26">
         <f>G82/(DATOS!$B$12*R82)</f>
@@ -11809,7 +11824,7 @@
         <v/>
       </c>
       <c r="G83" s="21">
-        <f>E83*F83*D83/3600000</f>
+        <f>E83*F83*D83*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H83" s="18">
@@ -11823,7 +11838,7 @@
         <v>0.3</v>
       </c>
       <c r="K83" s="25" t="n">
-        <v>0.1024</v>
+        <v>0.1129</v>
       </c>
       <c r="L83" s="21">
         <f>DATOS!$B$12*K83</f>
@@ -11850,7 +11865,7 @@
         <v/>
       </c>
       <c r="R83" s="25" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.1022</v>
       </c>
       <c r="S83" s="26">
         <f>G83/(DATOS!$B$12*R83)</f>
@@ -11888,7 +11903,7 @@
         <v/>
       </c>
       <c r="G84" s="21">
-        <f>E84*F84*D84/3600000</f>
+        <f>E84*F84*D84*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H84" s="18">
@@ -11902,7 +11917,7 @@
         <v>0.45</v>
       </c>
       <c r="K84" s="25" t="n">
-        <v>0.1075</v>
+        <v>0.1186</v>
       </c>
       <c r="L84" s="21">
         <f>DATOS!$B$12*K84</f>
@@ -11929,7 +11944,7 @@
         <v/>
       </c>
       <c r="R84" s="25" t="n">
-        <v>0.0973</v>
+        <v>0.1073</v>
       </c>
       <c r="S84" s="26">
         <f>G84/(DATOS!$B$12*R84)</f>
@@ -11967,7 +11982,7 @@
         <v/>
       </c>
       <c r="G85" s="21">
-        <f>E85*F85*D85/3600000</f>
+        <f>E85*F85*D85*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H85" s="18">
@@ -11981,7 +11996,7 @@
         <v>0.46</v>
       </c>
       <c r="K85" s="25" t="n">
-        <v>0.1099</v>
+        <v>0.1212</v>
       </c>
       <c r="L85" s="21">
         <f>DATOS!$B$12*K85</f>
@@ -12008,7 +12023,7 @@
         <v/>
       </c>
       <c r="R85" s="25" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.1096</v>
       </c>
       <c r="S85" s="26">
         <f>G85/(DATOS!$B$12*R85)</f>
@@ -12046,7 +12061,7 @@
         <v/>
       </c>
       <c r="G86" s="21">
-        <f>E86*F86*D86/3600000</f>
+        <f>E86*F86*D86*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H86" s="18">
@@ -12060,7 +12075,7 @@
         <v>0.47</v>
       </c>
       <c r="K86" s="25" t="n">
-        <v>0.1101</v>
+        <v>0.1214</v>
       </c>
       <c r="L86" s="21">
         <f>DATOS!$B$12*K86</f>
@@ -12087,7 +12102,7 @@
         <v/>
       </c>
       <c r="R86" s="25" t="n">
-        <v>0.0997</v>
+        <v>0.1098</v>
       </c>
       <c r="S86" s="26">
         <f>G86/(DATOS!$B$12*R86)</f>
@@ -12125,7 +12140,7 @@
         <v/>
       </c>
       <c r="G87" s="21">
-        <f>E87*F87*D87/3600000</f>
+        <f>E87*F87*D87*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H87" s="18">
@@ -12139,7 +12154,7 @@
         <v>0.4</v>
       </c>
       <c r="K87" s="25" t="n">
-        <v>0.136</v>
+        <v>0.1504</v>
       </c>
       <c r="L87" s="21">
         <f>DATOS!$B$12*K87</f>
@@ -12166,7 +12181,7 @@
         <v/>
       </c>
       <c r="R87" s="25" t="n">
-        <v>0.1228</v>
+        <v>0.1357</v>
       </c>
       <c r="S87" s="26">
         <f>G87/(DATOS!$B$12*R87)</f>
@@ -12204,7 +12219,7 @@
         <v/>
       </c>
       <c r="G88" s="21">
-        <f>E88*F88*D88/3600000</f>
+        <f>E88*F88*D88*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H88" s="18">
@@ -12218,7 +12233,7 @@
         <v>0.4</v>
       </c>
       <c r="K88" s="25" t="n">
-        <v>0.136</v>
+        <v>0.1504</v>
       </c>
       <c r="L88" s="21">
         <f>DATOS!$B$12*K88</f>
@@ -12245,7 +12260,7 @@
         <v/>
       </c>
       <c r="R88" s="25" t="n">
-        <v>0.1228</v>
+        <v>0.1357</v>
       </c>
       <c r="S88" s="26">
         <f>G88/(DATOS!$B$12*R88)</f>
@@ -12283,7 +12298,7 @@
         <v/>
       </c>
       <c r="G89" s="21">
-        <f>E89*F89*D89/3600000</f>
+        <f>E89*F89*D89*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H89" s="18">
@@ -12297,7 +12312,7 @@
         <v>0.2</v>
       </c>
       <c r="K89" s="25" t="n">
-        <v>0.0885</v>
+        <v>0.0973</v>
       </c>
       <c r="L89" s="21">
         <f>DATOS!$B$12*K89</f>
@@ -12324,7 +12339,7 @@
         <v/>
       </c>
       <c r="R89" s="25" t="n">
-        <v>0.0803</v>
+        <v>0.0882</v>
       </c>
       <c r="S89" s="26">
         <f>G89/(DATOS!$B$12*R89)</f>
@@ -12362,7 +12377,7 @@
         <v/>
       </c>
       <c r="G90" s="21">
-        <f>E90*F90*D90/3600000</f>
+        <f>E90*F90*D90*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H90" s="18">
@@ -12376,7 +12391,7 @@
         <v>0.5</v>
       </c>
       <c r="K90" s="25" t="n">
-        <v>0.0891</v>
+        <v>0.098</v>
       </c>
       <c r="L90" s="21">
         <f>DATOS!$B$12*K90</f>
@@ -12403,7 +12418,7 @@
         <v/>
       </c>
       <c r="R90" s="25" t="n">
-        <v>0.0808</v>
+        <v>0.0888</v>
       </c>
       <c r="S90" s="26">
         <f>G90/(DATOS!$B$12*R90)</f>
@@ -12441,7 +12456,7 @@
         <v/>
       </c>
       <c r="G91" s="21">
-        <f>E91*F91*D91/3600000</f>
+        <f>E91*F91*D91*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H91" s="18">
@@ -12455,7 +12470,7 @@
         <v>0.5</v>
       </c>
       <c r="K91" s="25" t="n">
-        <v>0.1364</v>
+        <v>0.1508</v>
       </c>
       <c r="L91" s="21">
         <f>DATOS!$B$12*K91</f>
@@ -12482,7 +12497,7 @@
         <v/>
       </c>
       <c r="R91" s="25" t="n">
-        <v>0.1232</v>
+        <v>0.136</v>
       </c>
       <c r="S91" s="26">
         <f>G91/(DATOS!$B$12*R91)</f>
@@ -12520,7 +12535,7 @@
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>E92*F92*D92/3600000</f>
+        <f>E92*F92*D92*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H92" s="18">
@@ -12534,7 +12549,7 @@
         <v>0.4</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>0.1368</v>
+        <v>0.1514</v>
       </c>
       <c r="L92" s="21">
         <f>DATOS!$B$12*K92</f>
@@ -12561,7 +12576,7 @@
         <v/>
       </c>
       <c r="R92" s="25" t="n">
-        <v>0.1236</v>
+        <v>0.1366</v>
       </c>
       <c r="S92" s="26">
         <f>G92/(DATOS!$B$12*R92)</f>
@@ -12599,7 +12614,7 @@
         <v/>
       </c>
       <c r="G93" s="21">
-        <f>E93*F93*D93/3600000</f>
+        <f>E93*F93*D93*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H93" s="18">
@@ -12613,7 +12628,7 @@
         <v>0.3</v>
       </c>
       <c r="K93" s="25" t="n">
-        <v>0.04</v>
+        <v>0.0438</v>
       </c>
       <c r="L93" s="21">
         <f>DATOS!$B$12*K93</f>
@@ -12640,7 +12655,7 @@
         <v/>
       </c>
       <c r="R93" s="25" t="n">
-        <v>0.0365</v>
+        <v>0.04</v>
       </c>
       <c r="S93" s="26">
         <f>G93/(DATOS!$B$12*R93)</f>
@@ -12678,7 +12693,7 @@
         <v/>
       </c>
       <c r="G94" s="21">
-        <f>E94*F94*D94/3600000</f>
+        <f>E94*F94*D94*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H94" s="18">
@@ -12692,7 +12707,7 @@
         <v>0.36</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0.0403</v>
+        <v>0.0441</v>
       </c>
       <c r="L94" s="21">
         <f>DATOS!$B$12*K94</f>
@@ -12719,7 +12734,7 @@
         <v/>
       </c>
       <c r="R94" s="25" t="n">
-        <v>0.0368</v>
+        <v>0.0402</v>
       </c>
       <c r="S94" s="26">
         <f>G94/(DATOS!$B$12*R94)</f>
@@ -12757,7 +12772,7 @@
         <v/>
       </c>
       <c r="G95" s="21">
-        <f>E95*F95*D95/3600000</f>
+        <f>E95*F95*D95*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H95" s="18">
@@ -12771,7 +12786,7 @@
         <v>0.36</v>
       </c>
       <c r="K95" s="25" t="n">
-        <v>0.0641</v>
+        <v>0.0706</v>
       </c>
       <c r="L95" s="21">
         <f>DATOS!$B$12*K95</f>
@@ -12798,7 +12813,7 @@
         <v/>
       </c>
       <c r="R95" s="25" t="n">
-        <v>0.0583</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="S95" s="26">
         <f>G95/(DATOS!$B$12*R95)</f>
@@ -12836,7 +12851,7 @@
         <v/>
       </c>
       <c r="G96" s="21">
-        <f>E96*F96*D96/3600000</f>
+        <f>E96*F96*D96*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H96" s="18">
@@ -12850,7 +12865,7 @@
         <v>0.48</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0.0641</v>
+        <v>0.0706</v>
       </c>
       <c r="L96" s="21">
         <f>DATOS!$B$12*K96</f>
@@ -12877,7 +12892,7 @@
         <v/>
       </c>
       <c r="R96" s="25" t="n">
-        <v>0.0583</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="S96" s="26">
         <f>G96/(DATOS!$B$12*R96)</f>
@@ -12915,7 +12930,7 @@
         <v/>
       </c>
       <c r="G97" s="21">
-        <f>E97*F97*D97/3600000</f>
+        <f>E97*F97*D97*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H97" s="18">
@@ -12929,7 +12944,7 @@
         <v>0.49</v>
       </c>
       <c r="K97" s="25" t="n">
-        <v>0.0791</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L97" s="21">
         <f>DATOS!$B$12*K97</f>
@@ -12956,7 +12971,7 @@
         <v/>
       </c>
       <c r="R97" s="25" t="n">
-        <v>0.0718</v>
+        <v>0.0789</v>
       </c>
       <c r="S97" s="26">
         <f>G97/(DATOS!$B$12*R97)</f>
@@ -12994,7 +13009,7 @@
         <v/>
       </c>
       <c r="G98" s="21">
-        <f>E98*F98*D98/3600000</f>
+        <f>E98*F98*D98*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H98" s="18">
@@ -13008,7 +13023,7 @@
         <v>0.3</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>0.0327</v>
+        <v>0.0356</v>
       </c>
       <c r="L98" s="21">
         <f>DATOS!$B$12*K98</f>
@@ -13035,7 +13050,7 @@
         <v/>
       </c>
       <c r="R98" s="25" t="n">
-        <v>0.0299</v>
+        <v>0.0325</v>
       </c>
       <c r="S98" s="26">
         <f>G98/(DATOS!$B$12*R98)</f>
@@ -13073,7 +13088,7 @@
         <v/>
       </c>
       <c r="G99" s="21">
-        <f>E99*F99*D99/3600000</f>
+        <f>E99*F99*D99*DATOS!$B$21/3600000</f>
         <v/>
       </c>
       <c r="H99" s="18">
@@ -13087,7 +13102,7 @@
         <v>0.37</v>
       </c>
       <c r="K99" s="25" t="n">
-        <v>0.0327</v>
+        <v>0.0356</v>
       </c>
       <c r="L99" s="21">
         <f>DATOS!$B$12*K99</f>
@@ -13114,7 +13129,7 @@
         <v/>
       </c>
       <c r="R99" s="25" t="n">
-        <v>0.0299</v>
+        <v>0.0325</v>
       </c>
       <c r="S99" s="26">
         <f>G99/(DATOS!$B$12*R99)</f>

--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -562,14 +562,14 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>CO Tarapoto (SENAMHI), 1999-2024, 26 anos</t>
+          <t>Pongo de Caynarachi (SENAMHI, codigo 003317), 1989–2013, 25 anos</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Factor de transposicion a Barranquita</t>
+          <t>Factor aplicado a la serie</t>
         </is>
       </c>
       <c r="B10" s="6">
@@ -585,7 +585,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Log-Normal (menor D de Kolmogorov-Smirnov)</t>
+          <t>Gumbel (menor D de Kolmogorov-Smirnov)</t>
         </is>
       </c>
     </row>
@@ -774,22 +774,22 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Precipitacion media anual - estacion CO Tarapoto (mm)</t>
+          <t>Precipitacion media anual - estacion Pongo de Caynarachi (mm)</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1073.1</v>
+        <v>3853.16</v>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>SENAMHI (dato de la estacion)</t>
+          <t>Referencial: SENAMHI 2013-2017, Cuadro N° 05 del estudio hidrologico de Barranquita</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Precipitacion media anual - llanura Caynarachi - Huallaga, Barranquita (mm)</t>
+          <t>Precipitacion media anual - llanura de Barranquita (mm)</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -797,23 +797,22 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Promedio de Navarro (2,349.79), Pelejo (2,332.92) y Shanusi (2,444.00), SENAMHI 2013-2017 (estudio hidrologico de Barranquita)</t>
+          <t>Referencial: promedio de Navarro (2,349.79), Pelejo (2,332.92) y Shanusi (2,444.00), SENAMHI 2013-2017</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Factor de transposicion Pa Barranquita / Pa Tarapoto</t>
-        </is>
-      </c>
-      <c r="B7" s="13">
-        <f>B6/B5</f>
-        <v/>
+          <t>Factor aplicado a la serie de maximas</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>MTC Manual de Hidrologia: transposicion de datos</t>
+          <t>Serie medida de Pongo de Caynarachi (misma subcuenca del rio Caynarachi): sin transposicion</t>
         </is>
       </c>
     </row>
@@ -934,7 +933,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Hoja FRECUENCIAS (Log-Normal)</t>
+          <t>Hoja FRECUENCIAS (Gumbel)</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1066,7 +1065,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>PRECIPITACION MAXIMA EN 24 HORAS - ESTACION CO TARAPOTO (SENAMHI) Y SERIE TRANSPUESTA A BARRANQUITA</t>
+          <t>PRECIPITACION MAXIMA EN 24 HORAS - ESTACION PONGO DE CAYNARACHI (SENAMHI, CODIGO 003317)</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1086,7 @@
     <row r="8">
       <c r="A8" s="17" t="inlineStr">
         <is>
-          <t>Estacion: CO "Tarapoto" - Meteorologica convencional - Lat. 06° 28' S - Long. 76° 22' O - Altitud 356 m s. n. m. - Tarapoto, San Martin - periodo 1999-2024</t>
+          <t>Estacion: Pongo de Caynarachi (codigo 003317) - Meteorologica convencional - Altitud 230 m s. n. m. - Caynarachi, Lamas, San Martin - periodo 1989–2013 (25 anos completos mas recientes del registro diario)</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1158,12 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>P MAX TARAPOTO (mm)</t>
+          <t>P MAX ANUAL (mm)</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>P MAX BARRANQUITA (mm)</t>
+          <t>P MAX DE DISENO (mm)</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
@@ -1175,43 +1174,43 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>1999</v>
+        <v>1989</v>
       </c>
       <c r="B11" s="18" t="n">
-        <v>79.3</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="C11" s="18" t="n">
-        <v>42.5</v>
+        <v>82.7</v>
       </c>
       <c r="D11" s="18" t="n">
-        <v>39.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>16.9</v>
+        <v>61.9</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>54.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>17.5</v>
+        <v>77.5</v>
       </c>
       <c r="H11" s="18" t="n">
-        <v>27.9</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>23</v>
+        <v>58.1</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>11.3</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K11" s="18" t="n">
-        <v>17.3</v>
+        <v>141.9</v>
       </c>
       <c r="L11" s="18" t="n">
-        <v>48.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="M11" s="18" t="n">
-        <v>46.5</v>
+        <v>46.9</v>
       </c>
       <c r="N11" s="19">
         <f>MAX(B11:M11)</f>
@@ -1228,43 +1227,43 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>2000</v>
+        <v>1990</v>
       </c>
       <c r="B12" s="18" t="n">
-        <v>27.5</v>
+        <v>81.5</v>
       </c>
       <c r="C12" s="18" t="n">
-        <v>34.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D12" s="18" t="n">
-        <v>15.6</v>
+        <v>62.6</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>34.7</v>
+        <v>78.8</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>30.2</v>
+        <v>61.2</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>12.6</v>
+        <v>56.2</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>17.5</v>
+        <v>41.6</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>52.6</v>
+        <v>49.5</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>82.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>19.4</v>
+        <v>57.4</v>
       </c>
       <c r="L12" s="18" t="n">
-        <v>24.2</v>
+        <v>115.1</v>
       </c>
       <c r="M12" s="18" t="n">
-        <v>30.3</v>
+        <v>74</v>
       </c>
       <c r="N12" s="19">
         <f>MAX(B12:M12)</f>
@@ -1281,43 +1280,43 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>2001</v>
+        <v>1991</v>
       </c>
       <c r="B13" s="18" t="n">
-        <v>16.2</v>
+        <v>46.5</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>32</v>
+        <v>53.7</v>
       </c>
       <c r="D13" s="18" t="n">
-        <v>35</v>
+        <v>106.7</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>75.90000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>40.3</v>
+        <v>60.3</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>13.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>40.6</v>
+        <v>33.4</v>
       </c>
       <c r="I13" s="18" t="n">
-        <v>21.3</v>
+        <v>32.5</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>24.3</v>
+        <v>95.3</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>61</v>
+        <v>55.3</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>30</v>
+        <v>114.8</v>
       </c>
       <c r="M13" s="18" t="n">
-        <v>42.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="N13" s="19">
         <f>MAX(B13:M13)</f>
@@ -1334,43 +1333,43 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>2002</v>
+        <v>1992</v>
       </c>
       <c r="B14" s="18" t="n">
-        <v>9.300000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="C14" s="18" t="n">
-        <v>30</v>
+        <v>37.3</v>
       </c>
       <c r="D14" s="18" t="n">
-        <v>14.8</v>
+        <v>103.8</v>
       </c>
       <c r="E14" s="18" t="n">
-        <v>39.8</v>
+        <v>123</v>
       </c>
       <c r="F14" s="18" t="n">
-        <v>12.5</v>
+        <v>98.7</v>
       </c>
       <c r="G14" s="18" t="n">
-        <v>43.6</v>
+        <v>30.5</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>35.3</v>
+        <v>45.3</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>7.1</v>
+        <v>70.7</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>5.8</v>
+        <v>60.2</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>32.3</v>
+        <v>77.5</v>
       </c>
       <c r="L14" s="18" t="n">
-        <v>27.5</v>
+        <v>50</v>
       </c>
       <c r="M14" s="18" t="n">
-        <v>20.7</v>
+        <v>120.4</v>
       </c>
       <c r="N14" s="19">
         <f>MAX(B14:M14)</f>
@@ -1387,43 +1386,43 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>2003</v>
+        <v>1993</v>
       </c>
       <c r="B15" s="18" t="n">
+        <v>64.2</v>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>75.2</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="L15" s="18" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="M15" s="18" t="n">
         <v>74</v>
-      </c>
-      <c r="C15" s="18" t="n">
-        <v>37</v>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>33.1</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>84.5</v>
-      </c>
-      <c r="L15" s="18" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="M15" s="18" t="n">
-        <v>52.2</v>
       </c>
       <c r="N15" s="19">
         <f>MAX(B15:M15)</f>
@@ -1440,43 +1439,43 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>2004</v>
+        <v>1994</v>
       </c>
       <c r="B16" s="18" t="n">
-        <v>15.8</v>
+        <v>63.2</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>64.2</v>
+        <v>64</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>24</v>
+        <v>143.2</v>
       </c>
       <c r="E16" s="18" t="n">
-        <v>26.2</v>
+        <v>84.5</v>
       </c>
       <c r="F16" s="18" t="n">
-        <v>48.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="G16" s="18" t="n">
-        <v>30.7</v>
+        <v>53.4</v>
       </c>
       <c r="H16" s="18" t="n">
-        <v>25.7</v>
+        <v>76</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>25.6</v>
+        <v>81.5</v>
       </c>
       <c r="J16" s="18" t="n">
-        <v>28.2</v>
+        <v>65.5</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>33.2</v>
+        <v>110.1</v>
       </c>
       <c r="L16" s="18" t="n">
-        <v>46.2</v>
+        <v>60</v>
       </c>
       <c r="M16" s="18" t="n">
-        <v>59.9</v>
+        <v>179.9</v>
       </c>
       <c r="N16" s="19">
         <f>MAX(B16:M16)</f>
@@ -1493,43 +1492,43 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>2005</v>
+        <v>1995</v>
       </c>
       <c r="B17" s="18" t="n">
-        <v>15.9</v>
+        <v>37</v>
       </c>
       <c r="C17" s="18" t="n">
-        <v>33.7</v>
+        <v>74.3</v>
       </c>
       <c r="D17" s="18" t="n">
-        <v>48.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="E17" s="18" t="n">
-        <v>44</v>
+        <v>50.9</v>
       </c>
       <c r="F17" s="18" t="n">
-        <v>22.4</v>
+        <v>84.2</v>
       </c>
       <c r="G17" s="18" t="n">
-        <v>26.8</v>
+        <v>29.2</v>
       </c>
       <c r="H17" s="18" t="n">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="I17" s="18" t="n">
-        <v>15.5</v>
+        <v>81.2</v>
       </c>
       <c r="J17" s="18" t="n">
-        <v>26</v>
+        <v>44.2</v>
       </c>
       <c r="K17" s="18" t="n">
-        <v>45</v>
+        <v>57.1</v>
       </c>
       <c r="L17" s="18" t="n">
-        <v>71</v>
+        <v>46.1</v>
       </c>
       <c r="M17" s="18" t="n">
-        <v>9.300000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="N17" s="19">
         <f>MAX(B17:M17)</f>
@@ -1546,43 +1545,43 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>2006</v>
+        <v>1996</v>
       </c>
       <c r="B18" s="18" t="n">
-        <v>38.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="C18" s="18" t="n">
-        <v>44.5</v>
+        <v>50.7</v>
       </c>
       <c r="D18" s="18" t="n">
-        <v>41.5</v>
+        <v>73.2</v>
       </c>
       <c r="E18" s="18" t="n">
-        <v>52</v>
+        <v>35.1</v>
       </c>
       <c r="F18" s="18" t="n">
-        <v>39</v>
+        <v>60.2</v>
       </c>
       <c r="G18" s="18" t="n">
-        <v>17.3</v>
+        <v>39.5</v>
       </c>
       <c r="H18" s="18" t="n">
-        <v>113.3</v>
+        <v>14.8</v>
       </c>
       <c r="I18" s="18" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="J18" s="18" t="n">
-        <v>18.5</v>
+        <v>29.1</v>
       </c>
       <c r="K18" s="18" t="n">
-        <v>39.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="L18" s="18" t="n">
-        <v>74</v>
+        <v>55.9</v>
       </c>
       <c r="M18" s="18" t="n">
-        <v>28</v>
+        <v>76.8</v>
       </c>
       <c r="N18" s="19">
         <f>MAX(B18:M18)</f>
@@ -1599,43 +1598,43 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>2007</v>
+        <v>1997</v>
       </c>
       <c r="B19" s="18" t="n">
-        <v>37</v>
+        <v>87.3</v>
       </c>
       <c r="C19" s="18" t="n">
-        <v>7.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="D19" s="18" t="n">
-        <v>48</v>
+        <v>53.1</v>
       </c>
       <c r="E19" s="18" t="n">
-        <v>21</v>
+        <v>71.2</v>
       </c>
       <c r="F19" s="18" t="n">
-        <v>45.4</v>
+        <v>51.5</v>
       </c>
       <c r="G19" s="18" t="n">
-        <v>16.5</v>
+        <v>41.9</v>
       </c>
       <c r="H19" s="18" t="n">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="I19" s="18" t="n">
-        <v>46.2</v>
+        <v>40</v>
       </c>
       <c r="J19" s="18" t="n">
-        <v>45.2</v>
+        <v>65.5</v>
       </c>
       <c r="K19" s="18" t="n">
-        <v>37.8</v>
+        <v>97.3</v>
       </c>
       <c r="L19" s="18" t="n">
-        <v>63.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="M19" s="18" t="n">
-        <v>18.5</v>
+        <v>103.9</v>
       </c>
       <c r="N19" s="19">
         <f>MAX(B19:M19)</f>
@@ -1652,43 +1651,43 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>2008</v>
+        <v>1998</v>
       </c>
       <c r="B20" s="18" t="n">
-        <v>25.6</v>
+        <v>72.5</v>
       </c>
       <c r="C20" s="18" t="n">
-        <v>91</v>
+        <v>78.2</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>27.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E20" s="18" t="n">
-        <v>51</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="F20" s="18" t="n">
-        <v>25.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G20" s="18" t="n">
-        <v>24</v>
+        <v>72.2</v>
       </c>
       <c r="H20" s="18" t="n">
-        <v>9.300000000000001</v>
+        <v>56.6</v>
       </c>
       <c r="I20" s="18" t="n">
-        <v>10.4</v>
+        <v>22</v>
       </c>
       <c r="J20" s="18" t="n">
-        <v>38</v>
+        <v>31.9</v>
       </c>
       <c r="K20" s="18" t="n">
-        <v>17.4</v>
+        <v>76.3</v>
       </c>
       <c r="L20" s="18" t="n">
-        <v>18</v>
+        <v>171.8</v>
       </c>
       <c r="M20" s="18" t="n">
-        <v>15.3</v>
+        <v>79.7</v>
       </c>
       <c r="N20" s="19">
         <f>MAX(B20:M20)</f>
@@ -1705,43 +1704,43 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>2009</v>
+        <v>1999</v>
       </c>
       <c r="B21" s="18" t="n">
-        <v>29.4</v>
+        <v>146</v>
       </c>
       <c r="C21" s="18" t="n">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="D21" s="18" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="E21" s="18" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="F21" s="18" t="n">
+        <v>64</v>
+      </c>
+      <c r="G21" s="18" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="H21" s="18" t="n">
         <v>35.5</v>
       </c>
-      <c r="F21" s="18" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="G21" s="18" t="n">
-        <v>47</v>
-      </c>
-      <c r="H21" s="18" t="n">
-        <v>9.1</v>
-      </c>
       <c r="I21" s="18" t="n">
-        <v>25</v>
+        <v>27.8</v>
       </c>
       <c r="J21" s="18" t="n">
-        <v>31.5</v>
+        <v>61.5</v>
       </c>
       <c r="K21" s="18" t="n">
-        <v>18.4</v>
+        <v>40.1</v>
       </c>
       <c r="L21" s="18" t="n">
-        <v>25.5</v>
+        <v>62.1</v>
       </c>
       <c r="M21" s="18" t="n">
-        <v>42</v>
+        <v>56.9</v>
       </c>
       <c r="N21" s="19">
         <f>MAX(B21:M21)</f>
@@ -1758,43 +1757,43 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>2010</v>
+        <v>2000</v>
       </c>
       <c r="B22" s="18" t="n">
-        <v>32.2</v>
+        <v>56.8</v>
       </c>
       <c r="C22" s="18" t="n">
-        <v>62.4</v>
+        <v>101.7</v>
       </c>
       <c r="D22" s="18" t="n">
-        <v>17.6</v>
+        <v>59.5</v>
       </c>
       <c r="E22" s="18" t="n">
-        <v>72.8</v>
+        <v>97</v>
       </c>
       <c r="F22" s="18" t="n">
-        <v>31.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G22" s="18" t="n">
-        <v>40.6</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="H22" s="18" t="n">
-        <v>6.1</v>
+        <v>43.1</v>
       </c>
       <c r="I22" s="18" t="n">
-        <v>44.5</v>
+        <v>31.1</v>
       </c>
       <c r="J22" s="18" t="n">
-        <v>23.9</v>
+        <v>108.5</v>
       </c>
       <c r="K22" s="18" t="n">
-        <v>27.7</v>
+        <v>71.3</v>
       </c>
       <c r="L22" s="18" t="n">
-        <v>98.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="M22" s="18" t="n">
-        <v>47.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="N22" s="19">
         <f>MAX(B22:M22)</f>
@@ -1811,43 +1810,43 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>2011</v>
+        <v>2001</v>
       </c>
       <c r="B23" s="18" t="n">
-        <v>42.4</v>
+        <v>47.7</v>
       </c>
       <c r="C23" s="18" t="n">
-        <v>11.8</v>
+        <v>76.8</v>
       </c>
       <c r="D23" s="18" t="n">
-        <v>63.2</v>
+        <v>75.8</v>
       </c>
       <c r="E23" s="18" t="n">
-        <v>51.9</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="F23" s="18" t="n">
-        <v>31.5</v>
+        <v>77.3</v>
       </c>
       <c r="G23" s="18" t="n">
-        <v>65.2</v>
+        <v>52.4</v>
       </c>
       <c r="H23" s="18" t="n">
-        <v>49.2</v>
+        <v>40.8</v>
       </c>
       <c r="I23" s="18" t="n">
-        <v>14.5</v>
+        <v>26.1</v>
       </c>
       <c r="J23" s="18" t="n">
-        <v>21.6</v>
+        <v>35</v>
       </c>
       <c r="K23" s="18" t="n">
-        <v>24.6</v>
+        <v>74.7</v>
       </c>
       <c r="L23" s="18" t="n">
-        <v>49.2</v>
+        <v>78</v>
       </c>
       <c r="M23" s="18" t="n">
-        <v>61.8</v>
+        <v>76.8</v>
       </c>
       <c r="N23" s="19">
         <f>MAX(B23:M23)</f>
@@ -1864,43 +1863,43 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="B24" s="18" t="n">
-        <v>71.7</v>
+        <v>27.8</v>
       </c>
       <c r="C24" s="18" t="n">
-        <v>35.6</v>
+        <v>77.2</v>
       </c>
       <c r="D24" s="18" t="n">
-        <v>53.1</v>
+        <v>63.4</v>
       </c>
       <c r="E24" s="18" t="n">
-        <v>100.5</v>
+        <v>78</v>
       </c>
       <c r="F24" s="18" t="n">
-        <v>40.8</v>
+        <v>46.7</v>
       </c>
       <c r="G24" s="18" t="n">
-        <v>28.8</v>
+        <v>35.5</v>
       </c>
       <c r="H24" s="18" t="n">
-        <v>20</v>
+        <v>52.3</v>
       </c>
       <c r="I24" s="18" t="n">
-        <v>8.300000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="J24" s="18" t="n">
-        <v>31.2</v>
+        <v>45.4</v>
       </c>
       <c r="K24" s="18" t="n">
-        <v>40.2</v>
+        <v>88.7</v>
       </c>
       <c r="L24" s="18" t="n">
-        <v>15.6</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M24" s="18" t="n">
-        <v>82.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="N24" s="19">
         <f>MAX(B24:M24)</f>
@@ -1917,43 +1916,43 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>2013</v>
+        <v>2003</v>
       </c>
       <c r="B25" s="18" t="n">
-        <v>71.7</v>
+        <v>59</v>
       </c>
       <c r="C25" s="18" t="n">
-        <v>32.7</v>
+        <v>45.1</v>
       </c>
       <c r="D25" s="18" t="n">
-        <v>45.3</v>
+        <v>61.2</v>
       </c>
       <c r="E25" s="18" t="n">
-        <v>27.4</v>
+        <v>75.5</v>
       </c>
       <c r="F25" s="18" t="n">
-        <v>32.1</v>
+        <v>138.5</v>
       </c>
       <c r="G25" s="18" t="n">
-        <v>20.1</v>
+        <v>75.2</v>
       </c>
       <c r="H25" s="18" t="n">
-        <v>15</v>
+        <v>57.1</v>
       </c>
       <c r="I25" s="18" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="J25" s="18" t="n">
-        <v>41.8</v>
+        <v>69.7</v>
       </c>
       <c r="K25" s="18" t="n">
-        <v>27</v>
+        <v>81.5</v>
       </c>
       <c r="L25" s="18" t="n">
-        <v>64.5</v>
+        <v>100.8</v>
       </c>
       <c r="M25" s="18" t="n">
-        <v>28.4</v>
+        <v>82.8</v>
       </c>
       <c r="N25" s="19">
         <f>MAX(B25:M25)</f>
@@ -1970,43 +1969,43 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="B26" s="18" t="n">
-        <v>33.4</v>
+        <v>47.4</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>29.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D26" s="18" t="n">
-        <v>60.3</v>
+        <v>76.3</v>
       </c>
       <c r="E26" s="18" t="n">
-        <v>37.6</v>
+        <v>75.3</v>
       </c>
       <c r="F26" s="18" t="n">
-        <v>32.1</v>
+        <v>87</v>
       </c>
       <c r="G26" s="18" t="n">
-        <v>13.2</v>
+        <v>32.5</v>
       </c>
       <c r="H26" s="18" t="n">
-        <v>32.5</v>
+        <v>44.4</v>
       </c>
       <c r="I26" s="18" t="n">
-        <v>22.4</v>
+        <v>55.5</v>
       </c>
       <c r="J26" s="18" t="n">
-        <v>28.2</v>
+        <v>44.3</v>
       </c>
       <c r="K26" s="18" t="n">
-        <v>89.5</v>
+        <v>75.5</v>
       </c>
       <c r="L26" s="18" t="n">
-        <v>46.1</v>
+        <v>90.2</v>
       </c>
       <c r="M26" s="18" t="n">
-        <v>26</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N26" s="19">
         <f>MAX(B26:M26)</f>
@@ -2023,43 +2022,45 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B27" s="18" t="n">
-        <v>28.4</v>
+        <v>2005</v>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>S/D</t>
+        </is>
       </c>
       <c r="C27" s="18" t="n">
-        <v>40.9</v>
+        <v>80.8</v>
       </c>
       <c r="D27" s="18" t="n">
-        <v>16.4</v>
+        <v>76.7</v>
       </c>
       <c r="E27" s="18" t="n">
-        <v>43.7</v>
+        <v>97.3</v>
       </c>
       <c r="F27" s="18" t="n">
-        <v>34.4</v>
+        <v>45</v>
       </c>
       <c r="G27" s="18" t="n">
-        <v>40.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H27" s="18" t="n">
-        <v>12.8</v>
+        <v>17</v>
       </c>
       <c r="I27" s="18" t="n">
-        <v>34.6</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="J27" s="18" t="n">
-        <v>13.7</v>
+        <v>23</v>
       </c>
       <c r="K27" s="18" t="n">
-        <v>32.9</v>
+        <v>70.5</v>
       </c>
       <c r="L27" s="18" t="n">
-        <v>64.2</v>
+        <v>77.3</v>
       </c>
       <c r="M27" s="18" t="n">
-        <v>60.3</v>
+        <v>66.2</v>
       </c>
       <c r="N27" s="19">
         <f>MAX(B27:M27)</f>
@@ -2076,43 +2077,43 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>2016</v>
+        <v>2006</v>
       </c>
       <c r="B28" s="18" t="n">
-        <v>36</v>
+        <v>80.7</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>40.1</v>
+        <v>39.5</v>
       </c>
       <c r="D28" s="18" t="n">
-        <v>35.9</v>
+        <v>81.5</v>
       </c>
       <c r="E28" s="18" t="n">
-        <v>18.6</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F28" s="18" t="n">
-        <v>32.2</v>
+        <v>48.7</v>
       </c>
       <c r="G28" s="18" t="n">
-        <v>47.5</v>
+        <v>68</v>
       </c>
       <c r="H28" s="18" t="n">
-        <v>19.4</v>
+        <v>35.8</v>
       </c>
       <c r="I28" s="18" t="n">
-        <v>10.3</v>
+        <v>51</v>
       </c>
       <c r="J28" s="18" t="n">
-        <v>19</v>
+        <v>52.7</v>
       </c>
       <c r="K28" s="18" t="n">
-        <v>50</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="L28" s="18" t="n">
-        <v>27</v>
+        <v>72.2</v>
       </c>
       <c r="M28" s="18" t="n">
-        <v>33.5</v>
+        <v>102.5</v>
       </c>
       <c r="N28" s="19">
         <f>MAX(B28:M28)</f>
@@ -2129,43 +2130,43 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>2017</v>
+        <v>2007</v>
       </c>
       <c r="B29" s="18" t="n">
-        <v>51.2</v>
+        <v>56.2</v>
       </c>
       <c r="C29" s="18" t="n">
-        <v>73.59999999999999</v>
+        <v>33.3</v>
       </c>
       <c r="D29" s="18" t="n">
-        <v>62.9</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="E29" s="18" t="n">
-        <v>51.8</v>
+        <v>76.5</v>
       </c>
       <c r="F29" s="18" t="n">
-        <v>36</v>
+        <v>39.2</v>
       </c>
       <c r="G29" s="18" t="n">
-        <v>39.6</v>
+        <v>46.8</v>
       </c>
       <c r="H29" s="18" t="n">
-        <v>19.5</v>
+        <v>58.7</v>
       </c>
       <c r="I29" s="18" t="n">
-        <v>30.8</v>
+        <v>33</v>
       </c>
       <c r="J29" s="18" t="n">
-        <v>47.7</v>
+        <v>47.5</v>
       </c>
       <c r="K29" s="18" t="n">
-        <v>15.7</v>
+        <v>76</v>
       </c>
       <c r="L29" s="18" t="n">
-        <v>72.5</v>
+        <v>77.3</v>
       </c>
       <c r="M29" s="18" t="n">
-        <v>63.7</v>
+        <v>76.5</v>
       </c>
       <c r="N29" s="19">
         <f>MAX(B29:M29)</f>
@@ -2182,43 +2183,45 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>2018</v>
+        <v>2008</v>
       </c>
       <c r="B30" s="18" t="n">
-        <v>25.6</v>
+        <v>57.8</v>
       </c>
       <c r="C30" s="18" t="n">
-        <v>42.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D30" s="18" t="n">
-        <v>55.4</v>
+        <v>74</v>
       </c>
       <c r="E30" s="18" t="n">
-        <v>47.4</v>
+        <v>70.5</v>
       </c>
       <c r="F30" s="18" t="n">
-        <v>27.5</v>
+        <v>67</v>
       </c>
       <c r="G30" s="18" t="n">
-        <v>35</v>
-      </c>
-      <c r="H30" s="18" t="n">
-        <v>34.2</v>
+        <v>51</v>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
+        <is>
+          <t>S/D</t>
+        </is>
       </c>
       <c r="I30" s="18" t="n">
-        <v>18.4</v>
+        <v>25.9</v>
       </c>
       <c r="J30" s="18" t="n">
-        <v>34.7</v>
+        <v>48</v>
       </c>
       <c r="K30" s="18" t="n">
-        <v>27.5</v>
+        <v>55.2</v>
       </c>
       <c r="L30" s="18" t="n">
-        <v>26.5</v>
+        <v>43</v>
       </c>
       <c r="M30" s="18" t="n">
-        <v>69.59999999999999</v>
+        <v>100.4</v>
       </c>
       <c r="N30" s="19">
         <f>MAX(B30:M30)</f>
@@ -2235,43 +2238,43 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>2019</v>
+        <v>2009</v>
       </c>
       <c r="B31" s="18" t="n">
-        <v>42.9</v>
+        <v>87</v>
       </c>
       <c r="C31" s="18" t="n">
-        <v>42.3</v>
+        <v>69.7</v>
       </c>
       <c r="D31" s="18" t="n">
-        <v>20.8</v>
+        <v>58</v>
       </c>
       <c r="E31" s="18" t="n">
-        <v>23.5</v>
+        <v>52.2</v>
       </c>
       <c r="F31" s="18" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="G31" s="18" t="n">
-        <v>9.699999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="H31" s="18" t="n">
-        <v>39.8</v>
+        <v>77.2</v>
       </c>
       <c r="I31" s="18" t="n">
-        <v>23.7</v>
+        <v>25.3</v>
       </c>
       <c r="J31" s="18" t="n">
-        <v>25.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K31" s="18" t="n">
-        <v>86.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="L31" s="18" t="n">
-        <v>36.4</v>
+        <v>59</v>
       </c>
       <c r="M31" s="18" t="n">
-        <v>44</v>
+        <v>78.8</v>
       </c>
       <c r="N31" s="19">
         <f>MAX(B31:M31)</f>
@@ -2288,51 +2291,43 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>2020</v>
+        <v>2010</v>
       </c>
       <c r="B32" s="18" t="n">
-        <v>152.5</v>
+        <v>40</v>
       </c>
       <c r="C32" s="18" t="n">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D32" s="18" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="E32" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="F32" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="G32" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
+        <v>69.2</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <v>128</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <v>103</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <v>56.5</v>
       </c>
       <c r="I32" s="18" t="n">
-        <v>32.2</v>
+        <v>15.2</v>
       </c>
       <c r="J32" s="18" t="n">
-        <v>32.9</v>
+        <v>36.5</v>
       </c>
       <c r="K32" s="18" t="n">
-        <v>50.6</v>
+        <v>75.8</v>
       </c>
       <c r="L32" s="18" t="n">
-        <v>38.4</v>
+        <v>80.8</v>
       </c>
       <c r="M32" s="18" t="n">
-        <v>14.2</v>
+        <v>73.8</v>
       </c>
       <c r="N32" s="19">
         <f>MAX(B32:M32)</f>
@@ -2349,43 +2344,43 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>2021</v>
+        <v>2011</v>
       </c>
       <c r="B33" s="18" t="n">
-        <v>42.4</v>
+        <v>73.8</v>
       </c>
       <c r="C33" s="18" t="n">
-        <v>46.8</v>
+        <v>76.3</v>
       </c>
       <c r="D33" s="18" t="n">
-        <v>73.5</v>
+        <v>80.8</v>
       </c>
       <c r="E33" s="18" t="n">
-        <v>28.5</v>
+        <v>60.7</v>
       </c>
       <c r="F33" s="18" t="n">
-        <v>12.9</v>
+        <v>77.8</v>
       </c>
       <c r="G33" s="18" t="n">
-        <v>32.4</v>
+        <v>67.3</v>
       </c>
       <c r="H33" s="18" t="n">
-        <v>59.9</v>
+        <v>58.8</v>
       </c>
       <c r="I33" s="18" t="n">
-        <v>24.3</v>
+        <v>57.3</v>
       </c>
       <c r="J33" s="18" t="n">
-        <v>54.3</v>
+        <v>57</v>
       </c>
       <c r="K33" s="18" t="n">
-        <v>28.8</v>
+        <v>70</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>30.8</v>
+        <v>101</v>
       </c>
       <c r="M33" s="18" t="n">
-        <v>69.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="N33" s="19">
         <f>MAX(B33:M33)</f>
@@ -2402,43 +2397,43 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
       <c r="B34" s="18" t="n">
-        <v>15</v>
+        <v>110.2</v>
       </c>
       <c r="C34" s="18" t="n">
-        <v>48.8</v>
+        <v>56.5</v>
       </c>
       <c r="D34" s="18" t="n">
-        <v>54.4</v>
+        <v>58</v>
       </c>
       <c r="E34" s="18" t="n">
-        <v>39</v>
+        <v>87.2</v>
       </c>
       <c r="F34" s="18" t="n">
-        <v>48.1</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="G34" s="18" t="n">
-        <v>17</v>
+        <v>25.5</v>
       </c>
       <c r="H34" s="18" t="n">
-        <v>15.8</v>
+        <v>51.2</v>
       </c>
       <c r="I34" s="18" t="n">
-        <v>40.9</v>
+        <v>12.1</v>
       </c>
       <c r="J34" s="18" t="n">
-        <v>32.8</v>
+        <v>48</v>
       </c>
       <c r="K34" s="18" t="n">
-        <v>31.6</v>
+        <v>48.2</v>
       </c>
       <c r="L34" s="18" t="n">
-        <v>85.2</v>
+        <v>72</v>
       </c>
       <c r="M34" s="18" t="n">
-        <v>43</v>
+        <v>54.8</v>
       </c>
       <c r="N34" s="19">
         <f>MAX(B34:M34)</f>
@@ -2455,43 +2450,43 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>2023</v>
+        <v>2013</v>
       </c>
       <c r="B35" s="18" t="n">
-        <v>58</v>
+        <v>78.7</v>
       </c>
       <c r="C35" s="18" t="n">
-        <v>22.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D35" s="18" t="n">
-        <v>92.40000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="E35" s="18" t="n">
-        <v>43.3</v>
+        <v>62.5</v>
       </c>
       <c r="F35" s="18" t="n">
-        <v>25.8</v>
+        <v>53.6</v>
       </c>
       <c r="G35" s="18" t="n">
-        <v>9.199999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="H35" s="18" t="n">
-        <v>14.5</v>
+        <v>81.2</v>
       </c>
       <c r="I35" s="18" t="n">
-        <v>26</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="J35" s="18" t="n">
-        <v>14</v>
+        <v>54.8</v>
       </c>
       <c r="K35" s="18" t="n">
-        <v>14.2</v>
+        <v>76.8</v>
       </c>
       <c r="L35" s="18" t="n">
-        <v>77.5</v>
+        <v>84</v>
       </c>
       <c r="M35" s="18" t="n">
-        <v>56.5</v>
+        <v>30.7</v>
       </c>
       <c r="N35" s="19">
         <f>MAX(B35:M35)</f>
@@ -2506,73 +2501,10 @@
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B36" s="18" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="C36" s="18" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="D36" s="18" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E36" s="18" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F36" s="18" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="G36" s="18" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H36" s="18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I36" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="J36" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="K36" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="L36" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="M36" s="18" t="inlineStr">
-        <is>
-          <t>S/D</t>
-        </is>
-      </c>
-      <c r="N36" s="19">
-        <f>MAX(B36:M36)</f>
-        <v/>
-      </c>
-      <c r="O36" s="20">
-        <f>N36*DATOS!$B$7</f>
-        <v/>
-      </c>
-      <c r="P36" s="21">
-        <f>LOG10(O36)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>2020: sin datos de abril a julio; 2024: datos de enero a julio (se conserva el maximo registrado, igual que en los estudios de Morales).</t>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Maximas mensuales obtenidas de los registros diarios del SENAMHI. S/D: enero de 2005 y julio de 2008 sin datos (se conservan los maximos de los otros once meses). 2014 (solo enero a abril) no se considera.</t>
         </is>
       </c>
     </row>
@@ -2605,7 +2537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ANALISIS DE FRECUENCIAS DE LA SERIE TRANSPUESTA (mm)</t>
+          <t>ANALISIS DE FRECUENCIAS DE LA SERIE DE PONGO DE CAYNARACHI 1989-2013 (mm)</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2562,7 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNT(SERIE!$O$11:$O$36)</f>
+        <f>COUNT(SERIE!$O$11:$O$35)</f>
         <v/>
       </c>
     </row>
@@ -2641,7 +2573,7 @@
         </is>
       </c>
       <c r="B6" s="19">
-        <f>AVERAGE(SERIE!$O$11:$O$36)</f>
+        <f>AVERAGE(SERIE!$O$11:$O$35)</f>
         <v/>
       </c>
     </row>
@@ -2652,7 +2584,7 @@
         </is>
       </c>
       <c r="B7" s="19">
-        <f>STDEV(SERIE!$O$11:$O$36)</f>
+        <f>STDEV(SERIE!$O$11:$O$35)</f>
         <v/>
       </c>
     </row>
@@ -2663,7 +2595,7 @@
         </is>
       </c>
       <c r="B8" s="23">
-        <f>SKEW(SERIE!$O$11:$O$36)</f>
+        <f>SKEW(SERIE!$O$11:$O$35)</f>
         <v/>
       </c>
     </row>
@@ -2674,7 +2606,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>AVERAGE(SERIE!$P$11:$P$36)</f>
+        <f>AVERAGE(SERIE!$P$11:$P$35)</f>
         <v/>
       </c>
     </row>
@@ -2685,7 +2617,7 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>STDEV(SERIE!$P$11:$P$36)</f>
+        <f>STDEV(SERIE!$P$11:$P$35)</f>
         <v/>
       </c>
     </row>
@@ -2696,7 +2628,7 @@
         </is>
       </c>
       <c r="B11" s="24">
-        <f>SKEW(SERIE!$P$11:$P$36)</f>
+        <f>SKEW(SERIE!$P$11:$P$35)</f>
         <v/>
       </c>
     </row>
@@ -2765,7 +2697,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>DISEÑO (Log-Normal)</t>
+          <t>DISEÑO (Gumbel)</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2734,7 @@
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>D17</f>
+        <f>H17</f>
         <v/>
       </c>
     </row>
@@ -2839,7 +2771,7 @@
         <v/>
       </c>
       <c r="I18" s="20">
-        <f>D18</f>
+        <f>H18</f>
         <v/>
       </c>
     </row>
@@ -2876,7 +2808,7 @@
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>D19</f>
+        <f>H19</f>
         <v/>
       </c>
     </row>
@@ -2913,7 +2845,7 @@
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>D20</f>
+        <f>H20</f>
         <v/>
       </c>
     </row>
@@ -2950,7 +2882,7 @@
         <v/>
       </c>
       <c r="I21" s="20">
-        <f>D21</f>
+        <f>H21</f>
         <v/>
       </c>
     </row>
@@ -2987,7 +2919,7 @@
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>D22</f>
+        <f>H22</f>
         <v/>
       </c>
     </row>
@@ -3024,7 +2956,7 @@
         <v/>
       </c>
       <c r="I23" s="20">
-        <f>D23</f>
+        <f>H23</f>
         <v/>
       </c>
     </row>
@@ -3061,7 +2993,7 @@
         <v/>
       </c>
       <c r="I24" s="20">
-        <f>D24</f>
+        <f>H24</f>
         <v/>
       </c>
     </row>
@@ -3098,14 +3030,14 @@
         <v/>
       </c>
       <c r="I25" s="20">
-        <f>D25</f>
+        <f>H25</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Se adopta la distribucion Log-Normal: menor estadistico de Kolmogorov-Smirnov (hoja KS), igual que en los estudios de Morales.</t>
+          <t>Se adopta la distribucion Gumbel: menor estadistico de Kolmogorov-Smirnov (hoja KS).</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3220,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A9)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A9)</f>
         <v/>
       </c>
       <c r="C9" s="21">
@@ -3236,7 +3168,7 @@
         <v/>
       </c>
       <c r="F9" s="21" t="n">
-        <v>0.012456</v>
+        <v>0.052148</v>
       </c>
       <c r="G9" s="21">
         <f>EXP(-EXP(-(B9-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3264,7 +3196,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A10)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A10)</f>
         <v/>
       </c>
       <c r="C10" s="21">
@@ -3280,7 +3212,7 @@
         <v/>
       </c>
       <c r="F10" s="21" t="n">
-        <v>0.04002</v>
+        <v>0.058865</v>
       </c>
       <c r="G10" s="21">
         <f>EXP(-EXP(-(B10-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3308,7 +3240,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A11)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A11)</f>
         <v/>
       </c>
       <c r="C11" s="21">
@@ -3324,7 +3256,7 @@
         <v/>
       </c>
       <c r="F11" s="21" t="n">
-        <v>0.047822</v>
+        <v>0.134433</v>
       </c>
       <c r="G11" s="21">
         <f>EXP(-EXP(-(B11-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3352,7 +3284,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A12)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A12)</f>
         <v/>
       </c>
       <c r="C12" s="21">
@@ -3368,7 +3300,7 @@
         <v/>
       </c>
       <c r="F12" s="21" t="n">
-        <v>0.241319</v>
+        <v>0.137447</v>
       </c>
       <c r="G12" s="21">
         <f>EXP(-EXP(-(B12-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3396,7 +3328,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A13)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A13)</f>
         <v/>
       </c>
       <c r="C13" s="21">
@@ -3412,7 +3344,7 @@
         <v/>
       </c>
       <c r="F13" s="21" t="n">
-        <v>0.254951</v>
+        <v>0.18227</v>
       </c>
       <c r="G13" s="21">
         <f>EXP(-EXP(-(B13-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3440,7 +3372,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A14)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A14)</f>
         <v/>
       </c>
       <c r="C14" s="21">
@@ -3456,7 +3388,7 @@
         <v/>
       </c>
       <c r="F14" s="21" t="n">
-        <v>0.254951</v>
+        <v>0.211482</v>
       </c>
       <c r="G14" s="21">
         <f>EXP(-EXP(-(B14-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3484,7 +3416,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A15)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A15)</f>
         <v/>
       </c>
       <c r="C15" s="21">
@@ -3500,7 +3432,7 @@
         <v/>
       </c>
       <c r="F15" s="21" t="n">
-        <v>0.274829</v>
+        <v>0.218529</v>
       </c>
       <c r="G15" s="21">
         <f>EXP(-EXP(-(B15-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3528,7 +3460,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A16)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A16)</f>
         <v/>
       </c>
       <c r="C16" s="21">
@@ -3544,7 +3476,7 @@
         <v/>
       </c>
       <c r="F16" s="21" t="n">
-        <v>0.365201</v>
+        <v>0.238188</v>
       </c>
       <c r="G16" s="21">
         <f>EXP(-EXP(-(B16-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3572,7 +3504,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A17)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A17)</f>
         <v/>
       </c>
       <c r="C17" s="21">
@@ -3588,7 +3520,7 @@
         <v/>
       </c>
       <c r="F17" s="21" t="n">
-        <v>0.394397</v>
+        <v>0.353051</v>
       </c>
       <c r="G17" s="21">
         <f>EXP(-EXP(-(B17-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3616,7 +3548,7 @@
         <v>10</v>
       </c>
       <c r="B18" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A18)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A18)</f>
         <v/>
       </c>
       <c r="C18" s="21">
@@ -3632,7 +3564,7 @@
         <v/>
       </c>
       <c r="F18" s="21" t="n">
-        <v>0.408968</v>
+        <v>0.369802</v>
       </c>
       <c r="G18" s="21">
         <f>EXP(-EXP(-(B18-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3660,7 +3592,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A19)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A19)</f>
         <v/>
       </c>
       <c r="C19" s="21">
@@ -3676,7 +3608,7 @@
         <v/>
       </c>
       <c r="F19" s="21" t="n">
-        <v>0.419283</v>
+        <v>0.426655</v>
       </c>
       <c r="G19" s="21">
         <f>EXP(-EXP(-(B19-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3704,7 +3636,7 @@
         <v>12</v>
       </c>
       <c r="B20" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A20)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A20)</f>
         <v/>
       </c>
       <c r="C20" s="21">
@@ -3720,7 +3652,7 @@
         <v/>
       </c>
       <c r="F20" s="21" t="n">
-        <v>0.446131</v>
+        <v>0.437443</v>
       </c>
       <c r="G20" s="21">
         <f>EXP(-EXP(-(B20-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3748,7 +3680,7 @@
         <v>13</v>
       </c>
       <c r="B21" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A21)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A21)</f>
         <v/>
       </c>
       <c r="C21" s="21">
@@ -3764,7 +3696,7 @@
         <v/>
       </c>
       <c r="F21" s="21" t="n">
-        <v>0.44817</v>
+        <v>0.464021</v>
       </c>
       <c r="G21" s="21">
         <f>EXP(-EXP(-(B21-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3792,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A22)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A22)</f>
         <v/>
       </c>
       <c r="C22" s="21">
@@ -3808,7 +3740,7 @@
         <v/>
       </c>
       <c r="F22" s="21" t="n">
-        <v>0.494709</v>
+        <v>0.488258</v>
       </c>
       <c r="G22" s="21">
         <f>EXP(-EXP(-(B22-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3836,7 +3768,7 @@
         <v>15</v>
       </c>
       <c r="B23" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A23)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A23)</f>
         <v/>
       </c>
       <c r="C23" s="21">
@@ -3852,7 +3784,7 @@
         <v/>
       </c>
       <c r="F23" s="21" t="n">
-        <v>0.56052</v>
+        <v>0.563322</v>
       </c>
       <c r="G23" s="21">
         <f>EXP(-EXP(-(B23-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3880,7 +3812,7 @@
         <v>16</v>
       </c>
       <c r="B24" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A24)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A24)</f>
         <v/>
       </c>
       <c r="C24" s="21">
@@ -3896,7 +3828,7 @@
         <v/>
       </c>
       <c r="F24" s="21" t="n">
-        <v>0.618056</v>
+        <v>0.589098</v>
       </c>
       <c r="G24" s="21">
         <f>EXP(-EXP(-(B24-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3924,7 +3856,7 @@
         <v>17</v>
       </c>
       <c r="B25" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A25)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A25)</f>
         <v/>
       </c>
       <c r="C25" s="21">
@@ -3940,7 +3872,7 @@
         <v/>
       </c>
       <c r="F25" s="21" t="n">
-        <v>0.651583</v>
+        <v>0.653161</v>
       </c>
       <c r="G25" s="21">
         <f>EXP(-EXP(-(B25-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -3968,7 +3900,7 @@
         <v>18</v>
       </c>
       <c r="B26" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A26)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A26)</f>
         <v/>
       </c>
       <c r="C26" s="21">
@@ -3984,7 +3916,7 @@
         <v/>
       </c>
       <c r="F26" s="21" t="n">
-        <v>0.662839</v>
+        <v>0.657047</v>
       </c>
       <c r="G26" s="21">
         <f>EXP(-EXP(-(B26-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4012,7 +3944,7 @@
         <v>19</v>
       </c>
       <c r="B27" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A27)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A27)</f>
         <v/>
       </c>
       <c r="C27" s="21">
@@ -4028,7 +3960,7 @@
         <v/>
       </c>
       <c r="F27" s="21" t="n">
-        <v>0.689093</v>
+        <v>0.746938</v>
       </c>
       <c r="G27" s="21">
         <f>EXP(-EXP(-(B27-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4056,7 +3988,7 @@
         <v>20</v>
       </c>
       <c r="B28" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A28)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A28)</f>
         <v/>
       </c>
       <c r="C28" s="21">
@@ -4072,7 +4004,7 @@
         <v/>
       </c>
       <c r="F28" s="21" t="n">
-        <v>0.726401</v>
+        <v>0.792312</v>
       </c>
       <c r="G28" s="21">
         <f>EXP(-EXP(-(B28-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4100,7 +4032,7 @@
         <v>21</v>
       </c>
       <c r="B29" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A29)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A29)</f>
         <v/>
       </c>
       <c r="C29" s="21">
@@ -4116,7 +4048,7 @@
         <v/>
       </c>
       <c r="F29" s="21" t="n">
-        <v>0.746308</v>
+        <v>0.863731</v>
       </c>
       <c r="G29" s="21">
         <f>EXP(-EXP(-(B29-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4144,7 +4076,7 @@
         <v>22</v>
       </c>
       <c r="B30" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A30)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A30)</f>
         <v/>
       </c>
       <c r="C30" s="21">
@@ -4160,7 +4092,7 @@
         <v/>
       </c>
       <c r="F30" s="21" t="n">
-        <v>0.763856</v>
+        <v>0.881198</v>
       </c>
       <c r="G30" s="21">
         <f>EXP(-EXP(-(B30-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4188,7 +4120,7 @@
         <v>23</v>
       </c>
       <c r="B31" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A31)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A31)</f>
         <v/>
       </c>
       <c r="C31" s="21">
@@ -4204,7 +4136,7 @@
         <v/>
       </c>
       <c r="F31" s="21" t="n">
-        <v>0.8282119999999999</v>
+        <v>0.899301</v>
       </c>
       <c r="G31" s="21">
         <f>EXP(-EXP(-(B31-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4232,7 +4164,7 @@
         <v>24</v>
       </c>
       <c r="B32" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A32)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A32)</f>
         <v/>
       </c>
       <c r="C32" s="21">
@@ -4248,7 +4180,7 @@
         <v/>
       </c>
       <c r="F32" s="21" t="n">
-        <v>0.846896</v>
+        <v>0.96378</v>
       </c>
       <c r="G32" s="21">
         <f>EXP(-EXP(-(B32-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4276,7 +4208,7 @@
         <v>25</v>
       </c>
       <c r="B33" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A33)</f>
+        <f>SMALL(SERIE!$O$11:$O$35,A33)</f>
         <v/>
       </c>
       <c r="C33" s="21">
@@ -4292,7 +4224,7 @@
         <v/>
       </c>
       <c r="F33" s="21" t="n">
-        <v>0.926423</v>
+        <v>0.973456</v>
       </c>
       <c r="G33" s="21">
         <f>EXP(-EXP(-(B33-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
@@ -4316,118 +4248,74 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n">
-        <v>26</v>
-      </c>
-      <c r="B34" s="26">
-        <f>SMALL(SERIE!$O$11:$O$36,A34)</f>
-        <v/>
-      </c>
-      <c r="C34" s="21">
-        <f>A34/(FRECUENCIAS!$B$5+1)</f>
-        <v/>
-      </c>
-      <c r="D34" s="21">
-        <f>NORMDIST(B34,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
-        <v/>
-      </c>
-      <c r="E34" s="21">
-        <f>NORMDIST(LOG10(B34),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F34" s="21" t="n">
-        <v>0.993222</v>
-      </c>
-      <c r="G34" s="21">
-        <f>EXP(-EXP(-(B34-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>ABS(C34-D34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="21">
-        <f>ABS(C34-E34)</f>
-        <v/>
-      </c>
-      <c r="J34" s="21">
-        <f>ABS(C34-F34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="21">
-        <f>ABS(C34-G34)</f>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>D max</t>
+        </is>
+      </c>
+      <c r="H34" s="28">
+        <f>MAX(H9:H33)</f>
+        <v/>
+      </c>
+      <c r="I34" s="28">
+        <f>MAX(I9:I33)</f>
+        <v/>
+      </c>
+      <c r="J34" s="28">
+        <f>MAX(J9:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="28">
+        <f>MAX(K9:K33)</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>D max</t>
-        </is>
-      </c>
-      <c r="H35" s="28">
-        <f>MAX(H9:H34)</f>
-        <v/>
-      </c>
-      <c r="I35" s="28">
-        <f>MAX(I9:I34)</f>
-        <v/>
-      </c>
-      <c r="J35" s="28">
-        <f>MAX(J9:J34)</f>
-        <v/>
-      </c>
-      <c r="K35" s="28">
-        <f>MAX(K9:K34)</f>
-        <v/>
+          <t>D critico</t>
+        </is>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <v>0.27</v>
       </c>
     </row>
     <row r="36">
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>D critico</t>
-        </is>
-      </c>
-      <c r="H36" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I36" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J36" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K36" s="26" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="G37" s="4" t="inlineStr">
-        <is>
           <t>Ajuste</t>
         </is>
       </c>
-      <c r="H37" s="5">
-        <f>IF(H35&lt;H36,"ACEPTA","RECHAZA")</f>
-        <v/>
-      </c>
-      <c r="I37" s="5">
-        <f>IF(I35&lt;I36,"ACEPTA","RECHAZA")</f>
-        <v/>
-      </c>
-      <c r="J37" s="5">
-        <f>IF(J35&lt;J36,"ACEPTA","RECHAZA")</f>
-        <v/>
-      </c>
-      <c r="K37" s="5">
-        <f>IF(K35&lt;K36,"ACEPTA","RECHAZA")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>F Log-Pearson III por Wilson-Hilferty (valor calculado). D critico para n = 26 y alfa = 0.05: 0.27 (tabla de Smirnov).</t>
+      <c r="H36" s="5">
+        <f>IF(H34&lt;H35,"ACEPTA","RECHAZA")</f>
+        <v/>
+      </c>
+      <c r="I36" s="5">
+        <f>IF(I34&lt;I35,"ACEPTA","RECHAZA")</f>
+        <v/>
+      </c>
+      <c r="J36" s="5">
+        <f>IF(J34&lt;J35,"ACEPTA","RECHAZA")</f>
+        <v/>
+      </c>
+      <c r="K36" s="5">
+        <f>IF(K34&lt;K35,"ACEPTA","RECHAZA")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>F Log-Pearson III por Wilson-Hilferty (valor calculado). D critico para n = 25 y alfa = 0.05: 0.27 (tabla de Smirnov).</t>
         </is>
       </c>
     </row>
@@ -5595,7 +5483,7 @@
         </is>
       </c>
       <c r="B41" s="30" t="n">
-        <v>1653.6294</v>
+        <v>1009.5117</v>
       </c>
     </row>
     <row r="42">
@@ -5605,7 +5493,7 @@
         </is>
       </c>
       <c r="B42" s="30" t="n">
-        <v>0.1315</v>
+        <v>0.1372</v>
       </c>
     </row>
     <row r="43">
@@ -5992,7 +5880,7 @@
         <v>0.3</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.1018</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="L9" s="21">
         <f>DATOS!$B$12*K9</f>
@@ -6019,7 +5907,7 @@
         <v/>
       </c>
       <c r="R9" s="25" t="n">
-        <v>0.0922</v>
+        <v>0.0667</v>
       </c>
       <c r="S9" s="26">
         <f>G9/(DATOS!$B$12*R9)</f>
@@ -6071,7 +5959,7 @@
         <v>0.46</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>0.1053</v>
+        <v>0.0756</v>
       </c>
       <c r="L10" s="21">
         <f>DATOS!$B$12*K10</f>
@@ -6098,7 +5986,7 @@
         <v/>
       </c>
       <c r="R10" s="25" t="n">
-        <v>0.0954</v>
+        <v>0.0687</v>
       </c>
       <c r="S10" s="26">
         <f>G10/(DATOS!$B$12*R10)</f>
@@ -6150,7 +6038,7 @@
         <v>0.3</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>0.0853</v>
+        <v>0.0617</v>
       </c>
       <c r="L11" s="21">
         <f>DATOS!$B$12*K11</f>
@@ -6177,7 +6065,7 @@
         <v/>
       </c>
       <c r="R11" s="25" t="n">
-        <v>0.0774</v>
+        <v>0.0562</v>
       </c>
       <c r="S11" s="26">
         <f>G11/(DATOS!$B$12*R11)</f>
@@ -6229,7 +6117,7 @@
         <v>0.46</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>0.0893</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="L12" s="21">
         <f>DATOS!$B$12*K12</f>
@@ -6256,7 +6144,7 @@
         <v/>
       </c>
       <c r="R12" s="25" t="n">
-        <v>0.081</v>
+        <v>0.0588</v>
       </c>
       <c r="S12" s="26">
         <f>G12/(DATOS!$B$12*R12)</f>
@@ -6308,7 +6196,7 @@
         <v>0.46</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0.1011</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="L13" s="21">
         <f>DATOS!$B$12*K13</f>
@@ -6335,7 +6223,7 @@
         <v/>
       </c>
       <c r="R13" s="25" t="n">
-        <v>0.0916</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="S13" s="26">
         <f>G13/(DATOS!$B$12*R13)</f>
@@ -6387,7 +6275,7 @@
         <v>0.52</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0838</v>
+        <v>0.0607</v>
       </c>
       <c r="L14" s="21">
         <f>DATOS!$B$12*K14</f>
@@ -6414,7 +6302,7 @@
         <v/>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0.0761</v>
+        <v>0.0552</v>
       </c>
       <c r="S14" s="26">
         <f>G14/(DATOS!$B$12*R14)</f>
@@ -6466,7 +6354,7 @@
         <v>0.77</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.3186</v>
+        <v>0.2193</v>
       </c>
       <c r="L15" s="21">
         <f>DATOS!$B$12*K15</f>
@@ -6493,7 +6381,7 @@
         <v/>
       </c>
       <c r="R15" s="25" t="n">
-        <v>0.2846</v>
+        <v>0.1969</v>
       </c>
       <c r="S15" s="26">
         <f>G15/(DATOS!$B$12*R15)</f>
@@ -6545,7 +6433,7 @@
         <v>0.83</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.3186</v>
+        <v>0.2193</v>
       </c>
       <c r="L16" s="21">
         <f>DATOS!$B$12*K16</f>
@@ -6572,7 +6460,7 @@
         <v/>
       </c>
       <c r="R16" s="25" t="n">
-        <v>0.2846</v>
+        <v>0.1969</v>
       </c>
       <c r="S16" s="26">
         <f>G16/(DATOS!$B$12*R16)</f>
@@ -6624,7 +6512,7 @@
         <v>0.83</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.4144</v>
+        <v>0.2816</v>
       </c>
       <c r="L17" s="21">
         <f>DATOS!$B$12*K17</f>
@@ -6651,7 +6539,7 @@
         <v/>
       </c>
       <c r="R17" s="25" t="n">
-        <v>0.3687</v>
+        <v>0.252</v>
       </c>
       <c r="S17" s="26">
         <f>G17/(DATOS!$B$12*R17)</f>
@@ -6703,7 +6591,7 @@
         <v>0.79</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.4144</v>
+        <v>0.2816</v>
       </c>
       <c r="L18" s="21">
         <f>DATOS!$B$12*K18</f>
@@ -6730,7 +6618,7 @@
         <v/>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0.3687</v>
+        <v>0.252</v>
       </c>
       <c r="S18" s="26">
         <f>G18/(DATOS!$B$12*R18)</f>
@@ -6782,7 +6670,7 @@
         <v>0.79</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.4694</v>
+        <v>0.3173</v>
       </c>
       <c r="L19" s="21">
         <f>DATOS!$B$12*K19</f>
@@ -6809,7 +6697,7 @@
         <v/>
       </c>
       <c r="R19" s="25" t="n">
-        <v>0.4169</v>
+        <v>0.2834</v>
       </c>
       <c r="S19" s="26">
         <f>G19/(DATOS!$B$12*R19)</f>
@@ -6861,7 +6749,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0796</v>
+        <v>0.0576</v>
       </c>
       <c r="L20" s="21">
         <f>DATOS!$B$12*K20</f>
@@ -6888,7 +6776,7 @@
         <v/>
       </c>
       <c r="R20" s="25" t="n">
-        <v>0.0722</v>
+        <v>0.0525</v>
       </c>
       <c r="S20" s="26">
         <f>G20/(DATOS!$B$12*R20)</f>
@@ -6940,7 +6828,7 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.1009</v>
+        <v>0.0727</v>
       </c>
       <c r="L21" s="21">
         <f>DATOS!$B$12*K21</f>
@@ -6967,7 +6855,7 @@
         <v/>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0.0914</v>
+        <v>0.066</v>
       </c>
       <c r="S21" s="26">
         <f>G21/(DATOS!$B$12*R21)</f>
@@ -7019,7 +6907,7 @@
         <v>0.43</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.1092</v>
+        <v>0.0786</v>
       </c>
       <c r="L22" s="21">
         <f>DATOS!$B$12*K22</f>
@@ -7046,7 +6934,7 @@
         <v/>
       </c>
       <c r="R22" s="25" t="n">
-        <v>0.0989</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="S22" s="26">
         <f>G22/(DATOS!$B$12*R22)</f>
@@ -7098,7 +6986,7 @@
         <v>0.47</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>0.1099</v>
+        <v>0.0788</v>
       </c>
       <c r="L23" s="21">
         <f>DATOS!$B$12*K23</f>
@@ -7125,7 +7013,7 @@
         <v/>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0.09950000000000001</v>
+        <v>0.0716</v>
       </c>
       <c r="S23" s="26">
         <f>G23/(DATOS!$B$12*R23)</f>
@@ -7177,7 +7065,7 @@
         <v>0.48</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.1374</v>
+        <v>0.098</v>
       </c>
       <c r="L24" s="21">
         <f>DATOS!$B$12*K24</f>
@@ -7204,7 +7092,7 @@
         <v/>
       </c>
       <c r="R24" s="25" t="n">
-        <v>0.1241</v>
+        <v>0.0888</v>
       </c>
       <c r="S24" s="26">
         <f>G24/(DATOS!$B$12*R24)</f>
@@ -7256,7 +7144,7 @@
         <v>0.49</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>0.1625</v>
+        <v>0.115</v>
       </c>
       <c r="L25" s="21">
         <f>DATOS!$B$12*K25</f>
@@ -7283,7 +7171,7 @@
         <v/>
       </c>
       <c r="R25" s="25" t="n">
-        <v>0.1465</v>
+        <v>0.1041</v>
       </c>
       <c r="S25" s="26">
         <f>G25/(DATOS!$B$12*R25)</f>
@@ -7335,7 +7223,7 @@
         <v>0.57</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.1723</v>
+        <v>0.1218</v>
       </c>
       <c r="L26" s="21">
         <f>DATOS!$B$12*K26</f>
@@ -7362,7 +7250,7 @@
         <v/>
       </c>
       <c r="R26" s="25" t="n">
-        <v>0.1552</v>
+        <v>0.1101</v>
       </c>
       <c r="S26" s="26">
         <f>G26/(DATOS!$B$12*R26)</f>
@@ -7414,7 +7302,7 @@
         <v>0.61</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.2073</v>
+        <v>0.1455</v>
       </c>
       <c r="L27" s="21">
         <f>DATOS!$B$12*K27</f>
@@ -7441,7 +7329,7 @@
         <v/>
       </c>
       <c r="R27" s="25" t="n">
-        <v>0.1862</v>
+        <v>0.1313</v>
       </c>
       <c r="S27" s="26">
         <f>G27/(DATOS!$B$12*R27)</f>
@@ -7493,7 +7381,7 @@
         <v>0.3</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>0.0815</v>
+        <v>0.059</v>
       </c>
       <c r="L28" s="21">
         <f>DATOS!$B$12*K28</f>
@@ -7520,7 +7408,7 @@
         <v/>
       </c>
       <c r="R28" s="25" t="n">
-        <v>0.074</v>
+        <v>0.0537</v>
       </c>
       <c r="S28" s="26">
         <f>G28/(DATOS!$B$12*R28)</f>
@@ -7572,7 +7460,7 @@
         <v>0.41</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>0.0881</v>
+        <v>0.0636</v>
       </c>
       <c r="L29" s="21">
         <f>DATOS!$B$12*K29</f>
@@ -7599,7 +7487,7 @@
         <v/>
       </c>
       <c r="R29" s="25" t="n">
-        <v>0.08</v>
+        <v>0.0579</v>
       </c>
       <c r="S29" s="26">
         <f>G29/(DATOS!$B$12*R29)</f>
@@ -7651,7 +7539,7 @@
         <v>0.44</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.1064</v>
+        <v>0.0766</v>
       </c>
       <c r="L30" s="21">
         <f>DATOS!$B$12*K30</f>
@@ -7678,7 +7566,7 @@
         <v/>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.0964</v>
+        <v>0.0696</v>
       </c>
       <c r="S30" s="26">
         <f>G30/(DATOS!$B$12*R30)</f>
@@ -7730,7 +7618,7 @@
         <v>0.53</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.1123</v>
+        <v>0.0805</v>
       </c>
       <c r="L31" s="21">
         <f>DATOS!$B$12*K31</f>
@@ -7757,7 +7645,7 @@
         <v/>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0.1016</v>
+        <v>0.0731</v>
       </c>
       <c r="S31" s="26">
         <f>G31/(DATOS!$B$12*R31)</f>
@@ -7809,7 +7697,7 @@
         <v>0.55</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0.1475</v>
+        <v>0.1049</v>
       </c>
       <c r="L32" s="21">
         <f>DATOS!$B$12*K32</f>
@@ -7836,7 +7724,7 @@
         <v/>
       </c>
       <c r="R32" s="25" t="n">
-        <v>0.1331</v>
+        <v>0.095</v>
       </c>
       <c r="S32" s="26">
         <f>G32/(DATOS!$B$12*R32)</f>
@@ -7888,7 +7776,7 @@
         <v>0.3</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>0.0523</v>
+        <v>0.0383</v>
       </c>
       <c r="L33" s="21">
         <f>DATOS!$B$12*K33</f>
@@ -7915,7 +7803,7 @@
         <v/>
       </c>
       <c r="R33" s="25" t="n">
-        <v>0.0476</v>
+        <v>0.0349</v>
       </c>
       <c r="S33" s="26">
         <f>G33/(DATOS!$B$12*R33)</f>
@@ -7967,7 +7855,7 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0.0356</v>
+        <v>0.0263</v>
       </c>
       <c r="L34" s="21">
         <f>DATOS!$B$12*K34</f>
@@ -7994,7 +7882,7 @@
         <v/>
       </c>
       <c r="R34" s="25" t="n">
-        <v>0.0325</v>
+        <v>0.0241</v>
       </c>
       <c r="S34" s="26">
         <f>G34/(DATOS!$B$12*R34)</f>
@@ -8046,7 +7934,7 @@
         <v>0.5</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>0.1662</v>
+        <v>0.1176</v>
       </c>
       <c r="L35" s="21">
         <f>DATOS!$B$12*K35</f>
@@ -8073,7 +7961,7 @@
         <v/>
       </c>
       <c r="R35" s="25" t="n">
-        <v>0.1498</v>
+        <v>0.1064</v>
       </c>
       <c r="S35" s="26">
         <f>G35/(DATOS!$B$12*R35)</f>
@@ -8125,7 +8013,7 @@
         <v>0.59</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0.218</v>
+        <v>0.1526</v>
       </c>
       <c r="L36" s="21">
         <f>DATOS!$B$12*K36</f>
@@ -8152,7 +8040,7 @@
         <v/>
       </c>
       <c r="R36" s="25" t="n">
-        <v>0.1958</v>
+        <v>0.1376</v>
       </c>
       <c r="S36" s="26">
         <f>G36/(DATOS!$B$12*R36)</f>
@@ -8204,7 +8092,7 @@
         <v>0.61</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>0.218</v>
+        <v>0.1526</v>
       </c>
       <c r="L37" s="21">
         <f>DATOS!$B$12*K37</f>
@@ -8231,7 +8119,7 @@
         <v/>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.1958</v>
+        <v>0.1376</v>
       </c>
       <c r="S37" s="26">
         <f>G37/(DATOS!$B$12*R37)</f>
@@ -8283,7 +8171,7 @@
         <v>0.62</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0.2593</v>
+        <v>0.1801</v>
       </c>
       <c r="L38" s="21">
         <f>DATOS!$B$12*K38</f>
@@ -8310,7 +8198,7 @@
         <v/>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0.2322</v>
+        <v>0.1621</v>
       </c>
       <c r="S38" s="26">
         <f>G38/(DATOS!$B$12*R38)</f>
@@ -8362,7 +8250,7 @@
         <v>0.73</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>0.2594</v>
+        <v>0.1801</v>
       </c>
       <c r="L39" s="21">
         <f>DATOS!$B$12*K39</f>
@@ -8389,7 +8277,7 @@
         <v/>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0.2324</v>
+        <v>0.1621</v>
       </c>
       <c r="S39" s="26">
         <f>G39/(DATOS!$B$12*R39)</f>
@@ -8441,7 +8329,7 @@
         <v>0.73</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.3412</v>
+        <v>0.2341</v>
       </c>
       <c r="L40" s="21">
         <f>DATOS!$B$12*K40</f>
@@ -8468,7 +8356,7 @@
         <v/>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0.3045</v>
+        <v>0.21</v>
       </c>
       <c r="S40" s="26">
         <f>G40/(DATOS!$B$12*R40)</f>
@@ -8520,7 +8408,7 @@
         <v>0.79</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.3949</v>
+        <v>0.2691</v>
       </c>
       <c r="L41" s="21">
         <f>DATOS!$B$12*K41</f>
@@ -8547,7 +8435,7 @@
         <v/>
       </c>
       <c r="R41" s="25" t="n">
-        <v>0.3516</v>
+        <v>0.2409</v>
       </c>
       <c r="S41" s="26">
         <f>G41/(DATOS!$B$12*R41)</f>
@@ -8599,7 +8487,7 @@
         <v>0.7</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>0.3951</v>
+        <v>0.2691</v>
       </c>
       <c r="L42" s="21">
         <f>DATOS!$B$12*K42</f>
@@ -8626,7 +8514,7 @@
         <v/>
       </c>
       <c r="R42" s="25" t="n">
-        <v>0.3518</v>
+        <v>0.2409</v>
       </c>
       <c r="S42" s="26">
         <f>G42/(DATOS!$B$12*R42)</f>
@@ -8678,7 +8566,7 @@
         <v>0.7</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>0.3964</v>
+        <v>0.27</v>
       </c>
       <c r="L43" s="21">
         <f>DATOS!$B$12*K43</f>
@@ -8705,7 +8593,7 @@
         <v/>
       </c>
       <c r="R43" s="25" t="n">
-        <v>0.353</v>
+        <v>0.2417</v>
       </c>
       <c r="S43" s="26">
         <f>G43/(DATOS!$B$12*R43)</f>
@@ -8757,7 +8645,7 @@
         <v>0.74</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>0.3968</v>
+        <v>0.2703</v>
       </c>
       <c r="L44" s="21">
         <f>DATOS!$B$12*K44</f>
@@ -8784,7 +8672,7 @@
         <v/>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0.3533</v>
+        <v>0.242</v>
       </c>
       <c r="S44" s="26">
         <f>G44/(DATOS!$B$12*R44)</f>
@@ -8836,7 +8724,7 @@
         <v>0.74</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>0.3991</v>
+        <v>0.2717</v>
       </c>
       <c r="L45" s="21">
         <f>DATOS!$B$12*K45</f>
@@ -8863,7 +8751,7 @@
         <v/>
       </c>
       <c r="R45" s="25" t="n">
-        <v>0.3553</v>
+        <v>0.2432</v>
       </c>
       <c r="S45" s="26">
         <f>G45/(DATOS!$B$12*R45)</f>
@@ -8915,7 +8803,7 @@
         <v>0.77</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>0.3992</v>
+        <v>0.2719</v>
       </c>
       <c r="L46" s="21">
         <f>DATOS!$B$12*K46</f>
@@ -8942,7 +8830,7 @@
         <v/>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0.3554</v>
+        <v>0.2434</v>
       </c>
       <c r="S46" s="26">
         <f>G46/(DATOS!$B$12*R46)</f>
@@ -8994,7 +8882,7 @@
         <v>0.77</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0.4042</v>
+        <v>0.275</v>
       </c>
       <c r="L47" s="21">
         <f>DATOS!$B$12*K47</f>
@@ -9021,7 +8909,7 @@
         <v/>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0.3598</v>
+        <v>0.2461</v>
       </c>
       <c r="S47" s="26">
         <f>G47/(DATOS!$B$12*R47)</f>
@@ -9073,7 +8961,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>0.4057</v>
+        <v>0.2761</v>
       </c>
       <c r="L48" s="21">
         <f>DATOS!$B$12*K48</f>
@@ -9100,7 +8988,7 @@
         <v/>
       </c>
       <c r="R48" s="25" t="n">
-        <v>0.3611</v>
+        <v>0.2471</v>
       </c>
       <c r="S48" s="26">
         <f>G48/(DATOS!$B$12*R48)</f>
@@ -9152,7 +9040,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.4057</v>
+        <v>0.2761</v>
       </c>
       <c r="L49" s="21">
         <f>DATOS!$B$12*K49</f>
@@ -9179,7 +9067,7 @@
         <v/>
       </c>
       <c r="R49" s="25" t="n">
-        <v>0.3611</v>
+        <v>0.2471</v>
       </c>
       <c r="S49" s="26">
         <f>G49/(DATOS!$B$12*R49)</f>
@@ -9231,7 +9119,7 @@
         <v>0.3</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>0.0327</v>
+        <v>0.024</v>
       </c>
       <c r="L50" s="21">
         <f>DATOS!$B$12*K50</f>
@@ -9258,7 +9146,7 @@
         <v/>
       </c>
       <c r="R50" s="25" t="n">
-        <v>0.0299</v>
+        <v>0.022</v>
       </c>
       <c r="S50" s="26">
         <f>G50/(DATOS!$B$12*R50)</f>
@@ -9310,7 +9198,7 @@
         <v>0.32</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.1046</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="L51" s="21">
         <f>DATOS!$B$12*K51</f>
@@ -9337,7 +9225,7 @@
         <v/>
       </c>
       <c r="R51" s="25" t="n">
-        <v>0.0948</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="S51" s="26">
         <f>G51/(DATOS!$B$12*R51)</f>
@@ -9389,7 +9277,7 @@
         <v>0.3</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>0.0891</v>
+        <v>0.0644</v>
       </c>
       <c r="L52" s="21">
         <f>DATOS!$B$12*K52</f>
@@ -9416,7 +9304,7 @@
         <v/>
       </c>
       <c r="R52" s="25" t="n">
-        <v>0.0808</v>
+        <v>0.0586</v>
       </c>
       <c r="S52" s="26">
         <f>G52/(DATOS!$B$12*R52)</f>
@@ -9468,7 +9356,7 @@
         <v>0.3</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.0548</v>
       </c>
       <c r="L53" s="21">
         <f>DATOS!$B$12*K53</f>
@@ -9495,7 +9383,7 @@
         <v/>
       </c>
       <c r="R53" s="25" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.0499</v>
       </c>
       <c r="S53" s="26">
         <f>G53/(DATOS!$B$12*R53)</f>
@@ -9547,7 +9435,7 @@
         <v>0.39</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>0.0825</v>
+        <v>0.0598</v>
       </c>
       <c r="L54" s="21">
         <f>DATOS!$B$12*K54</f>
@@ -9574,7 +9462,7 @@
         <v/>
       </c>
       <c r="R54" s="25" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0545</v>
       </c>
       <c r="S54" s="26">
         <f>G54/(DATOS!$B$12*R54)</f>
@@ -9626,7 +9514,7 @@
         <v>0.42</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>0.0863</v>
+        <v>0.0625</v>
       </c>
       <c r="L55" s="21">
         <f>DATOS!$B$12*K55</f>
@@ -9653,7 +9541,7 @@
         <v/>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0569</v>
       </c>
       <c r="S55" s="26">
         <f>G55/(DATOS!$B$12*R55)</f>
@@ -9705,7 +9593,7 @@
         <v>0.42</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>0.1112</v>
+        <v>0.0798</v>
       </c>
       <c r="L56" s="21">
         <f>DATOS!$B$12*K56</f>
@@ -9732,7 +9620,7 @@
         <v/>
       </c>
       <c r="R56" s="25" t="n">
-        <v>0.1006</v>
+        <v>0.0725</v>
       </c>
       <c r="S56" s="26">
         <f>G56/(DATOS!$B$12*R56)</f>
@@ -9784,7 +9672,7 @@
         <v>0.48</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>0.1112</v>
+        <v>0.0798</v>
       </c>
       <c r="L57" s="21">
         <f>DATOS!$B$12*K57</f>
@@ -9811,7 +9699,7 @@
         <v/>
       </c>
       <c r="R57" s="25" t="n">
-        <v>0.1006</v>
+        <v>0.0725</v>
       </c>
       <c r="S57" s="26">
         <f>G57/(DATOS!$B$12*R57)</f>
@@ -9863,7 +9751,7 @@
         <v>0.2</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>0.0987</v>
+        <v>0.0711</v>
       </c>
       <c r="L58" s="21">
         <f>DATOS!$B$12*K58</f>
@@ -9890,7 +9778,7 @@
         <v/>
       </c>
       <c r="R58" s="25" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="S58" s="26">
         <f>G58/(DATOS!$B$12*R58)</f>
@@ -9942,7 +9830,7 @@
         <v>0.3</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>0.0696</v>
+        <v>0.0505</v>
       </c>
       <c r="L59" s="21">
         <f>DATOS!$B$12*K59</f>
@@ -9969,7 +9857,7 @@
         <v/>
       </c>
       <c r="R59" s="25" t="n">
-        <v>0.0633</v>
+        <v>0.046</v>
       </c>
       <c r="S59" s="26">
         <f>G59/(DATOS!$B$12*R59)</f>
@@ -10021,7 +9909,7 @@
         <v>0.38</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.0526</v>
       </c>
       <c r="L60" s="21">
         <f>DATOS!$B$12*K60</f>
@@ -10048,7 +9936,7 @@
         <v/>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0.0658</v>
+        <v>0.0479</v>
       </c>
       <c r="S60" s="26">
         <f>G60/(DATOS!$B$12*R60)</f>
@@ -10100,7 +9988,7 @@
         <v>0.38</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0.1131</v>
+        <v>0.0813</v>
       </c>
       <c r="L61" s="21">
         <f>DATOS!$B$12*K61</f>
@@ -10127,7 +10015,7 @@
         <v/>
       </c>
       <c r="R61" s="25" t="n">
-        <v>0.1024</v>
+        <v>0.0738</v>
       </c>
       <c r="S61" s="26">
         <f>G61/(DATOS!$B$12*R61)</f>
@@ -10179,7 +10067,7 @@
         <v>0.49</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>0.1133</v>
+        <v>0.0813</v>
       </c>
       <c r="L62" s="21">
         <f>DATOS!$B$12*K62</f>
@@ -10206,7 +10094,7 @@
         <v/>
       </c>
       <c r="R62" s="25" t="n">
-        <v>0.1026</v>
+        <v>0.0738</v>
       </c>
       <c r="S62" s="26">
         <f>G62/(DATOS!$B$12*R62)</f>
@@ -10258,7 +10146,7 @@
         <v>0.5</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>0.1526</v>
+        <v>0.1084</v>
       </c>
       <c r="L63" s="21">
         <f>DATOS!$B$12*K63</f>
@@ -10285,7 +10173,7 @@
         <v/>
       </c>
       <c r="R63" s="25" t="n">
-        <v>0.1376</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="S63" s="26">
         <f>G63/(DATOS!$B$12*R63)</f>
@@ -10337,7 +10225,7 @@
         <v>0.52</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>0.1999</v>
+        <v>0.1405</v>
       </c>
       <c r="L64" s="21">
         <f>DATOS!$B$12*K64</f>
@@ -10364,7 +10252,7 @@
         <v/>
       </c>
       <c r="R64" s="25" t="n">
-        <v>0.1797</v>
+        <v>0.1268</v>
       </c>
       <c r="S64" s="26">
         <f>G64/(DATOS!$B$12*R64)</f>
@@ -10416,7 +10304,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>0.3519</v>
+        <v>0.241</v>
       </c>
       <c r="L65" s="21">
         <f>DATOS!$B$12*K65</f>
@@ -10443,7 +10331,7 @@
         <v/>
       </c>
       <c r="R65" s="25" t="n">
-        <v>0.3138</v>
+        <v>0.2161</v>
       </c>
       <c r="S65" s="26">
         <f>G65/(DATOS!$B$12*R65)</f>
@@ -10495,7 +10383,7 @@
         <v>0.62</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>0.4572</v>
+        <v>0.3094</v>
       </c>
       <c r="L66" s="21">
         <f>DATOS!$B$12*K66</f>
@@ -10522,7 +10410,7 @@
         <v/>
       </c>
       <c r="R66" s="25" t="n">
-        <v>0.4063</v>
+        <v>0.2765</v>
       </c>
       <c r="S66" s="26">
         <f>G66/(DATOS!$B$12*R66)</f>
@@ -10574,7 +10462,7 @@
         <v>0.57</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>0.4833</v>
+        <v>0.3261</v>
       </c>
       <c r="L67" s="21">
         <f>DATOS!$B$12*K67</f>
@@ -10601,7 +10489,7 @@
         <v/>
       </c>
       <c r="R67" s="25" t="n">
-        <v>0.4291</v>
+        <v>0.2912</v>
       </c>
       <c r="S67" s="26">
         <f>G67/(DATOS!$B$12*R67)</f>
@@ -10653,7 +10541,7 @@
         <v>0.63</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.4861</v>
+        <v>0.328</v>
       </c>
       <c r="L68" s="21">
         <f>DATOS!$B$12*K68</f>
@@ -10680,7 +10568,7 @@
         <v/>
       </c>
       <c r="R68" s="25" t="n">
-        <v>0.4315</v>
+        <v>0.2928</v>
       </c>
       <c r="S68" s="26">
         <f>G68/(DATOS!$B$12*R68)</f>
@@ -10732,7 +10620,7 @@
         <v>0.64</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>0.4861</v>
+        <v>0.328</v>
       </c>
       <c r="L69" s="21">
         <f>DATOS!$B$12*K69</f>
@@ -10759,7 +10647,7 @@
         <v/>
       </c>
       <c r="R69" s="25" t="n">
-        <v>0.4315</v>
+        <v>0.2928</v>
       </c>
       <c r="S69" s="26">
         <f>G69/(DATOS!$B$12*R69)</f>
@@ -10811,7 +10699,7 @@
         <v>0.64</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>0.5758</v>
+        <v>0.3854</v>
       </c>
       <c r="L70" s="21">
         <f>DATOS!$B$12*K70</f>
@@ -10838,7 +10726,7 @@
         <v/>
       </c>
       <c r="R70" s="25" t="n">
-        <v>0.51</v>
+        <v>0.3433</v>
       </c>
       <c r="S70" s="26">
         <f>G70/(DATOS!$B$12*R70)</f>
@@ -10890,7 +10778,7 @@
         <v>0.3</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0568</v>
       </c>
       <c r="L71" s="21">
         <f>DATOS!$B$12*K71</f>
@@ -10917,7 +10805,7 @@
         <v/>
       </c>
       <c r="R71" s="25" t="n">
-        <v>0.0712</v>
+        <v>0.0517</v>
       </c>
       <c r="S71" s="26">
         <f>G71/(DATOS!$B$12*R71)</f>
@@ -10969,7 +10857,7 @@
         <v>0.3</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>0.0886</v>
+        <v>0.0641</v>
       </c>
       <c r="L72" s="21">
         <f>DATOS!$B$12*K72</f>
@@ -10996,7 +10884,7 @@
         <v/>
       </c>
       <c r="R72" s="25" t="n">
-        <v>0.0804</v>
+        <v>0.0583</v>
       </c>
       <c r="S72" s="26">
         <f>G72/(DATOS!$B$12*R72)</f>
@@ -11048,7 +10936,7 @@
         <v>0.38</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>0.0921</v>
+        <v>0.0665</v>
       </c>
       <c r="L73" s="21">
         <f>DATOS!$B$12*K73</f>
@@ -11075,7 +10963,7 @@
         <v/>
       </c>
       <c r="R73" s="25" t="n">
-        <v>0.0835</v>
+        <v>0.0605</v>
       </c>
       <c r="S73" s="26">
         <f>G73/(DATOS!$B$12*R73)</f>
@@ -11127,7 +11015,7 @@
         <v>0.35</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>0.1475</v>
+        <v>0.1049</v>
       </c>
       <c r="L74" s="21">
         <f>DATOS!$B$12*K74</f>
@@ -11154,7 +11042,7 @@
         <v/>
       </c>
       <c r="R74" s="25" t="n">
-        <v>0.1331</v>
+        <v>0.095</v>
       </c>
       <c r="S74" s="26">
         <f>G74/(DATOS!$B$12*R74)</f>
@@ -11206,7 +11094,7 @@
         <v>0.35</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>0.1479</v>
+        <v>0.1051</v>
       </c>
       <c r="L75" s="21">
         <f>DATOS!$B$12*K75</f>
@@ -11233,7 +11121,7 @@
         <v/>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.1334</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="S75" s="26">
         <f>G75/(DATOS!$B$12*R75)</f>
@@ -11285,7 +11173,7 @@
         <v>0.35</v>
       </c>
       <c r="K76" s="25" t="n">
-        <v>0.15</v>
+        <v>0.1066</v>
       </c>
       <c r="L76" s="21">
         <f>DATOS!$B$12*K76</f>
@@ -11312,7 +11200,7 @@
         <v/>
       </c>
       <c r="R76" s="25" t="n">
-        <v>0.1353</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="S76" s="26">
         <f>G76/(DATOS!$B$12*R76)</f>
@@ -11364,7 +11252,7 @@
         <v>0.35</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.1957</v>
+        <v>0.1376</v>
       </c>
       <c r="L77" s="21">
         <f>DATOS!$B$12*K77</f>
@@ -11391,7 +11279,7 @@
         <v/>
       </c>
       <c r="R77" s="25" t="n">
-        <v>0.1759</v>
+        <v>0.1243</v>
       </c>
       <c r="S77" s="26">
         <f>G77/(DATOS!$B$12*R77)</f>
@@ -11443,7 +11331,7 @@
         <v>0.45</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0.2005</v>
+        <v>0.1409</v>
       </c>
       <c r="L78" s="21">
         <f>DATOS!$B$12*K78</f>
@@ -11470,7 +11358,7 @@
         <v/>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0.1802</v>
+        <v>0.1272</v>
       </c>
       <c r="S78" s="26">
         <f>G78/(DATOS!$B$12*R78)</f>
@@ -11522,7 +11410,7 @@
         <v>0.3</v>
       </c>
       <c r="K79" s="25" t="n">
-        <v>0.0747</v>
+        <v>0.0543</v>
       </c>
       <c r="L79" s="21">
         <f>DATOS!$B$12*K79</f>
@@ -11549,7 +11437,7 @@
         <v/>
       </c>
       <c r="R79" s="25" t="n">
-        <v>0.0678</v>
+        <v>0.0494</v>
       </c>
       <c r="S79" s="26">
         <f>G79/(DATOS!$B$12*R79)</f>
@@ -11601,7 +11489,7 @@
         <v>0.36</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>0.0751</v>
+        <v>0.0546</v>
       </c>
       <c r="L80" s="21">
         <f>DATOS!$B$12*K80</f>
@@ -11628,7 +11516,7 @@
         <v/>
       </c>
       <c r="R80" s="25" t="n">
-        <v>0.0683</v>
+        <v>0.0497</v>
       </c>
       <c r="S80" s="26">
         <f>G80/(DATOS!$B$12*R80)</f>
@@ -11680,7 +11568,7 @@
         <v>0.35</v>
       </c>
       <c r="K81" s="25" t="n">
-        <v>0.1439</v>
+        <v>0.1023</v>
       </c>
       <c r="L81" s="21">
         <f>DATOS!$B$12*K81</f>
@@ -11707,7 +11595,7 @@
         <v/>
       </c>
       <c r="R81" s="25" t="n">
-        <v>0.1299</v>
+        <v>0.0927</v>
       </c>
       <c r="S81" s="26">
         <f>G81/(DATOS!$B$12*R81)</f>
@@ -11759,7 +11647,7 @@
         <v>0.35</v>
       </c>
       <c r="K82" s="25" t="n">
-        <v>0.1583</v>
+        <v>0.1123</v>
       </c>
       <c r="L82" s="21">
         <f>DATOS!$B$12*K82</f>
@@ -11786,7 +11674,7 @@
         <v/>
       </c>
       <c r="R82" s="25" t="n">
-        <v>0.1427</v>
+        <v>0.1016</v>
       </c>
       <c r="S82" s="26">
         <f>G82/(DATOS!$B$12*R82)</f>
@@ -11838,7 +11726,7 @@
         <v>0.3</v>
       </c>
       <c r="K83" s="25" t="n">
-        <v>0.1129</v>
+        <v>0.081</v>
       </c>
       <c r="L83" s="21">
         <f>DATOS!$B$12*K83</f>
@@ -11865,7 +11753,7 @@
         <v/>
       </c>
       <c r="R83" s="25" t="n">
-        <v>0.1022</v>
+        <v>0.0736</v>
       </c>
       <c r="S83" s="26">
         <f>G83/(DATOS!$B$12*R83)</f>
@@ -11917,7 +11805,7 @@
         <v>0.45</v>
       </c>
       <c r="K84" s="25" t="n">
-        <v>0.1186</v>
+        <v>0.0851</v>
       </c>
       <c r="L84" s="21">
         <f>DATOS!$B$12*K84</f>
@@ -11944,7 +11832,7 @@
         <v/>
       </c>
       <c r="R84" s="25" t="n">
-        <v>0.1073</v>
+        <v>0.0772</v>
       </c>
       <c r="S84" s="26">
         <f>G84/(DATOS!$B$12*R84)</f>
@@ -11996,7 +11884,7 @@
         <v>0.46</v>
       </c>
       <c r="K85" s="25" t="n">
-        <v>0.1212</v>
+        <v>0.0867</v>
       </c>
       <c r="L85" s="21">
         <f>DATOS!$B$12*K85</f>
@@ -12023,7 +11911,7 @@
         <v/>
       </c>
       <c r="R85" s="25" t="n">
-        <v>0.1096</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="S85" s="26">
         <f>G85/(DATOS!$B$12*R85)</f>
@@ -12075,7 +11963,7 @@
         <v>0.47</v>
       </c>
       <c r="K86" s="25" t="n">
-        <v>0.1214</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L86" s="21">
         <f>DATOS!$B$12*K86</f>
@@ -12102,7 +11990,7 @@
         <v/>
       </c>
       <c r="R86" s="25" t="n">
-        <v>0.1098</v>
+        <v>0.0789</v>
       </c>
       <c r="S86" s="26">
         <f>G86/(DATOS!$B$12*R86)</f>
@@ -12154,7 +12042,7 @@
         <v>0.4</v>
       </c>
       <c r="K87" s="25" t="n">
-        <v>0.1504</v>
+        <v>0.1068</v>
       </c>
       <c r="L87" s="21">
         <f>DATOS!$B$12*K87</f>
@@ -12181,7 +12069,7 @@
         <v/>
       </c>
       <c r="R87" s="25" t="n">
-        <v>0.1357</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="S87" s="26">
         <f>G87/(DATOS!$B$12*R87)</f>
@@ -12233,7 +12121,7 @@
         <v>0.4</v>
       </c>
       <c r="K88" s="25" t="n">
-        <v>0.1504</v>
+        <v>0.1068</v>
       </c>
       <c r="L88" s="21">
         <f>DATOS!$B$12*K88</f>
@@ -12260,7 +12148,7 @@
         <v/>
       </c>
       <c r="R88" s="25" t="n">
-        <v>0.1357</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="S88" s="26">
         <f>G88/(DATOS!$B$12*R88)</f>
@@ -12312,7 +12200,7 @@
         <v>0.2</v>
       </c>
       <c r="K89" s="25" t="n">
-        <v>0.0973</v>
+        <v>0.0702</v>
       </c>
       <c r="L89" s="21">
         <f>DATOS!$B$12*K89</f>
@@ -12339,7 +12227,7 @@
         <v/>
       </c>
       <c r="R89" s="25" t="n">
-        <v>0.0882</v>
+        <v>0.0638</v>
       </c>
       <c r="S89" s="26">
         <f>G89/(DATOS!$B$12*R89)</f>
@@ -12391,7 +12279,7 @@
         <v>0.5</v>
       </c>
       <c r="K90" s="25" t="n">
-        <v>0.098</v>
+        <v>0.0706</v>
       </c>
       <c r="L90" s="21">
         <f>DATOS!$B$12*K90</f>
@@ -12418,7 +12306,7 @@
         <v/>
       </c>
       <c r="R90" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="S90" s="26">
         <f>G90/(DATOS!$B$12*R90)</f>
@@ -12470,7 +12358,7 @@
         <v>0.5</v>
       </c>
       <c r="K91" s="25" t="n">
-        <v>0.1508</v>
+        <v>0.1071</v>
       </c>
       <c r="L91" s="21">
         <f>DATOS!$B$12*K91</f>
@@ -12497,7 +12385,7 @@
         <v/>
       </c>
       <c r="R91" s="25" t="n">
-        <v>0.136</v>
+        <v>0.0969</v>
       </c>
       <c r="S91" s="26">
         <f>G91/(DATOS!$B$12*R91)</f>
@@ -12549,7 +12437,7 @@
         <v>0.4</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>0.1514</v>
+        <v>0.1075</v>
       </c>
       <c r="L92" s="21">
         <f>DATOS!$B$12*K92</f>
@@ -12576,7 +12464,7 @@
         <v/>
       </c>
       <c r="R92" s="25" t="n">
-        <v>0.1366</v>
+        <v>0.0973</v>
       </c>
       <c r="S92" s="26">
         <f>G92/(DATOS!$B$12*R92)</f>
@@ -12628,7 +12516,7 @@
         <v>0.3</v>
       </c>
       <c r="K93" s="25" t="n">
-        <v>0.0438</v>
+        <v>0.0323</v>
       </c>
       <c r="L93" s="21">
         <f>DATOS!$B$12*K93</f>
@@ -12655,7 +12543,7 @@
         <v/>
       </c>
       <c r="R93" s="25" t="n">
-        <v>0.04</v>
+        <v>0.0295</v>
       </c>
       <c r="S93" s="26">
         <f>G93/(DATOS!$B$12*R93)</f>
@@ -12707,7 +12595,7 @@
         <v>0.36</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0.0441</v>
+        <v>0.0323</v>
       </c>
       <c r="L94" s="21">
         <f>DATOS!$B$12*K94</f>
@@ -12734,7 +12622,7 @@
         <v/>
       </c>
       <c r="R94" s="25" t="n">
-        <v>0.0402</v>
+        <v>0.0295</v>
       </c>
       <c r="S94" s="26">
         <f>G94/(DATOS!$B$12*R94)</f>
@@ -12786,7 +12674,7 @@
         <v>0.36</v>
       </c>
       <c r="K95" s="25" t="n">
-        <v>0.0706</v>
+        <v>0.0514</v>
       </c>
       <c r="L95" s="21">
         <f>DATOS!$B$12*K95</f>
@@ -12813,7 +12701,7 @@
         <v/>
       </c>
       <c r="R95" s="25" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0468</v>
       </c>
       <c r="S95" s="26">
         <f>G95/(DATOS!$B$12*R95)</f>
@@ -12865,7 +12753,7 @@
         <v>0.48</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0.0706</v>
+        <v>0.0514</v>
       </c>
       <c r="L96" s="21">
         <f>DATOS!$B$12*K96</f>
@@ -12892,7 +12780,7 @@
         <v/>
       </c>
       <c r="R96" s="25" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0468</v>
       </c>
       <c r="S96" s="26">
         <f>G96/(DATOS!$B$12*R96)</f>
@@ -12944,7 +12832,7 @@
         <v>0.49</v>
       </c>
       <c r="K97" s="25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="L97" s="21">
         <f>DATOS!$B$12*K97</f>
@@ -12971,7 +12859,7 @@
         <v/>
       </c>
       <c r="R97" s="25" t="n">
-        <v>0.0789</v>
+        <v>0.0571</v>
       </c>
       <c r="S97" s="26">
         <f>G97/(DATOS!$B$12*R97)</f>
@@ -13023,7 +12911,7 @@
         <v>0.3</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>0.0356</v>
+        <v>0.0261</v>
       </c>
       <c r="L98" s="21">
         <f>DATOS!$B$12*K98</f>
@@ -13050,7 +12938,7 @@
         <v/>
       </c>
       <c r="R98" s="25" t="n">
-        <v>0.0325</v>
+        <v>0.0239</v>
       </c>
       <c r="S98" s="26">
         <f>G98/(DATOS!$B$12*R98)</f>
@@ -13102,7 +12990,7 @@
         <v>0.37</v>
       </c>
       <c r="K99" s="25" t="n">
-        <v>0.0356</v>
+        <v>0.0261</v>
       </c>
       <c r="L99" s="21">
         <f>DATOS!$B$12*K99</f>
@@ -13129,7 +13017,7 @@
         <v/>
       </c>
       <c r="R99" s="25" t="n">
-        <v>0.0325</v>
+        <v>0.0239</v>
       </c>
       <c r="S99" s="26">
         <f>G99/(DATOS!$B$12*R99)</f>

--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -107,7 +107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -147,6 +147,7 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -640,7 +641,7 @@
         </is>
       </c>
       <c r="B16" s="10">
-        <f>SUPERFICIES!C12</f>
+        <f>SUPERFICIES!C13</f>
         <v/>
       </c>
     </row>
@@ -651,7 +652,7 @@
         </is>
       </c>
       <c r="B17" s="11">
-        <f>SUPERFICIES!B12</f>
+        <f>SUPERFICIES!B13</f>
         <v/>
       </c>
     </row>
@@ -723,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -972,7 +973,7 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Coeficiente de escorrentia - techos</t>
+          <t>Coeficiente de escorrentia - techos y coberturas</t>
         </is>
       </c>
       <c r="B18" s="16" t="n">
@@ -980,14 +981,14 @@
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>T = 25 anos (proyectos de Morales)</t>
+          <t>CE.040 Anexo I, Tabla 1.a: concreto / techo, T = 25 anos</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Coeficiente de escorrentia - veredas, pisos y patio</t>
+          <t>Coeficiente de escorrentia - areas libres de concreto (veredas y patios)</t>
         </is>
       </c>
       <c r="B19" s="16" t="n">
@@ -995,35 +996,50 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>T = 25 anos</t>
+          <t>CE.040 Anexo I, Tabla 1.a: concreto, T = 25 anos</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Coeficiente de escorrentia - areas verdes y terreno</t>
+          <t>Coeficiente de escorrentia - patio de maniobra y estacionamiento</t>
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>0.4</v>
+        <v>0.88</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>T = 25 anos (pendiente moderada)</t>
+          <t>CE.040 Anexo I, Tabla 1.a: concreto, T = 25 anos</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>Coeficiente de escorrentia - areas verdes y terreno</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>CE.040 Anexo I, Tabla 1.a: zona verde, valor mayor de la tabla (rellenos compactados), T = 25 anos</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>Factor de seguridad de los caudales FS</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n">
+      <c r="B22" s="16" t="n">
         <v>1.15</v>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Mismo criterio de los proyectos de Morales (Q = C I A FS)</t>
         </is>
@@ -5529,7 +5545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -5590,11 +5606,11 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Techos y coberturas (TR4 / panel termoacustico)</t>
+          <t>Techos: edificaciones, corredores, patio civico techado y losa multiusos techada</t>
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>2158</v>
+        <v>5548</v>
       </c>
       <c r="C9" s="26">
         <f>DATOS!$B$18</f>
@@ -5605,18 +5621,18 @@
         <v/>
       </c>
       <c r="E9" s="33">
-        <f>B9/$B$12</f>
+        <f>B9/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Veredas, pisos, losa y patio de maniobra (concreto)</t>
+          <t>Areas libres de concreto: veredas, patios, atrio y circulaciones</t>
         </is>
       </c>
       <c r="B10" s="31" t="n">
-        <v>1177</v>
+        <v>901</v>
       </c>
       <c r="C10" s="26">
         <f>DATOS!$B$19</f>
@@ -5627,18 +5643,18 @@
         <v/>
       </c>
       <c r="E10" s="33">
-        <f>B10/$B$12</f>
+        <f>B10/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Areas verdes y terreno natural (relleno nivelado)</t>
+          <t>Patio de maniobra y estacionamiento (pavimento de concreto)</t>
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>6058</v>
+        <v>623</v>
       </c>
       <c r="C11" s="26">
         <f>DATOS!$B$20</f>
@@ -5649,33 +5665,342 @@
         <v/>
       </c>
       <c r="E11" s="33">
-        <f>B11/$B$12</f>
+        <f>B11/$B$13</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Areas verdes y terreno natural (relleno nivelado)</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="n">
+        <v>2321</v>
+      </c>
+      <c r="C12" s="26">
+        <f>DATOS!$B$21</f>
+        <v/>
+      </c>
+      <c r="D12" s="32">
+        <f>B12*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="33">
+        <f>B12/$B$13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>TOTAL / C PONDERADO</t>
         </is>
       </c>
-      <c r="B12" s="34">
-        <f>SUM(B9:B11)</f>
-        <v/>
-      </c>
-      <c r="C12" s="35">
-        <f>D12/B12</f>
-        <v/>
-      </c>
-      <c r="D12" s="36">
-        <f>SUM(D9:D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>Areas medidas en la planta del proyecto en celdas de 1 m2 dentro del cerco: techos = proyeccion de coberturas; pavimentos = veredas, circulaciones, pisos y patio de maniobra; el resto, area verde o terreno nivelado.</t>
+      <c r="B13" s="34">
+        <f>SUM(B9:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>D13/B13</f>
+        <v/>
+      </c>
+      <c r="D13" s="36">
+        <f>SUM(D9:D12)</f>
+        <v/>
+      </c>
+      <c r="E13" s="37">
+        <f>SUM(E9:E12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="inlineStr">
+        <is>
+          <t>DETALLE POR ZONA (NOMBRES DEL CUADRO DE AREAS DE ARQUITECTURA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>ZONA</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>AREA (m2)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>C x A</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Coberturas de las edificaciones y corredores techados</t>
+        </is>
+      </c>
+      <c r="B17" s="32" t="n">
+        <v>4129.6</v>
+      </c>
+      <c r="C17" s="26">
+        <f>DATOS!$B$18</f>
+        <v/>
+      </c>
+      <c r="D17" s="32">
+        <f>B17*C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>TECHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Patio civico techado</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="n">
+        <v>517.7</v>
+      </c>
+      <c r="C18" s="26">
+        <f>DATOS!$B$18</f>
+        <v/>
+      </c>
+      <c r="D18" s="32">
+        <f>B18*C18</f>
+        <v/>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>TECHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Losa multiusos tipo I techada</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="n">
+        <v>829.4</v>
+      </c>
+      <c r="C19" s="26">
+        <f>DATOS!$B$18</f>
+        <v/>
+      </c>
+      <c r="D19" s="32">
+        <f>B19*C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>TECHO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Patio 01: ingreso principal</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="n">
+        <v>118.8</v>
+      </c>
+      <c r="C20" s="26">
+        <f>DATOS!$B$19</f>
+        <v/>
+      </c>
+      <c r="D20" s="32">
+        <f>B20*C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>AREA LIBRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Patio 02: circulacion principal</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="n">
+        <v>194.2</v>
+      </c>
+      <c r="C21" s="26">
+        <f>DATOS!$B$19</f>
+        <v/>
+      </c>
+      <c r="D21" s="32">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>AREA LIBRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Patio 03: area privada de estudiantes</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="n">
+        <v>257.9</v>
+      </c>
+      <c r="C22" s="26">
+        <f>DATOS!$B$19</f>
+        <v/>
+      </c>
+      <c r="D22" s="32">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>AREA LIBRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Patio 04: asta de bandera</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="C23" s="26">
+        <f>DATOS!$B$19</f>
+        <v/>
+      </c>
+      <c r="D23" s="32">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>AREA LIBRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Veredas, circulaciones, atrio y losa del area de tratamiento</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="C24" s="26">
+        <f>DATOS!$B$19</f>
+        <v/>
+      </c>
+      <c r="D24" s="32">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>AREA LIBRE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Patio de maniobra y estacionamiento</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="n">
+        <v>647.3</v>
+      </c>
+      <c r="C25" s="26">
+        <f>DATOS!$B$20</f>
+        <v/>
+      </c>
+      <c r="D25" s="32">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>ESTACIONAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Areas verdes, jardines y terreno natural nivelado</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="n">
+        <v>2379.7</v>
+      </c>
+      <c r="C26" s="26">
+        <f>DATOS!$B$21</f>
+        <v/>
+      </c>
+      <c r="D26" s="32">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>AREA VERDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL (AREA DENTRO DEL CERCO)</t>
+        </is>
+      </c>
+      <c r="B27" s="36">
+        <f>SUM(B17:B26)</f>
+        <v/>
+      </c>
+      <c r="C27" s="35">
+        <f>D27/B27</f>
+        <v/>
+      </c>
+      <c r="D27" s="36">
+        <f>SUM(D17:D26)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Areas medidas a escala real en la planta del proyecto dentro del cerco. Tabla superior: celdas de 1 m2 asignadas a cada tramo (base del calculo de caudales). Detalle: poligonos de cada zona (techos = proyeccion de coberturas, incluye patio civico y losa multiusos techados; areas libres = veredas, patios, atrio y circulaciones; patio de maniobra y estacionamiento; el resto, areas verdes y terreno nivelado).</t>
         </is>
       </c>
     </row>
@@ -5859,14 +6184,14 @@
         <v>533</v>
       </c>
       <c r="E9" s="25" t="n">
-        <v>0.4</v>
+        <v>0.575</v>
       </c>
       <c r="F9" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G9" s="21">
-        <f>E9*F9*D9*DATOS!$B$21/3600000</f>
+        <f>E9*F9*D9*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H9" s="18">
@@ -5880,7 +6205,7 @@
         <v>0.3</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="L9" s="21">
         <f>DATOS!$B$12*K9</f>
@@ -5907,7 +6232,7 @@
         <v/>
       </c>
       <c r="R9" s="25" t="n">
-        <v>0.0667</v>
+        <v>0.0849</v>
       </c>
       <c r="S9" s="26">
         <f>G9/(DATOS!$B$12*R9)</f>
@@ -5938,14 +6263,14 @@
         <v>559</v>
       </c>
       <c r="E10" s="25" t="n">
-        <v>0.4</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="F10" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G10" s="21">
-        <f>E10*F10*D10*DATOS!$B$21/3600000</f>
+        <f>E10*F10*D10*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H10" s="18">
@@ -5959,7 +6284,7 @@
         <v>0.46</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>0.0756</v>
+        <v>0.0959</v>
       </c>
       <c r="L10" s="21">
         <f>DATOS!$B$12*K10</f>
@@ -5986,7 +6311,7 @@
         <v/>
       </c>
       <c r="R10" s="25" t="n">
-        <v>0.0687</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="S10" s="26">
         <f>G10/(DATOS!$B$12*R10)</f>
@@ -6017,14 +6342,14 @@
         <v>413</v>
       </c>
       <c r="E11" s="25" t="n">
-        <v>0.4</v>
+        <v>0.621</v>
       </c>
       <c r="F11" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G11" s="21">
-        <f>E11*F11*D11*DATOS!$B$21/3600000</f>
+        <f>E11*F11*D11*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H11" s="18">
@@ -6038,7 +6363,7 @@
         <v>0.3</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>0.0617</v>
+        <v>0.0829</v>
       </c>
       <c r="L11" s="21">
         <f>DATOS!$B$12*K11</f>
@@ -6065,7 +6390,7 @@
         <v/>
       </c>
       <c r="R11" s="25" t="n">
-        <v>0.0562</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="S11" s="26">
         <f>G11/(DATOS!$B$12*R11)</f>
@@ -6096,14 +6421,14 @@
         <v>440</v>
       </c>
       <c r="E12" s="25" t="n">
-        <v>0.4</v>
+        <v>0.617</v>
       </c>
       <c r="F12" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G12" s="21">
-        <f>E12*F12*D12*DATOS!$B$21/3600000</f>
+        <f>E12*F12*D12*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H12" s="18">
@@ -6117,7 +6442,7 @@
         <v>0.46</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0863</v>
       </c>
       <c r="L12" s="21">
         <f>DATOS!$B$12*K12</f>
@@ -6144,7 +6469,7 @@
         <v/>
       </c>
       <c r="R12" s="25" t="n">
-        <v>0.0588</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="S12" s="26">
         <f>G12/(DATOS!$B$12*R12)</f>
@@ -6175,14 +6500,14 @@
         <v>528</v>
       </c>
       <c r="E13" s="25" t="n">
-        <v>0.4</v>
+        <v>0.661</v>
       </c>
       <c r="F13" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G13" s="21">
-        <f>E13*F13*D13*DATOS!$B$21/3600000</f>
+        <f>E13*F13*D13*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H13" s="18">
@@ -6196,7 +6521,7 @@
         <v>0.46</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.1027</v>
       </c>
       <c r="L13" s="21">
         <f>DATOS!$B$12*K13</f>
@@ -6223,7 +6548,7 @@
         <v/>
       </c>
       <c r="R13" s="25" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.093</v>
       </c>
       <c r="S13" s="26">
         <f>G13/(DATOS!$B$12*R13)</f>
@@ -6254,14 +6579,14 @@
         <v>965</v>
       </c>
       <c r="E14" s="25" t="n">
-        <v>0.402</v>
+        <v>0.727</v>
       </c>
       <c r="F14" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G14" s="21">
-        <f>E14*F14*D14*DATOS!$B$21/3600000</f>
+        <f>E14*F14*D14*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H14" s="18">
@@ -6275,7 +6600,7 @@
         <v>0.52</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0607</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="L14" s="21">
         <f>DATOS!$B$12*K14</f>
@@ -6302,7 +6627,7 @@
         <v/>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0.0552</v>
+        <v>0.082</v>
       </c>
       <c r="S14" s="26">
         <f>G14/(DATOS!$B$12*R14)</f>
@@ -6333,14 +6658,14 @@
         <v>2225</v>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.447</v>
+        <v>0.711</v>
       </c>
       <c r="F15" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>E15*F15*D15*DATOS!$B$21/3600000</f>
+        <f>E15*F15*D15*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H15" s="18">
@@ -6354,7 +6679,7 @@
         <v>0.77</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.2193</v>
+        <v>0.314</v>
       </c>
       <c r="L15" s="21">
         <f>DATOS!$B$12*K15</f>
@@ -6381,7 +6706,7 @@
         <v/>
       </c>
       <c r="R15" s="25" t="n">
-        <v>0.1969</v>
+        <v>0.2805</v>
       </c>
       <c r="S15" s="26">
         <f>G15/(DATOS!$B$12*R15)</f>
@@ -6412,14 +6737,14 @@
         <v>2226</v>
       </c>
       <c r="E16" s="25" t="n">
-        <v>0.447</v>
+        <v>0.711</v>
       </c>
       <c r="F16" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G16" s="21">
-        <f>E16*F16*D16*DATOS!$B$21/3600000</f>
+        <f>E16*F16*D16*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H16" s="18">
@@ -6433,7 +6758,7 @@
         <v>0.83</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.2193</v>
+        <v>0.3142</v>
       </c>
       <c r="L16" s="21">
         <f>DATOS!$B$12*K16</f>
@@ -6460,7 +6785,7 @@
         <v/>
       </c>
       <c r="R16" s="25" t="n">
-        <v>0.1969</v>
+        <v>0.2807</v>
       </c>
       <c r="S16" s="26">
         <f>G16/(DATOS!$B$12*R16)</f>
@@ -6491,14 +6816,14 @@
         <v>2979</v>
       </c>
       <c r="E17" s="25" t="n">
-        <v>0.462</v>
+        <v>0.715</v>
       </c>
       <c r="F17" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G17" s="21">
-        <f>E17*F17*D17*DATOS!$B$21/3600000</f>
+        <f>E17*F17*D17*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H17" s="18">
@@ -6512,7 +6837,7 @@
         <v>0.83</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.2816</v>
+        <v>0.3992</v>
       </c>
       <c r="L17" s="21">
         <f>DATOS!$B$12*K17</f>
@@ -6539,7 +6864,7 @@
         <v/>
       </c>
       <c r="R17" s="25" t="n">
-        <v>0.252</v>
+        <v>0.3554</v>
       </c>
       <c r="S17" s="26">
         <f>G17/(DATOS!$B$12*R17)</f>
@@ -6570,14 +6895,14 @@
         <v>2980</v>
       </c>
       <c r="E18" s="25" t="n">
-        <v>0.462</v>
+        <v>0.715</v>
       </c>
       <c r="F18" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G18" s="21">
-        <f>E18*F18*D18*DATOS!$B$21/3600000</f>
+        <f>E18*F18*D18*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H18" s="18">
@@ -6591,7 +6916,7 @@
         <v>0.79</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.2816</v>
+        <v>0.3994</v>
       </c>
       <c r="L18" s="21">
         <f>DATOS!$B$12*K18</f>
@@ -6618,7 +6943,7 @@
         <v/>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0.252</v>
+        <v>0.3556</v>
       </c>
       <c r="S18" s="26">
         <f>G18/(DATOS!$B$12*R18)</f>
@@ -6649,14 +6974,14 @@
         <v>3539</v>
       </c>
       <c r="E19" s="25" t="n">
-        <v>0.452</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="F19" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G19" s="21">
-        <f>E19*F19*D19*DATOS!$B$21/3600000</f>
+        <f>E19*F19*D19*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H19" s="18">
@@ -6670,7 +6995,7 @@
         <v>0.79</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.3173</v>
+        <v>0.4477</v>
       </c>
       <c r="L19" s="21">
         <f>DATOS!$B$12*K19</f>
@@ -6697,7 +7022,7 @@
         <v/>
       </c>
       <c r="R19" s="25" t="n">
-        <v>0.2834</v>
+        <v>0.3979</v>
       </c>
       <c r="S19" s="26">
         <f>G19/(DATOS!$B$12*R19)</f>
@@ -6728,14 +7053,14 @@
         <v>368</v>
       </c>
       <c r="E20" s="25" t="n">
-        <v>0.405</v>
+        <v>0.794</v>
       </c>
       <c r="F20" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G20" s="21">
-        <f>E20*F20*D20*DATOS!$B$21/3600000</f>
+        <f>E20*F20*D20*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H20" s="18">
@@ -6749,7 +7074,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0576</v>
+        <v>0.0907</v>
       </c>
       <c r="L20" s="21">
         <f>DATOS!$B$12*K20</f>
@@ -6776,7 +7101,7 @@
         <v/>
       </c>
       <c r="R20" s="25" t="n">
-        <v>0.0525</v>
+        <v>0.0822</v>
       </c>
       <c r="S20" s="26">
         <f>G20/(DATOS!$B$12*R20)</f>
@@ -6807,14 +7132,14 @@
         <v>383</v>
       </c>
       <c r="E21" s="25" t="n">
-        <v>0.55</v>
+        <v>0.596</v>
       </c>
       <c r="F21" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G21" s="21">
-        <f>E21*F21*D21*DATOS!$B$21/3600000</f>
+        <f>E21*F21*D21*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H21" s="18">
@@ -6828,7 +7153,7 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.0727</v>
+        <v>0.0766</v>
       </c>
       <c r="L21" s="21">
         <f>DATOS!$B$12*K21</f>
@@ -6855,7 +7180,7 @@
         <v/>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0.066</v>
+        <v>0.0696</v>
       </c>
       <c r="S21" s="26">
         <f>G21/(DATOS!$B$12*R21)</f>
@@ -6886,14 +7211,14 @@
         <v>443</v>
       </c>
       <c r="E22" s="25" t="n">
-        <v>0.532</v>
+        <v>0.584</v>
       </c>
       <c r="F22" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G22" s="21">
-        <f>E22*F22*D22*DATOS!$B$21/3600000</f>
+        <f>E22*F22*D22*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H22" s="18">
@@ -6907,7 +7232,7 @@
         <v>0.43</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.0786</v>
+        <v>0.0837</v>
       </c>
       <c r="L22" s="21">
         <f>DATOS!$B$12*K22</f>
@@ -6934,7 +7259,7 @@
         <v/>
       </c>
       <c r="R22" s="25" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.0759</v>
       </c>
       <c r="S22" s="26">
         <f>G22/(DATOS!$B$12*R22)</f>
@@ -6965,14 +7290,14 @@
         <v>448</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0.531</v>
+        <v>0.582</v>
       </c>
       <c r="F23" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G23" s="21">
-        <f>E23*F23*D23*DATOS!$B$21/3600000</f>
+        <f>E23*F23*D23*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H23" s="18">
@@ -6986,7 +7311,7 @@
         <v>0.47</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>0.0788</v>
+        <v>0.0839</v>
       </c>
       <c r="L23" s="21">
         <f>DATOS!$B$12*K23</f>
@@ -7013,7 +7338,7 @@
         <v/>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0.0716</v>
+        <v>0.0761</v>
       </c>
       <c r="S23" s="26">
         <f>G23/(DATOS!$B$12*R23)</f>
@@ -7044,14 +7369,14 @@
         <v>584</v>
       </c>
       <c r="E24" s="25" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="F24" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G24" s="21">
-        <f>E24*F24*D24*DATOS!$B$21/3600000</f>
+        <f>E24*F24*D24*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H24" s="18">
@@ -7065,7 +7390,7 @@
         <v>0.48</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.098</v>
+        <v>0.1044</v>
       </c>
       <c r="L24" s="21">
         <f>DATOS!$B$12*K24</f>
@@ -7092,7 +7417,7 @@
         <v/>
       </c>
       <c r="R24" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.0946</v>
       </c>
       <c r="S24" s="26">
         <f>G24/(DATOS!$B$12*R24)</f>
@@ -7123,14 +7448,14 @@
         <v>781</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0.527</v>
+        <v>0.619</v>
       </c>
       <c r="F25" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G25" s="21">
-        <f>E25*F25*D25*DATOS!$B$21/3600000</f>
+        <f>E25*F25*D25*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H25" s="18">
@@ -7144,7 +7469,7 @@
         <v>0.49</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>0.115</v>
+        <v>0.1291</v>
       </c>
       <c r="L25" s="21">
         <f>DATOS!$B$12*K25</f>
@@ -7171,7 +7496,7 @@
         <v/>
       </c>
       <c r="R25" s="25" t="n">
-        <v>0.1041</v>
+        <v>0.1166</v>
       </c>
       <c r="S25" s="26">
         <f>G25/(DATOS!$B$12*R25)</f>
@@ -7202,14 +7527,14 @@
         <v>857</v>
       </c>
       <c r="E26" s="25" t="n">
-        <v>0.52</v>
+        <v>0.627</v>
       </c>
       <c r="F26" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G26" s="21">
-        <f>E26*F26*D26*DATOS!$B$21/3600000</f>
+        <f>E26*F26*D26*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H26" s="18">
@@ -7223,7 +7548,7 @@
         <v>0.57</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.1218</v>
+        <v>0.1391</v>
       </c>
       <c r="L26" s="21">
         <f>DATOS!$B$12*K26</f>
@@ -7250,7 +7575,7 @@
         <v/>
       </c>
       <c r="R26" s="25" t="n">
-        <v>0.1101</v>
+        <v>0.1256</v>
       </c>
       <c r="S26" s="26">
         <f>G26/(DATOS!$B$12*R26)</f>
@@ -7281,14 +7606,14 @@
         <v>1170</v>
       </c>
       <c r="E27" s="25" t="n">
-        <v>0.488</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="F27" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G27" s="21">
-        <f>E27*F27*D27*DATOS!$B$21/3600000</f>
+        <f>E27*F27*D27*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H27" s="18">
@@ -7302,7 +7627,7 @@
         <v>0.61</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.1455</v>
+        <v>0.1861</v>
       </c>
       <c r="L27" s="21">
         <f>DATOS!$B$12*K27</f>
@@ -7329,7 +7654,7 @@
         <v/>
       </c>
       <c r="R27" s="25" t="n">
-        <v>0.1313</v>
+        <v>0.1675</v>
       </c>
       <c r="S27" s="26">
         <f>G27/(DATOS!$B$12*R27)</f>
@@ -7367,7 +7692,7 @@
         <v/>
       </c>
       <c r="G28" s="21">
-        <f>E28*F28*D28*DATOS!$B$21/3600000</f>
+        <f>E28*F28*D28*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H28" s="18">
@@ -7439,14 +7764,14 @@
         <v>230</v>
       </c>
       <c r="E29" s="25" t="n">
-        <v>0.751</v>
+        <v>0.755</v>
       </c>
       <c r="F29" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G29" s="21">
-        <f>E29*F29*D29*DATOS!$B$21/3600000</f>
+        <f>E29*F29*D29*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H29" s="18">
@@ -7460,7 +7785,7 @@
         <v>0.41</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>0.0636</v>
+        <v>0.0639</v>
       </c>
       <c r="L29" s="21">
         <f>DATOS!$B$12*K29</f>
@@ -7487,7 +7812,7 @@
         <v/>
       </c>
       <c r="R29" s="25" t="n">
-        <v>0.0579</v>
+        <v>0.0581</v>
       </c>
       <c r="S29" s="26">
         <f>G29/(DATOS!$B$12*R29)</f>
@@ -7518,14 +7843,14 @@
         <v>367</v>
       </c>
       <c r="E30" s="25" t="n">
-        <v>0.62</v>
+        <v>0.76</v>
       </c>
       <c r="F30" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G30" s="21">
-        <f>E30*F30*D30*DATOS!$B$21/3600000</f>
+        <f>E30*F30*D30*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H30" s="18">
@@ -7539,7 +7864,7 @@
         <v>0.44</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.0766</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="L30" s="21">
         <f>DATOS!$B$12*K30</f>
@@ -7566,7 +7891,7 @@
         <v/>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.0696</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="S30" s="26">
         <f>G30/(DATOS!$B$12*R30)</f>
@@ -7597,14 +7922,14 @@
         <v>411</v>
       </c>
       <c r="E31" s="25" t="n">
-        <v>0.596</v>
+        <v>0.734</v>
       </c>
       <c r="F31" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G31" s="21">
-        <f>E31*F31*D31*DATOS!$B$21/3600000</f>
+        <f>E31*F31*D31*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H31" s="18">
@@ -7618,7 +7943,7 @@
         <v>0.53</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.0805</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="L31" s="21">
         <f>DATOS!$B$12*K31</f>
@@ -7645,7 +7970,7 @@
         <v/>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0.0731</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="S31" s="26">
         <f>G31/(DATOS!$B$12*R31)</f>
@@ -7676,14 +8001,14 @@
         <v>699</v>
       </c>
       <c r="E32" s="25" t="n">
-        <v>0.515</v>
+        <v>0.736</v>
       </c>
       <c r="F32" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G32" s="21">
-        <f>E32*F32*D32*DATOS!$B$21/3600000</f>
+        <f>E32*F32*D32*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H32" s="18">
@@ -7697,7 +8022,7 @@
         <v>0.55</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0.1049</v>
+        <v>0.135</v>
       </c>
       <c r="L32" s="21">
         <f>DATOS!$B$12*K32</f>
@@ -7724,7 +8049,7 @@
         <v/>
       </c>
       <c r="R32" s="25" t="n">
-        <v>0.095</v>
+        <v>0.1219</v>
       </c>
       <c r="S32" s="26">
         <f>G32/(DATOS!$B$12*R32)</f>
@@ -7762,7 +8087,7 @@
         <v/>
       </c>
       <c r="G33" s="21">
-        <f>E33*F33*D33*DATOS!$B$21/3600000</f>
+        <f>E33*F33*D33*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H33" s="18">
@@ -7834,14 +8159,14 @@
         <v>116</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0.698</v>
+        <v>0.822</v>
       </c>
       <c r="F34" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G34" s="21">
-        <f>E34*F34*D34*DATOS!$B$21/3600000</f>
+        <f>E34*F34*D34*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H34" s="18">
@@ -7855,7 +8180,7 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0.0263</v>
+        <v>0.0291</v>
       </c>
       <c r="L34" s="21">
         <f>DATOS!$B$12*K34</f>
@@ -7882,7 +8207,7 @@
         <v/>
       </c>
       <c r="R34" s="25" t="n">
-        <v>0.0241</v>
+        <v>0.0266</v>
       </c>
       <c r="S34" s="26">
         <f>G34/(DATOS!$B$12*R34)</f>
@@ -7913,14 +8238,14 @@
         <v>784</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>0.541</v>
+        <v>0.865</v>
       </c>
       <c r="F35" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G35" s="21">
-        <f>E35*F35*D35*DATOS!$B$21/3600000</f>
+        <f>E35*F35*D35*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H35" s="18">
@@ -7934,7 +8259,7 @@
         <v>0.5</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>0.1176</v>
+        <v>0.1647</v>
       </c>
       <c r="L35" s="21">
         <f>DATOS!$B$12*K35</f>
@@ -7961,7 +8286,7 @@
         <v/>
       </c>
       <c r="R35" s="25" t="n">
-        <v>0.1064</v>
+        <v>0.1484</v>
       </c>
       <c r="S35" s="26">
         <f>G35/(DATOS!$B$12*R35)</f>
@@ -7992,14 +8317,14 @@
         <v>1153</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0.529</v>
+        <v>0.861</v>
       </c>
       <c r="F36" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G36" s="21">
-        <f>E36*F36*D36*DATOS!$B$21/3600000</f>
+        <f>E36*F36*D36*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H36" s="18">
@@ -8013,7 +8338,7 @@
         <v>0.59</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0.1526</v>
+        <v>0.2188</v>
       </c>
       <c r="L36" s="21">
         <f>DATOS!$B$12*K36</f>
@@ -8040,7 +8365,7 @@
         <v/>
       </c>
       <c r="R36" s="25" t="n">
-        <v>0.1376</v>
+        <v>0.1964</v>
       </c>
       <c r="S36" s="26">
         <f>G36/(DATOS!$B$12*R36)</f>
@@ -8071,14 +8396,14 @@
         <v>1154</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0.529</v>
+        <v>0.861</v>
       </c>
       <c r="F37" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G37" s="21">
-        <f>E37*F37*D37*DATOS!$B$21/3600000</f>
+        <f>E37*F37*D37*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H37" s="18">
@@ -8092,7 +8417,7 @@
         <v>0.61</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>0.1526</v>
+        <v>0.2189</v>
       </c>
       <c r="L37" s="21">
         <f>DATOS!$B$12*K37</f>
@@ -8119,7 +8444,7 @@
         <v/>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.1376</v>
+        <v>0.1966</v>
       </c>
       <c r="S37" s="26">
         <f>G37/(DATOS!$B$12*R37)</f>
@@ -8150,14 +8475,14 @@
         <v>1339</v>
       </c>
       <c r="E38" s="25" t="n">
-        <v>0.572</v>
+        <v>0.864</v>
       </c>
       <c r="F38" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G38" s="21">
-        <f>E38*F38*D38*DATOS!$B$21/3600000</f>
+        <f>E38*F38*D38*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H38" s="18">
@@ -8171,7 +8496,7 @@
         <v>0.62</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0.1801</v>
+        <v>0.2458</v>
       </c>
       <c r="L38" s="21">
         <f>DATOS!$B$12*K38</f>
@@ -8198,7 +8523,7 @@
         <v/>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0.1621</v>
+        <v>0.2204</v>
       </c>
       <c r="S38" s="26">
         <f>G38/(DATOS!$B$12*R38)</f>
@@ -8229,14 +8554,14 @@
         <v>1340</v>
       </c>
       <c r="E39" s="25" t="n">
-        <v>0.572</v>
+        <v>0.863</v>
       </c>
       <c r="F39" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G39" s="21">
-        <f>E39*F39*D39*DATOS!$B$21/3600000</f>
+        <f>E39*F39*D39*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H39" s="18">
@@ -8250,7 +8575,7 @@
         <v>0.73</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>0.1801</v>
+        <v>0.2458</v>
       </c>
       <c r="L39" s="21">
         <f>DATOS!$B$12*K39</f>
@@ -8277,7 +8602,7 @@
         <v/>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0.1621</v>
+        <v>0.2204</v>
       </c>
       <c r="S39" s="26">
         <f>G39/(DATOS!$B$12*R39)</f>
@@ -8308,14 +8633,14 @@
         <v>1768</v>
       </c>
       <c r="E40" s="25" t="n">
-        <v>0.613</v>
+        <v>0.858</v>
       </c>
       <c r="F40" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G40" s="21">
-        <f>E40*F40*D40*DATOS!$B$21/3600000</f>
+        <f>E40*F40*D40*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H40" s="18">
@@ -8329,7 +8654,7 @@
         <v>0.73</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.2341</v>
+        <v>0.3037</v>
       </c>
       <c r="L40" s="21">
         <f>DATOS!$B$12*K40</f>
@@ -8356,7 +8681,7 @@
         <v/>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0.21</v>
+        <v>0.2715</v>
       </c>
       <c r="S40" s="26">
         <f>G40/(DATOS!$B$12*R40)</f>
@@ -8387,14 +8712,14 @@
         <v>2084</v>
       </c>
       <c r="E41" s="25" t="n">
-        <v>0.623</v>
+        <v>0.831</v>
       </c>
       <c r="F41" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G41" s="21">
-        <f>E41*F41*D41*DATOS!$B$21/3600000</f>
+        <f>E41*F41*D41*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H41" s="18">
@@ -8408,7 +8733,7 @@
         <v>0.79</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.2691</v>
+        <v>0.3375</v>
       </c>
       <c r="L41" s="21">
         <f>DATOS!$B$12*K41</f>
@@ -8435,7 +8760,7 @@
         <v/>
       </c>
       <c r="R41" s="25" t="n">
-        <v>0.2409</v>
+        <v>0.3012</v>
       </c>
       <c r="S41" s="26">
         <f>G41/(DATOS!$B$12*R41)</f>
@@ -8466,14 +8791,14 @@
         <v>2085</v>
       </c>
       <c r="E42" s="25" t="n">
-        <v>0.623</v>
+        <v>0.831</v>
       </c>
       <c r="F42" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G42" s="21">
-        <f>E42*F42*D42*DATOS!$B$21/3600000</f>
+        <f>E42*F42*D42*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H42" s="18">
@@ -8487,7 +8812,7 @@
         <v>0.7</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>0.2691</v>
+        <v>0.3377</v>
       </c>
       <c r="L42" s="21">
         <f>DATOS!$B$12*K42</f>
@@ -8514,7 +8839,7 @@
         <v/>
       </c>
       <c r="R42" s="25" t="n">
-        <v>0.2409</v>
+        <v>0.3013</v>
       </c>
       <c r="S42" s="26">
         <f>G42/(DATOS!$B$12*R42)</f>
@@ -8545,14 +8870,14 @@
         <v>2099</v>
       </c>
       <c r="E43" s="25" t="n">
-        <v>0.622</v>
+        <v>0.828</v>
       </c>
       <c r="F43" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G43" s="21">
-        <f>E43*F43*D43*DATOS!$B$21/3600000</f>
+        <f>E43*F43*D43*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H43" s="18">
@@ -8566,7 +8891,7 @@
         <v>0.7</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>0.27</v>
+        <v>0.3385</v>
       </c>
       <c r="L43" s="21">
         <f>DATOS!$B$12*K43</f>
@@ -8593,7 +8918,7 @@
         <v/>
       </c>
       <c r="R43" s="25" t="n">
-        <v>0.2417</v>
+        <v>0.3021</v>
       </c>
       <c r="S43" s="26">
         <f>G43/(DATOS!$B$12*R43)</f>
@@ -8624,14 +8949,14 @@
         <v>2102</v>
       </c>
       <c r="E44" s="25" t="n">
-        <v>0.622</v>
+        <v>0.827</v>
       </c>
       <c r="F44" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G44" s="21">
-        <f>E44*F44*D44*DATOS!$B$21/3600000</f>
+        <f>E44*F44*D44*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H44" s="18">
@@ -8645,7 +8970,7 @@
         <v>0.74</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>0.2703</v>
+        <v>0.3387</v>
       </c>
       <c r="L44" s="21">
         <f>DATOS!$B$12*K44</f>
@@ -8672,7 +8997,7 @@
         <v/>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0.242</v>
+        <v>0.3022</v>
       </c>
       <c r="S44" s="26">
         <f>G44/(DATOS!$B$12*R44)</f>
@@ -8703,14 +9028,14 @@
         <v>2126</v>
       </c>
       <c r="E45" s="25" t="n">
-        <v>0.619</v>
+        <v>0.822</v>
       </c>
       <c r="F45" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G45" s="21">
-        <f>E45*F45*D45*DATOS!$B$21/3600000</f>
+        <f>E45*F45*D45*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H45" s="18">
@@ -8724,7 +9049,7 @@
         <v>0.74</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>0.2717</v>
+        <v>0.3402</v>
       </c>
       <c r="L45" s="21">
         <f>DATOS!$B$12*K45</f>
@@ -8751,7 +9076,7 @@
         <v/>
       </c>
       <c r="R45" s="25" t="n">
-        <v>0.2432</v>
+        <v>0.3036</v>
       </c>
       <c r="S45" s="26">
         <f>G45/(DATOS!$B$12*R45)</f>
@@ -8782,14 +9107,14 @@
         <v>2127</v>
       </c>
       <c r="E46" s="25" t="n">
-        <v>0.619</v>
+        <v>0.822</v>
       </c>
       <c r="F46" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G46" s="21">
-        <f>E46*F46*D46*DATOS!$B$21/3600000</f>
+        <f>E46*F46*D46*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H46" s="18">
@@ -8803,7 +9128,7 @@
         <v>0.77</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>0.2719</v>
+        <v>0.3402</v>
       </c>
       <c r="L46" s="21">
         <f>DATOS!$B$12*K46</f>
@@ -8830,7 +9155,7 @@
         <v/>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0.2434</v>
+        <v>0.3036</v>
       </c>
       <c r="S46" s="26">
         <f>G46/(DATOS!$B$12*R46)</f>
@@ -8861,14 +9186,14 @@
         <v>2178</v>
       </c>
       <c r="E47" s="25" t="n">
-        <v>0.614</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="F47" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G47" s="21">
-        <f>E47*F47*D47*DATOS!$B$21/3600000</f>
+        <f>E47*F47*D47*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H47" s="18">
@@ -8882,7 +9207,7 @@
         <v>0.77</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0.275</v>
+        <v>0.3434</v>
       </c>
       <c r="L47" s="21">
         <f>DATOS!$B$12*K47</f>
@@ -8909,7 +9234,7 @@
         <v/>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0.2461</v>
+        <v>0.3064</v>
       </c>
       <c r="S47" s="26">
         <f>G47/(DATOS!$B$12*R47)</f>
@@ -8940,14 +9265,14 @@
         <v>2192</v>
       </c>
       <c r="E48" s="25" t="n">
-        <v>0.612</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F48" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G48" s="21">
-        <f>E48*F48*D48*DATOS!$B$21/3600000</f>
+        <f>E48*F48*D48*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H48" s="18">
@@ -8961,7 +9286,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>0.2761</v>
+        <v>0.3443</v>
       </c>
       <c r="L48" s="21">
         <f>DATOS!$B$12*K48</f>
@@ -8988,7 +9313,7 @@
         <v/>
       </c>
       <c r="R48" s="25" t="n">
-        <v>0.2471</v>
+        <v>0.3072</v>
       </c>
       <c r="S48" s="26">
         <f>G48/(DATOS!$B$12*R48)</f>
@@ -9019,14 +9344,14 @@
         <v>2193</v>
       </c>
       <c r="E49" s="25" t="n">
-        <v>0.612</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="F49" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G49" s="21">
-        <f>E49*F49*D49*DATOS!$B$21/3600000</f>
+        <f>E49*F49*D49*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H49" s="18">
@@ -9040,7 +9365,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.2761</v>
+        <v>0.3443</v>
       </c>
       <c r="L49" s="21">
         <f>DATOS!$B$12*K49</f>
@@ -9067,7 +9392,7 @@
         <v/>
       </c>
       <c r="R49" s="25" t="n">
-        <v>0.2471</v>
+        <v>0.3072</v>
       </c>
       <c r="S49" s="26">
         <f>G49/(DATOS!$B$12*R49)</f>
@@ -9098,14 +9423,14 @@
         <v>47</v>
       </c>
       <c r="E50" s="25" t="n">
-        <v>0.819</v>
+        <v>0.88</v>
       </c>
       <c r="F50" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G50" s="21">
-        <f>E50*F50*D50*DATOS!$B$21/3600000</f>
+        <f>E50*F50*D50*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H50" s="18">
@@ -9119,7 +9444,7 @@
         <v>0.3</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>0.024</v>
+        <v>0.0253</v>
       </c>
       <c r="L50" s="21">
         <f>DATOS!$B$12*K50</f>
@@ -9146,7 +9471,7 @@
         <v/>
       </c>
       <c r="R50" s="25" t="n">
-        <v>0.022</v>
+        <v>0.0231</v>
       </c>
       <c r="S50" s="26">
         <f>G50/(DATOS!$B$12*R50)</f>
@@ -9177,14 +9502,14 @@
         <v>488</v>
       </c>
       <c r="E51" s="25" t="n">
-        <v>0.455</v>
+        <v>0.88</v>
       </c>
       <c r="F51" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G51" s="21">
-        <f>E51*F51*D51*DATOS!$B$21/3600000</f>
+        <f>E51*F51*D51*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H51" s="18">
@@ -9198,7 +9523,7 @@
         <v>0.32</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1186</v>
       </c>
       <c r="L51" s="21">
         <f>DATOS!$B$12*K51</f>
@@ -9225,7 +9550,7 @@
         <v/>
       </c>
       <c r="R51" s="25" t="n">
-        <v>0.06850000000000001</v>
+        <v>0.1073</v>
       </c>
       <c r="S51" s="26">
         <f>G51/(DATOS!$B$12*R51)</f>
@@ -9256,14 +9581,14 @@
         <v>342</v>
       </c>
       <c r="E52" s="25" t="n">
-        <v>0.514</v>
+        <v>0.88</v>
       </c>
       <c r="F52" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G52" s="21">
-        <f>E52*F52*D52*DATOS!$B$21/3600000</f>
+        <f>E52*F52*D52*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H52" s="18">
@@ -9277,7 +9602,7 @@
         <v>0.3</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>0.0644</v>
+        <v>0.0925</v>
       </c>
       <c r="L52" s="21">
         <f>DATOS!$B$12*K52</f>
@@ -9304,7 +9629,7 @@
         <v/>
       </c>
       <c r="R52" s="25" t="n">
-        <v>0.0586</v>
+        <v>0.0839</v>
       </c>
       <c r="S52" s="26">
         <f>G52/(DATOS!$B$12*R52)</f>
@@ -9335,14 +9660,14 @@
         <v>205</v>
       </c>
       <c r="E53" s="25" t="n">
-        <v>0.669</v>
+        <v>0.838</v>
       </c>
       <c r="F53" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G53" s="21">
-        <f>E53*F53*D53*DATOS!$B$21/3600000</f>
+        <f>E53*F53*D53*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H53" s="18">
@@ -9356,7 +9681,7 @@
         <v>0.3</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.0548</v>
+        <v>0.0633</v>
       </c>
       <c r="L53" s="21">
         <f>DATOS!$B$12*K53</f>
@@ -9383,7 +9708,7 @@
         <v/>
       </c>
       <c r="R53" s="25" t="n">
-        <v>0.0499</v>
+        <v>0.0576</v>
       </c>
       <c r="S53" s="26">
         <f>G53/(DATOS!$B$12*R53)</f>
@@ -9414,14 +9739,14 @@
         <v>232</v>
       </c>
       <c r="E54" s="25" t="n">
-        <v>0.675</v>
+        <v>0.832</v>
       </c>
       <c r="F54" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G54" s="21">
-        <f>E54*F54*D54*DATOS!$B$21/3600000</f>
+        <f>E54*F54*D54*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H54" s="18">
@@ -9435,7 +9760,7 @@
         <v>0.39</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>0.0598</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="L54" s="21">
         <f>DATOS!$B$12*K54</f>
@@ -9462,7 +9787,7 @@
         <v/>
       </c>
       <c r="R54" s="25" t="n">
-        <v>0.0545</v>
+        <v>0.0623</v>
       </c>
       <c r="S54" s="26">
         <f>G54/(DATOS!$B$12*R54)</f>
@@ -9493,14 +9818,14 @@
         <v>245</v>
       </c>
       <c r="E55" s="25" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.833</v>
       </c>
       <c r="F55" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G55" s="21">
-        <f>E55*F55*D55*DATOS!$B$21/3600000</f>
+        <f>E55*F55*D55*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H55" s="18">
@@ -9514,7 +9839,7 @@
         <v>0.42</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>0.0625</v>
+        <v>0.0711</v>
       </c>
       <c r="L55" s="21">
         <f>DATOS!$B$12*K55</f>
@@ -9541,7 +9866,7 @@
         <v/>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0.0569</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="S55" s="26">
         <f>G55/(DATOS!$B$12*R55)</f>
@@ -9572,14 +9897,14 @@
         <v>335</v>
       </c>
       <c r="E56" s="25" t="n">
-        <v>0.722</v>
+        <v>0.846</v>
       </c>
       <c r="F56" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G56" s="21">
-        <f>E56*F56*D56*DATOS!$B$21/3600000</f>
+        <f>E56*F56*D56*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H56" s="18">
@@ -9593,7 +9918,7 @@
         <v>0.42</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>0.0798</v>
+        <v>0.0888</v>
       </c>
       <c r="L56" s="21">
         <f>DATOS!$B$12*K56</f>
@@ -9620,7 +9945,7 @@
         <v/>
       </c>
       <c r="R56" s="25" t="n">
-        <v>0.0725</v>
+        <v>0.0806</v>
       </c>
       <c r="S56" s="26">
         <f>G56/(DATOS!$B$12*R56)</f>
@@ -9651,14 +9976,14 @@
         <v>335</v>
       </c>
       <c r="E57" s="25" t="n">
-        <v>0.722</v>
+        <v>0.846</v>
       </c>
       <c r="F57" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G57" s="21">
-        <f>E57*F57*D57*DATOS!$B$21/3600000</f>
+        <f>E57*F57*D57*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H57" s="18">
@@ -9672,7 +9997,7 @@
         <v>0.48</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>0.0798</v>
+        <v>0.0888</v>
       </c>
       <c r="L57" s="21">
         <f>DATOS!$B$12*K57</f>
@@ -9699,7 +10024,7 @@
         <v/>
       </c>
       <c r="R57" s="25" t="n">
-        <v>0.0725</v>
+        <v>0.0806</v>
       </c>
       <c r="S57" s="26">
         <f>G57/(DATOS!$B$12*R57)</f>
@@ -9737,7 +10062,7 @@
         <v/>
       </c>
       <c r="G58" s="21">
-        <f>E58*F58*D58*DATOS!$B$21/3600000</f>
+        <f>E58*F58*D58*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H58" s="18">
@@ -9809,14 +10134,14 @@
         <v>238</v>
       </c>
       <c r="E59" s="25" t="n">
-        <v>0.513</v>
+        <v>0.842</v>
       </c>
       <c r="F59" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G59" s="21">
-        <f>E59*F59*D59*DATOS!$B$21/3600000</f>
+        <f>E59*F59*D59*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H59" s="18">
@@ -9830,7 +10155,7 @@
         <v>0.3</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>0.0505</v>
+        <v>0.0704</v>
       </c>
       <c r="L59" s="21">
         <f>DATOS!$B$12*K59</f>
@@ -9857,7 +10182,7 @@
         <v/>
       </c>
       <c r="R59" s="25" t="n">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="S59" s="26">
         <f>G59/(DATOS!$B$12*R59)</f>
@@ -9888,14 +10213,14 @@
         <v>247</v>
       </c>
       <c r="E60" s="25" t="n">
-        <v>0.524</v>
+        <v>0.843</v>
       </c>
       <c r="F60" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G60" s="21">
-        <f>E60*F60*D60*DATOS!$B$21/3600000</f>
+        <f>E60*F60*D60*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H60" s="18">
@@ -9909,7 +10234,7 @@
         <v>0.38</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>0.0526</v>
+        <v>0.0721</v>
       </c>
       <c r="L60" s="21">
         <f>DATOS!$B$12*K60</f>
@@ -9936,7 +10261,7 @@
         <v/>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0.0479</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="S60" s="26">
         <f>G60/(DATOS!$B$12*R60)</f>
@@ -9967,14 +10292,14 @@
         <v>533</v>
       </c>
       <c r="E61" s="25" t="n">
-        <v>0.465</v>
+        <v>0.731</v>
       </c>
       <c r="F61" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G61" s="21">
-        <f>E61*F61*D61*DATOS!$B$21/3600000</f>
+        <f>E61*F61*D61*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H61" s="18">
@@ -9988,7 +10313,7 @@
         <v>0.38</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0.0813</v>
+        <v>0.1107</v>
       </c>
       <c r="L61" s="21">
         <f>DATOS!$B$12*K61</f>
@@ -10015,7 +10340,7 @@
         <v/>
       </c>
       <c r="R61" s="25" t="n">
-        <v>0.0738</v>
+        <v>0.1002</v>
       </c>
       <c r="S61" s="26">
         <f>G61/(DATOS!$B$12*R61)</f>
@@ -10046,14 +10371,14 @@
         <v>536</v>
       </c>
       <c r="E62" s="25" t="n">
-        <v>0.464</v>
+        <v>0.73</v>
       </c>
       <c r="F62" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G62" s="21">
-        <f>E62*F62*D62*DATOS!$B$21/3600000</f>
+        <f>E62*F62*D62*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H62" s="18">
@@ -10067,7 +10392,7 @@
         <v>0.49</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>0.0813</v>
+        <v>0.1112</v>
       </c>
       <c r="L62" s="21">
         <f>DATOS!$B$12*K62</f>
@@ -10094,7 +10419,7 @@
         <v/>
       </c>
       <c r="R62" s="25" t="n">
-        <v>0.0738</v>
+        <v>0.1006</v>
       </c>
       <c r="S62" s="26">
         <f>G62/(DATOS!$B$12*R62)</f>
@@ -10125,14 +10450,14 @@
         <v>857</v>
       </c>
       <c r="E63" s="25" t="n">
-        <v>0.44</v>
+        <v>0.767</v>
       </c>
       <c r="F63" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G63" s="21">
-        <f>E63*F63*D63*DATOS!$B$21/3600000</f>
+        <f>E63*F63*D63*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H63" s="18">
@@ -10146,7 +10471,7 @@
         <v>0.5</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>0.1084</v>
+        <v>0.161</v>
       </c>
       <c r="L63" s="21">
         <f>DATOS!$B$12*K63</f>
@@ -10173,7 +10498,7 @@
         <v/>
       </c>
       <c r="R63" s="25" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1451</v>
       </c>
       <c r="S63" s="26">
         <f>G63/(DATOS!$B$12*R63)</f>
@@ -10204,14 +10529,14 @@
         <v>1130</v>
       </c>
       <c r="E64" s="25" t="n">
-        <v>0.482</v>
+        <v>0.791</v>
       </c>
       <c r="F64" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G64" s="21">
-        <f>E64*F64*D64*DATOS!$B$21/3600000</f>
+        <f>E64*F64*D64*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H64" s="18">
@@ -10225,7 +10550,7 @@
         <v>0.52</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>0.1405</v>
+        <v>0.2021</v>
       </c>
       <c r="L64" s="21">
         <f>DATOS!$B$12*K64</f>
@@ -10252,7 +10577,7 @@
         <v/>
       </c>
       <c r="R64" s="25" t="n">
-        <v>0.1268</v>
+        <v>0.1817</v>
       </c>
       <c r="S64" s="26">
         <f>G64/(DATOS!$B$12*R64)</f>
@@ -10283,14 +10608,14 @@
         <v>1869</v>
       </c>
       <c r="E65" s="25" t="n">
-        <v>0.603</v>
+        <v>0.819</v>
       </c>
       <c r="F65" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G65" s="21">
-        <f>E65*F65*D65*DATOS!$B$21/3600000</f>
+        <f>E65*F65*D65*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H65" s="18">
@@ -10304,7 +10629,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>0.241</v>
+        <v>0.306</v>
       </c>
       <c r="L65" s="21">
         <f>DATOS!$B$12*K65</f>
@@ -10331,7 +10656,7 @@
         <v/>
       </c>
       <c r="R65" s="25" t="n">
-        <v>0.2161</v>
+        <v>0.2734</v>
       </c>
       <c r="S65" s="26">
         <f>G65/(DATOS!$B$12*R65)</f>
@@ -10362,14 +10687,14 @@
         <v>2360</v>
       </c>
       <c r="E66" s="25" t="n">
-        <v>0.657</v>
+        <v>0.828</v>
       </c>
       <c r="F66" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G66" s="21">
-        <f>E66*F66*D66*DATOS!$B$21/3600000</f>
+        <f>E66*F66*D66*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H66" s="18">
@@ -10383,7 +10708,7 @@
         <v>0.62</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>0.3094</v>
+        <v>0.3722</v>
       </c>
       <c r="L66" s="21">
         <f>DATOS!$B$12*K66</f>
@@ -10410,7 +10735,7 @@
         <v/>
       </c>
       <c r="R66" s="25" t="n">
-        <v>0.2765</v>
+        <v>0.3317</v>
       </c>
       <c r="S66" s="26">
         <f>G66/(DATOS!$B$12*R66)</f>
@@ -10441,14 +10766,14 @@
         <v>2486</v>
       </c>
       <c r="E67" s="25" t="n">
-        <v>0.667</v>
+        <v>0.829</v>
       </c>
       <c r="F67" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G67" s="21">
-        <f>E67*F67*D67*DATOS!$B$21/3600000</f>
+        <f>E67*F67*D67*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H67" s="18">
@@ -10462,7 +10787,7 @@
         <v>0.57</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>0.3261</v>
+        <v>0.3888</v>
       </c>
       <c r="L67" s="21">
         <f>DATOS!$B$12*K67</f>
@@ -10489,7 +10814,7 @@
         <v/>
       </c>
       <c r="R67" s="25" t="n">
-        <v>0.2912</v>
+        <v>0.3462</v>
       </c>
       <c r="S67" s="26">
         <f>G67/(DATOS!$B$12*R67)</f>
@@ -10520,14 +10845,14 @@
         <v>2499</v>
       </c>
       <c r="E68" s="25" t="n">
-        <v>0.668</v>
+        <v>0.829</v>
       </c>
       <c r="F68" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G68" s="21">
-        <f>E68*F68*D68*DATOS!$B$21/3600000</f>
+        <f>E68*F68*D68*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H68" s="18">
@@ -10541,7 +10866,7 @@
         <v>0.63</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.328</v>
+        <v>0.3904</v>
       </c>
       <c r="L68" s="21">
         <f>DATOS!$B$12*K68</f>
@@ -10568,7 +10893,7 @@
         <v/>
       </c>
       <c r="R68" s="25" t="n">
-        <v>0.2928</v>
+        <v>0.3477</v>
       </c>
       <c r="S68" s="26">
         <f>G68/(DATOS!$B$12*R68)</f>
@@ -10599,14 +10924,14 @@
         <v>2499</v>
       </c>
       <c r="E69" s="25" t="n">
-        <v>0.668</v>
+        <v>0.829</v>
       </c>
       <c r="F69" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G69" s="21">
-        <f>E69*F69*D69*DATOS!$B$21/3600000</f>
+        <f>E69*F69*D69*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H69" s="18">
@@ -10620,7 +10945,7 @@
         <v>0.64</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>0.328</v>
+        <v>0.3904</v>
       </c>
       <c r="L69" s="21">
         <f>DATOS!$B$12*K69</f>
@@ -10647,7 +10972,7 @@
         <v/>
       </c>
       <c r="R69" s="25" t="n">
-        <v>0.2928</v>
+        <v>0.3477</v>
       </c>
       <c r="S69" s="26">
         <f>G69/(DATOS!$B$12*R69)</f>
@@ -10678,14 +11003,14 @@
         <v>3028</v>
       </c>
       <c r="E70" s="25" t="n">
-        <v>0.674</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="F70" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G70" s="21">
-        <f>E70*F70*D70*DATOS!$B$21/3600000</f>
+        <f>E70*F70*D70*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H70" s="18">
@@ -10699,7 +11024,7 @@
         <v>0.64</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>0.3854</v>
+        <v>0.447</v>
       </c>
       <c r="L70" s="21">
         <f>DATOS!$B$12*K70</f>
@@ -10726,7 +11051,7 @@
         <v/>
       </c>
       <c r="R70" s="25" t="n">
-        <v>0.3433</v>
+        <v>0.3974</v>
       </c>
       <c r="S70" s="26">
         <f>G70/(DATOS!$B$12*R70)</f>
@@ -10757,14 +11082,14 @@
         <v>244</v>
       </c>
       <c r="E71" s="25" t="n">
-        <v>0.597</v>
+        <v>0.88</v>
       </c>
       <c r="F71" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G71" s="21">
-        <f>E71*F71*D71*DATOS!$B$21/3600000</f>
+        <f>E71*F71*D71*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H71" s="18">
@@ -10778,7 +11103,7 @@
         <v>0.3</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>0.0568</v>
+        <v>0.0737</v>
       </c>
       <c r="L71" s="21">
         <f>DATOS!$B$12*K71</f>
@@ -10805,7 +11130,7 @@
         <v/>
       </c>
       <c r="R71" s="25" t="n">
-        <v>0.0517</v>
+        <v>0.0669</v>
       </c>
       <c r="S71" s="26">
         <f>G71/(DATOS!$B$12*R71)</f>
@@ -10843,7 +11168,7 @@
         <v/>
       </c>
       <c r="G72" s="21">
-        <f>E72*F72*D72*DATOS!$B$21/3600000</f>
+        <f>E72*F72*D72*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H72" s="18">
@@ -10915,14 +11240,14 @@
         <v>222</v>
       </c>
       <c r="E73" s="25" t="n">
-        <v>0.83</v>
+        <v>0.878</v>
       </c>
       <c r="F73" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G73" s="21">
-        <f>E73*F73*D73*DATOS!$B$21/3600000</f>
+        <f>E73*F73*D73*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H73" s="18">
@@ -10936,7 +11261,7 @@
         <v>0.38</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>0.0665</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="L73" s="21">
         <f>DATOS!$B$12*K73</f>
@@ -10963,7 +11288,7 @@
         <v/>
       </c>
       <c r="R73" s="25" t="n">
-        <v>0.0605</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="S73" s="26">
         <f>G73/(DATOS!$B$12*R73)</f>
@@ -10994,14 +11319,14 @@
         <v>478</v>
       </c>
       <c r="E74" s="25" t="n">
-        <v>0.752</v>
+        <v>0.865</v>
       </c>
       <c r="F74" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G74" s="21">
-        <f>E74*F74*D74*DATOS!$B$21/3600000</f>
+        <f>E74*F74*D74*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H74" s="18">
@@ -11015,7 +11340,7 @@
         <v>0.35</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>0.1049</v>
+        <v>0.1155</v>
       </c>
       <c r="L74" s="21">
         <f>DATOS!$B$12*K74</f>
@@ -11042,7 +11367,7 @@
         <v/>
       </c>
       <c r="R74" s="25" t="n">
-        <v>0.095</v>
+        <v>0.1045</v>
       </c>
       <c r="S74" s="26">
         <f>G74/(DATOS!$B$12*R74)</f>
@@ -11073,14 +11398,14 @@
         <v>481</v>
       </c>
       <c r="E75" s="25" t="n">
-        <v>0.751</v>
+        <v>0.863</v>
       </c>
       <c r="F75" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G75" s="21">
-        <f>E75*F75*D75*DATOS!$B$21/3600000</f>
+        <f>E75*F75*D75*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H75" s="18">
@@ -11094,7 +11419,7 @@
         <v>0.35</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>0.1051</v>
+        <v>0.1159</v>
       </c>
       <c r="L75" s="21">
         <f>DATOS!$B$12*K75</f>
@@ -11121,7 +11446,7 @@
         <v/>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.1049</v>
       </c>
       <c r="S75" s="26">
         <f>G75/(DATOS!$B$12*R75)</f>
@@ -11152,14 +11477,14 @@
         <v>489</v>
       </c>
       <c r="E76" s="25" t="n">
-        <v>0.753</v>
+        <v>0.863</v>
       </c>
       <c r="F76" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G76" s="21">
-        <f>E76*F76*D76*DATOS!$B$21/3600000</f>
+        <f>E76*F76*D76*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H76" s="18">
@@ -11173,7 +11498,7 @@
         <v>0.35</v>
       </c>
       <c r="K76" s="25" t="n">
-        <v>0.1066</v>
+        <v>0.1172</v>
       </c>
       <c r="L76" s="21">
         <f>DATOS!$B$12*K76</f>
@@ -11200,7 +11525,7 @@
         <v/>
       </c>
       <c r="R76" s="25" t="n">
-        <v>0.09660000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="S76" s="26">
         <f>G76/(DATOS!$B$12*R76)</f>
@@ -11231,14 +11556,14 @@
         <v>671</v>
       </c>
       <c r="E77" s="25" t="n">
-        <v>0.788</v>
+        <v>0.868</v>
       </c>
       <c r="F77" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G77" s="21">
-        <f>E77*F77*D77*DATOS!$B$21/3600000</f>
+        <f>E77*F77*D77*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H77" s="18">
@@ -11252,7 +11577,7 @@
         <v>0.35</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.1376</v>
+        <v>0.1475</v>
       </c>
       <c r="L77" s="21">
         <f>DATOS!$B$12*K77</f>
@@ -11279,7 +11604,7 @@
         <v/>
       </c>
       <c r="R77" s="25" t="n">
-        <v>0.1243</v>
+        <v>0.1331</v>
       </c>
       <c r="S77" s="26">
         <f>G77/(DATOS!$B$12*R77)</f>
@@ -11310,14 +11635,14 @@
         <v>691</v>
       </c>
       <c r="E78" s="25" t="n">
-        <v>0.79</v>
+        <v>0.868</v>
       </c>
       <c r="F78" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G78" s="21">
-        <f>E78*F78*D78*DATOS!$B$21/3600000</f>
+        <f>E78*F78*D78*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H78" s="18">
@@ -11331,7 +11656,7 @@
         <v>0.45</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0.1409</v>
+        <v>0.1506</v>
       </c>
       <c r="L78" s="21">
         <f>DATOS!$B$12*K78</f>
@@ -11358,7 +11683,7 @@
         <v/>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0.1272</v>
+        <v>0.1359</v>
       </c>
       <c r="S78" s="26">
         <f>G78/(DATOS!$B$12*R78)</f>
@@ -11396,7 +11721,7 @@
         <v/>
       </c>
       <c r="G79" s="21">
-        <f>E79*F79*D79*DATOS!$B$21/3600000</f>
+        <f>E79*F79*D79*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H79" s="18">
@@ -11475,7 +11800,7 @@
         <v/>
       </c>
       <c r="G80" s="21">
-        <f>E80*F80*D80*DATOS!$B$21/3600000</f>
+        <f>E80*F80*D80*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H80" s="18">
@@ -11554,7 +11879,7 @@
         <v/>
       </c>
       <c r="G81" s="21">
-        <f>E81*F81*D81*DATOS!$B$21/3600000</f>
+        <f>E81*F81*D81*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H81" s="18">
@@ -11633,7 +11958,7 @@
         <v/>
       </c>
       <c r="G82" s="21">
-        <f>E82*F82*D82*DATOS!$B$21/3600000</f>
+        <f>E82*F82*D82*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H82" s="18">
@@ -11712,7 +12037,7 @@
         <v/>
       </c>
       <c r="G83" s="21">
-        <f>E83*F83*D83*DATOS!$B$21/3600000</f>
+        <f>E83*F83*D83*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H83" s="18">
@@ -11791,7 +12116,7 @@
         <v/>
       </c>
       <c r="G84" s="21">
-        <f>E84*F84*D84*DATOS!$B$21/3600000</f>
+        <f>E84*F84*D84*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H84" s="18">
@@ -11870,7 +12195,7 @@
         <v/>
       </c>
       <c r="G85" s="21">
-        <f>E85*F85*D85*DATOS!$B$21/3600000</f>
+        <f>E85*F85*D85*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H85" s="18">
@@ -11949,7 +12274,7 @@
         <v/>
       </c>
       <c r="G86" s="21">
-        <f>E86*F86*D86*DATOS!$B$21/3600000</f>
+        <f>E86*F86*D86*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H86" s="18">
@@ -12028,7 +12353,7 @@
         <v/>
       </c>
       <c r="G87" s="21">
-        <f>E87*F87*D87*DATOS!$B$21/3600000</f>
+        <f>E87*F87*D87*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H87" s="18">
@@ -12107,7 +12432,7 @@
         <v/>
       </c>
       <c r="G88" s="21">
-        <f>E88*F88*D88*DATOS!$B$21/3600000</f>
+        <f>E88*F88*D88*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H88" s="18">
@@ -12186,7 +12511,7 @@
         <v/>
       </c>
       <c r="G89" s="21">
-        <f>E89*F89*D89*DATOS!$B$21/3600000</f>
+        <f>E89*F89*D89*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H89" s="18">
@@ -12265,7 +12590,7 @@
         <v/>
       </c>
       <c r="G90" s="21">
-        <f>E90*F90*D90*DATOS!$B$21/3600000</f>
+        <f>E90*F90*D90*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H90" s="18">
@@ -12337,14 +12662,14 @@
         <v>629</v>
       </c>
       <c r="E91" s="25" t="n">
-        <v>0.591</v>
+        <v>0.769</v>
       </c>
       <c r="F91" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G91" s="21">
-        <f>E91*F91*D91*DATOS!$B$21/3600000</f>
+        <f>E91*F91*D91*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H91" s="18">
@@ -12358,7 +12683,7 @@
         <v>0.5</v>
       </c>
       <c r="K91" s="25" t="n">
-        <v>0.1071</v>
+        <v>0.1291</v>
       </c>
       <c r="L91" s="21">
         <f>DATOS!$B$12*K91</f>
@@ -12385,7 +12710,7 @@
         <v/>
       </c>
       <c r="R91" s="25" t="n">
-        <v>0.0969</v>
+        <v>0.1166</v>
       </c>
       <c r="S91" s="26">
         <f>G91/(DATOS!$B$12*R91)</f>
@@ -12416,14 +12741,14 @@
         <v>633</v>
       </c>
       <c r="E92" s="25" t="n">
-        <v>0.59</v>
+        <v>0.767</v>
       </c>
       <c r="F92" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G92" s="21">
-        <f>E92*F92*D92*DATOS!$B$21/3600000</f>
+        <f>E92*F92*D92*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H92" s="18">
@@ -12437,7 +12762,7 @@
         <v>0.4</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>0.1075</v>
+        <v>0.1295</v>
       </c>
       <c r="L92" s="21">
         <f>DATOS!$B$12*K92</f>
@@ -12464,7 +12789,7 @@
         <v/>
       </c>
       <c r="R92" s="25" t="n">
-        <v>0.0973</v>
+        <v>0.117</v>
       </c>
       <c r="S92" s="26">
         <f>G92/(DATOS!$B$12*R92)</f>
@@ -12495,14 +12820,14 @@
         <v>91</v>
       </c>
       <c r="E93" s="25" t="n">
-        <v>0.664</v>
+        <v>0.822</v>
       </c>
       <c r="F93" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G93" s="21">
-        <f>E93*F93*D93*DATOS!$B$21/3600000</f>
+        <f>E93*F93*D93*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H93" s="18">
@@ -12516,7 +12841,7 @@
         <v>0.3</v>
       </c>
       <c r="K93" s="25" t="n">
-        <v>0.0323</v>
+        <v>0.0369</v>
       </c>
       <c r="L93" s="21">
         <f>DATOS!$B$12*K93</f>
@@ -12543,7 +12868,7 @@
         <v/>
       </c>
       <c r="R93" s="25" t="n">
-        <v>0.0295</v>
+        <v>0.0337</v>
       </c>
       <c r="S93" s="26">
         <f>G93/(DATOS!$B$12*R93)</f>
@@ -12574,14 +12899,14 @@
         <v>92</v>
       </c>
       <c r="E94" s="25" t="n">
-        <v>0.661</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="F94" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G94" s="21">
-        <f>E94*F94*D94*DATOS!$B$21/3600000</f>
+        <f>E94*F94*D94*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H94" s="18">
@@ -12595,7 +12920,7 @@
         <v>0.36</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0.0323</v>
+        <v>0.0369</v>
       </c>
       <c r="L94" s="21">
         <f>DATOS!$B$12*K94</f>
@@ -12622,7 +12947,7 @@
         <v/>
       </c>
       <c r="R94" s="25" t="n">
-        <v>0.0295</v>
+        <v>0.0337</v>
       </c>
       <c r="S94" s="26">
         <f>G94/(DATOS!$B$12*R94)</f>
@@ -12653,14 +12978,14 @@
         <v>251</v>
       </c>
       <c r="E95" s="25" t="n">
-        <v>0.496</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F95" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G95" s="21">
-        <f>E95*F95*D95*DATOS!$B$21/3600000</f>
+        <f>E95*F95*D95*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H95" s="18">
@@ -12674,7 +12999,7 @@
         <v>0.36</v>
       </c>
       <c r="K95" s="25" t="n">
-        <v>0.0514</v>
+        <v>0.0711</v>
       </c>
       <c r="L95" s="21">
         <f>DATOS!$B$12*K95</f>
@@ -12701,7 +13026,7 @@
         <v/>
       </c>
       <c r="R95" s="25" t="n">
-        <v>0.0468</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="S95" s="26">
         <f>G95/(DATOS!$B$12*R95)</f>
@@ -12732,14 +13057,14 @@
         <v>251</v>
       </c>
       <c r="E96" s="25" t="n">
-        <v>0.496</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F96" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G96" s="21">
-        <f>E96*F96*D96*DATOS!$B$21/3600000</f>
+        <f>E96*F96*D96*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H96" s="18">
@@ -12753,7 +13078,7 @@
         <v>0.48</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0.0514</v>
+        <v>0.0711</v>
       </c>
       <c r="L96" s="21">
         <f>DATOS!$B$12*K96</f>
@@ -12780,7 +13105,7 @@
         <v/>
       </c>
       <c r="R96" s="25" t="n">
-        <v>0.0468</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="S96" s="26">
         <f>G96/(DATOS!$B$12*R96)</f>
@@ -12811,14 +13136,14 @@
         <v>364</v>
       </c>
       <c r="E97" s="25" t="n">
-        <v>0.466</v>
+        <v>0.775</v>
       </c>
       <c r="F97" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G97" s="21">
-        <f>E97*F97*D97*DATOS!$B$21/3600000</f>
+        <f>E97*F97*D97*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H97" s="18">
@@ -12832,7 +13157,7 @@
         <v>0.49</v>
       </c>
       <c r="K97" s="25" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0886</v>
       </c>
       <c r="L97" s="21">
         <f>DATOS!$B$12*K97</f>
@@ -12859,7 +13184,7 @@
         <v/>
       </c>
       <c r="R97" s="25" t="n">
-        <v>0.0571</v>
+        <v>0.0804</v>
       </c>
       <c r="S97" s="26">
         <f>G97/(DATOS!$B$12*R97)</f>
@@ -12890,14 +13215,14 @@
         <v>109</v>
       </c>
       <c r="E98" s="25" t="n">
-        <v>0.4</v>
+        <v>0.704</v>
       </c>
       <c r="F98" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G98" s="21">
-        <f>E98*F98*D98*DATOS!$B$21/3600000</f>
+        <f>E98*F98*D98*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H98" s="18">
@@ -12911,7 +13236,7 @@
         <v>0.3</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>0.0261</v>
+        <v>0.0376</v>
       </c>
       <c r="L98" s="21">
         <f>DATOS!$B$12*K98</f>
@@ -12938,7 +13263,7 @@
         <v/>
       </c>
       <c r="R98" s="25" t="n">
-        <v>0.0239</v>
+        <v>0.0343</v>
       </c>
       <c r="S98" s="26">
         <f>G98/(DATOS!$B$12*R98)</f>
@@ -12969,14 +13294,14 @@
         <v>109</v>
       </c>
       <c r="E99" s="25" t="n">
-        <v>0.4</v>
+        <v>0.704</v>
       </c>
       <c r="F99" s="26">
         <f>DATOS!$B$17</f>
         <v/>
       </c>
       <c r="G99" s="21">
-        <f>E99*F99*D99*DATOS!$B$21/3600000</f>
+        <f>E99*F99*D99*DATOS!$B$22/3600000</f>
         <v/>
       </c>
       <c r="H99" s="18">
@@ -12990,7 +13315,7 @@
         <v>0.37</v>
       </c>
       <c r="K99" s="25" t="n">
-        <v>0.0261</v>
+        <v>0.0376</v>
       </c>
       <c r="L99" s="21">
         <f>DATOS!$B$12*K99</f>
@@ -13017,7 +13342,7 @@
         <v/>
       </c>
       <c r="R99" s="25" t="n">
-        <v>0.0239</v>
+        <v>0.0343</v>
       </c>
       <c r="S99" s="26">
         <f>G99/(DATOS!$B$12*R99)</f>

--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -24,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -107,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,16 +139,18 @@
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -586,7 +589,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Gumbel (menor D de Kolmogorov-Smirnov)</t>
+          <t>Log-Pearson III (menor D de Kolmogorov-Smirnov)</t>
         </is>
       </c>
     </row>
@@ -934,7 +937,7 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Hoja FRECUENCIAS (Gumbel)</t>
+          <t>Hoja FRECUENCIAS (Log-Pearson III)</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2713,7 +2716,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>DISEÑO (Gumbel)</t>
+          <t>DISEÑO (Log-Pearson III)</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2725,7 @@
         <v>2</v>
       </c>
       <c r="B17" s="25">
-        <f>NORMSINV(1-1/A17)</f>
+        <f>SQRT(LN(A17^2))-(2.515517+0.802853*SQRT(LN(A17^2))+0.010328*SQRT(LN(A17^2))^2)/(1+1.432788*SQRT(LN(A17^2))+0.189269*SQRT(LN(A17^2))^2+0.001308*SQRT(LN(A17^2))^3)</f>
         <v/>
       </c>
       <c r="C17" s="26">
@@ -2734,7 +2737,7 @@
         <v/>
       </c>
       <c r="E17" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B17-($B$11/6)^2)^3-1)</f>
+        <f>B17+(B17^2-1)*($B$11/6)+1/3*(B17^3-6*B17)*($B$11/6)^2-(B17^2-1)*($B$11/6)^3+B17*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F17" s="26">
@@ -2750,7 +2753,7 @@
         <v/>
       </c>
       <c r="I17" s="20">
-        <f>H17</f>
+        <f>F17</f>
         <v/>
       </c>
     </row>
@@ -2759,7 +2762,7 @@
         <v>5</v>
       </c>
       <c r="B18" s="25">
-        <f>NORMSINV(1-1/A18)</f>
+        <f>SQRT(LN(A18^2))-(2.515517+0.802853*SQRT(LN(A18^2))+0.010328*SQRT(LN(A18^2))^2)/(1+1.432788*SQRT(LN(A18^2))+0.189269*SQRT(LN(A18^2))^2+0.001308*SQRT(LN(A18^2))^3)</f>
         <v/>
       </c>
       <c r="C18" s="26">
@@ -2771,7 +2774,7 @@
         <v/>
       </c>
       <c r="E18" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B18-($B$11/6)^2)^3-1)</f>
+        <f>B18+(B18^2-1)*($B$11/6)+1/3*(B18^3-6*B18)*($B$11/6)^2-(B18^2-1)*($B$11/6)^3+B18*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F18" s="26">
@@ -2787,7 +2790,7 @@
         <v/>
       </c>
       <c r="I18" s="20">
-        <f>H18</f>
+        <f>F18</f>
         <v/>
       </c>
     </row>
@@ -2796,7 +2799,7 @@
         <v>10</v>
       </c>
       <c r="B19" s="25">
-        <f>NORMSINV(1-1/A19)</f>
+        <f>SQRT(LN(A19^2))-(2.515517+0.802853*SQRT(LN(A19^2))+0.010328*SQRT(LN(A19^2))^2)/(1+1.432788*SQRT(LN(A19^2))+0.189269*SQRT(LN(A19^2))^2+0.001308*SQRT(LN(A19^2))^3)</f>
         <v/>
       </c>
       <c r="C19" s="26">
@@ -2808,7 +2811,7 @@
         <v/>
       </c>
       <c r="E19" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B19-($B$11/6)^2)^3-1)</f>
+        <f>B19+(B19^2-1)*($B$11/6)+1/3*(B19^3-6*B19)*($B$11/6)^2-(B19^2-1)*($B$11/6)^3+B19*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F19" s="26">
@@ -2824,7 +2827,7 @@
         <v/>
       </c>
       <c r="I19" s="20">
-        <f>H19</f>
+        <f>F19</f>
         <v/>
       </c>
     </row>
@@ -2833,7 +2836,7 @@
         <v>20</v>
       </c>
       <c r="B20" s="25">
-        <f>NORMSINV(1-1/A20)</f>
+        <f>SQRT(LN(A20^2))-(2.515517+0.802853*SQRT(LN(A20^2))+0.010328*SQRT(LN(A20^2))^2)/(1+1.432788*SQRT(LN(A20^2))+0.189269*SQRT(LN(A20^2))^2+0.001308*SQRT(LN(A20^2))^3)</f>
         <v/>
       </c>
       <c r="C20" s="26">
@@ -2845,7 +2848,7 @@
         <v/>
       </c>
       <c r="E20" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B20-($B$11/6)^2)^3-1)</f>
+        <f>B20+(B20^2-1)*($B$11/6)+1/3*(B20^3-6*B20)*($B$11/6)^2-(B20^2-1)*($B$11/6)^3+B20*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F20" s="26">
@@ -2861,7 +2864,7 @@
         <v/>
       </c>
       <c r="I20" s="20">
-        <f>H20</f>
+        <f>F20</f>
         <v/>
       </c>
     </row>
@@ -2870,7 +2873,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="25">
-        <f>NORMSINV(1-1/A21)</f>
+        <f>SQRT(LN(A21^2))-(2.515517+0.802853*SQRT(LN(A21^2))+0.010328*SQRT(LN(A21^2))^2)/(1+1.432788*SQRT(LN(A21^2))+0.189269*SQRT(LN(A21^2))^2+0.001308*SQRT(LN(A21^2))^3)</f>
         <v/>
       </c>
       <c r="C21" s="26">
@@ -2882,7 +2885,7 @@
         <v/>
       </c>
       <c r="E21" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B21-($B$11/6)^2)^3-1)</f>
+        <f>B21+(B21^2-1)*($B$11/6)+1/3*(B21^3-6*B21)*($B$11/6)^2-(B21^2-1)*($B$11/6)^3+B21*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F21" s="26">
@@ -2898,7 +2901,7 @@
         <v/>
       </c>
       <c r="I21" s="20">
-        <f>H21</f>
+        <f>F21</f>
         <v/>
       </c>
     </row>
@@ -2907,7 +2910,7 @@
         <v>50</v>
       </c>
       <c r="B22" s="25">
-        <f>NORMSINV(1-1/A22)</f>
+        <f>SQRT(LN(A22^2))-(2.515517+0.802853*SQRT(LN(A22^2))+0.010328*SQRT(LN(A22^2))^2)/(1+1.432788*SQRT(LN(A22^2))+0.189269*SQRT(LN(A22^2))^2+0.001308*SQRT(LN(A22^2))^3)</f>
         <v/>
       </c>
       <c r="C22" s="26">
@@ -2919,7 +2922,7 @@
         <v/>
       </c>
       <c r="E22" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B22-($B$11/6)^2)^3-1)</f>
+        <f>B22+(B22^2-1)*($B$11/6)+1/3*(B22^3-6*B22)*($B$11/6)^2-(B22^2-1)*($B$11/6)^3+B22*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F22" s="26">
@@ -2935,7 +2938,7 @@
         <v/>
       </c>
       <c r="I22" s="20">
-        <f>H22</f>
+        <f>F22</f>
         <v/>
       </c>
     </row>
@@ -2944,7 +2947,7 @@
         <v>100</v>
       </c>
       <c r="B23" s="25">
-        <f>NORMSINV(1-1/A23)</f>
+        <f>SQRT(LN(A23^2))-(2.515517+0.802853*SQRT(LN(A23^2))+0.010328*SQRT(LN(A23^2))^2)/(1+1.432788*SQRT(LN(A23^2))+0.189269*SQRT(LN(A23^2))^2+0.001308*SQRT(LN(A23^2))^3)</f>
         <v/>
       </c>
       <c r="C23" s="26">
@@ -2956,7 +2959,7 @@
         <v/>
       </c>
       <c r="E23" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B23-($B$11/6)^2)^3-1)</f>
+        <f>B23+(B23^2-1)*($B$11/6)+1/3*(B23^3-6*B23)*($B$11/6)^2-(B23^2-1)*($B$11/6)^3+B23*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F23" s="26">
@@ -2972,7 +2975,7 @@
         <v/>
       </c>
       <c r="I23" s="20">
-        <f>H23</f>
+        <f>F23</f>
         <v/>
       </c>
     </row>
@@ -2981,7 +2984,7 @@
         <v>200</v>
       </c>
       <c r="B24" s="25">
-        <f>NORMSINV(1-1/A24)</f>
+        <f>SQRT(LN(A24^2))-(2.515517+0.802853*SQRT(LN(A24^2))+0.010328*SQRT(LN(A24^2))^2)/(1+1.432788*SQRT(LN(A24^2))+0.189269*SQRT(LN(A24^2))^2+0.001308*SQRT(LN(A24^2))^3)</f>
         <v/>
       </c>
       <c r="C24" s="26">
@@ -2993,7 +2996,7 @@
         <v/>
       </c>
       <c r="E24" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B24-($B$11/6)^2)^3-1)</f>
+        <f>B24+(B24^2-1)*($B$11/6)+1/3*(B24^3-6*B24)*($B$11/6)^2-(B24^2-1)*($B$11/6)^3+B24*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F24" s="26">
@@ -3009,7 +3012,7 @@
         <v/>
       </c>
       <c r="I24" s="20">
-        <f>H24</f>
+        <f>F24</f>
         <v/>
       </c>
     </row>
@@ -3018,7 +3021,7 @@
         <v>500</v>
       </c>
       <c r="B25" s="25">
-        <f>NORMSINV(1-1/A25)</f>
+        <f>SQRT(LN(A25^2))-(2.515517+0.802853*SQRT(LN(A25^2))+0.010328*SQRT(LN(A25^2))^2)/(1+1.432788*SQRT(LN(A25^2))+0.189269*SQRT(LN(A25^2))^2+0.001308*SQRT(LN(A25^2))^3)</f>
         <v/>
       </c>
       <c r="C25" s="26">
@@ -3030,7 +3033,7 @@
         <v/>
       </c>
       <c r="E25" s="25">
-        <f>(2/$B$11)*((1+$B$11/6*B25-($B$11/6)^2)^3-1)</f>
+        <f>B25+(B25^2-1)*($B$11/6)+1/3*(B25^3-6*B25)*($B$11/6)^2-(B25^2-1)*($B$11/6)^3+B25*($B$11/6)^4+1/3*($B$11/6)^5</f>
         <v/>
       </c>
       <c r="F25" s="26">
@@ -3046,14 +3049,21 @@
         <v/>
       </c>
       <c r="I25" s="20">
-        <f>H25</f>
+        <f>F25</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Se adopta la distribucion Gumbel: menor estadistico de Kolmogorov-Smirnov (hoja KS).</t>
+          <t>Se adopta la distribucion Log-Pearson III: menor estadistico de Kolmogorov-Smirnov (hoja KS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>z por la aproximacion de Abramowitz y Stegun; KT de Log Pearson III por la expresion de Kite (k = Cs/6); mismos calculos de la hoja ANALISIS_ESTADISTICO_IE0590_BARRANQUITA.xlsx.</t>
         </is>
       </c>
     </row>
@@ -3069,20 +3079,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3114,32 +3126,32 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>P ordenada (mm)</t>
+          <t>P ordenada de mayor a menor (mm)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>F empirica m/(n+1)</t>
+          <t>P(X&gt;=x) observada m/(n+1)</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>F Normal</t>
+          <t>P teorica Normal</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>F Log-Normal</t>
+          <t>P teorica Log-Normal</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>F Log-Pearson III</t>
+          <t>P teorica Log-Pearson III</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>F Gumbel</t>
+          <t>P teorica Gumbel</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
@@ -3168,42 +3180,52 @@
         <v>1</v>
       </c>
       <c r="B9" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A9)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A9)</f>
         <v/>
       </c>
       <c r="C9" s="21">
-        <f>A9/(FRECUENCIAS!$B$5+1)</f>
+        <f>A9/($N$9+1)</f>
         <v/>
       </c>
       <c r="D9" s="21">
-        <f>NORMDIST(B9,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B9-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E9" s="21">
-        <f>NORMDIST(LOG10(B9),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>0.052148</v>
+        <f>1-NORMSDIST((LOG10(B9)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F9" s="21">
+        <f>CHIDIST(2*(LN(B9)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G9" s="21">
-        <f>EXP(-EXP(-(B9-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B9-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H9" s="21">
-        <f>ABS(C9-D9)</f>
+        <f>ABS(D9-C9)</f>
         <v/>
       </c>
       <c r="I9" s="21">
-        <f>ABS(C9-E9)</f>
+        <f>ABS(E9-C9)</f>
         <v/>
       </c>
       <c r="J9" s="21">
-        <f>ABS(C9-F9)</f>
+        <f>ABS(F9-C9)</f>
         <v/>
       </c>
       <c r="K9" s="21">
-        <f>ABS(C9-G9)</f>
+        <f>ABS(G9-C9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="N9" s="28">
+        <f>COUNT(SERIE!$O$11:$O$35)</f>
         <v/>
       </c>
     </row>
@@ -3212,43 +3234,52 @@
         <v>2</v>
       </c>
       <c r="B10" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A10)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A10)</f>
         <v/>
       </c>
       <c r="C10" s="21">
-        <f>A10/(FRECUENCIAS!$B$5+1)</f>
+        <f>A10/($N$9+1)</f>
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>NORMDIST(B10,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B10-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E10" s="21">
-        <f>NORMDIST(LOG10(B10),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0.058865</v>
+        <f>1-NORMSDIST((LOG10(B10)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>CHIDIST(2*(LN(B10)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G10" s="21">
-        <f>EXP(-EXP(-(B10-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B10-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H10" s="21">
-        <f>ABS(C10-D10)</f>
+        <f>ABS(D10-C10)</f>
         <v/>
       </c>
       <c r="I10" s="21">
-        <f>ABS(C10-E10)</f>
+        <f>ABS(E10-C10)</f>
         <v/>
       </c>
       <c r="J10" s="21">
-        <f>ABS(C10-F10)</f>
+        <f>ABS(F10-C10)</f>
         <v/>
       </c>
       <c r="K10" s="21">
-        <f>ABS(C10-G10)</f>
-        <v/>
+        <f>ABS(G10-C10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>media ln P</t>
+        </is>
+      </c>
+      <c r="N10" s="29" t="n">
+        <v>4.676233482163762</v>
       </c>
     </row>
     <row r="11">
@@ -3256,43 +3287,52 @@
         <v>3</v>
       </c>
       <c r="B11" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A11)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A11)</f>
         <v/>
       </c>
       <c r="C11" s="21">
-        <f>A11/(FRECUENCIAS!$B$5+1)</f>
+        <f>A11/($N$9+1)</f>
         <v/>
       </c>
       <c r="D11" s="21">
-        <f>NORMDIST(B11,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B11-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E11" s="21">
-        <f>NORMDIST(LOG10(B11),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>0.134433</v>
+        <f>1-NORMSDIST((LOG10(B11)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="21">
+        <f>CHIDIST(2*(LN(B11)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G11" s="21">
-        <f>EXP(-EXP(-(B11-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B11-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H11" s="21">
-        <f>ABS(C11-D11)</f>
+        <f>ABS(D11-C11)</f>
         <v/>
       </c>
       <c r="I11" s="21">
-        <f>ABS(C11-E11)</f>
+        <f>ABS(E11-C11)</f>
         <v/>
       </c>
       <c r="J11" s="21">
-        <f>ABS(C11-F11)</f>
+        <f>ABS(F11-C11)</f>
         <v/>
       </c>
       <c r="K11" s="21">
-        <f>ABS(C11-G11)</f>
-        <v/>
+        <f>ABS(G11-C11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>desv. ln P</t>
+        </is>
+      </c>
+      <c r="N11" s="29" t="n">
+        <v>0.2320139222017669</v>
       </c>
     </row>
     <row r="12">
@@ -3300,43 +3340,52 @@
         <v>4</v>
       </c>
       <c r="B12" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A12)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A12)</f>
         <v/>
       </c>
       <c r="C12" s="21">
-        <f>A12/(FRECUENCIAS!$B$5+1)</f>
+        <f>A12/($N$9+1)</f>
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>NORMDIST(B12,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B12-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E12" s="21">
-        <f>NORMDIST(LOG10(B12),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.137447</v>
+        <f>1-NORMSDIST((LOG10(B12)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>CHIDIST(2*(LN(B12)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G12" s="21">
-        <f>EXP(-EXP(-(B12-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B12-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H12" s="21">
-        <f>ABS(C12-D12)</f>
+        <f>ABS(D12-C12)</f>
         <v/>
       </c>
       <c r="I12" s="21">
-        <f>ABS(C12-E12)</f>
+        <f>ABS(E12-C12)</f>
         <v/>
       </c>
       <c r="J12" s="21">
-        <f>ABS(C12-F12)</f>
+        <f>ABS(F12-C12)</f>
         <v/>
       </c>
       <c r="K12" s="21">
-        <f>ABS(C12-G12)</f>
-        <v/>
+        <f>ABS(G12-C12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Cs ln P</t>
+        </is>
+      </c>
+      <c r="N12" s="29" t="n">
+        <v>0.6858110029244965</v>
       </c>
     </row>
     <row r="13">
@@ -3344,42 +3393,52 @@
         <v>5</v>
       </c>
       <c r="B13" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A13)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A13)</f>
         <v/>
       </c>
       <c r="C13" s="21">
-        <f>A13/(FRECUENCIAS!$B$5+1)</f>
+        <f>A13/($N$9+1)</f>
         <v/>
       </c>
       <c r="D13" s="21">
-        <f>NORMDIST(B13,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B13-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E13" s="21">
-        <f>NORMDIST(LOG10(B13),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>0.18227</v>
+        <f>1-NORMSDIST((LOG10(B13)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F13" s="21">
+        <f>CHIDIST(2*(LN(B13)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G13" s="21">
-        <f>EXP(-EXP(-(B13-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B13-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H13" s="21">
-        <f>ABS(C13-D13)</f>
+        <f>ABS(D13-C13)</f>
         <v/>
       </c>
       <c r="I13" s="21">
-        <f>ABS(C13-E13)</f>
+        <f>ABS(E13-C13)</f>
         <v/>
       </c>
       <c r="J13" s="21">
-        <f>ABS(C13-F13)</f>
+        <f>ABS(F13-C13)</f>
         <v/>
       </c>
       <c r="K13" s="21">
-        <f>ABS(C13-G13)</f>
+        <f>ABS(G13-C13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>beta = (2/Cs)^2</t>
+        </is>
+      </c>
+      <c r="N13" s="29">
+        <f>(2/N12)^2</f>
         <v/>
       </c>
     </row>
@@ -3388,42 +3447,52 @@
         <v>6</v>
       </c>
       <c r="B14" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A14)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A14)</f>
         <v/>
       </c>
       <c r="C14" s="21">
-        <f>A14/(FRECUENCIAS!$B$5+1)</f>
+        <f>A14/($N$9+1)</f>
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>NORMDIST(B14,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B14-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E14" s="21">
-        <f>NORMDIST(LOG10(B14),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>0.211482</v>
+        <f>1-NORMSDIST((LOG10(B14)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>CHIDIST(2*(LN(B14)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G14" s="21">
-        <f>EXP(-EXP(-(B14-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B14-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H14" s="21">
-        <f>ABS(C14-D14)</f>
+        <f>ABS(D14-C14)</f>
         <v/>
       </c>
       <c r="I14" s="21">
-        <f>ABS(C14-E14)</f>
+        <f>ABS(E14-C14)</f>
         <v/>
       </c>
       <c r="J14" s="21">
-        <f>ABS(C14-F14)</f>
+        <f>ABS(F14-C14)</f>
         <v/>
       </c>
       <c r="K14" s="21">
-        <f>ABS(C14-G14)</f>
+        <f>ABS(G14-C14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>alfa = s/raiz(beta)</t>
+        </is>
+      </c>
+      <c r="N14" s="30">
+        <f>N11/SQRT(N13)</f>
         <v/>
       </c>
     </row>
@@ -3432,42 +3501,52 @@
         <v>7</v>
       </c>
       <c r="B15" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A15)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A15)</f>
         <v/>
       </c>
       <c r="C15" s="21">
-        <f>A15/(FRECUENCIAS!$B$5+1)</f>
+        <f>A15/($N$9+1)</f>
         <v/>
       </c>
       <c r="D15" s="21">
-        <f>NORMDIST(B15,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B15-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E15" s="21">
-        <f>NORMDIST(LOG10(B15),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.218529</v>
+        <f>1-NORMSDIST((LOG10(B15)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F15" s="21">
+        <f>CHIDIST(2*(LN(B15)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G15" s="21">
-        <f>EXP(-EXP(-(B15-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B15-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H15" s="21">
-        <f>ABS(C15-D15)</f>
+        <f>ABS(D15-C15)</f>
         <v/>
       </c>
       <c r="I15" s="21">
-        <f>ABS(C15-E15)</f>
+        <f>ABS(E15-C15)</f>
         <v/>
       </c>
       <c r="J15" s="21">
-        <f>ABS(C15-F15)</f>
+        <f>ABS(F15-C15)</f>
         <v/>
       </c>
       <c r="K15" s="21">
-        <f>ABS(C15-G15)</f>
+        <f>ABS(G15-C15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>delta = media - alfa beta</t>
+        </is>
+      </c>
+      <c r="N15" s="29">
+        <f>N10-N14*N13</f>
         <v/>
       </c>
     </row>
@@ -3476,43 +3555,52 @@
         <v>8</v>
       </c>
       <c r="B16" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A16)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A16)</f>
         <v/>
       </c>
       <c r="C16" s="21">
-        <f>A16/(FRECUENCIAS!$B$5+1)</f>
+        <f>A16/($N$9+1)</f>
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>NORMDIST(B16,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B16-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>NORMDIST(LOG10(B16),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>0.238188</v>
+        <f>1-NORMSDIST((LOG10(B16)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>CHIDIST(2*(LN(B16)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G16" s="21">
-        <f>EXP(-EXP(-(B16-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B16-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H16" s="21">
-        <f>ABS(C16-D16)</f>
+        <f>ABS(D16-C16)</f>
         <v/>
       </c>
       <c r="I16" s="21">
-        <f>ABS(C16-E16)</f>
+        <f>ABS(E16-C16)</f>
         <v/>
       </c>
       <c r="J16" s="21">
-        <f>ABS(C16-F16)</f>
+        <f>ABS(F16-C16)</f>
         <v/>
       </c>
       <c r="K16" s="21">
-        <f>ABS(C16-G16)</f>
-        <v/>
+        <f>ABS(G16-C16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Gumbel: media yn (Aparicio, n = 25)</t>
+        </is>
+      </c>
+      <c r="N16" s="29" t="n">
+        <v>0.5309</v>
       </c>
     </row>
     <row r="17">
@@ -3520,43 +3608,52 @@
         <v>9</v>
       </c>
       <c r="B17" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A17)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A17)</f>
         <v/>
       </c>
       <c r="C17" s="21">
-        <f>A17/(FRECUENCIAS!$B$5+1)</f>
+        <f>A17/($N$9+1)</f>
         <v/>
       </c>
       <c r="D17" s="21">
-        <f>NORMDIST(B17,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B17-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E17" s="21">
-        <f>NORMDIST(LOG10(B17),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>0.353051</v>
+        <f>1-NORMSDIST((LOG10(B17)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F17" s="21">
+        <f>CHIDIST(2*(LN(B17)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G17" s="21">
-        <f>EXP(-EXP(-(B17-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B17-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H17" s="21">
-        <f>ABS(C17-D17)</f>
+        <f>ABS(D17-C17)</f>
         <v/>
       </c>
       <c r="I17" s="21">
-        <f>ABS(C17-E17)</f>
+        <f>ABS(E17-C17)</f>
         <v/>
       </c>
       <c r="J17" s="21">
-        <f>ABS(C17-F17)</f>
+        <f>ABS(F17-C17)</f>
         <v/>
       </c>
       <c r="K17" s="21">
-        <f>ABS(C17-G17)</f>
-        <v/>
+        <f>ABS(G17-C17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Gumbel: desviacion sn</t>
+        </is>
+      </c>
+      <c r="N17" s="29" t="n">
+        <v>1.0914</v>
       </c>
     </row>
     <row r="18">
@@ -3564,42 +3661,52 @@
         <v>10</v>
       </c>
       <c r="B18" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A18)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A18)</f>
         <v/>
       </c>
       <c r="C18" s="21">
-        <f>A18/(FRECUENCIAS!$B$5+1)</f>
+        <f>A18/($N$9+1)</f>
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>NORMDIST(B18,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B18-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E18" s="21">
-        <f>NORMDIST(LOG10(B18),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>0.369802</v>
+        <f>1-NORMSDIST((LOG10(B18)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>CHIDIST(2*(LN(B18)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G18" s="21">
-        <f>EXP(-EXP(-(B18-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B18-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H18" s="21">
-        <f>ABS(C18-D18)</f>
+        <f>ABS(D18-C18)</f>
         <v/>
       </c>
       <c r="I18" s="21">
-        <f>ABS(C18-E18)</f>
+        <f>ABS(E18-C18)</f>
         <v/>
       </c>
       <c r="J18" s="21">
-        <f>ABS(C18-F18)</f>
+        <f>ABS(F18-C18)</f>
         <v/>
       </c>
       <c r="K18" s="21">
-        <f>ABS(C18-G18)</f>
+        <f>ABS(G18-C18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>D critico (alfa 0.05)</t>
+        </is>
+      </c>
+      <c r="N18" s="29">
+        <f>SQRT(-LN(0.05/2)/(2*N9))-1/(6*N9)</f>
         <v/>
       </c>
     </row>
@@ -3608,42 +3715,43 @@
         <v>11</v>
       </c>
       <c r="B19" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A19)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A19)</f>
         <v/>
       </c>
       <c r="C19" s="21">
-        <f>A19/(FRECUENCIAS!$B$5+1)</f>
+        <f>A19/($N$9+1)</f>
         <v/>
       </c>
       <c r="D19" s="21">
-        <f>NORMDIST(B19,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B19-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E19" s="21">
-        <f>NORMDIST(LOG10(B19),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>0.426655</v>
+        <f>1-NORMSDIST((LOG10(B19)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F19" s="21">
+        <f>CHIDIST(2*(LN(B19)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G19" s="21">
-        <f>EXP(-EXP(-(B19-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B19-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H19" s="21">
-        <f>ABS(C19-D19)</f>
+        <f>ABS(D19-C19)</f>
         <v/>
       </c>
       <c r="I19" s="21">
-        <f>ABS(C19-E19)</f>
+        <f>ABS(E19-C19)</f>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f>ABS(C19-F19)</f>
+        <f>ABS(F19-C19)</f>
         <v/>
       </c>
       <c r="K19" s="21">
-        <f>ABS(C19-G19)</f>
+        <f>ABS(G19-C19)</f>
         <v/>
       </c>
     </row>
@@ -3652,42 +3760,43 @@
         <v>12</v>
       </c>
       <c r="B20" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A20)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A20)</f>
         <v/>
       </c>
       <c r="C20" s="21">
-        <f>A20/(FRECUENCIAS!$B$5+1)</f>
+        <f>A20/($N$9+1)</f>
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>NORMDIST(B20,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B20-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E20" s="21">
-        <f>NORMDIST(LOG10(B20),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>0.437443</v>
+        <f>1-NORMSDIST((LOG10(B20)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>CHIDIST(2*(LN(B20)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G20" s="21">
-        <f>EXP(-EXP(-(B20-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B20-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H20" s="21">
-        <f>ABS(C20-D20)</f>
+        <f>ABS(D20-C20)</f>
         <v/>
       </c>
       <c r="I20" s="21">
-        <f>ABS(C20-E20)</f>
+        <f>ABS(E20-C20)</f>
         <v/>
       </c>
       <c r="J20" s="21">
-        <f>ABS(C20-F20)</f>
+        <f>ABS(F20-C20)</f>
         <v/>
       </c>
       <c r="K20" s="21">
-        <f>ABS(C20-G20)</f>
+        <f>ABS(G20-C20)</f>
         <v/>
       </c>
     </row>
@@ -3696,42 +3805,43 @@
         <v>13</v>
       </c>
       <c r="B21" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A21)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A21)</f>
         <v/>
       </c>
       <c r="C21" s="21">
-        <f>A21/(FRECUENCIAS!$B$5+1)</f>
+        <f>A21/($N$9+1)</f>
         <v/>
       </c>
       <c r="D21" s="21">
-        <f>NORMDIST(B21,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B21-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E21" s="21">
-        <f>NORMDIST(LOG10(B21),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F21" s="21" t="n">
-        <v>0.464021</v>
+        <f>1-NORMSDIST((LOG10(B21)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F21" s="21">
+        <f>CHIDIST(2*(LN(B21)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G21" s="21">
-        <f>EXP(-EXP(-(B21-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B21-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H21" s="21">
-        <f>ABS(C21-D21)</f>
+        <f>ABS(D21-C21)</f>
         <v/>
       </c>
       <c r="I21" s="21">
-        <f>ABS(C21-E21)</f>
+        <f>ABS(E21-C21)</f>
         <v/>
       </c>
       <c r="J21" s="21">
-        <f>ABS(C21-F21)</f>
+        <f>ABS(F21-C21)</f>
         <v/>
       </c>
       <c r="K21" s="21">
-        <f>ABS(C21-G21)</f>
+        <f>ABS(G21-C21)</f>
         <v/>
       </c>
     </row>
@@ -3740,42 +3850,43 @@
         <v>14</v>
       </c>
       <c r="B22" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A22)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A22)</f>
         <v/>
       </c>
       <c r="C22" s="21">
-        <f>A22/(FRECUENCIAS!$B$5+1)</f>
+        <f>A22/($N$9+1)</f>
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>NORMDIST(B22,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B22-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E22" s="21">
-        <f>NORMDIST(LOG10(B22),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F22" s="21" t="n">
-        <v>0.488258</v>
+        <f>1-NORMSDIST((LOG10(B22)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>CHIDIST(2*(LN(B22)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G22" s="21">
-        <f>EXP(-EXP(-(B22-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B22-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H22" s="21">
-        <f>ABS(C22-D22)</f>
+        <f>ABS(D22-C22)</f>
         <v/>
       </c>
       <c r="I22" s="21">
-        <f>ABS(C22-E22)</f>
+        <f>ABS(E22-C22)</f>
         <v/>
       </c>
       <c r="J22" s="21">
-        <f>ABS(C22-F22)</f>
+        <f>ABS(F22-C22)</f>
         <v/>
       </c>
       <c r="K22" s="21">
-        <f>ABS(C22-G22)</f>
+        <f>ABS(G22-C22)</f>
         <v/>
       </c>
     </row>
@@ -3784,42 +3895,43 @@
         <v>15</v>
       </c>
       <c r="B23" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A23)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A23)</f>
         <v/>
       </c>
       <c r="C23" s="21">
-        <f>A23/(FRECUENCIAS!$B$5+1)</f>
+        <f>A23/($N$9+1)</f>
         <v/>
       </c>
       <c r="D23" s="21">
-        <f>NORMDIST(B23,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B23-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E23" s="21">
-        <f>NORMDIST(LOG10(B23),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F23" s="21" t="n">
-        <v>0.563322</v>
+        <f>1-NORMSDIST((LOG10(B23)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F23" s="21">
+        <f>CHIDIST(2*(LN(B23)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G23" s="21">
-        <f>EXP(-EXP(-(B23-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B23-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H23" s="21">
-        <f>ABS(C23-D23)</f>
+        <f>ABS(D23-C23)</f>
         <v/>
       </c>
       <c r="I23" s="21">
-        <f>ABS(C23-E23)</f>
+        <f>ABS(E23-C23)</f>
         <v/>
       </c>
       <c r="J23" s="21">
-        <f>ABS(C23-F23)</f>
+        <f>ABS(F23-C23)</f>
         <v/>
       </c>
       <c r="K23" s="21">
-        <f>ABS(C23-G23)</f>
+        <f>ABS(G23-C23)</f>
         <v/>
       </c>
     </row>
@@ -3828,42 +3940,43 @@
         <v>16</v>
       </c>
       <c r="B24" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A24)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A24)</f>
         <v/>
       </c>
       <c r="C24" s="21">
-        <f>A24/(FRECUENCIAS!$B$5+1)</f>
+        <f>A24/($N$9+1)</f>
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>NORMDIST(B24,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B24-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E24" s="21">
-        <f>NORMDIST(LOG10(B24),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F24" s="21" t="n">
-        <v>0.589098</v>
+        <f>1-NORMSDIST((LOG10(B24)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>CHIDIST(2*(LN(B24)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G24" s="21">
-        <f>EXP(-EXP(-(B24-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B24-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H24" s="21">
-        <f>ABS(C24-D24)</f>
+        <f>ABS(D24-C24)</f>
         <v/>
       </c>
       <c r="I24" s="21">
-        <f>ABS(C24-E24)</f>
+        <f>ABS(E24-C24)</f>
         <v/>
       </c>
       <c r="J24" s="21">
-        <f>ABS(C24-F24)</f>
+        <f>ABS(F24-C24)</f>
         <v/>
       </c>
       <c r="K24" s="21">
-        <f>ABS(C24-G24)</f>
+        <f>ABS(G24-C24)</f>
         <v/>
       </c>
     </row>
@@ -3872,42 +3985,43 @@
         <v>17</v>
       </c>
       <c r="B25" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A25)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A25)</f>
         <v/>
       </c>
       <c r="C25" s="21">
-        <f>A25/(FRECUENCIAS!$B$5+1)</f>
+        <f>A25/($N$9+1)</f>
         <v/>
       </c>
       <c r="D25" s="21">
-        <f>NORMDIST(B25,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B25-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E25" s="21">
-        <f>NORMDIST(LOG10(B25),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F25" s="21" t="n">
-        <v>0.653161</v>
+        <f>1-NORMSDIST((LOG10(B25)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F25" s="21">
+        <f>CHIDIST(2*(LN(B25)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G25" s="21">
-        <f>EXP(-EXP(-(B25-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B25-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H25" s="21">
-        <f>ABS(C25-D25)</f>
+        <f>ABS(D25-C25)</f>
         <v/>
       </c>
       <c r="I25" s="21">
-        <f>ABS(C25-E25)</f>
+        <f>ABS(E25-C25)</f>
         <v/>
       </c>
       <c r="J25" s="21">
-        <f>ABS(C25-F25)</f>
+        <f>ABS(F25-C25)</f>
         <v/>
       </c>
       <c r="K25" s="21">
-        <f>ABS(C25-G25)</f>
+        <f>ABS(G25-C25)</f>
         <v/>
       </c>
     </row>
@@ -3916,42 +4030,43 @@
         <v>18</v>
       </c>
       <c r="B26" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A26)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A26)</f>
         <v/>
       </c>
       <c r="C26" s="21">
-        <f>A26/(FRECUENCIAS!$B$5+1)</f>
+        <f>A26/($N$9+1)</f>
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>NORMDIST(B26,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B26-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E26" s="21">
-        <f>NORMDIST(LOG10(B26),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F26" s="21" t="n">
-        <v>0.657047</v>
+        <f>1-NORMSDIST((LOG10(B26)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>CHIDIST(2*(LN(B26)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G26" s="21">
-        <f>EXP(-EXP(-(B26-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B26-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H26" s="21">
-        <f>ABS(C26-D26)</f>
+        <f>ABS(D26-C26)</f>
         <v/>
       </c>
       <c r="I26" s="21">
-        <f>ABS(C26-E26)</f>
+        <f>ABS(E26-C26)</f>
         <v/>
       </c>
       <c r="J26" s="21">
-        <f>ABS(C26-F26)</f>
+        <f>ABS(F26-C26)</f>
         <v/>
       </c>
       <c r="K26" s="21">
-        <f>ABS(C26-G26)</f>
+        <f>ABS(G26-C26)</f>
         <v/>
       </c>
     </row>
@@ -3960,42 +4075,43 @@
         <v>19</v>
       </c>
       <c r="B27" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A27)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A27)</f>
         <v/>
       </c>
       <c r="C27" s="21">
-        <f>A27/(FRECUENCIAS!$B$5+1)</f>
+        <f>A27/($N$9+1)</f>
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>NORMDIST(B27,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B27-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E27" s="21">
-        <f>NORMDIST(LOG10(B27),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F27" s="21" t="n">
-        <v>0.746938</v>
+        <f>1-NORMSDIST((LOG10(B27)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F27" s="21">
+        <f>CHIDIST(2*(LN(B27)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G27" s="21">
-        <f>EXP(-EXP(-(B27-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B27-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H27" s="21">
-        <f>ABS(C27-D27)</f>
+        <f>ABS(D27-C27)</f>
         <v/>
       </c>
       <c r="I27" s="21">
-        <f>ABS(C27-E27)</f>
+        <f>ABS(E27-C27)</f>
         <v/>
       </c>
       <c r="J27" s="21">
-        <f>ABS(C27-F27)</f>
+        <f>ABS(F27-C27)</f>
         <v/>
       </c>
       <c r="K27" s="21">
-        <f>ABS(C27-G27)</f>
+        <f>ABS(G27-C27)</f>
         <v/>
       </c>
     </row>
@@ -4004,42 +4120,43 @@
         <v>20</v>
       </c>
       <c r="B28" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A28)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A28)</f>
         <v/>
       </c>
       <c r="C28" s="21">
-        <f>A28/(FRECUENCIAS!$B$5+1)</f>
+        <f>A28/($N$9+1)</f>
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>NORMDIST(B28,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B28-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E28" s="21">
-        <f>NORMDIST(LOG10(B28),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F28" s="21" t="n">
-        <v>0.792312</v>
+        <f>1-NORMSDIST((LOG10(B28)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>CHIDIST(2*(LN(B28)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G28" s="21">
-        <f>EXP(-EXP(-(B28-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B28-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H28" s="21">
-        <f>ABS(C28-D28)</f>
+        <f>ABS(D28-C28)</f>
         <v/>
       </c>
       <c r="I28" s="21">
-        <f>ABS(C28-E28)</f>
+        <f>ABS(E28-C28)</f>
         <v/>
       </c>
       <c r="J28" s="21">
-        <f>ABS(C28-F28)</f>
+        <f>ABS(F28-C28)</f>
         <v/>
       </c>
       <c r="K28" s="21">
-        <f>ABS(C28-G28)</f>
+        <f>ABS(G28-C28)</f>
         <v/>
       </c>
     </row>
@@ -4048,42 +4165,43 @@
         <v>21</v>
       </c>
       <c r="B29" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A29)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A29)</f>
         <v/>
       </c>
       <c r="C29" s="21">
-        <f>A29/(FRECUENCIAS!$B$5+1)</f>
+        <f>A29/($N$9+1)</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>NORMDIST(B29,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B29-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E29" s="21">
-        <f>NORMDIST(LOG10(B29),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F29" s="21" t="n">
-        <v>0.863731</v>
+        <f>1-NORMSDIST((LOG10(B29)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F29" s="21">
+        <f>CHIDIST(2*(LN(B29)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G29" s="21">
-        <f>EXP(-EXP(-(B29-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B29-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H29" s="21">
-        <f>ABS(C29-D29)</f>
+        <f>ABS(D29-C29)</f>
         <v/>
       </c>
       <c r="I29" s="21">
-        <f>ABS(C29-E29)</f>
+        <f>ABS(E29-C29)</f>
         <v/>
       </c>
       <c r="J29" s="21">
-        <f>ABS(C29-F29)</f>
+        <f>ABS(F29-C29)</f>
         <v/>
       </c>
       <c r="K29" s="21">
-        <f>ABS(C29-G29)</f>
+        <f>ABS(G29-C29)</f>
         <v/>
       </c>
     </row>
@@ -4092,42 +4210,43 @@
         <v>22</v>
       </c>
       <c r="B30" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A30)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A30)</f>
         <v/>
       </c>
       <c r="C30" s="21">
-        <f>A30/(FRECUENCIAS!$B$5+1)</f>
+        <f>A30/($N$9+1)</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>NORMDIST(B30,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B30-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>NORMDIST(LOG10(B30),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F30" s="21" t="n">
-        <v>0.881198</v>
+        <f>1-NORMSDIST((LOG10(B30)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>CHIDIST(2*(LN(B30)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G30" s="21">
-        <f>EXP(-EXP(-(B30-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B30-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H30" s="21">
-        <f>ABS(C30-D30)</f>
+        <f>ABS(D30-C30)</f>
         <v/>
       </c>
       <c r="I30" s="21">
-        <f>ABS(C30-E30)</f>
+        <f>ABS(E30-C30)</f>
         <v/>
       </c>
       <c r="J30" s="21">
-        <f>ABS(C30-F30)</f>
+        <f>ABS(F30-C30)</f>
         <v/>
       </c>
       <c r="K30" s="21">
-        <f>ABS(C30-G30)</f>
+        <f>ABS(G30-C30)</f>
         <v/>
       </c>
     </row>
@@ -4136,42 +4255,43 @@
         <v>23</v>
       </c>
       <c r="B31" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A31)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A31)</f>
         <v/>
       </c>
       <c r="C31" s="21">
-        <f>A31/(FRECUENCIAS!$B$5+1)</f>
+        <f>A31/($N$9+1)</f>
         <v/>
       </c>
       <c r="D31" s="21">
-        <f>NORMDIST(B31,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B31-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E31" s="21">
-        <f>NORMDIST(LOG10(B31),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F31" s="21" t="n">
-        <v>0.899301</v>
+        <f>1-NORMSDIST((LOG10(B31)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>CHIDIST(2*(LN(B31)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G31" s="21">
-        <f>EXP(-EXP(-(B31-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B31-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H31" s="21">
-        <f>ABS(C31-D31)</f>
+        <f>ABS(D31-C31)</f>
         <v/>
       </c>
       <c r="I31" s="21">
-        <f>ABS(C31-E31)</f>
+        <f>ABS(E31-C31)</f>
         <v/>
       </c>
       <c r="J31" s="21">
-        <f>ABS(C31-F31)</f>
+        <f>ABS(F31-C31)</f>
         <v/>
       </c>
       <c r="K31" s="21">
-        <f>ABS(C31-G31)</f>
+        <f>ABS(G31-C31)</f>
         <v/>
       </c>
     </row>
@@ -4180,42 +4300,43 @@
         <v>24</v>
       </c>
       <c r="B32" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A32)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A32)</f>
         <v/>
       </c>
       <c r="C32" s="21">
-        <f>A32/(FRECUENCIAS!$B$5+1)</f>
+        <f>A32/($N$9+1)</f>
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>NORMDIST(B32,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B32-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E32" s="21">
-        <f>NORMDIST(LOG10(B32),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F32" s="21" t="n">
-        <v>0.96378</v>
+        <f>1-NORMSDIST((LOG10(B32)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>CHIDIST(2*(LN(B32)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G32" s="21">
-        <f>EXP(-EXP(-(B32-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B32-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H32" s="21">
-        <f>ABS(C32-D32)</f>
+        <f>ABS(D32-C32)</f>
         <v/>
       </c>
       <c r="I32" s="21">
-        <f>ABS(C32-E32)</f>
+        <f>ABS(E32-C32)</f>
         <v/>
       </c>
       <c r="J32" s="21">
-        <f>ABS(C32-F32)</f>
+        <f>ABS(F32-C32)</f>
         <v/>
       </c>
       <c r="K32" s="21">
-        <f>ABS(C32-G32)</f>
+        <f>ABS(G32-C32)</f>
         <v/>
       </c>
     </row>
@@ -4224,42 +4345,43 @@
         <v>25</v>
       </c>
       <c r="B33" s="26">
-        <f>SMALL(SERIE!$O$11:$O$35,A33)</f>
+        <f>LARGE(SERIE!$O$11:$O$35,A33)</f>
         <v/>
       </c>
       <c r="C33" s="21">
-        <f>A33/(FRECUENCIAS!$B$5+1)</f>
+        <f>A33/($N$9+1)</f>
         <v/>
       </c>
       <c r="D33" s="21">
-        <f>NORMDIST(B33,FRECUENCIAS!$B$6,FRECUENCIAS!$B$7,TRUE())</f>
+        <f>1-NORMSDIST((B33-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7)</f>
         <v/>
       </c>
       <c r="E33" s="21">
-        <f>NORMDIST(LOG10(B33),FRECUENCIAS!$B$9,FRECUENCIAS!$B$10,TRUE())</f>
-        <v/>
-      </c>
-      <c r="F33" s="21" t="n">
-        <v>0.973456</v>
+        <f>1-NORMSDIST((LOG10(B33)-FRECUENCIAS!$B$9)/FRECUENCIAS!$B$10)</f>
+        <v/>
+      </c>
+      <c r="F33" s="21">
+        <f>CHIDIST(2*(LN(B33)-$N$15)/$N$14,2*$N$13)</f>
+        <v/>
       </c>
       <c r="G33" s="21">
-        <f>EXP(-EXP(-(B33-FRECUENCIAS!$B$13)/FRECUENCIAS!$B$12))</f>
+        <f>1-EXP(-EXP(-((B33-FRECUENCIAS!$B$6)/FRECUENCIAS!$B$7*$N$17+$N$16)))</f>
         <v/>
       </c>
       <c r="H33" s="21">
-        <f>ABS(C33-D33)</f>
+        <f>ABS(D33-C33)</f>
         <v/>
       </c>
       <c r="I33" s="21">
-        <f>ABS(C33-E33)</f>
+        <f>ABS(E33-C33)</f>
         <v/>
       </c>
       <c r="J33" s="21">
-        <f>ABS(C33-F33)</f>
+        <f>ABS(F33-C33)</f>
         <v/>
       </c>
       <c r="K33" s="21">
-        <f>ABS(C33-G33)</f>
+        <f>ABS(G33-C33)</f>
         <v/>
       </c>
     </row>
@@ -4269,19 +4391,19 @@
           <t>D max</t>
         </is>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="31">
         <f>MAX(H9:H33)</f>
         <v/>
       </c>
-      <c r="I34" s="28">
+      <c r="I34" s="31">
         <f>MAX(I9:I33)</f>
         <v/>
       </c>
-      <c r="J34" s="28">
+      <c r="J34" s="31">
         <f>MAX(J9:J33)</f>
         <v/>
       </c>
-      <c r="K34" s="28">
+      <c r="K34" s="31">
         <f>MAX(K9:K33)</f>
         <v/>
       </c>
@@ -4292,17 +4414,21 @@
           <t>D critico</t>
         </is>
       </c>
-      <c r="H35" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I35" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J35" s="26" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="K35" s="26" t="n">
-        <v>0.27</v>
+      <c r="H35" s="21">
+        <f>$N$18</f>
+        <v/>
+      </c>
+      <c r="I35" s="21">
+        <f>$N$18</f>
+        <v/>
+      </c>
+      <c r="J35" s="21">
+        <f>$N$18</f>
+        <v/>
+      </c>
+      <c r="K35" s="21">
+        <f>$N$18</f>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -4331,7 +4457,7 @@
     <row r="38">
       <c r="A38" s="17" t="inlineStr">
         <is>
-          <t>F Log-Pearson III por Wilson-Hilferty (valor calculado). D critico para n = 25 y alfa = 0.05: 0.27 (tabla de Smirnov).</t>
+          <t>Log-Pearson III: distribucion gamma de ln P (CHIDIST con 2 beta grados de libertad); Gumbel con la media yn y la desviacion sn de la variable reducida para n datos (Aparicio, pag. 264); D critico = raiz(-ln(alfa/2)/(2n)) - 1/(6n). Se adopta la de menor D: Log-Pearson III.</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4473,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4365,7 +4491,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>LLUVIAS E INTENSIDADES MAXIMAS (DICK Y PESCHKE) Y CURVAS IDF</t>
+          <t>LLUVIAS E INTENSIDADES MAXIMAS: MODELO DE BELL (CURVAS IDF) Y DICK Y PESCHKE (DISENO)</t>
         </is>
       </c>
     </row>
@@ -4384,9 +4510,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
-        <is>
-          <t>P (mm) para la duracion D: P = P24 (D / 1440)^0.25</t>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>Intensidades de diseno - Dick y Peschke: P (mm) para la duracion D: P = P24 (D / 1440)^0.25</t>
         </is>
       </c>
     </row>
@@ -4935,7 +5061,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="32" t="inlineStr">
         <is>
           <t>I (mm/h) = P x 60 / D</t>
         </is>
@@ -5486,9 +5612,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Regresion multiple I = K T^m / t^n (duraciones de 5 a 60 min):</t>
+      <c r="A40" s="32" t="inlineStr">
+        <is>
+          <t>Regresion multiple I = K T^m / t^n de las intensidades del modelo de Bell (filas inferiores; 5 a 60 min, todos los T):</t>
         </is>
       </c>
     </row>
@@ -5498,8 +5624,8 @@
           <t>K</t>
         </is>
       </c>
-      <c r="B41" s="30" t="n">
-        <v>1009.5117</v>
+      <c r="B41" s="29" t="n">
+        <v>211.66</v>
       </c>
     </row>
     <row r="42">
@@ -5508,8 +5634,8 @@
           <t>m</t>
         </is>
       </c>
-      <c r="B42" s="30" t="n">
-        <v>0.1372</v>
+      <c r="B42" s="29" t="n">
+        <v>0.1786</v>
       </c>
     </row>
     <row r="43">
@@ -5518,8 +5644,8 @@
           <t>n</t>
         </is>
       </c>
-      <c r="B43" s="30" t="n">
-        <v>0.75</v>
+      <c r="B43" s="29" t="n">
+        <v>0.5269</v>
       </c>
     </row>
     <row r="45">
@@ -5530,6 +5656,622 @@
       </c>
       <c r="F45" s="19">
         <f>B41*25^B42/10^B43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="inlineStr">
+        <is>
+          <t>Modelo de Bell: P(T,t) = (0.21 ln T + 0.52)(0.54 t^0.25 - 0.50) P60(10);  P60(10) = 0.4602 P24(10)^0.876 =</t>
+        </is>
+      </c>
+      <c r="I46" s="16">
+        <f>0.4602*FRECUENCIAS!$I$19^0.876</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>T (anos)</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 5 min</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 10 min</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 15 min</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 20 min</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 30 min</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>P t = 60 min</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr"/>
+      <c r="I47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="B48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G48" s="26">
+        <f>(0.21*LN($A48)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="B49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G49" s="26">
+        <f>(0.21*LN($A49)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G50" s="26">
+        <f>(0.21*LN($A50)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G51" s="26">
+        <f>(0.21*LN($A51)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G52" s="26">
+        <f>(0.21*LN($A52)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G53" s="26">
+        <f>(0.21*LN($A53)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B54" s="26">
+        <f>(0.21*LN($A54)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C54" s="26">
+        <f>(0.21*LN($A54)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D54" s="26">
+        <f>(0.21*LN($A54)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E54" s="26">
+        <f>(0.21*LN($A54)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F54" s="26">
+        <f>(0.21*LN($A54)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G54" s="26">
+        <f>$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G55" s="26">
+        <f>(0.21*LN($A55)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*5^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="C56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*10^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="D56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*15^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="E56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*20^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="F56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*30^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+      <c r="G56" s="26">
+        <f>(0.21*LN($A56)+0.52)*(0.54*60^0.25-0.5)*$I$46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Intensidades maximas (mm/h) = 60 P / t, redondeadas a 0.1 (regresion de las curvas IDF)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>T (anos)</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>t = 5 min</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>t = 10 min</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>t = 15 min</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>t = 20 min</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>t = 30 min</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>t = 60 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="n">
+        <v>500</v>
+      </c>
+      <c r="B60" s="18">
+        <f>ROUND(60*B48/5,1)</f>
+        <v/>
+      </c>
+      <c r="C60" s="18">
+        <f>ROUND(60*C48/10,1)</f>
+        <v/>
+      </c>
+      <c r="D60" s="18">
+        <f>ROUND(60*D48/15,1)</f>
+        <v/>
+      </c>
+      <c r="E60" s="18">
+        <f>ROUND(60*E48/20,1)</f>
+        <v/>
+      </c>
+      <c r="F60" s="18">
+        <f>ROUND(60*F48/30,1)</f>
+        <v/>
+      </c>
+      <c r="G60" s="18">
+        <f>ROUND(60*G48/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="B61" s="18">
+        <f>ROUND(60*B49/5,1)</f>
+        <v/>
+      </c>
+      <c r="C61" s="18">
+        <f>ROUND(60*C49/10,1)</f>
+        <v/>
+      </c>
+      <c r="D61" s="18">
+        <f>ROUND(60*D49/15,1)</f>
+        <v/>
+      </c>
+      <c r="E61" s="18">
+        <f>ROUND(60*E49/20,1)</f>
+        <v/>
+      </c>
+      <c r="F61" s="18">
+        <f>ROUND(60*F49/30,1)</f>
+        <v/>
+      </c>
+      <c r="G61" s="18">
+        <f>ROUND(60*G49/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="n">
+        <v>100</v>
+      </c>
+      <c r="B62" s="18">
+        <f>ROUND(60*B50/5,1)</f>
+        <v/>
+      </c>
+      <c r="C62" s="18">
+        <f>ROUND(60*C50/10,1)</f>
+        <v/>
+      </c>
+      <c r="D62" s="18">
+        <f>ROUND(60*D50/15,1)</f>
+        <v/>
+      </c>
+      <c r="E62" s="18">
+        <f>ROUND(60*E50/20,1)</f>
+        <v/>
+      </c>
+      <c r="F62" s="18">
+        <f>ROUND(60*F50/30,1)</f>
+        <v/>
+      </c>
+      <c r="G62" s="18">
+        <f>ROUND(60*G50/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="B63" s="18">
+        <f>ROUND(60*B51/5,1)</f>
+        <v/>
+      </c>
+      <c r="C63" s="18">
+        <f>ROUND(60*C51/10,1)</f>
+        <v/>
+      </c>
+      <c r="D63" s="18">
+        <f>ROUND(60*D51/15,1)</f>
+        <v/>
+      </c>
+      <c r="E63" s="18">
+        <f>ROUND(60*E51/20,1)</f>
+        <v/>
+      </c>
+      <c r="F63" s="18">
+        <f>ROUND(60*F51/30,1)</f>
+        <v/>
+      </c>
+      <c r="G63" s="18">
+        <f>ROUND(60*G51/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B64" s="18">
+        <f>ROUND(60*B52/5,1)</f>
+        <v/>
+      </c>
+      <c r="C64" s="18">
+        <f>ROUND(60*C52/10,1)</f>
+        <v/>
+      </c>
+      <c r="D64" s="18">
+        <f>ROUND(60*D52/15,1)</f>
+        <v/>
+      </c>
+      <c r="E64" s="18">
+        <f>ROUND(60*E52/20,1)</f>
+        <v/>
+      </c>
+      <c r="F64" s="18">
+        <f>ROUND(60*F52/30,1)</f>
+        <v/>
+      </c>
+      <c r="G64" s="18">
+        <f>ROUND(60*G52/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B65" s="18">
+        <f>ROUND(60*B53/5,1)</f>
+        <v/>
+      </c>
+      <c r="C65" s="18">
+        <f>ROUND(60*C53/10,1)</f>
+        <v/>
+      </c>
+      <c r="D65" s="18">
+        <f>ROUND(60*D53/15,1)</f>
+        <v/>
+      </c>
+      <c r="E65" s="18">
+        <f>ROUND(60*E53/20,1)</f>
+        <v/>
+      </c>
+      <c r="F65" s="18">
+        <f>ROUND(60*F53/30,1)</f>
+        <v/>
+      </c>
+      <c r="G65" s="18">
+        <f>ROUND(60*G53/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B66" s="18">
+        <f>ROUND(60*B54/5,1)</f>
+        <v/>
+      </c>
+      <c r="C66" s="18">
+        <f>ROUND(60*C54/10,1)</f>
+        <v/>
+      </c>
+      <c r="D66" s="18">
+        <f>ROUND(60*D54/15,1)</f>
+        <v/>
+      </c>
+      <c r="E66" s="18">
+        <f>ROUND(60*E54/20,1)</f>
+        <v/>
+      </c>
+      <c r="F66" s="18">
+        <f>ROUND(60*F54/30,1)</f>
+        <v/>
+      </c>
+      <c r="G66" s="18">
+        <f>ROUND(60*G54/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="n">
+        <v>5</v>
+      </c>
+      <c r="B67" s="18">
+        <f>ROUND(60*B55/5,1)</f>
+        <v/>
+      </c>
+      <c r="C67" s="18">
+        <f>ROUND(60*C55/10,1)</f>
+        <v/>
+      </c>
+      <c r="D67" s="18">
+        <f>ROUND(60*D55/15,1)</f>
+        <v/>
+      </c>
+      <c r="E67" s="18">
+        <f>ROUND(60*E55/20,1)</f>
+        <v/>
+      </c>
+      <c r="F67" s="18">
+        <f>ROUND(60*F55/30,1)</f>
+        <v/>
+      </c>
+      <c r="G67" s="18">
+        <f>ROUND(60*G55/60,1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B68" s="18">
+        <f>ROUND(60*B56/5,1)</f>
+        <v/>
+      </c>
+      <c r="C68" s="18">
+        <f>ROUND(60*C56/10,1)</f>
+        <v/>
+      </c>
+      <c r="D68" s="18">
+        <f>ROUND(60*D56/15,1)</f>
+        <v/>
+      </c>
+      <c r="E68" s="18">
+        <f>ROUND(60*E56/20,1)</f>
+        <v/>
+      </c>
+      <c r="F68" s="18">
+        <f>ROUND(60*F56/30,1)</f>
+        <v/>
+      </c>
+      <c r="G68" s="18">
+        <f>ROUND(60*G56/60,1)</f>
         <v/>
       </c>
     </row>
@@ -5609,18 +6351,18 @@
           <t>Techos: edificaciones, corredores, patio civico techado y losa multiusos techada</t>
         </is>
       </c>
-      <c r="B9" s="31" t="n">
+      <c r="B9" s="33" t="n">
         <v>5548</v>
       </c>
       <c r="C9" s="26">
         <f>DATOS!$B$18</f>
         <v/>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="34">
         <f>B9*C9</f>
         <v/>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="35">
         <f>B9/$B$13</f>
         <v/>
       </c>
@@ -5631,18 +6373,18 @@
           <t>Areas libres de concreto: veredas, patios, atrio y circulaciones</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="33" t="n">
         <v>901</v>
       </c>
       <c r="C10" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D10" s="32">
+      <c r="D10" s="34">
         <f>B10*C10</f>
         <v/>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="35">
         <f>B10/$B$13</f>
         <v/>
       </c>
@@ -5653,18 +6395,18 @@
           <t>Patio de maniobra y estacionamiento (pavimento de concreto)</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="33" t="n">
         <v>623</v>
       </c>
       <c r="C11" s="26">
         <f>DATOS!$B$20</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="34">
         <f>B11*C11</f>
         <v/>
       </c>
-      <c r="E11" s="33">
+      <c r="E11" s="35">
         <f>B11/$B$13</f>
         <v/>
       </c>
@@ -5675,18 +6417,18 @@
           <t>Areas verdes y terreno natural (relleno nivelado)</t>
         </is>
       </c>
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="33" t="n">
         <v>2321</v>
       </c>
       <c r="C12" s="26">
         <f>DATOS!$B$21</f>
         <v/>
       </c>
-      <c r="D12" s="32">
+      <c r="D12" s="34">
         <f>B12*C12</f>
         <v/>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="35">
         <f>B12/$B$13</f>
         <v/>
       </c>
@@ -5697,25 +6439,25 @@
           <t>TOTAL / C PONDERADO</t>
         </is>
       </c>
-      <c r="B13" s="34">
+      <c r="B13" s="36">
         <f>SUM(B9:B12)</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>D13/B13</f>
         <v/>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="38">
         <f>SUM(D9:D12)</f>
         <v/>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="39">
         <f>SUM(E9:E12)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="32" t="inlineStr">
         <is>
           <t>DETALLE POR ZONA (NOMBRES DEL CUADRO DE AREAS DE ARQUITECTURA)</t>
         </is>
@@ -5754,14 +6496,14 @@
           <t>Coberturas de las edificaciones y corredores techados</t>
         </is>
       </c>
-      <c r="B17" s="32" t="n">
+      <c r="B17" s="34" t="n">
         <v>4129.6</v>
       </c>
       <c r="C17" s="26">
         <f>DATOS!$B$18</f>
         <v/>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="34">
         <f>B17*C17</f>
         <v/>
       </c>
@@ -5777,14 +6519,14 @@
           <t>Patio civico techado</t>
         </is>
       </c>
-      <c r="B18" s="32" t="n">
+      <c r="B18" s="34" t="n">
         <v>517.7</v>
       </c>
       <c r="C18" s="26">
         <f>DATOS!$B$18</f>
         <v/>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="34">
         <f>B18*C18</f>
         <v/>
       </c>
@@ -5800,14 +6542,14 @@
           <t>Losa multiusos tipo I techada</t>
         </is>
       </c>
-      <c r="B19" s="32" t="n">
+      <c r="B19" s="34" t="n">
         <v>829.4</v>
       </c>
       <c r="C19" s="26">
         <f>DATOS!$B$18</f>
         <v/>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="34">
         <f>B19*C19</f>
         <v/>
       </c>
@@ -5823,14 +6565,14 @@
           <t>Patio 01: ingreso principal</t>
         </is>
       </c>
-      <c r="B20" s="32" t="n">
+      <c r="B20" s="34" t="n">
         <v>118.8</v>
       </c>
       <c r="C20" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D20" s="32">
+      <c r="D20" s="34">
         <f>B20*C20</f>
         <v/>
       </c>
@@ -5846,14 +6588,14 @@
           <t>Patio 02: circulacion principal</t>
         </is>
       </c>
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="34" t="n">
         <v>194.2</v>
       </c>
       <c r="C21" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="34">
         <f>B21*C21</f>
         <v/>
       </c>
@@ -5869,14 +6611,14 @@
           <t>Patio 03: area privada de estudiantes</t>
         </is>
       </c>
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="34" t="n">
         <v>257.9</v>
       </c>
       <c r="C22" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="34">
         <f>B22*C22</f>
         <v/>
       </c>
@@ -5892,14 +6634,14 @@
           <t>Patio 04: asta de bandera</t>
         </is>
       </c>
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="34" t="n">
         <v>87.7</v>
       </c>
       <c r="C23" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D23" s="32">
+      <c r="D23" s="34">
         <f>B23*C23</f>
         <v/>
       </c>
@@ -5915,14 +6657,14 @@
           <t>Veredas, circulaciones, atrio y losa del area de tratamiento</t>
         </is>
       </c>
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="34" t="n">
         <v>202.5</v>
       </c>
       <c r="C24" s="26">
         <f>DATOS!$B$19</f>
         <v/>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="34">
         <f>B24*C24</f>
         <v/>
       </c>
@@ -5938,14 +6680,14 @@
           <t>Patio de maniobra y estacionamiento</t>
         </is>
       </c>
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="34" t="n">
         <v>647.3</v>
       </c>
       <c r="C25" s="26">
         <f>DATOS!$B$20</f>
         <v/>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="34">
         <f>B25*C25</f>
         <v/>
       </c>
@@ -5961,14 +6703,14 @@
           <t>Areas verdes, jardines y terreno natural nivelado</t>
         </is>
       </c>
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="34" t="n">
         <v>2379.7</v>
       </c>
       <c r="C26" s="26">
         <f>DATOS!$B$21</f>
         <v/>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="34">
         <f>B26*C26</f>
         <v/>
       </c>
@@ -5984,15 +6726,15 @@
           <t>TOTAL (AREA DENTRO DEL CERCO)</t>
         </is>
       </c>
-      <c r="B27" s="36">
+      <c r="B27" s="38">
         <f>SUM(B17:B26)</f>
         <v/>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <f>D27/B27</f>
         <v/>
       </c>
-      <c r="D27" s="36">
+      <c r="D27" s="38">
         <f>SUM(D17:D26)</f>
         <v/>
       </c>
@@ -6180,7 +6922,7 @@
           <t>P-02</t>
         </is>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="33" t="n">
         <v>533</v>
       </c>
       <c r="E9" s="25" t="n">
@@ -6205,7 +6947,7 @@
         <v>0.3</v>
       </c>
       <c r="K9" s="25" t="n">
-        <v>0.09370000000000001</v>
+        <v>0.0948</v>
       </c>
       <c r="L9" s="21">
         <f>DATOS!$B$12*K9</f>
@@ -6232,7 +6974,7 @@
         <v/>
       </c>
       <c r="R9" s="25" t="n">
-        <v>0.0849</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="S9" s="26">
         <f>G9/(DATOS!$B$12*R9)</f>
@@ -6259,7 +7001,7 @@
           <t>P-03</t>
         </is>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="33" t="n">
         <v>559</v>
       </c>
       <c r="E10" s="25" t="n">
@@ -6284,7 +7026,7 @@
         <v>0.46</v>
       </c>
       <c r="K10" s="25" t="n">
-        <v>0.0959</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="L10" s="21">
         <f>DATOS!$B$12*K10</f>
@@ -6311,7 +7053,7 @@
         <v/>
       </c>
       <c r="R10" s="25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="S10" s="26">
         <f>G10/(DATOS!$B$12*R10)</f>
@@ -6338,7 +7080,7 @@
           <t>P-05</t>
         </is>
       </c>
-      <c r="D11" s="31" t="n">
+      <c r="D11" s="33" t="n">
         <v>413</v>
       </c>
       <c r="E11" s="25" t="n">
@@ -6363,7 +7105,7 @@
         <v>0.3</v>
       </c>
       <c r="K11" s="25" t="n">
-        <v>0.0829</v>
+        <v>0.0839</v>
       </c>
       <c r="L11" s="21">
         <f>DATOS!$B$12*K11</f>
@@ -6390,7 +7132,7 @@
         <v/>
       </c>
       <c r="R11" s="25" t="n">
-        <v>0.07530000000000001</v>
+        <v>0.0761</v>
       </c>
       <c r="S11" s="26">
         <f>G11/(DATOS!$B$12*R11)</f>
@@ -6417,7 +7159,7 @@
           <t>P-06</t>
         </is>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="33" t="n">
         <v>440</v>
       </c>
       <c r="E12" s="25" t="n">
@@ -6442,7 +7184,7 @@
         <v>0.46</v>
       </c>
       <c r="K12" s="25" t="n">
-        <v>0.0863</v>
+        <v>0.0872</v>
       </c>
       <c r="L12" s="21">
         <f>DATOS!$B$12*K12</f>
@@ -6469,7 +7211,7 @@
         <v/>
       </c>
       <c r="R12" s="25" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.0791</v>
       </c>
       <c r="S12" s="26">
         <f>G12/(DATOS!$B$12*R12)</f>
@@ -6496,7 +7238,7 @@
           <t>P-07</t>
         </is>
       </c>
-      <c r="D13" s="31" t="n">
+      <c r="D13" s="33" t="n">
         <v>528</v>
       </c>
       <c r="E13" s="25" t="n">
@@ -6521,7 +7263,7 @@
         <v>0.46</v>
       </c>
       <c r="K13" s="25" t="n">
-        <v>0.1027</v>
+        <v>0.1038</v>
       </c>
       <c r="L13" s="21">
         <f>DATOS!$B$12*K13</f>
@@ -6548,7 +7290,7 @@
         <v/>
       </c>
       <c r="R13" s="25" t="n">
-        <v>0.093</v>
+        <v>0.094</v>
       </c>
       <c r="S13" s="26">
         <f>G13/(DATOS!$B$12*R13)</f>
@@ -6575,7 +7317,7 @@
           <t>P-08</t>
         </is>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="33" t="n">
         <v>965</v>
       </c>
       <c r="E14" s="25" t="n">
@@ -6600,7 +7342,7 @@
         <v>0.52</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.09130000000000001</v>
       </c>
       <c r="L14" s="21">
         <f>DATOS!$B$12*K14</f>
@@ -6627,7 +7369,7 @@
         <v/>
       </c>
       <c r="R14" s="25" t="n">
-        <v>0.082</v>
+        <v>0.0828</v>
       </c>
       <c r="S14" s="26">
         <f>G14/(DATOS!$B$12*R14)</f>
@@ -6654,7 +7396,7 @@
           <t>P-09</t>
         </is>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="33" t="n">
         <v>2225</v>
       </c>
       <c r="E15" s="25" t="n">
@@ -6679,7 +7421,7 @@
         <v>0.77</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.314</v>
+        <v>0.318</v>
       </c>
       <c r="L15" s="21">
         <f>DATOS!$B$12*K15</f>
@@ -6706,7 +7448,7 @@
         <v/>
       </c>
       <c r="R15" s="25" t="n">
-        <v>0.2805</v>
+        <v>0.284</v>
       </c>
       <c r="S15" s="26">
         <f>G15/(DATOS!$B$12*R15)</f>
@@ -6733,7 +7475,7 @@
           <t>P-10</t>
         </is>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="33" t="n">
         <v>2226</v>
       </c>
       <c r="E16" s="25" t="n">
@@ -6758,7 +7500,7 @@
         <v>0.83</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.3142</v>
+        <v>0.3181</v>
       </c>
       <c r="L16" s="21">
         <f>DATOS!$B$12*K16</f>
@@ -6785,7 +7527,7 @@
         <v/>
       </c>
       <c r="R16" s="25" t="n">
-        <v>0.2807</v>
+        <v>0.2841</v>
       </c>
       <c r="S16" s="26">
         <f>G16/(DATOS!$B$12*R16)</f>
@@ -6812,7 +7554,7 @@
           <t>P-11</t>
         </is>
       </c>
-      <c r="D17" s="31" t="n">
+      <c r="D17" s="33" t="n">
         <v>2979</v>
       </c>
       <c r="E17" s="25" t="n">
@@ -6837,7 +7579,7 @@
         <v>0.83</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.3992</v>
+        <v>0.4044</v>
       </c>
       <c r="L17" s="21">
         <f>DATOS!$B$12*K17</f>
@@ -6864,7 +7606,7 @@
         <v/>
       </c>
       <c r="R17" s="25" t="n">
-        <v>0.3554</v>
+        <v>0.36</v>
       </c>
       <c r="S17" s="26">
         <f>G17/(DATOS!$B$12*R17)</f>
@@ -6891,7 +7633,7 @@
           <t>P-03</t>
         </is>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="33" t="n">
         <v>2980</v>
       </c>
       <c r="E18" s="25" t="n">
@@ -6916,7 +7658,7 @@
         <v>0.79</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.3994</v>
+        <v>0.4046</v>
       </c>
       <c r="L18" s="21">
         <f>DATOS!$B$12*K18</f>
@@ -6943,7 +7685,7 @@
         <v/>
       </c>
       <c r="R18" s="25" t="n">
-        <v>0.3556</v>
+        <v>0.3601</v>
       </c>
       <c r="S18" s="26">
         <f>G18/(DATOS!$B$12*R18)</f>
@@ -6970,7 +7712,7 @@
           <t>D1</t>
         </is>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="33" t="n">
         <v>3539</v>
       </c>
       <c r="E19" s="25" t="n">
@@ -6995,7 +7737,7 @@
         <v>0.79</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.4477</v>
+        <v>0.4535</v>
       </c>
       <c r="L19" s="21">
         <f>DATOS!$B$12*K19</f>
@@ -7022,7 +7764,7 @@
         <v/>
       </c>
       <c r="R19" s="25" t="n">
-        <v>0.3979</v>
+        <v>0.403</v>
       </c>
       <c r="S19" s="26">
         <f>G19/(DATOS!$B$12*R19)</f>
@@ -7049,7 +7791,7 @@
           <t>P-07</t>
         </is>
       </c>
-      <c r="D20" s="31" t="n">
+      <c r="D20" s="33" t="n">
         <v>368</v>
       </c>
       <c r="E20" s="25" t="n">
@@ -7074,7 +7816,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0907</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="L20" s="21">
         <f>DATOS!$B$12*K20</f>
@@ -7101,7 +7843,7 @@
         <v/>
       </c>
       <c r="R20" s="25" t="n">
-        <v>0.0822</v>
+        <v>0.0833</v>
       </c>
       <c r="S20" s="26">
         <f>G20/(DATOS!$B$12*R20)</f>
@@ -7128,7 +7870,7 @@
           <t>P-14</t>
         </is>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="33" t="n">
         <v>383</v>
       </c>
       <c r="E21" s="25" t="n">
@@ -7153,7 +7895,7 @@
         <v>0.3</v>
       </c>
       <c r="K21" s="25" t="n">
-        <v>0.0766</v>
+        <v>0.0776</v>
       </c>
       <c r="L21" s="21">
         <f>DATOS!$B$12*K21</f>
@@ -7180,7 +7922,7 @@
         <v/>
       </c>
       <c r="R21" s="25" t="n">
-        <v>0.0696</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="S21" s="26">
         <f>G21/(DATOS!$B$12*R21)</f>
@@ -7207,7 +7949,7 @@
           <t>P-15</t>
         </is>
       </c>
-      <c r="D22" s="31" t="n">
+      <c r="D22" s="33" t="n">
         <v>443</v>
       </c>
       <c r="E22" s="25" t="n">
@@ -7232,7 +7974,7 @@
         <v>0.43</v>
       </c>
       <c r="K22" s="25" t="n">
-        <v>0.0837</v>
+        <v>0.0844</v>
       </c>
       <c r="L22" s="21">
         <f>DATOS!$B$12*K22</f>
@@ -7259,7 +8001,7 @@
         <v/>
       </c>
       <c r="R22" s="25" t="n">
-        <v>0.0759</v>
+        <v>0.0766</v>
       </c>
       <c r="S22" s="26">
         <f>G22/(DATOS!$B$12*R22)</f>
@@ -7286,7 +8028,7 @@
           <t>P-16</t>
         </is>
       </c>
-      <c r="D23" s="31" t="n">
+      <c r="D23" s="33" t="n">
         <v>448</v>
       </c>
       <c r="E23" s="25" t="n">
@@ -7311,7 +8053,7 @@
         <v>0.47</v>
       </c>
       <c r="K23" s="25" t="n">
-        <v>0.0839</v>
+        <v>0.0848</v>
       </c>
       <c r="L23" s="21">
         <f>DATOS!$B$12*K23</f>
@@ -7338,7 +8080,7 @@
         <v/>
       </c>
       <c r="R23" s="25" t="n">
-        <v>0.0761</v>
+        <v>0.077</v>
       </c>
       <c r="S23" s="26">
         <f>G23/(DATOS!$B$12*R23)</f>
@@ -7365,7 +8107,7 @@
           <t>P-17</t>
         </is>
       </c>
-      <c r="D24" s="31" t="n">
+      <c r="D24" s="33" t="n">
         <v>584</v>
       </c>
       <c r="E24" s="25" t="n">
@@ -7390,7 +8132,7 @@
         <v>0.48</v>
       </c>
       <c r="K24" s="25" t="n">
-        <v>0.1044</v>
+        <v>0.1055</v>
       </c>
       <c r="L24" s="21">
         <f>DATOS!$B$12*K24</f>
@@ -7417,7 +8159,7 @@
         <v/>
       </c>
       <c r="R24" s="25" t="n">
-        <v>0.0946</v>
+        <v>0.0956</v>
       </c>
       <c r="S24" s="26">
         <f>G24/(DATOS!$B$12*R24)</f>
@@ -7444,7 +8186,7 @@
           <t>P-18</t>
         </is>
       </c>
-      <c r="D25" s="31" t="n">
+      <c r="D25" s="33" t="n">
         <v>781</v>
       </c>
       <c r="E25" s="25" t="n">
@@ -7469,7 +8211,7 @@
         <v>0.49</v>
       </c>
       <c r="K25" s="25" t="n">
-        <v>0.1291</v>
+        <v>0.1305</v>
       </c>
       <c r="L25" s="21">
         <f>DATOS!$B$12*K25</f>
@@ -7496,7 +8238,7 @@
         <v/>
       </c>
       <c r="R25" s="25" t="n">
-        <v>0.1166</v>
+        <v>0.1179</v>
       </c>
       <c r="S25" s="26">
         <f>G25/(DATOS!$B$12*R25)</f>
@@ -7523,7 +8265,7 @@
           <t>P-19</t>
         </is>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="33" t="n">
         <v>857</v>
       </c>
       <c r="E26" s="25" t="n">
@@ -7548,7 +8290,7 @@
         <v>0.57</v>
       </c>
       <c r="K26" s="25" t="n">
-        <v>0.1391</v>
+        <v>0.1407</v>
       </c>
       <c r="L26" s="21">
         <f>DATOS!$B$12*K26</f>
@@ -7575,7 +8317,7 @@
         <v/>
       </c>
       <c r="R26" s="25" t="n">
-        <v>0.1256</v>
+        <v>0.127</v>
       </c>
       <c r="S26" s="26">
         <f>G26/(DATOS!$B$12*R26)</f>
@@ -7602,7 +8344,7 @@
           <t>P-08</t>
         </is>
       </c>
-      <c r="D27" s="31" t="n">
+      <c r="D27" s="33" t="n">
         <v>1170</v>
       </c>
       <c r="E27" s="25" t="n">
@@ -7627,7 +8369,7 @@
         <v>0.61</v>
       </c>
       <c r="K27" s="25" t="n">
-        <v>0.1861</v>
+        <v>0.1882</v>
       </c>
       <c r="L27" s="21">
         <f>DATOS!$B$12*K27</f>
@@ -7654,7 +8396,7 @@
         <v/>
       </c>
       <c r="R27" s="25" t="n">
-        <v>0.1675</v>
+        <v>0.1693</v>
       </c>
       <c r="S27" s="26">
         <f>G27/(DATOS!$B$12*R27)</f>
@@ -7681,7 +8423,7 @@
           <t>P-21</t>
         </is>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="33" t="n">
         <v>188</v>
       </c>
       <c r="E28" s="25" t="n">
@@ -7706,7 +8448,7 @@
         <v>0.3</v>
       </c>
       <c r="K28" s="25" t="n">
-        <v>0.059</v>
+        <v>0.0596</v>
       </c>
       <c r="L28" s="21">
         <f>DATOS!$B$12*K28</f>
@@ -7733,7 +8475,7 @@
         <v/>
       </c>
       <c r="R28" s="25" t="n">
-        <v>0.0537</v>
+        <v>0.0542</v>
       </c>
       <c r="S28" s="26">
         <f>G28/(DATOS!$B$12*R28)</f>
@@ -7760,7 +8502,7 @@
           <t>P-22</t>
         </is>
       </c>
-      <c r="D29" s="31" t="n">
+      <c r="D29" s="33" t="n">
         <v>230</v>
       </c>
       <c r="E29" s="25" t="n">
@@ -7785,7 +8527,7 @@
         <v>0.41</v>
       </c>
       <c r="K29" s="25" t="n">
-        <v>0.0639</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="L29" s="21">
         <f>DATOS!$B$12*K29</f>
@@ -7812,7 +8554,7 @@
         <v/>
       </c>
       <c r="R29" s="25" t="n">
-        <v>0.0581</v>
+        <v>0.0588</v>
       </c>
       <c r="S29" s="26">
         <f>G29/(DATOS!$B$12*R29)</f>
@@ -7839,7 +8581,7 @@
           <t>P-23</t>
         </is>
       </c>
-      <c r="D30" s="31" t="n">
+      <c r="D30" s="33" t="n">
         <v>367</v>
       </c>
       <c r="E30" s="25" t="n">
@@ -7864,7 +8606,7 @@
         <v>0.44</v>
       </c>
       <c r="K30" s="25" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0888</v>
       </c>
       <c r="L30" s="21">
         <f>DATOS!$B$12*K30</f>
@@ -7891,7 +8633,7 @@
         <v/>
       </c>
       <c r="R30" s="25" t="n">
-        <v>0.07969999999999999</v>
+        <v>0.0806</v>
       </c>
       <c r="S30" s="26">
         <f>G30/(DATOS!$B$12*R30)</f>
@@ -7918,7 +8660,7 @@
           <t>P-24</t>
         </is>
       </c>
-      <c r="D31" s="31" t="n">
+      <c r="D31" s="33" t="n">
         <v>411</v>
       </c>
       <c r="E31" s="25" t="n">
@@ -7943,7 +8685,7 @@
         <v>0.53</v>
       </c>
       <c r="K31" s="25" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.0939</v>
       </c>
       <c r="L31" s="21">
         <f>DATOS!$B$12*K31</f>
@@ -7970,7 +8712,7 @@
         <v/>
       </c>
       <c r="R31" s="25" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.0851</v>
       </c>
       <c r="S31" s="26">
         <f>G31/(DATOS!$B$12*R31)</f>
@@ -7997,7 +8739,7 @@
           <t>P-10</t>
         </is>
       </c>
-      <c r="D32" s="31" t="n">
+      <c r="D32" s="33" t="n">
         <v>699</v>
       </c>
       <c r="E32" s="25" t="n">
@@ -8022,7 +8764,7 @@
         <v>0.55</v>
       </c>
       <c r="K32" s="25" t="n">
-        <v>0.135</v>
+        <v>0.1364</v>
       </c>
       <c r="L32" s="21">
         <f>DATOS!$B$12*K32</f>
@@ -8049,7 +8791,7 @@
         <v/>
       </c>
       <c r="R32" s="25" t="n">
-        <v>0.1219</v>
+        <v>0.1232</v>
       </c>
       <c r="S32" s="26">
         <f>G32/(DATOS!$B$12*R32)</f>
@@ -8076,7 +8818,7 @@
           <t>P-16</t>
         </is>
       </c>
-      <c r="D33" s="31" t="n">
+      <c r="D33" s="33" t="n">
         <v>112</v>
       </c>
       <c r="E33" s="25" t="n">
@@ -8101,7 +8843,7 @@
         <v>0.3</v>
       </c>
       <c r="K33" s="25" t="n">
-        <v>0.0383</v>
+        <v>0.0386</v>
       </c>
       <c r="L33" s="21">
         <f>DATOS!$B$12*K33</f>
@@ -8128,7 +8870,7 @@
         <v/>
       </c>
       <c r="R33" s="25" t="n">
-        <v>0.0349</v>
+        <v>0.0353</v>
       </c>
       <c r="S33" s="26">
         <f>G33/(DATOS!$B$12*R33)</f>
@@ -8155,7 +8897,7 @@
           <t>P-27</t>
         </is>
       </c>
-      <c r="D34" s="31" t="n">
+      <c r="D34" s="33" t="n">
         <v>116</v>
       </c>
       <c r="E34" s="25" t="n">
@@ -8180,7 +8922,7 @@
         <v>0.3</v>
       </c>
       <c r="K34" s="25" t="n">
-        <v>0.0291</v>
+        <v>0.0293</v>
       </c>
       <c r="L34" s="21">
         <f>DATOS!$B$12*K34</f>
@@ -8207,7 +8949,7 @@
         <v/>
       </c>
       <c r="R34" s="25" t="n">
-        <v>0.0266</v>
+        <v>0.0268</v>
       </c>
       <c r="S34" s="26">
         <f>G34/(DATOS!$B$12*R34)</f>
@@ -8234,7 +8976,7 @@
           <t>P-28</t>
         </is>
       </c>
-      <c r="D35" s="31" t="n">
+      <c r="D35" s="33" t="n">
         <v>784</v>
       </c>
       <c r="E35" s="25" t="n">
@@ -8259,7 +9001,7 @@
         <v>0.5</v>
       </c>
       <c r="K35" s="25" t="n">
-        <v>0.1647</v>
+        <v>0.1666</v>
       </c>
       <c r="L35" s="21">
         <f>DATOS!$B$12*K35</f>
@@ -8286,7 +9028,7 @@
         <v/>
       </c>
       <c r="R35" s="25" t="n">
-        <v>0.1484</v>
+        <v>0.1501</v>
       </c>
       <c r="S35" s="26">
         <f>G35/(DATOS!$B$12*R35)</f>
@@ -8313,7 +9055,7 @@
           <t>P-29</t>
         </is>
       </c>
-      <c r="D36" s="31" t="n">
+      <c r="D36" s="33" t="n">
         <v>1153</v>
       </c>
       <c r="E36" s="25" t="n">
@@ -8338,7 +9080,7 @@
         <v>0.59</v>
       </c>
       <c r="K36" s="25" t="n">
-        <v>0.2188</v>
+        <v>0.2215</v>
       </c>
       <c r="L36" s="21">
         <f>DATOS!$B$12*K36</f>
@@ -8365,7 +9107,7 @@
         <v/>
       </c>
       <c r="R36" s="25" t="n">
-        <v>0.1964</v>
+        <v>0.1988</v>
       </c>
       <c r="S36" s="26">
         <f>G36/(DATOS!$B$12*R36)</f>
@@ -8392,7 +9134,7 @@
           <t>P-30</t>
         </is>
       </c>
-      <c r="D37" s="31" t="n">
+      <c r="D37" s="33" t="n">
         <v>1154</v>
       </c>
       <c r="E37" s="25" t="n">
@@ -8417,7 +9159,7 @@
         <v>0.61</v>
       </c>
       <c r="K37" s="25" t="n">
-        <v>0.2189</v>
+        <v>0.2215</v>
       </c>
       <c r="L37" s="21">
         <f>DATOS!$B$12*K37</f>
@@ -8444,7 +9186,7 @@
         <v/>
       </c>
       <c r="R37" s="25" t="n">
-        <v>0.1966</v>
+        <v>0.1988</v>
       </c>
       <c r="S37" s="26">
         <f>G37/(DATOS!$B$12*R37)</f>
@@ -8471,7 +9213,7 @@
           <t>P-31</t>
         </is>
       </c>
-      <c r="D38" s="31" t="n">
+      <c r="D38" s="33" t="n">
         <v>1339</v>
       </c>
       <c r="E38" s="25" t="n">
@@ -8496,7 +9238,7 @@
         <v>0.62</v>
       </c>
       <c r="K38" s="25" t="n">
-        <v>0.2458</v>
+        <v>0.2488</v>
       </c>
       <c r="L38" s="21">
         <f>DATOS!$B$12*K38</f>
@@ -8523,7 +9265,7 @@
         <v/>
       </c>
       <c r="R38" s="25" t="n">
-        <v>0.2204</v>
+        <v>0.223</v>
       </c>
       <c r="S38" s="26">
         <f>G38/(DATOS!$B$12*R38)</f>
@@ -8550,7 +9292,7 @@
           <t>P-32</t>
         </is>
       </c>
-      <c r="D39" s="31" t="n">
+      <c r="D39" s="33" t="n">
         <v>1340</v>
       </c>
       <c r="E39" s="25" t="n">
@@ -8575,7 +9317,7 @@
         <v>0.73</v>
       </c>
       <c r="K39" s="25" t="n">
-        <v>0.2458</v>
+        <v>0.2488</v>
       </c>
       <c r="L39" s="21">
         <f>DATOS!$B$12*K39</f>
@@ -8602,7 +9344,7 @@
         <v/>
       </c>
       <c r="R39" s="25" t="n">
-        <v>0.2204</v>
+        <v>0.223</v>
       </c>
       <c r="S39" s="26">
         <f>G39/(DATOS!$B$12*R39)</f>
@@ -8629,7 +9371,7 @@
           <t>P-33</t>
         </is>
       </c>
-      <c r="D40" s="31" t="n">
+      <c r="D40" s="33" t="n">
         <v>1768</v>
       </c>
       <c r="E40" s="25" t="n">
@@ -8654,7 +9396,7 @@
         <v>0.73</v>
       </c>
       <c r="K40" s="25" t="n">
-        <v>0.3037</v>
+        <v>0.3075</v>
       </c>
       <c r="L40" s="21">
         <f>DATOS!$B$12*K40</f>
@@ -8681,7 +9423,7 @@
         <v/>
       </c>
       <c r="R40" s="25" t="n">
-        <v>0.2715</v>
+        <v>0.2748</v>
       </c>
       <c r="S40" s="26">
         <f>G40/(DATOS!$B$12*R40)</f>
@@ -8708,7 +9450,7 @@
           <t>P-34</t>
         </is>
       </c>
-      <c r="D41" s="31" t="n">
+      <c r="D41" s="33" t="n">
         <v>2084</v>
       </c>
       <c r="E41" s="25" t="n">
@@ -8733,7 +9475,7 @@
         <v>0.79</v>
       </c>
       <c r="K41" s="25" t="n">
-        <v>0.3375</v>
+        <v>0.3417</v>
       </c>
       <c r="L41" s="21">
         <f>DATOS!$B$12*K41</f>
@@ -8760,7 +9502,7 @@
         <v/>
       </c>
       <c r="R41" s="25" t="n">
-        <v>0.3012</v>
+        <v>0.3049</v>
       </c>
       <c r="S41" s="26">
         <f>G41/(DATOS!$B$12*R41)</f>
@@ -8787,7 +9529,7 @@
           <t>P-35</t>
         </is>
       </c>
-      <c r="D42" s="31" t="n">
+      <c r="D42" s="33" t="n">
         <v>2085</v>
       </c>
       <c r="E42" s="25" t="n">
@@ -8812,7 +9554,7 @@
         <v>0.7</v>
       </c>
       <c r="K42" s="25" t="n">
-        <v>0.3377</v>
+        <v>0.3419</v>
       </c>
       <c r="L42" s="21">
         <f>DATOS!$B$12*K42</f>
@@ -8839,7 +9581,7 @@
         <v/>
       </c>
       <c r="R42" s="25" t="n">
-        <v>0.3013</v>
+        <v>0.3051</v>
       </c>
       <c r="S42" s="26">
         <f>G42/(DATOS!$B$12*R42)</f>
@@ -8866,7 +9608,7 @@
           <t>P-36</t>
         </is>
       </c>
-      <c r="D43" s="31" t="n">
+      <c r="D43" s="33" t="n">
         <v>2099</v>
       </c>
       <c r="E43" s="25" t="n">
@@ -8891,7 +9633,7 @@
         <v>0.7</v>
       </c>
       <c r="K43" s="25" t="n">
-        <v>0.3385</v>
+        <v>0.3428</v>
       </c>
       <c r="L43" s="21">
         <f>DATOS!$B$12*K43</f>
@@ -8918,7 +9660,7 @@
         <v/>
       </c>
       <c r="R43" s="25" t="n">
-        <v>0.3021</v>
+        <v>0.3058</v>
       </c>
       <c r="S43" s="26">
         <f>G43/(DATOS!$B$12*R43)</f>
@@ -8945,7 +9687,7 @@
           <t>P-37</t>
         </is>
       </c>
-      <c r="D44" s="31" t="n">
+      <c r="D44" s="33" t="n">
         <v>2102</v>
       </c>
       <c r="E44" s="25" t="n">
@@ -8970,7 +9712,7 @@
         <v>0.74</v>
       </c>
       <c r="K44" s="25" t="n">
-        <v>0.3387</v>
+        <v>0.3429</v>
       </c>
       <c r="L44" s="21">
         <f>DATOS!$B$12*K44</f>
@@ -8997,7 +9739,7 @@
         <v/>
       </c>
       <c r="R44" s="25" t="n">
-        <v>0.3022</v>
+        <v>0.306</v>
       </c>
       <c r="S44" s="26">
         <f>G44/(DATOS!$B$12*R44)</f>
@@ -9024,7 +9766,7 @@
           <t>P-38</t>
         </is>
       </c>
-      <c r="D45" s="31" t="n">
+      <c r="D45" s="33" t="n">
         <v>2126</v>
       </c>
       <c r="E45" s="25" t="n">
@@ -9049,7 +9791,7 @@
         <v>0.74</v>
       </c>
       <c r="K45" s="25" t="n">
-        <v>0.3402</v>
+        <v>0.3445</v>
       </c>
       <c r="L45" s="21">
         <f>DATOS!$B$12*K45</f>
@@ -9076,7 +9818,7 @@
         <v/>
       </c>
       <c r="R45" s="25" t="n">
-        <v>0.3036</v>
+        <v>0.3073</v>
       </c>
       <c r="S45" s="26">
         <f>G45/(DATOS!$B$12*R45)</f>
@@ -9103,7 +9845,7 @@
           <t>P-39</t>
         </is>
       </c>
-      <c r="D46" s="31" t="n">
+      <c r="D46" s="33" t="n">
         <v>2127</v>
       </c>
       <c r="E46" s="25" t="n">
@@ -9128,7 +9870,7 @@
         <v>0.77</v>
       </c>
       <c r="K46" s="25" t="n">
-        <v>0.3402</v>
+        <v>0.3445</v>
       </c>
       <c r="L46" s="21">
         <f>DATOS!$B$12*K46</f>
@@ -9155,7 +9897,7 @@
         <v/>
       </c>
       <c r="R46" s="25" t="n">
-        <v>0.3036</v>
+        <v>0.3073</v>
       </c>
       <c r="S46" s="26">
         <f>G46/(DATOS!$B$12*R46)</f>
@@ -9182,7 +9924,7 @@
           <t>P-40</t>
         </is>
       </c>
-      <c r="D47" s="31" t="n">
+      <c r="D47" s="33" t="n">
         <v>2178</v>
       </c>
       <c r="E47" s="25" t="n">
@@ -9207,7 +9949,7 @@
         <v>0.77</v>
       </c>
       <c r="K47" s="25" t="n">
-        <v>0.3434</v>
+        <v>0.3478</v>
       </c>
       <c r="L47" s="21">
         <f>DATOS!$B$12*K47</f>
@@ -9234,7 +9976,7 @@
         <v/>
       </c>
       <c r="R47" s="25" t="n">
-        <v>0.3064</v>
+        <v>0.3103</v>
       </c>
       <c r="S47" s="26">
         <f>G47/(DATOS!$B$12*R47)</f>
@@ -9261,7 +10003,7 @@
           <t>P-41</t>
         </is>
       </c>
-      <c r="D48" s="31" t="n">
+      <c r="D48" s="33" t="n">
         <v>2192</v>
       </c>
       <c r="E48" s="25" t="n">
@@ -9286,7 +10028,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K48" s="25" t="n">
-        <v>0.3443</v>
+        <v>0.3487</v>
       </c>
       <c r="L48" s="21">
         <f>DATOS!$B$12*K48</f>
@@ -9313,7 +10055,7 @@
         <v/>
       </c>
       <c r="R48" s="25" t="n">
-        <v>0.3072</v>
+        <v>0.311</v>
       </c>
       <c r="S48" s="26">
         <f>G48/(DATOS!$B$12*R48)</f>
@@ -9340,7 +10082,7 @@
           <t>D3</t>
         </is>
       </c>
-      <c r="D49" s="31" t="n">
+      <c r="D49" s="33" t="n">
         <v>2193</v>
       </c>
       <c r="E49" s="25" t="n">
@@ -9365,7 +10107,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="K49" s="25" t="n">
-        <v>0.3443</v>
+        <v>0.3487</v>
       </c>
       <c r="L49" s="21">
         <f>DATOS!$B$12*K49</f>
@@ -9392,7 +10134,7 @@
         <v/>
       </c>
       <c r="R49" s="25" t="n">
-        <v>0.3072</v>
+        <v>0.311</v>
       </c>
       <c r="S49" s="26">
         <f>G49/(DATOS!$B$12*R49)</f>
@@ -9419,7 +10161,7 @@
           <t>P-43</t>
         </is>
       </c>
-      <c r="D50" s="31" t="n">
+      <c r="D50" s="33" t="n">
         <v>47</v>
       </c>
       <c r="E50" s="25" t="n">
@@ -9444,7 +10186,7 @@
         <v>0.3</v>
       </c>
       <c r="K50" s="25" t="n">
-        <v>0.0253</v>
+        <v>0.0257</v>
       </c>
       <c r="L50" s="21">
         <f>DATOS!$B$12*K50</f>
@@ -9471,7 +10213,7 @@
         <v/>
       </c>
       <c r="R50" s="25" t="n">
-        <v>0.0231</v>
+        <v>0.0235</v>
       </c>
       <c r="S50" s="26">
         <f>G50/(DATOS!$B$12*R50)</f>
@@ -9498,7 +10240,7 @@
           <t>P-27</t>
         </is>
       </c>
-      <c r="D51" s="31" t="n">
+      <c r="D51" s="33" t="n">
         <v>488</v>
       </c>
       <c r="E51" s="25" t="n">
@@ -9523,7 +10265,7 @@
         <v>0.32</v>
       </c>
       <c r="K51" s="25" t="n">
-        <v>0.1186</v>
+        <v>0.1199</v>
       </c>
       <c r="L51" s="21">
         <f>DATOS!$B$12*K51</f>
@@ -9550,7 +10292,7 @@
         <v/>
       </c>
       <c r="R51" s="25" t="n">
-        <v>0.1073</v>
+        <v>0.1085</v>
       </c>
       <c r="S51" s="26">
         <f>G51/(DATOS!$B$12*R51)</f>
@@ -9577,7 +10319,7 @@
           <t>P-28</t>
         </is>
       </c>
-      <c r="D52" s="31" t="n">
+      <c r="D52" s="33" t="n">
         <v>342</v>
       </c>
       <c r="E52" s="25" t="n">
@@ -9602,7 +10344,7 @@
         <v>0.3</v>
       </c>
       <c r="K52" s="25" t="n">
-        <v>0.0925</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="L52" s="21">
         <f>DATOS!$B$12*K52</f>
@@ -9629,7 +10371,7 @@
         <v/>
       </c>
       <c r="R52" s="25" t="n">
-        <v>0.0839</v>
+        <v>0.0849</v>
       </c>
       <c r="S52" s="26">
         <f>G52/(DATOS!$B$12*R52)</f>
@@ -9656,7 +10398,7 @@
           <t>P-44</t>
         </is>
       </c>
-      <c r="D53" s="31" t="n">
+      <c r="D53" s="33" t="n">
         <v>205</v>
       </c>
       <c r="E53" s="25" t="n">
@@ -9681,7 +10423,7 @@
         <v>0.3</v>
       </c>
       <c r="K53" s="25" t="n">
-        <v>0.0633</v>
+        <v>0.0641</v>
       </c>
       <c r="L53" s="21">
         <f>DATOS!$B$12*K53</f>
@@ -9708,7 +10450,7 @@
         <v/>
       </c>
       <c r="R53" s="25" t="n">
-        <v>0.0576</v>
+        <v>0.0583</v>
       </c>
       <c r="S53" s="26">
         <f>G53/(DATOS!$B$12*R53)</f>
@@ -9735,7 +10477,7 @@
           <t>P-45</t>
         </is>
       </c>
-      <c r="D54" s="31" t="n">
+      <c r="D54" s="33" t="n">
         <v>232</v>
       </c>
       <c r="E54" s="25" t="n">
@@ -9760,7 +10502,7 @@
         <v>0.39</v>
       </c>
       <c r="K54" s="25" t="n">
-        <v>0.06859999999999999</v>
+        <v>0.0694</v>
       </c>
       <c r="L54" s="21">
         <f>DATOS!$B$12*K54</f>
@@ -9787,7 +10529,7 @@
         <v/>
       </c>
       <c r="R54" s="25" t="n">
-        <v>0.0623</v>
+        <v>0.063</v>
       </c>
       <c r="S54" s="26">
         <f>G54/(DATOS!$B$12*R54)</f>
@@ -9814,7 +10556,7 @@
           <t>P-46</t>
         </is>
       </c>
-      <c r="D55" s="31" t="n">
+      <c r="D55" s="33" t="n">
         <v>245</v>
       </c>
       <c r="E55" s="25" t="n">
@@ -9839,7 +10581,7 @@
         <v>0.42</v>
       </c>
       <c r="K55" s="25" t="n">
-        <v>0.0711</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L55" s="21">
         <f>DATOS!$B$12*K55</f>
@@ -9866,7 +10608,7 @@
         <v/>
       </c>
       <c r="R55" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="S55" s="26">
         <f>G55/(DATOS!$B$12*R55)</f>
@@ -9893,7 +10635,7 @@
           <t>P-47</t>
         </is>
       </c>
-      <c r="D56" s="31" t="n">
+      <c r="D56" s="33" t="n">
         <v>335</v>
       </c>
       <c r="E56" s="25" t="n">
@@ -9918,7 +10660,7 @@
         <v>0.42</v>
       </c>
       <c r="K56" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.0898</v>
       </c>
       <c r="L56" s="21">
         <f>DATOS!$B$12*K56</f>
@@ -9945,7 +10687,7 @@
         <v/>
       </c>
       <c r="R56" s="25" t="n">
-        <v>0.0806</v>
+        <v>0.0814</v>
       </c>
       <c r="S56" s="26">
         <f>G56/(DATOS!$B$12*R56)</f>
@@ -9972,7 +10714,7 @@
           <t>P-32</t>
         </is>
       </c>
-      <c r="D57" s="31" t="n">
+      <c r="D57" s="33" t="n">
         <v>335</v>
       </c>
       <c r="E57" s="25" t="n">
@@ -9997,7 +10739,7 @@
         <v>0.48</v>
       </c>
       <c r="K57" s="25" t="n">
-        <v>0.0888</v>
+        <v>0.0898</v>
       </c>
       <c r="L57" s="21">
         <f>DATOS!$B$12*K57</f>
@@ -10024,7 +10766,7 @@
         <v/>
       </c>
       <c r="R57" s="25" t="n">
-        <v>0.0806</v>
+        <v>0.0814</v>
       </c>
       <c r="S57" s="26">
         <f>G57/(DATOS!$B$12*R57)</f>
@@ -10051,7 +10793,7 @@
           <t>P-33</t>
         </is>
       </c>
-      <c r="D58" s="31" t="n">
+      <c r="D58" s="33" t="n">
         <v>302</v>
       </c>
       <c r="E58" s="25" t="n">
@@ -10076,7 +10818,7 @@
         <v>0.2</v>
       </c>
       <c r="K58" s="25" t="n">
-        <v>0.0711</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L58" s="21">
         <f>DATOS!$B$12*K58</f>
@@ -10103,7 +10845,7 @@
         <v/>
       </c>
       <c r="R58" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="S58" s="26">
         <f>G58/(DATOS!$B$12*R58)</f>
@@ -10130,7 +10872,7 @@
           <t>P-50</t>
         </is>
       </c>
-      <c r="D59" s="31" t="n">
+      <c r="D59" s="33" t="n">
         <v>238</v>
       </c>
       <c r="E59" s="25" t="n">
@@ -10155,7 +10897,7 @@
         <v>0.3</v>
       </c>
       <c r="K59" s="25" t="n">
-        <v>0.0704</v>
+        <v>0.0711</v>
       </c>
       <c r="L59" s="21">
         <f>DATOS!$B$12*K59</f>
@@ -10182,7 +10924,7 @@
         <v/>
       </c>
       <c r="R59" s="25" t="n">
-        <v>0.064</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="S59" s="26">
         <f>G59/(DATOS!$B$12*R59)</f>
@@ -10209,7 +10951,7 @@
           <t>P-51</t>
         </is>
       </c>
-      <c r="D60" s="31" t="n">
+      <c r="D60" s="33" t="n">
         <v>247</v>
       </c>
       <c r="E60" s="25" t="n">
@@ -10234,7 +10976,7 @@
         <v>0.38</v>
       </c>
       <c r="K60" s="25" t="n">
-        <v>0.0721</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="L60" s="21">
         <f>DATOS!$B$12*K60</f>
@@ -10261,7 +11003,7 @@
         <v/>
       </c>
       <c r="R60" s="25" t="n">
-        <v>0.06560000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="S60" s="26">
         <f>G60/(DATOS!$B$12*R60)</f>
@@ -10288,7 +11030,7 @@
           <t>P-52</t>
         </is>
       </c>
-      <c r="D61" s="31" t="n">
+      <c r="D61" s="33" t="n">
         <v>533</v>
       </c>
       <c r="E61" s="25" t="n">
@@ -10313,7 +11055,7 @@
         <v>0.38</v>
       </c>
       <c r="K61" s="25" t="n">
-        <v>0.1107</v>
+        <v>0.112</v>
       </c>
       <c r="L61" s="21">
         <f>DATOS!$B$12*K61</f>
@@ -10340,7 +11082,7 @@
         <v/>
       </c>
       <c r="R61" s="25" t="n">
-        <v>0.1002</v>
+        <v>0.1014</v>
       </c>
       <c r="S61" s="26">
         <f>G61/(DATOS!$B$12*R61)</f>
@@ -10367,7 +11109,7 @@
           <t>P-53</t>
         </is>
       </c>
-      <c r="D62" s="31" t="n">
+      <c r="D62" s="33" t="n">
         <v>536</v>
       </c>
       <c r="E62" s="25" t="n">
@@ -10392,7 +11134,7 @@
         <v>0.49</v>
       </c>
       <c r="K62" s="25" t="n">
-        <v>0.1112</v>
+        <v>0.1125</v>
       </c>
       <c r="L62" s="21">
         <f>DATOS!$B$12*K62</f>
@@ -10419,7 +11161,7 @@
         <v/>
       </c>
       <c r="R62" s="25" t="n">
-        <v>0.1006</v>
+        <v>0.1018</v>
       </c>
       <c r="S62" s="26">
         <f>G62/(DATOS!$B$12*R62)</f>
@@ -10446,7 +11188,7 @@
           <t>P-54</t>
         </is>
       </c>
-      <c r="D63" s="31" t="n">
+      <c r="D63" s="33" t="n">
         <v>857</v>
       </c>
       <c r="E63" s="25" t="n">
@@ -10471,7 +11213,7 @@
         <v>0.5</v>
       </c>
       <c r="K63" s="25" t="n">
-        <v>0.161</v>
+        <v>0.1629</v>
       </c>
       <c r="L63" s="21">
         <f>DATOS!$B$12*K63</f>
@@ -10498,7 +11240,7 @@
         <v/>
       </c>
       <c r="R63" s="25" t="n">
-        <v>0.1451</v>
+        <v>0.1468</v>
       </c>
       <c r="S63" s="26">
         <f>G63/(DATOS!$B$12*R63)</f>
@@ -10525,7 +11267,7 @@
           <t>P-55</t>
         </is>
       </c>
-      <c r="D64" s="31" t="n">
+      <c r="D64" s="33" t="n">
         <v>1130</v>
       </c>
       <c r="E64" s="25" t="n">
@@ -10550,7 +11292,7 @@
         <v>0.52</v>
       </c>
       <c r="K64" s="25" t="n">
-        <v>0.2021</v>
+        <v>0.2045</v>
       </c>
       <c r="L64" s="21">
         <f>DATOS!$B$12*K64</f>
@@ -10577,7 +11319,7 @@
         <v/>
       </c>
       <c r="R64" s="25" t="n">
-        <v>0.1817</v>
+        <v>0.1838</v>
       </c>
       <c r="S64" s="26">
         <f>G64/(DATOS!$B$12*R64)</f>
@@ -10604,7 +11346,7 @@
           <t>P-56</t>
         </is>
       </c>
-      <c r="D65" s="31" t="n">
+      <c r="D65" s="33" t="n">
         <v>1869</v>
       </c>
       <c r="E65" s="25" t="n">
@@ -10629,7 +11371,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="25" t="n">
-        <v>0.306</v>
+        <v>0.3097</v>
       </c>
       <c r="L65" s="21">
         <f>DATOS!$B$12*K65</f>
@@ -10656,7 +11398,7 @@
         <v/>
       </c>
       <c r="R65" s="25" t="n">
-        <v>0.2734</v>
+        <v>0.2768</v>
       </c>
       <c r="S65" s="26">
         <f>G65/(DATOS!$B$12*R65)</f>
@@ -10683,7 +11425,7 @@
           <t>P-57</t>
         </is>
       </c>
-      <c r="D66" s="31" t="n">
+      <c r="D66" s="33" t="n">
         <v>2360</v>
       </c>
       <c r="E66" s="25" t="n">
@@ -10708,7 +11450,7 @@
         <v>0.62</v>
       </c>
       <c r="K66" s="25" t="n">
-        <v>0.3722</v>
+        <v>0.3771</v>
       </c>
       <c r="L66" s="21">
         <f>DATOS!$B$12*K66</f>
@@ -10735,7 +11477,7 @@
         <v/>
       </c>
       <c r="R66" s="25" t="n">
-        <v>0.3317</v>
+        <v>0.336</v>
       </c>
       <c r="S66" s="26">
         <f>G66/(DATOS!$B$12*R66)</f>
@@ -10762,7 +11504,7 @@
           <t>P-58</t>
         </is>
       </c>
-      <c r="D67" s="31" t="n">
+      <c r="D67" s="33" t="n">
         <v>2486</v>
       </c>
       <c r="E67" s="25" t="n">
@@ -10787,7 +11529,7 @@
         <v>0.57</v>
       </c>
       <c r="K67" s="25" t="n">
-        <v>0.3888</v>
+        <v>0.3938</v>
       </c>
       <c r="L67" s="21">
         <f>DATOS!$B$12*K67</f>
@@ -10814,7 +11556,7 @@
         <v/>
       </c>
       <c r="R67" s="25" t="n">
-        <v>0.3462</v>
+        <v>0.3506</v>
       </c>
       <c r="S67" s="26">
         <f>G67/(DATOS!$B$12*R67)</f>
@@ -10841,7 +11583,7 @@
           <t>P-59</t>
         </is>
       </c>
-      <c r="D68" s="31" t="n">
+      <c r="D68" s="33" t="n">
         <v>2499</v>
       </c>
       <c r="E68" s="25" t="n">
@@ -10866,7 +11608,7 @@
         <v>0.63</v>
       </c>
       <c r="K68" s="25" t="n">
-        <v>0.3904</v>
+        <v>0.3954</v>
       </c>
       <c r="L68" s="21">
         <f>DATOS!$B$12*K68</f>
@@ -10893,7 +11635,7 @@
         <v/>
       </c>
       <c r="R68" s="25" t="n">
-        <v>0.3477</v>
+        <v>0.3521</v>
       </c>
       <c r="S68" s="26">
         <f>G68/(DATOS!$B$12*R68)</f>
@@ -10920,7 +11662,7 @@
           <t>P-60</t>
         </is>
       </c>
-      <c r="D69" s="31" t="n">
+      <c r="D69" s="33" t="n">
         <v>2499</v>
       </c>
       <c r="E69" s="25" t="n">
@@ -10945,7 +11687,7 @@
         <v>0.64</v>
       </c>
       <c r="K69" s="25" t="n">
-        <v>0.3904</v>
+        <v>0.3954</v>
       </c>
       <c r="L69" s="21">
         <f>DATOS!$B$12*K69</f>
@@ -10972,7 +11714,7 @@
         <v/>
       </c>
       <c r="R69" s="25" t="n">
-        <v>0.3477</v>
+        <v>0.3521</v>
       </c>
       <c r="S69" s="26">
         <f>G69/(DATOS!$B$12*R69)</f>
@@ -10999,7 +11741,7 @@
           <t>D2</t>
         </is>
       </c>
-      <c r="D70" s="31" t="n">
+      <c r="D70" s="33" t="n">
         <v>3028</v>
       </c>
       <c r="E70" s="25" t="n">
@@ -11024,7 +11766,7 @@
         <v>0.64</v>
       </c>
       <c r="K70" s="25" t="n">
-        <v>0.447</v>
+        <v>0.453</v>
       </c>
       <c r="L70" s="21">
         <f>DATOS!$B$12*K70</f>
@@ -11051,7 +11793,7 @@
         <v/>
       </c>
       <c r="R70" s="25" t="n">
-        <v>0.3974</v>
+        <v>0.4025</v>
       </c>
       <c r="S70" s="26">
         <f>G70/(DATOS!$B$12*R70)</f>
@@ -11078,7 +11820,7 @@
           <t>P-54</t>
         </is>
       </c>
-      <c r="D71" s="31" t="n">
+      <c r="D71" s="33" t="n">
         <v>244</v>
       </c>
       <c r="E71" s="25" t="n">
@@ -11103,7 +11845,7 @@
         <v>0.3</v>
       </c>
       <c r="K71" s="25" t="n">
-        <v>0.0737</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L71" s="21">
         <f>DATOS!$B$12*K71</f>
@@ -11130,7 +11872,7 @@
         <v/>
       </c>
       <c r="R71" s="25" t="n">
-        <v>0.0669</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="S71" s="26">
         <f>G71/(DATOS!$B$12*R71)</f>
@@ -11157,7 +11899,7 @@
           <t>P-63</t>
         </is>
       </c>
-      <c r="D72" s="31" t="n">
+      <c r="D72" s="33" t="n">
         <v>198</v>
       </c>
       <c r="E72" s="25" t="n">
@@ -11182,7 +11924,7 @@
         <v>0.3</v>
       </c>
       <c r="K72" s="25" t="n">
-        <v>0.0641</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="L72" s="21">
         <f>DATOS!$B$12*K72</f>
@@ -11209,7 +11951,7 @@
         <v/>
       </c>
       <c r="R72" s="25" t="n">
-        <v>0.0583</v>
+        <v>0.0588</v>
       </c>
       <c r="S72" s="26">
         <f>G72/(DATOS!$B$12*R72)</f>
@@ -11236,7 +11978,7 @@
           <t>P-64</t>
         </is>
       </c>
-      <c r="D73" s="31" t="n">
+      <c r="D73" s="33" t="n">
         <v>222</v>
       </c>
       <c r="E73" s="25" t="n">
@@ -11261,7 +12003,7 @@
         <v>0.38</v>
       </c>
       <c r="K73" s="25" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.0699</v>
       </c>
       <c r="L73" s="21">
         <f>DATOS!$B$12*K73</f>
@@ -11288,7 +12030,7 @@
         <v/>
       </c>
       <c r="R73" s="25" t="n">
-        <v>0.06279999999999999</v>
+        <v>0.0635</v>
       </c>
       <c r="S73" s="26">
         <f>G73/(DATOS!$B$12*R73)</f>
@@ -11315,7 +12057,7 @@
           <t>P-65</t>
         </is>
       </c>
-      <c r="D74" s="31" t="n">
+      <c r="D74" s="33" t="n">
         <v>478</v>
       </c>
       <c r="E74" s="25" t="n">
@@ -11340,7 +12082,7 @@
         <v>0.35</v>
       </c>
       <c r="K74" s="25" t="n">
-        <v>0.1155</v>
+        <v>0.1167</v>
       </c>
       <c r="L74" s="21">
         <f>DATOS!$B$12*K74</f>
@@ -11367,7 +12109,7 @@
         <v/>
       </c>
       <c r="R74" s="25" t="n">
-        <v>0.1045</v>
+        <v>0.1056</v>
       </c>
       <c r="S74" s="26">
         <f>G74/(DATOS!$B$12*R74)</f>
@@ -11394,7 +12136,7 @@
           <t>P-66</t>
         </is>
       </c>
-      <c r="D75" s="31" t="n">
+      <c r="D75" s="33" t="n">
         <v>481</v>
       </c>
       <c r="E75" s="25" t="n">
@@ -11419,7 +12161,7 @@
         <v>0.35</v>
       </c>
       <c r="K75" s="25" t="n">
-        <v>0.1159</v>
+        <v>0.1172</v>
       </c>
       <c r="L75" s="21">
         <f>DATOS!$B$12*K75</f>
@@ -11446,7 +12188,7 @@
         <v/>
       </c>
       <c r="R75" s="25" t="n">
-        <v>0.1049</v>
+        <v>0.106</v>
       </c>
       <c r="S75" s="26">
         <f>G75/(DATOS!$B$12*R75)</f>
@@ -11473,7 +12215,7 @@
           <t>P-67</t>
         </is>
       </c>
-      <c r="D76" s="31" t="n">
+      <c r="D76" s="33" t="n">
         <v>489</v>
       </c>
       <c r="E76" s="25" t="n">
@@ -11498,7 +12240,7 @@
         <v>0.35</v>
       </c>
       <c r="K76" s="25" t="n">
-        <v>0.1172</v>
+        <v>0.1184</v>
       </c>
       <c r="L76" s="21">
         <f>DATOS!$B$12*K76</f>
@@ -11525,7 +12267,7 @@
         <v/>
       </c>
       <c r="R76" s="25" t="n">
-        <v>0.106</v>
+        <v>0.1071</v>
       </c>
       <c r="S76" s="26">
         <f>G76/(DATOS!$B$12*R76)</f>
@@ -11552,7 +12294,7 @@
           <t>P-68</t>
         </is>
       </c>
-      <c r="D77" s="31" t="n">
+      <c r="D77" s="33" t="n">
         <v>671</v>
       </c>
       <c r="E77" s="25" t="n">
@@ -11577,7 +12319,7 @@
         <v>0.35</v>
       </c>
       <c r="K77" s="25" t="n">
-        <v>0.1475</v>
+        <v>0.149</v>
       </c>
       <c r="L77" s="21">
         <f>DATOS!$B$12*K77</f>
@@ -11604,7 +12346,7 @@
         <v/>
       </c>
       <c r="R77" s="25" t="n">
-        <v>0.1331</v>
+        <v>0.1345</v>
       </c>
       <c r="S77" s="26">
         <f>G77/(DATOS!$B$12*R77)</f>
@@ -11631,7 +12373,7 @@
           <t>P-55</t>
         </is>
       </c>
-      <c r="D78" s="31" t="n">
+      <c r="D78" s="33" t="n">
         <v>691</v>
       </c>
       <c r="E78" s="25" t="n">
@@ -11656,7 +12398,7 @@
         <v>0.45</v>
       </c>
       <c r="K78" s="25" t="n">
-        <v>0.1506</v>
+        <v>0.1524</v>
       </c>
       <c r="L78" s="21">
         <f>DATOS!$B$12*K78</f>
@@ -11683,7 +12425,7 @@
         <v/>
       </c>
       <c r="R78" s="25" t="n">
-        <v>0.1359</v>
+        <v>0.1375</v>
       </c>
       <c r="S78" s="26">
         <f>G78/(DATOS!$B$12*R78)</f>
@@ -11710,7 +12452,7 @@
           <t>P-70</t>
         </is>
       </c>
-      <c r="D79" s="31" t="n">
+      <c r="D79" s="33" t="n">
         <v>155</v>
       </c>
       <c r="E79" s="25" t="n">
@@ -11735,7 +12477,7 @@
         <v>0.3</v>
       </c>
       <c r="K79" s="25" t="n">
-        <v>0.0543</v>
+        <v>0.0548</v>
       </c>
       <c r="L79" s="21">
         <f>DATOS!$B$12*K79</f>
@@ -11762,7 +12504,7 @@
         <v/>
       </c>
       <c r="R79" s="25" t="n">
-        <v>0.0494</v>
+        <v>0.0499</v>
       </c>
       <c r="S79" s="26">
         <f>G79/(DATOS!$B$12*R79)</f>
@@ -11789,7 +12531,7 @@
           <t>P-71</t>
         </is>
       </c>
-      <c r="D80" s="31" t="n">
+      <c r="D80" s="33" t="n">
         <v>157</v>
       </c>
       <c r="E80" s="25" t="n">
@@ -11814,7 +12556,7 @@
         <v>0.36</v>
       </c>
       <c r="K80" s="25" t="n">
-        <v>0.0546</v>
+        <v>0.0551</v>
       </c>
       <c r="L80" s="21">
         <f>DATOS!$B$12*K80</f>
@@ -11841,7 +12583,7 @@
         <v/>
       </c>
       <c r="R80" s="25" t="n">
-        <v>0.0497</v>
+        <v>0.0502</v>
       </c>
       <c r="S80" s="26">
         <f>G80/(DATOS!$B$12*R80)</f>
@@ -11868,7 +12610,7 @@
           <t>P-72</t>
         </is>
       </c>
-      <c r="D81" s="31" t="n">
+      <c r="D81" s="33" t="n">
         <v>429</v>
       </c>
       <c r="E81" s="25" t="n">
@@ -11893,7 +12635,7 @@
         <v>0.35</v>
       </c>
       <c r="K81" s="25" t="n">
-        <v>0.1023</v>
+        <v>0.1035</v>
       </c>
       <c r="L81" s="21">
         <f>DATOS!$B$12*K81</f>
@@ -11920,7 +12662,7 @@
         <v/>
       </c>
       <c r="R81" s="25" t="n">
-        <v>0.0927</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="S81" s="26">
         <f>G81/(DATOS!$B$12*R81)</f>
@@ -11947,7 +12689,7 @@
           <t>P-56</t>
         </is>
       </c>
-      <c r="D82" s="31" t="n">
+      <c r="D82" s="33" t="n">
         <v>454</v>
       </c>
       <c r="E82" s="25" t="n">
@@ -11972,7 +12714,7 @@
         <v>0.35</v>
       </c>
       <c r="K82" s="25" t="n">
-        <v>0.1123</v>
+        <v>0.1133</v>
       </c>
       <c r="L82" s="21">
         <f>DATOS!$B$12*K82</f>
@@ -11999,7 +12741,7 @@
         <v/>
       </c>
       <c r="R82" s="25" t="n">
-        <v>0.1016</v>
+        <v>0.1026</v>
       </c>
       <c r="S82" s="26">
         <f>G82/(DATOS!$B$12*R82)</f>
@@ -12026,7 +12768,7 @@
           <t>P-74</t>
         </is>
       </c>
-      <c r="D83" s="31" t="n">
+      <c r="D83" s="33" t="n">
         <v>376</v>
       </c>
       <c r="E83" s="25" t="n">
@@ -12051,7 +12793,7 @@
         <v>0.3</v>
       </c>
       <c r="K83" s="25" t="n">
-        <v>0.081</v>
+        <v>0.082</v>
       </c>
       <c r="L83" s="21">
         <f>DATOS!$B$12*K83</f>
@@ -12078,7 +12820,7 @@
         <v/>
       </c>
       <c r="R83" s="25" t="n">
-        <v>0.0736</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="S83" s="26">
         <f>G83/(DATOS!$B$12*R83)</f>
@@ -12105,7 +12847,7 @@
           <t>P-75</t>
         </is>
       </c>
-      <c r="D84" s="31" t="n">
+      <c r="D84" s="33" t="n">
         <v>399</v>
       </c>
       <c r="E84" s="25" t="n">
@@ -12130,7 +12872,7 @@
         <v>0.45</v>
       </c>
       <c r="K84" s="25" t="n">
-        <v>0.0851</v>
+        <v>0.0858</v>
       </c>
       <c r="L84" s="21">
         <f>DATOS!$B$12*K84</f>
@@ -12157,7 +12899,7 @@
         <v/>
       </c>
       <c r="R84" s="25" t="n">
-        <v>0.0772</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="S84" s="26">
         <f>G84/(DATOS!$B$12*R84)</f>
@@ -12184,7 +12926,7 @@
           <t>P-76</t>
         </is>
       </c>
-      <c r="D85" s="31" t="n">
+      <c r="D85" s="33" t="n">
         <v>416</v>
       </c>
       <c r="E85" s="25" t="n">
@@ -12209,7 +12951,7 @@
         <v>0.46</v>
       </c>
       <c r="K85" s="25" t="n">
-        <v>0.0867</v>
+        <v>0.0877</v>
       </c>
       <c r="L85" s="21">
         <f>DATOS!$B$12*K85</f>
@@ -12236,7 +12978,7 @@
         <v/>
       </c>
       <c r="R85" s="25" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.0795</v>
       </c>
       <c r="S85" s="26">
         <f>G85/(DATOS!$B$12*R85)</f>
@@ -12263,7 +13005,7 @@
           <t>P-77</t>
         </is>
       </c>
-      <c r="D86" s="31" t="n">
+      <c r="D86" s="33" t="n">
         <v>418</v>
       </c>
       <c r="E86" s="25" t="n">
@@ -12288,7 +13030,7 @@
         <v>0.47</v>
       </c>
       <c r="K86" s="25" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="L86" s="21">
         <f>DATOS!$B$12*K86</f>
@@ -12315,7 +13057,7 @@
         <v/>
       </c>
       <c r="R86" s="25" t="n">
-        <v>0.0789</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="S86" s="26">
         <f>G86/(DATOS!$B$12*R86)</f>
@@ -12342,7 +13084,7 @@
           <t>P-78</t>
         </is>
       </c>
-      <c r="D87" s="31" t="n">
+      <c r="D87" s="33" t="n">
         <v>528</v>
       </c>
       <c r="E87" s="25" t="n">
@@ -12367,7 +13109,7 @@
         <v>0.4</v>
       </c>
       <c r="K87" s="25" t="n">
-        <v>0.1068</v>
+        <v>0.1081</v>
       </c>
       <c r="L87" s="21">
         <f>DATOS!$B$12*K87</f>
@@ -12394,7 +13136,7 @@
         <v/>
       </c>
       <c r="R87" s="25" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0979</v>
       </c>
       <c r="S87" s="26">
         <f>G87/(DATOS!$B$12*R87)</f>
@@ -12421,7 +13163,7 @@
           <t>P-60</t>
         </is>
       </c>
-      <c r="D88" s="31" t="n">
+      <c r="D88" s="33" t="n">
         <v>528</v>
       </c>
       <c r="E88" s="25" t="n">
@@ -12446,7 +13188,7 @@
         <v>0.4</v>
       </c>
       <c r="K88" s="25" t="n">
-        <v>0.1068</v>
+        <v>0.1081</v>
       </c>
       <c r="L88" s="21">
         <f>DATOS!$B$12*K88</f>
@@ -12473,7 +13215,7 @@
         <v/>
       </c>
       <c r="R88" s="25" t="n">
-        <v>0.09669999999999999</v>
+        <v>0.0979</v>
       </c>
       <c r="S88" s="26">
         <f>G88/(DATOS!$B$12*R88)</f>
@@ -12500,7 +13242,7 @@
           <t>P-80</t>
         </is>
       </c>
-      <c r="D89" s="31" t="n">
+      <c r="D89" s="33" t="n">
         <v>265</v>
       </c>
       <c r="E89" s="25" t="n">
@@ -12525,7 +13267,7 @@
         <v>0.2</v>
       </c>
       <c r="K89" s="25" t="n">
-        <v>0.0702</v>
+        <v>0.0709</v>
       </c>
       <c r="L89" s="21">
         <f>DATOS!$B$12*K89</f>
@@ -12552,7 +13294,7 @@
         <v/>
       </c>
       <c r="R89" s="25" t="n">
-        <v>0.0638</v>
+        <v>0.0645</v>
       </c>
       <c r="S89" s="26">
         <f>G89/(DATOS!$B$12*R89)</f>
@@ -12579,7 +13321,7 @@
           <t>P-81</t>
         </is>
       </c>
-      <c r="D90" s="31" t="n">
+      <c r="D90" s="33" t="n">
         <v>265</v>
       </c>
       <c r="E90" s="25" t="n">
@@ -12604,7 +13346,7 @@
         <v>0.5</v>
       </c>
       <c r="K90" s="25" t="n">
-        <v>0.0706</v>
+        <v>0.07140000000000001</v>
       </c>
       <c r="L90" s="21">
         <f>DATOS!$B$12*K90</f>
@@ -12631,7 +13373,7 @@
         <v/>
       </c>
       <c r="R90" s="25" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.0649</v>
       </c>
       <c r="S90" s="26">
         <f>G90/(DATOS!$B$12*R90)</f>
@@ -12658,7 +13400,7 @@
           <t>P-82</t>
         </is>
       </c>
-      <c r="D91" s="31" t="n">
+      <c r="D91" s="33" t="n">
         <v>629</v>
       </c>
       <c r="E91" s="25" t="n">
@@ -12683,7 +13425,7 @@
         <v>0.5</v>
       </c>
       <c r="K91" s="25" t="n">
-        <v>0.1291</v>
+        <v>0.1305</v>
       </c>
       <c r="L91" s="21">
         <f>DATOS!$B$12*K91</f>
@@ -12710,7 +13452,7 @@
         <v/>
       </c>
       <c r="R91" s="25" t="n">
-        <v>0.1166</v>
+        <v>0.1179</v>
       </c>
       <c r="S91" s="26">
         <f>G91/(DATOS!$B$12*R91)</f>
@@ -12737,7 +13479,7 @@
           <t>D4</t>
         </is>
       </c>
-      <c r="D92" s="31" t="n">
+      <c r="D92" s="33" t="n">
         <v>633</v>
       </c>
       <c r="E92" s="25" t="n">
@@ -12762,7 +13504,7 @@
         <v>0.4</v>
       </c>
       <c r="K92" s="25" t="n">
-        <v>0.1295</v>
+        <v>0.1309</v>
       </c>
       <c r="L92" s="21">
         <f>DATOS!$B$12*K92</f>
@@ -12789,7 +13531,7 @@
         <v/>
       </c>
       <c r="R92" s="25" t="n">
-        <v>0.117</v>
+        <v>0.1183</v>
       </c>
       <c r="S92" s="26">
         <f>G92/(DATOS!$B$12*R92)</f>
@@ -12816,7 +13558,7 @@
           <t>P-83</t>
         </is>
       </c>
-      <c r="D93" s="31" t="n">
+      <c r="D93" s="33" t="n">
         <v>91</v>
       </c>
       <c r="E93" s="25" t="n">
@@ -12841,7 +13583,7 @@
         <v>0.3</v>
       </c>
       <c r="K93" s="25" t="n">
-        <v>0.0369</v>
+        <v>0.0373</v>
       </c>
       <c r="L93" s="21">
         <f>DATOS!$B$12*K93</f>
@@ -12868,7 +13610,7 @@
         <v/>
       </c>
       <c r="R93" s="25" t="n">
-        <v>0.0337</v>
+        <v>0.034</v>
       </c>
       <c r="S93" s="26">
         <f>G93/(DATOS!$B$12*R93)</f>
@@ -12895,7 +13637,7 @@
           <t>P-84</t>
         </is>
       </c>
-      <c r="D94" s="31" t="n">
+      <c r="D94" s="33" t="n">
         <v>92</v>
       </c>
       <c r="E94" s="25" t="n">
@@ -12920,7 +13662,7 @@
         <v>0.36</v>
       </c>
       <c r="K94" s="25" t="n">
-        <v>0.0369</v>
+        <v>0.0373</v>
       </c>
       <c r="L94" s="21">
         <f>DATOS!$B$12*K94</f>
@@ -12947,7 +13689,7 @@
         <v/>
       </c>
       <c r="R94" s="25" t="n">
-        <v>0.0337</v>
+        <v>0.034</v>
       </c>
       <c r="S94" s="26">
         <f>G94/(DATOS!$B$12*R94)</f>
@@ -12974,7 +13716,7 @@
           <t>P-85</t>
         </is>
       </c>
-      <c r="D95" s="31" t="n">
+      <c r="D95" s="33" t="n">
         <v>251</v>
       </c>
       <c r="E95" s="25" t="n">
@@ -12999,7 +13741,7 @@
         <v>0.36</v>
       </c>
       <c r="K95" s="25" t="n">
-        <v>0.0711</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L95" s="21">
         <f>DATOS!$B$12*K95</f>
@@ -13026,7 +13768,7 @@
         <v/>
       </c>
       <c r="R95" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="S95" s="26">
         <f>G95/(DATOS!$B$12*R95)</f>
@@ -13053,7 +13795,7 @@
           <t>P-86</t>
         </is>
       </c>
-      <c r="D96" s="31" t="n">
+      <c r="D96" s="33" t="n">
         <v>251</v>
       </c>
       <c r="E96" s="25" t="n">
@@ -13078,7 +13820,7 @@
         <v>0.48</v>
       </c>
       <c r="K96" s="25" t="n">
-        <v>0.0711</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="L96" s="21">
         <f>DATOS!$B$12*K96</f>
@@ -13105,7 +13847,7 @@
         <v/>
       </c>
       <c r="R96" s="25" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.0653</v>
       </c>
       <c r="S96" s="26">
         <f>G96/(DATOS!$B$12*R96)</f>
@@ -13132,7 +13874,7 @@
           <t>P-81</t>
         </is>
       </c>
-      <c r="D97" s="31" t="n">
+      <c r="D97" s="33" t="n">
         <v>364</v>
       </c>
       <c r="E97" s="25" t="n">
@@ -13157,7 +13899,7 @@
         <v>0.49</v>
       </c>
       <c r="K97" s="25" t="n">
-        <v>0.0886</v>
+        <v>0.0895</v>
       </c>
       <c r="L97" s="21">
         <f>DATOS!$B$12*K97</f>
@@ -13184,7 +13926,7 @@
         <v/>
       </c>
       <c r="R97" s="25" t="n">
-        <v>0.0804</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="S97" s="26">
         <f>G97/(DATOS!$B$12*R97)</f>
@@ -13211,7 +13953,7 @@
           <t>P-88</t>
         </is>
       </c>
-      <c r="D98" s="31" t="n">
+      <c r="D98" s="33" t="n">
         <v>109</v>
       </c>
       <c r="E98" s="25" t="n">
@@ -13236,7 +13978,7 @@
         <v>0.3</v>
       </c>
       <c r="K98" s="25" t="n">
-        <v>0.0376</v>
+        <v>0.038</v>
       </c>
       <c r="L98" s="21">
         <f>DATOS!$B$12*K98</f>
@@ -13263,7 +14005,7 @@
         <v/>
       </c>
       <c r="R98" s="25" t="n">
-        <v>0.0343</v>
+        <v>0.0346</v>
       </c>
       <c r="S98" s="26">
         <f>G98/(DATOS!$B$12*R98)</f>
@@ -13290,7 +14032,7 @@
           <t>P-86</t>
         </is>
       </c>
-      <c r="D99" s="31" t="n">
+      <c r="D99" s="33" t="n">
         <v>109</v>
       </c>
       <c r="E99" s="25" t="n">
@@ -13315,7 +14057,7 @@
         <v>0.37</v>
       </c>
       <c r="K99" s="25" t="n">
-        <v>0.0376</v>
+        <v>0.038</v>
       </c>
       <c r="L99" s="21">
         <f>DATOS!$B$12*K99</f>
@@ -13342,7 +14084,7 @@
         <v/>
       </c>
       <c r="R99" s="25" t="n">
-        <v>0.0343</v>
+        <v>0.0346</v>
       </c>
       <c r="S99" s="26">
         <f>G99/(DATOS!$B$12*R99)</f>

--- a/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
+++ b/entregables_barranquita/MEMORIA_CALCULO_DRENAJE_PLUVIAL_IE0590_BARRANQUITA.xlsx
@@ -703,7 +703,7 @@
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>EXPEDIENTE TÉCNICO</t>
+          <t>SERVICIO DE DISEÑO - DRENAJE PLUVIAL</t>
         </is>
       </c>
     </row>
